--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -78,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,6 +92,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1189,9 +1192,19 @@
       </c>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="F31" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>67% (37/55)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -19340,7 +19353,7 @@
       <c r="F672" s="3" t="n"/>
       <c r="G672" s="3" t="n"/>
     </row>
-    <row r="673">
+    <row r="673" ht="80" customHeight="1">
       <c r="A673" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19362,10 +19375,18 @@
         </is>
       </c>
       <c r="E673" s="3" t="n"/>
-      <c r="F673" s="3" t="n"/>
+      <c r="F673" s="6" t="inlineStr">
+        <is>
+          <t>mode=T+无OrderTag过滤 — 56.4%
+mode=T+不传orderTagIds — 38.2%
+mode=N+无OrderTag过滤 — 2.2%
+不传mode+不传orderTagIds — 1.8%
+mode=N+不传orderTagIds — 1.4%</t>
+        </is>
+      </c>
       <c r="G673" s="3" t="n"/>
     </row>
-    <row r="674">
+    <row r="674" ht="112" customHeight="1">
       <c r="A674" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19387,10 +19408,20 @@
         </is>
       </c>
       <c r="E674" s="3" t="n"/>
-      <c r="F674" s="3" t="n"/>
+      <c r="F674" s="6" t="inlineStr">
+        <is>
+          <t>mode=T+无OrderTag过滤+不含compareStart+不含comparePreStart+含DspProfileIds — 44.4%
+mode=T+不传orderTagIds+不含compareStart+不含comparePreStart+含DspProfileIds — 34.2%
+mode=T+无OrderTag过滤+含compareStart+不含comparePreStart+不含DspProfileIds — 6.4%
+mode=T+无OrderTag过滤+不含compareStart+含comparePreStart+含DspProfileIds — 4.4%
+mode=T+无OrderTag过滤+不含compareStart+含comparePreStart+不含DspProfileIds — 2.8%
+不传mode+不传orderTagIds+不含compareStart+不含comparePreStart+不含DspProfileIds — 2.0%
+mode=T+不传orderTagIds+不含compareStart+含comparePreStart+含DspProfileIds — 1.0%</t>
+        </is>
+      </c>
       <c r="G674" s="3" t="n"/>
     </row>
-    <row r="675">
+    <row r="675" ht="128" customHeight="1">
       <c r="A675" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19412,10 +19443,21 @@
         </is>
       </c>
       <c r="E675" s="3" t="n"/>
-      <c r="F675" s="3" t="n"/>
+      <c r="F675" s="6" t="inlineStr">
+        <is>
+          <t>mode=T+无OrderTag过滤+不含comparePreStart — 52.0%
+mode=T+不传orderTagIds+不含comparePreStart — 36.2%
+mode=T+不传orderTagIds+含comparePreStart — 2.6%
+mode=N+不传orderTagIds+不含comparePreStart — 2.4%
+mode=T+无OrderTag过滤+含comparePreStart — 2.4%
+不传mode+不传orderTagIds+不含comparePreStart — 1.8%
+mode=N+无OrderTag过滤+不含comparePreStart — 1.2%
+mode=N+无OrderTag过滤+含comparePreStart — 1.0%</t>
+        </is>
+      </c>
       <c r="G675" s="3" t="n"/>
     </row>
-    <row r="676">
+    <row r="676" ht="96" customHeight="1">
       <c r="A676" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19437,8 +19479,21 @@
         </is>
       </c>
       <c r="E676" s="3" t="n"/>
-      <c r="F676" s="3" t="n"/>
-      <c r="G676" s="3" t="n"/>
+      <c r="F676" s="6" t="inlineStr">
+        <is>
+          <t>mode=T+不传orderTagIds — 46.2%
+mode=T+无OrderTag过滤 — 25.0%
+mode=N+不传orderTagIds — 19.2%
+mode=T+按OrderTag过滤 — 5.8%
+mode=N+无OrderTag过滤 — 1.9%
+mode=N+按OrderTag过滤 — 1.9%</t>
+        </is>
+      </c>
+      <c r="G676" s="5" t="inlineStr">
+        <is>
+          <t>6场景中2个(按OrderTag过滤)需要 ams_campaign_tag_id(账号内无实体)，技术受限未执行；其余4个(无/不传OrderTag)已执行PASS</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" s="2" t="inlineStr">
@@ -19462,8 +19517,16 @@
         </is>
       </c>
       <c r="E677" s="3" t="n"/>
-      <c r="F677" s="3" t="n"/>
-      <c r="G677" s="3" t="n"/>
+      <c r="F677" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G677" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，未生成case</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" s="2" t="inlineStr">
@@ -19487,8 +19550,16 @@
         </is>
       </c>
       <c r="E678" s="3" t="n"/>
-      <c r="F678" s="3" t="n"/>
-      <c r="G678" s="3" t="n"/>
+      <c r="F678" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G678" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，未生成case</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" s="2" t="inlineStr">
@@ -19512,10 +19583,18 @@
         </is>
       </c>
       <c r="E679" s="3" t="n"/>
-      <c r="F679" s="3" t="n"/>
-      <c r="G679" s="3" t="n"/>
-    </row>
-    <row r="680">
+      <c r="F679" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G679" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，备份/BK版本疑似已下线，未生成case</t>
+        </is>
+      </c>
+    </row>
+    <row r="680" ht="144" customHeight="1">
       <c r="A680" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19537,7 +19616,19 @@
         </is>
       </c>
       <c r="E680" s="3" t="n"/>
-      <c r="F680" s="3" t="n"/>
+      <c r="F680" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤+不含comparePreStart — 41.2%
+无Advertiser过滤+无OrderTag过滤+不含comparePreStart — 35.2%
+按Advertiser过滤+按OrderTag过滤+不含comparePreStart — 5.8%
+按Advertiser过滤+无OrderTag过滤+含comparePreStart — 5.8%
+按Advertiser过滤+按OrderTag过滤+含comparePreStart — 3.2%
+无Advertiser过滤+无OrderTag过滤+含comparePreStart — 2.6%
+无Advertiser过滤+按OrderTag过滤+不含comparePreStart — 2.2%
+无Advertiser过滤+按OrderTag过滤+含comparePreStart — 1.4%
+按Advertiser过滤+不传orderTagIds+含comparePreStart — 1.0%</t>
+        </is>
+      </c>
       <c r="G680" s="3" t="n"/>
     </row>
     <row r="681">
@@ -19562,10 +19653,18 @@
         </is>
       </c>
       <c r="E681" s="3" t="n"/>
-      <c r="F681" s="3" t="n"/>
-      <c r="G681" s="3" t="n"/>
-    </row>
-    <row r="682">
+      <c r="F681" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G681" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，未生成case</t>
+        </is>
+      </c>
+    </row>
+    <row r="682" ht="80" customHeight="1">
       <c r="A682" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19587,7 +19686,15 @@
         </is>
       </c>
       <c r="E682" s="3" t="n"/>
-      <c r="F682" s="3" t="n"/>
+      <c r="F682" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无OrderTag过滤 — 46.0%
+按Advertiser过滤+无OrderTag过滤 — 45.0%
+按Advertiser过滤+按OrderTag过滤 — 4.8%
+无Advertiser过滤+按OrderTag过滤 — 2.2%
+不传advertiserIds+不传orderTagIds — 1.8%</t>
+        </is>
+      </c>
       <c r="G682" s="3" t="n"/>
     </row>
     <row r="683">
@@ -19612,8 +19719,16 @@
         </is>
       </c>
       <c r="E683" s="3" t="n"/>
-      <c r="F683" s="3" t="n"/>
-      <c r="G683" s="3" t="n"/>
+      <c r="F683" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G683" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，未生成case</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" s="2" t="inlineStr">
@@ -19637,8 +19752,16 @@
         </is>
       </c>
       <c r="E684" s="3" t="n"/>
-      <c r="F684" s="3" t="n"/>
-      <c r="G684" s="3" t="n"/>
+      <c r="F684" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G684" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，未生成case</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" s="2" t="inlineStr">
@@ -19662,10 +19785,18 @@
         </is>
       </c>
       <c r="E685" s="3" t="n"/>
-      <c r="F685" s="3" t="n"/>
-      <c r="G685" s="3" t="n"/>
-    </row>
-    <row r="686">
+      <c r="F685" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G685" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)；同模块CreativeTagListAndTotal已覆盖，未生成case</t>
+        </is>
+      </c>
+    </row>
+    <row r="686" ht="144" customHeight="1">
       <c r="A686" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19687,10 +19818,26 @@
         </is>
       </c>
       <c r="E686" s="3" t="n"/>
-      <c r="F686" s="3" t="n"/>
-      <c r="G686" s="3" t="n"/>
-    </row>
-    <row r="687">
+      <c r="F686" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤+不含compareStart — 42.6%
+无Advertiser过滤+无OrderTag过滤+不含compareStart — 31.4%
+按Advertiser过滤+无OrderTag过滤+含compareStart — 8.2%
+按Advertiser过滤+按OrderTag过滤+不含compareStart — 5.0%
+按Advertiser过滤+按OrderTag过滤+含compareStart — 3.6%
+无Advertiser过滤+无OrderTag过滤+含compareStart — 3.4%
+不传advertiserIds+不传orderTagIds+不含compareStart — 1.6%
+无Advertiser过滤+按OrderTag过滤+不含compareStart — 1.4%
+按Advertiser过滤+不传orderTagIds+含compareStart — 1.0%</t>
+        </is>
+      </c>
+      <c r="G686" s="5" t="inlineStr">
+        <is>
+          <t>9场景中1个(含compareStart+按CreativeTag过滤)需要 creative_tag_id(账号内无实体)，技术受限未执行；其余8个已执行PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="687" ht="32" customHeight="1">
       <c r="A687" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19712,10 +19859,15 @@
         </is>
       </c>
       <c r="E687" s="3" t="n"/>
-      <c r="F687" s="3" t="n"/>
+      <c r="F687" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤 — 51.6%
+无Advertiser过滤 — 48.2%</t>
+        </is>
+      </c>
       <c r="G687" s="3" t="n"/>
     </row>
-    <row r="688">
+    <row r="688" ht="80" customHeight="1">
       <c r="A688" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19737,7 +19889,15 @@
         </is>
       </c>
       <c r="E688" s="3" t="n"/>
-      <c r="F688" s="3" t="n"/>
+      <c r="F688" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无OrderTag过滤 — 51.2%
+按Advertiser过滤+无OrderTag过滤 — 38.6%
+按Advertiser过滤+按OrderTag过滤 — 5.2%
+不传advertiserIds+不传orderTagIds — 2.0%
+无Advertiser过滤+按OrderTag过滤 — 1.8%</t>
+        </is>
+      </c>
       <c r="G688" s="3" t="n"/>
     </row>
     <row r="689">
@@ -19762,8 +19922,16 @@
         </is>
       </c>
       <c r="E689" s="3" t="n"/>
-      <c r="F689" s="3" t="n"/>
-      <c r="G689" s="3" t="n"/>
+      <c r="F689" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G689" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，未生成case</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" s="2" t="inlineStr">
@@ -19787,10 +19955,18 @@
         </is>
       </c>
       <c r="E690" s="3" t="n"/>
-      <c r="F690" s="3" t="n"/>
-      <c r="G690" s="3" t="n"/>
-    </row>
-    <row r="691">
+      <c r="F690" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G690" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，未生成case</t>
+        </is>
+      </c>
+    </row>
+    <row r="691" ht="240" customHeight="1">
       <c r="A691" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19812,10 +19988,28 @@
         </is>
       </c>
       <c r="E691" s="3" t="n"/>
-      <c r="F691" s="3" t="n"/>
+      <c r="F691" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+type=[eCPM,eCPP]+无OrderTag过滤 — 30.2%
+按Advertiser过滤+type=[eCPM,eCPP]+无OrderTag过滤 — 20.6%
+无Advertiser过滤+type=[Impressions,eCPM]+无OrderTag过滤 — 12.0%
+按Advertiser过滤+type=[Impressions,eCPM]+无OrderTag过滤 — 11.6%
+无Advertiser过滤+type=[eCPDPV,eCPM]+无OrderTag过滤 — 3.0%
+按Advertiser过滤+type=[eCPM,eCPP]+按OrderTag过滤 — 3.0%
+按Advertiser过滤+type=[PurchaseRate,eCPP]+无OrderTag过滤 — 2.6%
+无Advertiser过滤+type=[PurchaseRate,eCPP]+无OrderTag过滤 — 1.8%
+不传advertiserIds+不传type+不传orderTagIds — 1.8%
+按Advertiser过滤+type=[eCPDPV,eCPM]+无OrderTag过滤 — 1.8%
+无Advertiser过滤+type=[ATCR,DPVR,PurchaseRate]+无OrderTag过滤 — 1.4%
+无Advertiser过滤+type=[Impressions,eCPM]+按OrderTag过滤 — 1.4%
+按Advertiser过滤+type=[NewToBrandProductUnitsSoldPercent,UnitsSold]+无OrderTag过滤 — 1.2%
+按Advertiser过滤+type=[Impressions,eCPM]+按OrderTag过滤 — 1.0%
+无Advertiser过滤+type=[NewToBrandProductUnitsSoldPercent,UnitsSold]+无OrderTag过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G691" s="3" t="n"/>
     </row>
-    <row r="692">
+    <row r="692" ht="80" customHeight="1">
       <c r="A692" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19837,10 +20031,18 @@
         </is>
       </c>
       <c r="E692" s="3" t="n"/>
-      <c r="F692" s="3" t="n"/>
+      <c r="F692" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+不含type — 36.8%
+无Advertiser过滤+含type — 21.1%
+按Advertiser过滤+不含type — 18.4%
+按Advertiser过滤+含type — 18.4%
+不传advertiserIds+不含type — 5.3%</t>
+        </is>
+      </c>
       <c r="G692" s="3" t="n"/>
     </row>
-    <row r="693">
+    <row r="693" ht="144" customHeight="1">
       <c r="A693" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19862,7 +20064,19 @@
         </is>
       </c>
       <c r="E693" s="3" t="n"/>
-      <c r="F693" s="3" t="n"/>
+      <c r="F693" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+不含type+无OrderTag过滤 — 26.8%
+按Advertiser过滤+不含type+无OrderTag过滤 — 22.4%
+无Advertiser过滤+含type+无OrderTag过滤 — 19.6%
+按Advertiser过滤+含type+无OrderTag过滤 — 15.0%
+按Advertiser过滤+含type+按OrderTag过滤 — 6.2%
+按Advertiser过滤+不含type+按OrderTag过滤 — 5.0%
+无Advertiser过滤+不含type+按OrderTag过滤 — 2.0%
+无Advertiser过滤+含type+按OrderTag过滤 — 1.6%
+不传advertiserIds+不含type+不传orderTagIds — 1.0%</t>
+        </is>
+      </c>
       <c r="G693" s="3" t="n"/>
     </row>
     <row r="694">
@@ -19887,10 +20101,18 @@
         </is>
       </c>
       <c r="E694" s="3" t="n"/>
-      <c r="F694" s="3" t="n"/>
-      <c r="G694" s="3" t="n"/>
-    </row>
-    <row r="695">
+      <c r="F694" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G694" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，未生成case</t>
+        </is>
+      </c>
+    </row>
+    <row r="695" ht="64" customHeight="1">
       <c r="A695" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19912,10 +20134,17 @@
         </is>
       </c>
       <c r="E695" s="3" t="n"/>
-      <c r="F695" s="3" t="n"/>
+      <c r="F695" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不含compareStart — 51.0%
+无Advertiser过滤+不含compareStart — 31.6%
+按Advertiser过滤+含compareStart — 12.0%
+无Advertiser过滤+含compareStart — 4.8%</t>
+        </is>
+      </c>
       <c r="G695" s="3" t="n"/>
     </row>
-    <row r="696">
+    <row r="696" ht="80" customHeight="1">
       <c r="A696" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19937,10 +20166,18 @@
         </is>
       </c>
       <c r="E696" s="3" t="n"/>
-      <c r="F696" s="3" t="n"/>
+      <c r="F696" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤 — 48.4%
+无Advertiser过滤+无OrderTag过滤 — 38.8%
+按Advertiser过滤+按OrderTag过滤 — 8.0%
+无Advertiser过滤+按OrderTag过滤 — 2.8%
+不传advertiserIds+不传orderTagIds — 1.4%</t>
+        </is>
+      </c>
       <c r="G696" s="3" t="n"/>
     </row>
-    <row r="697">
+    <row r="697" ht="64" customHeight="1">
       <c r="A697" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19962,10 +20199,21 @@
         </is>
       </c>
       <c r="E697" s="3" t="n"/>
-      <c r="F697" s="3" t="n"/>
-      <c r="G697" s="3" t="n"/>
-    </row>
-    <row r="698">
+      <c r="F697" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+含toFinalMarket — 35.8%
+无Advertiser过滤+含toFinalMarket — 29.9%
+按Advertiser过滤+不含toFinalMarket — 20.9%
+无Advertiser过滤+不含toFinalMarket — 13.4%</t>
+        </is>
+      </c>
+      <c r="G697" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：需要 lineitem_tag_id，账号内无 LineItem 标签实体，4个场景均未执行，仅生成case</t>
+        </is>
+      </c>
+    </row>
+    <row r="698" ht="128" customHeight="1">
       <c r="A698" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19987,10 +20235,21 @@
         </is>
       </c>
       <c r="E698" s="3" t="n"/>
-      <c r="F698" s="3" t="n"/>
+      <c r="F698" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤+不含compareStart — 42.6%
+无Advertiser过滤+无OrderTag过滤+不含compareStart — 32.0%
+按Advertiser过滤+按OrderTag过滤+不含compareStart — 7.2%
+按Advertiser过滤+无OrderTag过滤+含compareStart — 6.0%
+按Advertiser过滤+按OrderTag过滤+含compareStart — 4.2%
+无Advertiser过滤+按OrderTag过滤+不含compareStart — 2.4%
+无Advertiser过滤+无OrderTag过滤+含compareStart — 2.4%
+不传advertiserIds+不传orderTagIds+不含compareStart — 1.4%</t>
+        </is>
+      </c>
       <c r="G698" s="3" t="n"/>
     </row>
-    <row r="699">
+    <row r="699" ht="128" customHeight="1">
       <c r="A699" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20012,10 +20271,21 @@
         </is>
       </c>
       <c r="E699" s="3" t="n"/>
-      <c r="F699" s="3" t="n"/>
+      <c r="F699" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤+不含comparePreStart — 35.0%
+无Advertiser过滤+无OrderTag过滤+不含comparePreStart — 31.2%
+按Advertiser过滤+按OrderTag过滤+不含comparePreStart — 9.8%
+按Advertiser过滤+无OrderTag过滤+含comparePreStart — 9.2%
+按Advertiser过滤+按OrderTag过滤+含comparePreStart — 6.4%
+无Advertiser过滤+无OrderTag过滤+含comparePreStart — 3.4%
+无Advertiser过滤+按OrderTag过滤+不含comparePreStart — 1.6%
+按Advertiser过滤+不传orderTagIds+不含comparePreStart — 1.2%</t>
+        </is>
+      </c>
       <c r="G699" s="3" t="n"/>
     </row>
-    <row r="700">
+    <row r="700" ht="80" customHeight="1">
       <c r="A700" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20037,10 +20307,22 @@
         </is>
       </c>
       <c r="E700" s="3" t="n"/>
-      <c r="F700" s="3" t="n"/>
-      <c r="G700" s="3" t="n"/>
-    </row>
-    <row r="701">
+      <c r="F700" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤 — 51.2%
+无Advertiser过滤+无OrderTag过滤 — 38.4%
+按Advertiser过滤+按OrderTag过滤 — 6.0%
+无Advertiser过滤+按OrderTag过滤 — 2.0%
+不传advertiserIds+不传orderTagIds — 1.0%</t>
+        </is>
+      </c>
+      <c r="G700" s="5" t="inlineStr">
+        <is>
+          <t>真实后端bug：不传advertiserIds/orderTagIds(空request body，真实流量占比约1%)时抛NullReferenceException(DashboardPerformanceBuilder.Result_GetDSPDashboardOrderChart)，HTTP 200外层包裹513+完整堆栈泄露，如实记录FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="701" ht="96" customHeight="1">
       <c r="A701" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20062,10 +20344,19 @@
         </is>
       </c>
       <c r="E701" s="3" t="n"/>
-      <c r="F701" s="3" t="n"/>
+      <c r="F701" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+按OrderTag过滤+不含toFinalMarket — 56.0%
+按Advertiser过滤+按OrderTag过滤+含toFinalMarket — 17.8%
+无Advertiser过滤+按OrderTag过滤+不含toFinalMarket — 14.8%
+按Advertiser过滤+无OrderTag过滤+不含toFinalMarket — 4.4%
+无Advertiser过滤+按OrderTag过滤+含toFinalMarket — 3.8%
+无Advertiser过滤+无OrderTag过滤+不含toFinalMarket — 2.0%</t>
+        </is>
+      </c>
       <c r="G701" s="3" t="n"/>
     </row>
-    <row r="702">
+    <row r="702" ht="128" customHeight="1">
       <c r="A702" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20087,10 +20378,21 @@
         </is>
       </c>
       <c r="E702" s="3" t="n"/>
-      <c r="F702" s="3" t="n"/>
+      <c r="F702" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤+不含compareStart — 42.0%
+无Advertiser过滤+无OrderTag过滤+不含compareStart — 30.0%
+按Advertiser过滤+无OrderTag过滤+含compareStart — 8.4%
+按Advertiser过滤+按OrderTag过滤+不含compareStart — 7.0%
+按Advertiser过滤+按OrderTag过滤+含compareStart — 4.0%
+无Advertiser过滤+无OrderTag过滤+含compareStart — 2.6%
+不传advertiserIds+不传orderTagIds+不含compareStart — 2.0%
+无Advertiser过滤+按OrderTag过滤+不含compareStart — 1.8%</t>
+        </is>
+      </c>
       <c r="G702" s="3" t="n"/>
     </row>
-    <row r="703">
+    <row r="703" ht="80" customHeight="1">
       <c r="A703" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20112,10 +20414,18 @@
         </is>
       </c>
       <c r="E703" s="3" t="n"/>
-      <c r="F703" s="3" t="n"/>
+      <c r="F703" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤 — 46.8%
+无Advertiser过滤+无OrderTag过滤 — 43.8%
+按Advertiser过滤+按OrderTag过滤 — 5.4%
+不传advertiserIds+不传orderTagIds — 1.8%
+无Advertiser过滤+按OrderTag过滤 — 1.4%</t>
+        </is>
+      </c>
       <c r="G703" s="3" t="n"/>
     </row>
-    <row r="704">
+    <row r="704" ht="80" customHeight="1">
       <c r="A704" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20137,10 +20447,18 @@
         </is>
       </c>
       <c r="E704" s="3" t="n"/>
-      <c r="F704" s="3" t="n"/>
+      <c r="F704" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无OrderTag过滤 — 45.0%
+按Advertiser过滤+无OrderTag过滤 — 37.6%
+按Advertiser过滤+按OrderTag过滤 — 9.4%
+无Advertiser过滤+按OrderTag过滤 — 4.6%
+不传advertiserIds+不传orderTagIds — 2.2%</t>
+        </is>
+      </c>
       <c r="G704" s="3" t="n"/>
     </row>
-    <row r="705">
+    <row r="705" ht="128" customHeight="1">
       <c r="A705" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20162,10 +20480,21 @@
         </is>
       </c>
       <c r="E705" s="3" t="n"/>
-      <c r="F705" s="3" t="n"/>
+      <c r="F705" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无OrderTag过滤+不含compareStart — 46.6%
+按Advertiser过滤+无OrderTag过滤+不含compareStart — 34.6%
+按Advertiser过滤+按OrderTag过滤+不含compareStart — 4.8%
+按Advertiser过滤+无OrderTag过滤+含compareStart — 3.8%
+无Advertiser过滤+无OrderTag过滤+含compareStart — 3.8%
+不传advertiserIds+不传orderTagIds+不含compareStart — 2.2%
+按Advertiser过滤+按OrderTag过滤+含compareStart — 1.6%
+无Advertiser过滤+按OrderTag过滤+不含compareStart — 1.4%</t>
+        </is>
+      </c>
       <c r="G705" s="3" t="n"/>
     </row>
-    <row r="706">
+    <row r="706" ht="128" customHeight="1">
       <c r="A706" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20187,10 +20516,25 @@
         </is>
       </c>
       <c r="E706" s="3" t="n"/>
-      <c r="F706" s="3" t="n"/>
-      <c r="G706" s="3" t="n"/>
-    </row>
-    <row r="707">
+      <c r="F706" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤+不含comparePreStart — 44.8%
+无Advertiser过滤+无OrderTag过滤+不含comparePreStart — 37.6%
+按Advertiser过滤+按OrderTag过滤+不含comparePreStart — 7.2%
+无Advertiser过滤+按OrderTag过滤+不含comparePreStart — 3.8%
+无Advertiser过滤+无OrderTag过滤+含comparePreStart — 1.6%
+不传advertiserIds+不传orderTagIds+不含comparePreStart — 1.6%
+按Advertiser过滤+无OrderTag过滤+含comparePreStart — 1.6%
+按Advertiser过滤+按OrderTag过滤+含comparePreStart — 1.2%</t>
+        </is>
+      </c>
+      <c r="G706" s="5" t="inlineStr">
+        <is>
+          <t>真实后端bug：不传advertiserIds/orderTagIds(空request body)时抛NullReferenceException，同OrderMultiChart根因，如实记录FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="707" ht="176" customHeight="1">
       <c r="A707" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20212,10 +20556,28 @@
         </is>
       </c>
       <c r="E707" s="3" t="n"/>
-      <c r="F707" s="3" t="n"/>
-      <c r="G707" s="3" t="n"/>
-    </row>
-    <row r="708">
+      <c r="F707" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+含dashboradLineItemType+无OrderTag过滤+不含comparePreStart — 25.4%
+无Advertiser过滤+不含dashboradLineItemType+无OrderTag过滤+不含comparePreStart — 20.6%
+按Advertiser过滤+不含dashboradLineItemType+无OrderTag过滤+不含comparePreStart — 19.0%
+按Advertiser过滤+含dashboradLineItemType+无OrderTag过滤+不含comparePreStart — 16.6%
+按Advertiser过滤+不含dashboradLineItemType+无OrderTag过滤+含comparePreStart — 4.0%
+按Advertiser过滤+不含dashboradLineItemType+按OrderTag过滤+不含comparePreStart — 3.4%
+按Advertiser过滤+含dashboradLineItemType+按OrderTag过滤+不含comparePreStart — 1.8%
+按Advertiser过滤+含dashboradLineItemType+无OrderTag过滤+含comparePreStart — 1.8%
+无Advertiser过滤+不含dashboradLineItemType+无OrderTag过滤+含comparePreStart — 1.6%
+不传advertiserIds+不含dashboradLineItemType+不传orderTagIds+不含comparePreStart — 1.2%
+按Advertiser过滤+含dashboradLineItemType+按OrderTag过滤+含comparePreStart — 1.0%</t>
+        </is>
+      </c>
+      <c r="G707" s="5" t="inlineStr">
+        <is>
+          <t>真实后端bug：不传advertiserIds(空request body)时抛NullReferenceException，同OrderMultiChart根因，如实记录FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="708" ht="96" customHeight="1">
       <c r="A708" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20237,10 +20599,19 @@
         </is>
       </c>
       <c r="E708" s="3" t="n"/>
-      <c r="F708" s="3" t="n"/>
+      <c r="F708" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤+不含comparePreStart — 43.8%
+无Advertiser过滤+无OrderTag过滤+不含comparePreStart — 36.0%
+按Advertiser过滤+按OrderTag过滤+不含comparePreStart — 7.4%
+按Advertiser过滤+无OrderTag过滤+含comparePreStart — 4.8%
+按Advertiser过滤+按OrderTag过滤+含comparePreStart — 3.6%
+无Advertiser过滤+无OrderTag过滤+含comparePreStart — 2.8%</t>
+        </is>
+      </c>
       <c r="G708" s="3" t="n"/>
     </row>
-    <row r="709">
+    <row r="709" ht="112" customHeight="1">
       <c r="A709" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20262,10 +20633,20 @@
         </is>
       </c>
       <c r="E709" s="3" t="n"/>
-      <c r="F709" s="3" t="n"/>
+      <c r="F709" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无OrderTag过滤+不含comparePreStart — 42.8%
+按Advertiser过滤+无OrderTag过滤+不含comparePreStart — 36.2%
+按Advertiser过滤+按OrderTag过滤+不含comparePreStart — 6.6%
+按Advertiser过滤+无OrderTag过滤+含comparePreStart — 5.4%
+按Advertiser过滤+按OrderTag过滤+含comparePreStart — 3.4%
+无Advertiser过滤+无OrderTag过滤+含comparePreStart — 3.0%
+无Advertiser过滤+按OrderTag过滤+不含comparePreStart — 1.4%</t>
+        </is>
+      </c>
       <c r="G709" s="3" t="n"/>
     </row>
-    <row r="710">
+    <row r="710" ht="80" customHeight="1">
       <c r="A710" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20287,8 +20668,20 @@
         </is>
       </c>
       <c r="E710" s="3" t="n"/>
-      <c r="F710" s="3" t="n"/>
-      <c r="G710" s="3" t="n"/>
+      <c r="F710" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤 — 46.0%
+无Advertiser过滤+无OrderTag过滤 — 35.4%
+按Advertiser过滤+按OrderTag过滤 — 13.0%
+无Advertiser过滤+按OrderTag过滤 — 3.0%
+不传advertiserIds+不传orderTagIds — 1.0%</t>
+        </is>
+      </c>
+      <c r="G710" s="5" t="inlineStr">
+        <is>
+          <t>真实后端bug：不传advertiserIds(空request body)时抛NullReferenceException，同OrderMultiChart根因，如实记录FAIL</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" s="2" t="inlineStr">
@@ -20312,10 +20705,18 @@
         </is>
       </c>
       <c r="E711" s="3" t="n"/>
-      <c r="F711" s="3" t="n"/>
-      <c r="G711" s="3" t="n"/>
-    </row>
-    <row r="712">
+      <c r="F711" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G711" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)；同模块SupplySourcePerformanceAndTotal已覆盖，未生成case</t>
+        </is>
+      </c>
+    </row>
+    <row r="712" ht="160" customHeight="1">
       <c r="A712" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20337,8 +20738,25 @@
         </is>
       </c>
       <c r="E712" s="3" t="n"/>
-      <c r="F712" s="3" t="n"/>
-      <c r="G712" s="3" t="n"/>
+      <c r="F712" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不含dashboradLineItemType+无OrderTag过滤 — 25.0%
+无Advertiser过滤+含dashboradLineItemType+无OrderTag过滤 — 23.4%
+按Advertiser过滤+含dashboradLineItemType+无OrderTag过滤 — 19.4%
+无Advertiser过滤+不含dashboradLineItemType+无OrderTag过滤 — 16.0%
+按Advertiser过滤+不含dashboradLineItemType+按OrderTag过滤 — 5.0%
+按Advertiser过滤+含dashboradLineItemType+按OrderTag过滤 — 4.2%
+无Advertiser过滤+不含dashboradLineItemType+按OrderTag过滤 — 2.6%
+按Advertiser过滤+含dashboradLineItemType+不传orderTagIds — 1.6%
+不传advertiserIds+不含dashboradLineItemType+不传orderTagIds — 1.4%
+无Advertiser过滤+含dashboradLineItemType+按OrderTag过滤 — 1.2%</t>
+        </is>
+      </c>
+      <c r="G712" s="5" t="inlineStr">
+        <is>
+          <t>10场景中1个(按LineItemTag过滤)需要 lineitem_tag_id(账号内无实体)，技术受限未执行；1个(不传advertiserIds空body)复现真实后端NullReferenceException(HTTP 513)，如实FAIL；其余8个已执行PASS</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" s="2" t="inlineStr">
@@ -20362,8 +20780,16 @@
         </is>
       </c>
       <c r="E713" s="3" t="n"/>
-      <c r="F713" s="3" t="n"/>
-      <c r="G713" s="3" t="n"/>
+      <c r="F713" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G713" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，备份/BK版本疑似已下线，未生成case</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" s="2" t="inlineStr">
@@ -20387,10 +20813,18 @@
         </is>
       </c>
       <c r="E714" s="3" t="n"/>
-      <c r="F714" s="3" t="n"/>
-      <c r="G714" s="3" t="n"/>
-    </row>
-    <row r="715">
+      <c r="F714" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G714" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)；同模块Top10AsinPromoted/Top10AsinBrandhalo已覆盖，未生成case</t>
+        </is>
+      </c>
+    </row>
+    <row r="715" ht="144" customHeight="1">
       <c r="A715" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20412,10 +20846,26 @@
         </is>
       </c>
       <c r="E715" s="3" t="n"/>
-      <c r="F715" s="3" t="n"/>
-      <c r="G715" s="3" t="n"/>
-    </row>
-    <row r="716">
+      <c r="F715" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤+不含comparePreStart — 33.8%
+无Advertiser过滤+无OrderTag过滤+不含comparePreStart — 18.1%
+按Advertiser过滤+按OrderTag过滤+不含comparePreStart — 14.4%
+按Advertiser过滤+无OrderTag过滤+含comparePreStart — 11.0%
+无Advertiser过滤+按OrderTag过滤+不含comparePreStart — 8.0%
+按Advertiser过滤+按OrderTag过滤+含comparePreStart — 7.7%
+无Advertiser过滤+无OrderTag过滤+含comparePreStart — 4.3%
+不传advertiserIds+不传orderTagIds+不含comparePreStart — 1.0%
+无Advertiser过滤+不传orderTagIds+不含comparePreStart — 1.0%</t>
+        </is>
+      </c>
+      <c r="G715" s="5" t="inlineStr">
+        <is>
+          <t>真实后端bug：不传advertiserIds/orderTagIds(空request body)时抛NullReferenceException(GetTop10ASINBrandhalo)，如实记录FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="716" ht="128" customHeight="1">
       <c r="A716" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20437,10 +20887,25 @@
         </is>
       </c>
       <c r="E716" s="3" t="n"/>
-      <c r="F716" s="3" t="n"/>
-      <c r="G716" s="3" t="n"/>
-    </row>
-    <row r="717">
+      <c r="F716" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤+不含comparePreStart — 40.6%
+无Advertiser过滤+无OrderTag过滤+不含comparePreStart — 38.8%
+按Advertiser过滤+按OrderTag过滤+不含comparePreStart — 6.0%
+按Advertiser过滤+无OrderTag过滤+含comparePreStart — 5.8%
+不传advertiserIds+不传orderTagIds+不含comparePreStart — 3.2%
+按Advertiser过滤+按OrderTag过滤+含comparePreStart — 2.0%
+无Advertiser过滤+无OrderTag过滤+含comparePreStart — 1.6%
+无Advertiser过滤+按OrderTag过滤+不含comparePreStart — 1.2%</t>
+        </is>
+      </c>
+      <c r="G716" s="5" t="inlineStr">
+        <is>
+          <t>真实后端bug：不传advertiserIds/orderTagIds(空request body，真实流量占比约3.2%)时抛NullReferenceException(GetTop10ASINPromoted)，如实记录FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="717" ht="128" customHeight="1">
       <c r="A717" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20462,7 +20927,18 @@
         </is>
       </c>
       <c r="E717" s="3" t="n"/>
-      <c r="F717" s="3" t="n"/>
+      <c r="F717" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤+不含compareStart — 41.8%
+无Advertiser过滤+无OrderTag过滤+不含compareStart — 37.4%
+按Advertiser过滤+无OrderTag过滤+含compareStart — 7.4%
+按Advertiser过滤+按OrderTag过滤+不含compareStart — 4.0%
+无Advertiser过滤+无OrderTag过滤+含compareStart — 3.0%
+按Advertiser过滤+按OrderTag过滤+含compareStart — 2.2%
+不传advertiserIds+不传orderTagIds+不含compareStart — 1.2%
+无Advertiser过滤+按OrderTag过滤+不含compareStart — 1.0%</t>
+        </is>
+      </c>
       <c r="G717" s="3" t="n"/>
     </row>
     <row r="718">
@@ -20487,8 +20963,16 @@
         </is>
       </c>
       <c r="E718" s="3" t="n"/>
-      <c r="F718" s="3" t="n"/>
-      <c r="G718" s="3" t="n"/>
+      <c r="F718" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G718" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，未生成case</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" s="2" t="inlineStr">
@@ -20512,10 +20996,18 @@
         </is>
       </c>
       <c r="E719" s="3" t="n"/>
-      <c r="F719" s="3" t="n"/>
-      <c r="G719" s="3" t="n"/>
-    </row>
-    <row r="720">
+      <c r="F719" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G719" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)；V2版本TopLineItemMoversV2已覆盖，未生成case</t>
+        </is>
+      </c>
+    </row>
+    <row r="720" ht="80" customHeight="1">
       <c r="A720" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20537,7 +21029,15 @@
         </is>
       </c>
       <c r="E720" s="3" t="n"/>
-      <c r="F720" s="3" t="n"/>
+      <c r="F720" s="6" t="inlineStr">
+        <is>
+          <t>compareColumn=TotalCost — 39.5%
+compareColumn=TotalSales — 28.9%
+compareColumn=ProductSales — 10.5%
+compareColumn=TotalROAS — 7.9%
+compareColumn=PercentOfPurchasesNewToBrand — 7.9%</t>
+        </is>
+      </c>
       <c r="G720" s="3" t="n"/>
     </row>
     <row r="721">
@@ -20562,10 +21062,18 @@
         </is>
       </c>
       <c r="E721" s="3" t="n"/>
-      <c r="F721" s="3" t="n"/>
-      <c r="G721" s="3" t="n"/>
-    </row>
-    <row r="722">
+      <c r="F721" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G721" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)；V2版本TopOrderMoversV2已覆盖，未生成case</t>
+        </is>
+      </c>
+    </row>
+    <row r="722" ht="160" customHeight="1">
       <c r="A722" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20587,10 +21095,27 @@
         </is>
       </c>
       <c r="E722" s="3" t="n"/>
-      <c r="F722" s="3" t="n"/>
-      <c r="G722" s="3" t="n"/>
-    </row>
-    <row r="723">
+      <c r="F722" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤+不含comparePreStart — 36.8%
+无Advertiser过滤+无OrderTag过滤+不含comparePreStart — 31.0%
+按Advertiser过滤+按OrderTag过滤+不含comparePreStart — 11.6%
+按Advertiser过滤+无OrderTag过滤+含comparePreStart — 7.2%
+无Advertiser过滤+无OrderTag过滤+含comparePreStart — 3.8%
+按Advertiser过滤+按OrderTag过滤+含comparePreStart — 3.8%
+无Advertiser过滤+按OrderTag过滤+不含comparePreStart — 2.6%
+不传advertiserIds+不传orderTagIds+不含comparePreStart — 1.0%
+按Advertiser过滤+不传orderTagIds+不含comparePreStart — 1.0%
+无Advertiser过滤+按OrderTag过滤+含comparePreStart — 1.0%</t>
+        </is>
+      </c>
+      <c r="G722" s="5" t="inlineStr">
+        <is>
+          <t>真实后端bug：不传advertiserIds/orderTagIds(空request body)时抛NullReferenceException，同OrderMultiChart根因，如实记录FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="723" ht="112" customHeight="1">
       <c r="A723" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20612,10 +21137,20 @@
         </is>
       </c>
       <c r="E723" s="3" t="n"/>
-      <c r="F723" s="3" t="n"/>
+      <c r="F723" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无OrderTag过滤+不含comparePreStart — 45.6%
+按Advertiser过滤+无OrderTag过滤+不含comparePreStart — 39.2%
+无Advertiser过滤+无OrderTag过滤+含comparePreStart — 4.0%
+按Advertiser过滤+按OrderTag过滤+不含comparePreStart — 3.8%
+按Advertiser过滤+无OrderTag过滤+含comparePreStart — 3.6%
+无Advertiser过滤+按OrderTag过滤+不含comparePreStart — 1.4%
+按Advertiser过滤+按OrderTag过滤+含comparePreStart — 1.2%</t>
+        </is>
+      </c>
       <c r="G723" s="3" t="n"/>
     </row>
-    <row r="724">
+    <row r="724" ht="64" customHeight="1">
       <c r="A724" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20637,7 +21172,14 @@
         </is>
       </c>
       <c r="E724" s="3" t="n"/>
-      <c r="F724" s="3" t="n"/>
+      <c r="F724" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤 — 46.8%
+无Advertiser过滤+无OrderTag过滤 — 27.0%
+按Advertiser过滤+按OrderTag过滤 — 20.6%
+无Advertiser过滤+按OrderTag过滤 — 4.8%</t>
+        </is>
+      </c>
       <c r="G724" s="3" t="n"/>
     </row>
     <row r="725">
@@ -20662,8 +21204,16 @@
         </is>
       </c>
       <c r="E725" s="3" t="n"/>
-      <c r="F725" s="3" t="n"/>
-      <c r="G725" s="3" t="n"/>
+      <c r="F725" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G725" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，未生成case</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" s="2" t="inlineStr">
@@ -20687,10 +21237,18 @@
         </is>
       </c>
       <c r="E726" s="3" t="n"/>
-      <c r="F726" s="3" t="n"/>
-      <c r="G726" s="3" t="n"/>
-    </row>
-    <row r="727">
+      <c r="F726" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G726" s="5" t="inlineStr">
+        <is>
+          <t>零流量(365天0次，已排除clientId 0/62)，未生成case</t>
+        </is>
+      </c>
+    </row>
+    <row r="727" ht="112" customHeight="1">
       <c r="A727" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20712,7 +21270,17 @@
         </is>
       </c>
       <c r="E727" s="3" t="n"/>
-      <c r="F727" s="3" t="n"/>
+      <c r="F727" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无OrderTag过滤+不含widgetType — 28.2%
+无Advertiser过滤+无OrderTag过滤+不含widgetType — 22.2%
+按Advertiser过滤+无OrderTag过滤+含widgetType — 18.0%
+按Advertiser过滤+按OrderTag过滤+不含widgetType — 11.0%
+无Advertiser过滤+无OrderTag过滤+含widgetType — 9.8%
+按Advertiser过滤+按OrderTag过滤+含widgetType — 5.8%
+无Advertiser过滤+按OrderTag过滤+不含widgetType — 2.0%</t>
+        </is>
+      </c>
       <c r="G727" s="3" t="n"/>
     </row>
     <row r="728">
@@ -31581,12 +32149,12 @@
       <c r="E1154" s="3" t="n"/>
       <c r="F1154" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1154" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有13次，全部来自clientId 0/62内部系统/自动化噪音)；路径含禁用关键词refresh，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有13次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -31680,12 +32248,12 @@
       <c r="E1157" s="3" t="n"/>
       <c r="F1157" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1157" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词run，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -31713,12 +32281,12 @@
       <c r="E1158" s="3" t="n"/>
       <c r="F1158" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1158" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -31746,12 +32314,12 @@
       <c r="E1159" s="3" t="n"/>
       <c r="F1159" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1159" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有15次，全部来自clientId 0/62内部系统/自动化噪音)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有15次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -31779,12 +32347,12 @@
       <c r="E1160" s="3" t="n"/>
       <c r="F1160" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1160" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -31812,12 +32380,12 @@
       <c r="E1161" s="3" t="n"/>
       <c r="F1161" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1161" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有12次，全部来自clientId 0/62内部系统/自动化噪音)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有12次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -31845,12 +32413,12 @@
       <c r="E1162" s="3" t="n"/>
       <c r="F1162" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1162" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -31878,12 +32446,12 @@
       <c r="E1163" s="3" t="n"/>
       <c r="F1163" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1163" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -31911,12 +32479,12 @@
       <c r="E1164" s="3" t="n"/>
       <c r="F1164" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1164" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -31944,12 +32512,12 @@
       <c r="E1165" s="3" t="n"/>
       <c r="F1165" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1165" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有4次，全部来自clientId 0/62内部系统/自动化噪音)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有4次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -37517,12 +38085,12 @@
       <c r="E1386" s="3" t="n"/>
       <c r="F1386" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1386" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39331,12 +39899,12 @@
       <c r="E1456" s="3" t="n"/>
       <c r="F1456" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1456" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39364,12 +39932,12 @@
       <c r="E1457" s="3" t="n"/>
       <c r="F1457" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1457" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39397,12 +39965,12 @@
       <c r="E1458" s="3" t="n"/>
       <c r="F1458" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1458" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39430,12 +39998,12 @@
       <c r="E1459" s="3" t="n"/>
       <c r="F1459" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1459" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39463,12 +40031,12 @@
       <c r="E1460" s="3" t="n"/>
       <c r="F1460" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1460" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39496,12 +40064,12 @@
       <c r="E1461" s="3" t="n"/>
       <c r="F1461" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1461" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39529,12 +40097,12 @@
       <c r="E1462" s="3" t="n"/>
       <c r="F1462" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1462" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39562,12 +40130,12 @@
       <c r="E1463" s="3" t="n"/>
       <c r="F1463" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1463" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39595,12 +40163,12 @@
       <c r="E1464" s="3" t="n"/>
       <c r="F1464" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1464" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39628,12 +40196,12 @@
       <c r="E1465" s="3" t="n"/>
       <c r="F1465" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1465" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39661,12 +40229,12 @@
       <c r="E1466" s="3" t="n"/>
       <c r="F1466" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1466" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39694,12 +40262,12 @@
       <c r="E1467" s="3" t="n"/>
       <c r="F1467" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1467" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39727,12 +40295,12 @@
       <c r="E1468" s="3" t="n"/>
       <c r="F1468" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1468" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39760,12 +40328,12 @@
       <c r="E1469" s="3" t="n"/>
       <c r="F1469" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1469" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39793,12 +40361,12 @@
       <c r="E1470" s="3" t="n"/>
       <c r="F1470" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1470" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39826,12 +40394,12 @@
       <c r="E1471" s="3" t="n"/>
       <c r="F1471" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1471" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39859,12 +40427,12 @@
       <c r="E1472" s="3" t="n"/>
       <c r="F1472" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1472" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39892,12 +40460,12 @@
       <c r="E1473" s="3" t="n"/>
       <c r="F1473" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1473" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39925,12 +40493,12 @@
       <c r="E1474" s="3" t="n"/>
       <c r="F1474" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1474" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39958,12 +40526,12 @@
       <c r="E1475" s="3" t="n"/>
       <c r="F1475" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1475" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -39991,12 +40559,12 @@
       <c r="E1476" s="3" t="n"/>
       <c r="F1476" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1476" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40024,12 +40592,12 @@
       <c r="E1477" s="3" t="n"/>
       <c r="F1477" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1477" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40057,12 +40625,12 @@
       <c r="E1478" s="3" t="n"/>
       <c r="F1478" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1478" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40090,12 +40658,12 @@
       <c r="E1479" s="3" t="n"/>
       <c r="F1479" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1479" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40123,12 +40691,12 @@
       <c r="E1480" s="3" t="n"/>
       <c r="F1480" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1480" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40156,12 +40724,12 @@
       <c r="E1481" s="3" t="n"/>
       <c r="F1481" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1481" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40189,12 +40757,12 @@
       <c r="E1482" s="3" t="n"/>
       <c r="F1482" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1482" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40222,12 +40790,12 @@
       <c r="E1483" s="3" t="n"/>
       <c r="F1483" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1483" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40255,12 +40823,12 @@
       <c r="E1484" s="3" t="n"/>
       <c r="F1484" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1484" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40288,12 +40856,12 @@
       <c r="E1485" s="3" t="n"/>
       <c r="F1485" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1485" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40321,12 +40889,12 @@
       <c r="E1486" s="3" t="n"/>
       <c r="F1486" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1486" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40354,12 +40922,12 @@
       <c r="E1487" s="3" t="n"/>
       <c r="F1487" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1487" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40387,12 +40955,12 @@
       <c r="E1488" s="3" t="n"/>
       <c r="F1488" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1488" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有12次，全部来自clientId 0/62内部系统/自动化噪音)；路径含禁用关键词sync/test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有12次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40420,12 +40988,12 @@
       <c r="E1489" s="3" t="n"/>
       <c r="F1489" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1489" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有7次，全部来自clientId 0/62内部系统/自动化噪音)；路径含禁用关键词sync/test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有7次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40453,12 +41021,12 @@
       <c r="E1490" s="3" t="n"/>
       <c r="F1490" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1490" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync/test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40486,12 +41054,12 @@
       <c r="E1491" s="3" t="n"/>
       <c r="F1491" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1491" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40519,12 +41087,12 @@
       <c r="E1492" s="3" t="n"/>
       <c r="F1492" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1492" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40651,12 +41219,12 @@
       <c r="E1496" s="3" t="n"/>
       <c r="F1496" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1496" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40684,12 +41252,12 @@
       <c r="E1497" s="3" t="n"/>
       <c r="F1497" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1497" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40717,12 +41285,12 @@
       <c r="E1498" s="3" t="n"/>
       <c r="F1498" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1498" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -40750,12 +41318,12 @@
       <c r="E1499" s="3" t="n"/>
       <c r="F1499" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1499" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42466,12 +43034,12 @@
       <c r="E1567" s="3" t="n"/>
       <c r="F1567" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1567" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42499,12 +43067,12 @@
       <c r="E1568" s="3" t="n"/>
       <c r="F1568" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1568" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42532,12 +43100,12 @@
       <c r="E1569" s="3" t="n"/>
       <c r="F1569" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1569" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42565,12 +43133,12 @@
       <c r="E1570" s="3" t="n"/>
       <c r="F1570" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1570" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有9次，全部来自clientId 0/62内部系统/自动化噪音)；路径含禁用关键词run/test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有9次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42598,12 +43166,12 @@
       <c r="E1571" s="3" t="n"/>
       <c r="F1571" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1571" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词sync/test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42631,12 +43199,12 @@
       <c r="E1572" s="3" t="n"/>
       <c r="F1572" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词+文件上传类型，需人工测试</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1572" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test；multipart/form-data文件上传接口，无法生成JSON case，需人工测试，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42664,12 +43232,12 @@
       <c r="E1573" s="3" t="n"/>
       <c r="F1573" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1573" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42697,12 +43265,12 @@
       <c r="E1574" s="3" t="n"/>
       <c r="F1574" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1574" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42730,12 +43298,12 @@
       <c r="E1575" s="3" t="n"/>
       <c r="F1575" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1575" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42763,12 +43331,12 @@
       <c r="E1576" s="3" t="n"/>
       <c r="F1576" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1576" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42796,12 +43364,12 @@
       <c r="E1577" s="3" t="n"/>
       <c r="F1577" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1577" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42829,12 +43397,12 @@
       <c r="E1578" s="3" t="n"/>
       <c r="F1578" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1578" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42862,12 +43430,12 @@
       <c r="E1579" s="3" t="n"/>
       <c r="F1579" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1579" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42895,12 +43463,12 @@
       <c r="E1580" s="3" t="n"/>
       <c r="F1580" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1580" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42928,12 +43496,12 @@
       <c r="E1581" s="3" t="n"/>
       <c r="F1581" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1581" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42961,12 +43529,12 @@
       <c r="E1582" s="3" t="n"/>
       <c r="F1582" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1582" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -42994,12 +43562,12 @@
       <c r="E1583" s="3" t="n"/>
       <c r="F1583" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1583" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -43027,12 +43595,12 @@
       <c r="E1584" s="3" t="n"/>
       <c r="F1584" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1584" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -43060,12 +43628,12 @@
       <c r="E1585" s="3" t="n"/>
       <c r="F1585" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1585" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -43093,12 +43661,12 @@
       <c r="E1586" s="3" t="n"/>
       <c r="F1586" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1586" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -43126,12 +43694,12 @@
       <c r="E1587" s="3" t="n"/>
       <c r="F1587" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1587" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -43159,12 +43727,12 @@
       <c r="E1588" s="3" t="n"/>
       <c r="F1588" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1588" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -43192,12 +43760,12 @@
       <c r="E1589" s="3" t="n"/>
       <c r="F1589" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1589" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -43225,12 +43793,12 @@
       <c r="E1590" s="3" t="n"/>
       <c r="F1590" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量+路径含禁用关键词</t>
+          <t>ES 无流量</t>
         </is>
       </c>
       <c r="G1590" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)；路径含禁用关键词test，双重原因不生成不执行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -43610,7 +44178,7 @@
       </c>
       <c r="G1602" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖；路径字面含'init'(属单词内字面误伤，同latest先例)，待用户复核是否放行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -44237,7 +44805,7 @@
       </c>
       <c r="G1621" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖；路径字面含'init'(属单词内字面误伤，同latest先例)，待用户复核是否放行</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1378,9 +1378,19 @@
       </c>
       <c r="D39" s="3" t="n"/>
       <c r="E39" s="3" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
+      <c r="F39" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>88% (43/49)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -25083,7 +25093,7 @@
       <c r="F879" s="3" t="n"/>
       <c r="G879" s="3" t="n"/>
     </row>
-    <row r="880">
+    <row r="880" ht="80" customHeight="1">
       <c r="A880" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25105,10 +25115,18 @@
         </is>
       </c>
       <c r="E880" s="3" t="n"/>
-      <c r="F880" s="3" t="n"/>
+      <c r="F880" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不传OrderTagIds+不含CompareStart — 70.2%
+无Advertiser过滤+不传OrderTagIds+不含CompareStart — 19.6%
+按Advertiser过滤+按OrderTag过滤+不含CompareStart — 4.0%
+按Advertiser过滤+不传OrderTagIds+含CompareStart — 2.8%
+无Advertiser过滤+不传OrderTagIds+含CompareStart — 2.6%</t>
+        </is>
+      </c>
       <c r="G880" s="3" t="n"/>
     </row>
-    <row r="881">
+    <row r="881" ht="64" customHeight="1">
       <c r="A881" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25130,10 +25148,17 @@
         </is>
       </c>
       <c r="E881" s="3" t="n"/>
-      <c r="F881" s="3" t="n"/>
+      <c r="F881" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不含CompareStart — 50.6%
+无Advertiser过滤+不含CompareStart — 35.4%
+按Advertiser过滤+含CompareStart — 9.4%
+无Advertiser过滤+含CompareStart — 4.6%</t>
+        </is>
+      </c>
       <c r="G881" s="3" t="n"/>
     </row>
-    <row r="882">
+    <row r="882" ht="96" customHeight="1">
       <c r="A882" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25155,10 +25180,19 @@
         </is>
       </c>
       <c r="E882" s="3" t="n"/>
-      <c r="F882" s="3" t="n"/>
+      <c r="F882" s="6" t="inlineStr">
+        <is>
+          <t>timeType=month+不含isShowIRoas — 50.0%
+timeType=date+不含isShowIRoas — 26.6%
+timeType=month+含isShowIRoas — 10.0%
+timeType=ytd+不含isShowIRoas — 7.4%
+timeType=date+含isShowIRoas — 4.2%
+timeType=ytd+含isShowIRoas — 1.8%</t>
+        </is>
+      </c>
       <c r="G882" s="3" t="n"/>
     </row>
-    <row r="883">
+    <row r="883" ht="64" customHeight="1">
       <c r="A883" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25180,10 +25214,17 @@
         </is>
       </c>
       <c r="E883" s="3" t="n"/>
-      <c r="F883" s="3" t="n"/>
+      <c r="F883" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不传OrderTagIds+含CompareStart — 67.6%
+按Advertiser过滤+不传OrderTagIds+不含CompareStart — 13.4%
+无Advertiser过滤+不传OrderTagIds+不含CompareStart — 11.2%
+按Advertiser过滤+按OrderTag过滤+含CompareStart — 7.2%</t>
+        </is>
+      </c>
       <c r="G883" s="3" t="n"/>
     </row>
-    <row r="884">
+    <row r="884" ht="112" customHeight="1">
       <c r="A884" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25205,10 +25246,20 @@
         </is>
       </c>
       <c r="E884" s="3" t="n"/>
-      <c r="F884" s="3" t="n"/>
+      <c r="F884" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+无OrderTag过滤 — 37.0%
+无Advertiser过滤+无Order过滤+无OrderTag过滤 — 25.0%
+按Advertiser过滤+按Order过滤+无OrderTag过滤 — 13.8%
+无Advertiser过滤+无Order过滤+按OrderTag过滤 — 7.8%
+按Advertiser过滤+无Order过滤+按OrderTag过滤 — 6.8%
+无Advertiser过滤+按Order过滤+无OrderTag过滤 — 6.4%
+按Advertiser过滤+按Order过滤+按OrderTag过滤 — 2.0%</t>
+        </is>
+      </c>
       <c r="G884" s="3" t="n"/>
     </row>
-    <row r="885">
+    <row r="885" ht="80" customHeight="1">
       <c r="A885" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25230,10 +25281,18 @@
         </is>
       </c>
       <c r="E885" s="3" t="n"/>
-      <c r="F885" s="3" t="n"/>
+      <c r="F885" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤 — 39.0%
+无Advertiser过滤+无Order过滤 — 34.0%
+按Advertiser过滤+按Order过滤 — 17.2%
+无Advertiser过滤+按Order过滤 — 7.4%
+按Advertiser过滤+不传OrderIds — 1.8%</t>
+        </is>
+      </c>
       <c r="G885" s="3" t="n"/>
     </row>
-    <row r="886">
+    <row r="886" ht="128" customHeight="1">
       <c r="A886" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25255,7 +25314,18 @@
         </is>
       </c>
       <c r="E886" s="3" t="n"/>
-      <c r="F886" s="3" t="n"/>
+      <c r="F886" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无Order过滤+无OrderTag过滤 — 36.0%
+按Advertiser过滤+无Order过滤+无OrderTag过滤 — 24.0%
+按Advertiser过滤+按Order过滤+无OrderTag过滤 — 16.4%
+无Advertiser过滤+按Order过滤+无OrderTag过滤 — 8.2%
+按Advertiser过滤+无Order过滤+按OrderTag过滤 — 5.8%
+无Advertiser过滤+无Order过滤+按OrderTag过滤 — 5.4%
+按Advertiser过滤+不传OrderIds+不传OrderTagIds — 2.0%
+按Advertiser过滤+按Order过滤+按OrderTag过滤 — 1.4%</t>
+        </is>
+      </c>
       <c r="G886" s="3" t="n"/>
     </row>
     <row r="887">
@@ -25280,8 +25350,16 @@
         </is>
       </c>
       <c r="E887" s="3" t="n"/>
-      <c r="F887" s="3" t="n"/>
-      <c r="G887" s="3" t="n"/>
+      <c r="F887" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G887" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="888">
       <c r="A888" s="2" t="inlineStr">
@@ -25305,10 +25383,18 @@
         </is>
       </c>
       <c r="E888" s="3" t="n"/>
-      <c r="F888" s="3" t="n"/>
-      <c r="G888" s="3" t="n"/>
-    </row>
-    <row r="889">
+      <c r="F888" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G888" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="889" ht="144" customHeight="1">
       <c r="A889" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25330,10 +25416,22 @@
         </is>
       </c>
       <c r="E889" s="3" t="n"/>
-      <c r="F889" s="3" t="n"/>
+      <c r="F889" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+CreativeIds=[]+无Order过滤 — 29.0%
+无Advertiser过滤+CreativeIds=[]+无Order过滤 — 25.6%
+不传AdvertiserIds+不传CreativeIds+不传OrderIds — 15.0%
+按Advertiser过滤+CreativeIds=[]+按Order过滤 — 11.2%
+按Advertiser过滤+CreativeIds=[ids+]+不传OrderIds — 5.4%
+按Advertiser过滤+CreativeIds=[ids+]+无Order过滤 — 5.2%
+无Advertiser过滤+CreativeIds=[]+按Order过滤 — 3.8%
+无Advertiser过滤+CreativeIds=[ids+]+无Order过滤 — 2.6%
+按Advertiser过滤+CreativeIds=[ids+]+按Order过滤 — 1.6%</t>
+        </is>
+      </c>
       <c r="G889" s="3" t="n"/>
     </row>
-    <row r="890">
+    <row r="890" ht="144" customHeight="1">
       <c r="A890" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25355,7 +25453,19 @@
         </is>
       </c>
       <c r="E890" s="3" t="n"/>
-      <c r="F890" s="3" t="n"/>
+      <c r="F890" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+CreativeIds=[]+无Order过滤 — 31.2%
+无Advertiser过滤+CreativeIds=[]+无Order过滤 — 27.8%
+按Advertiser过滤+CreativeIds=[]+按Order过滤 — 11.0%
+不传AdvertiserIds+不传CreativeIds+不传OrderIds — 10.8%
+按Advertiser过滤+CreativeIds=[ids+]+无Order过滤 — 6.6%
+无Advertiser过滤+CreativeIds=[ids+]+无Order过滤 — 4.2%
+无Advertiser过滤+CreativeIds=[]+按Order过滤 — 4.0%
+按Advertiser过滤+CreativeIds=[ids+]+按Order过滤 — 2.6%
+按Advertiser过滤+CreativeIds=[ids+]+不传OrderIds — 1.6%</t>
+        </is>
+      </c>
       <c r="G890" s="3" t="n"/>
     </row>
     <row r="891">
@@ -25380,10 +25490,18 @@
         </is>
       </c>
       <c r="E891" s="3" t="n"/>
-      <c r="F891" s="3" t="n"/>
-      <c r="G891" s="3" t="n"/>
-    </row>
-    <row r="892">
+      <c r="F891" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G891" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="892" ht="144" customHeight="1">
       <c r="A892" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25405,10 +25523,22 @@
         </is>
       </c>
       <c r="E892" s="3" t="n"/>
-      <c r="F892" s="3" t="n"/>
+      <c r="F892" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+CreativeIds=[]+无Order过滤 — 31.8%
+按Advertiser过滤+CreativeIds=[]+无Order过滤 — 25.6%
+按Advertiser过滤+CreativeIds=[ids+]+不传OrderIds — 14.4%
+按Advertiser过滤+CreativeIds=[]+按Order过滤 — 7.4%
+不传AdvertiserIds+不传CreativeIds+不传OrderIds — 6.0%
+按Advertiser过滤+CreativeIds=[ids+]+无Order过滤 — 5.2%
+无Advertiser过滤+CreativeIds=[]+按Order过滤 — 4.4%
+无Advertiser过滤+CreativeIds=[ids+]+无Order过滤 — 2.2%
+按Advertiser过滤+CreativeIds=[ids+]+按Order过滤 — 2.0%</t>
+        </is>
+      </c>
       <c r="G892" s="3" t="n"/>
     </row>
-    <row r="893">
+    <row r="893" ht="48" customHeight="1">
       <c r="A893" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25430,10 +25560,16 @@
         </is>
       </c>
       <c r="E893" s="3" t="n"/>
-      <c r="F893" s="3" t="n"/>
+      <c r="F893" s="6" t="inlineStr">
+        <is>
+          <t>不传OrderTagIds+含CompareStart — 77.2%
+按OrderTag过滤+含CompareStart — 12.8%
+不传OrderTagIds+不含CompareStart — 9.8%</t>
+        </is>
+      </c>
       <c r="G893" s="3" t="n"/>
     </row>
-    <row r="894">
+    <row r="894" ht="80" customHeight="1">
       <c r="A894" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25455,10 +25591,18 @@
         </is>
       </c>
       <c r="E894" s="3" t="n"/>
-      <c r="F894" s="3" t="n"/>
+      <c r="F894" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不传OrderTagIds+含CompareStart — 64.2%
+按Advertiser过滤+按OrderTag过滤+含CompareStart — 16.4%
+按Advertiser过滤+按OrderTag过滤+不含CompareStart — 10.0%
+按Advertiser过滤+不传OrderTagIds+不含CompareStart — 7.6%
+不传AdvertiserIds+按OrderTag过滤+不含CompareStart — 1.2%</t>
+        </is>
+      </c>
       <c r="G894" s="3" t="n"/>
     </row>
-    <row r="895">
+    <row r="895" ht="64" customHeight="1">
       <c r="A895" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25480,10 +25624,17 @@
         </is>
       </c>
       <c r="E895" s="3" t="n"/>
-      <c r="F895" s="3" t="n"/>
+      <c r="F895" s="6" t="inlineStr">
+        <is>
+          <t>不传OrderTagIds+含CompareStart — 61.2%
+按OrderTag过滤+不含CompareStart — 32.8%
+不传OrderTagIds+不含CompareStart — 4.6%
+按OrderTag过滤+含CompareStart — 1.4%</t>
+        </is>
+      </c>
       <c r="G895" s="3" t="n"/>
     </row>
-    <row r="896">
+    <row r="896" ht="48" customHeight="1">
       <c r="A896" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25505,10 +25656,16 @@
         </is>
       </c>
       <c r="E896" s="3" t="n"/>
-      <c r="F896" s="3" t="n"/>
+      <c r="F896" s="6" t="inlineStr">
+        <is>
+          <t>不传OrderTagIds+含CompareStart — 68.4%
+按OrderTag过滤+含CompareStart — 18.2%
+不传OrderTagIds+不含CompareStart — 12.8%</t>
+        </is>
+      </c>
       <c r="G896" s="3" t="n"/>
     </row>
-    <row r="897">
+    <row r="897" ht="48" customHeight="1">
       <c r="A897" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25530,10 +25687,16 @@
         </is>
       </c>
       <c r="E897" s="3" t="n"/>
-      <c r="F897" s="3" t="n"/>
+      <c r="F897" s="6" t="inlineStr">
+        <is>
+          <t>不传OrderTagIds+含CompareStart — 81.4%
+不传OrderTagIds+不含CompareStart — 9.6%
+按OrderTag过滤+含CompareStart — 9.0%</t>
+        </is>
+      </c>
       <c r="G897" s="3" t="n"/>
     </row>
-    <row r="898">
+    <row r="898" ht="48" customHeight="1">
       <c r="A898" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25555,10 +25718,16 @@
         </is>
       </c>
       <c r="E898" s="3" t="n"/>
-      <c r="F898" s="3" t="n"/>
+      <c r="F898" s="6" t="inlineStr">
+        <is>
+          <t>不传OrderTagIds+forceExchangeCode=US — 79.8%
+不传OrderTagIds+forceExchangeCode=MX — 16.4%
+按OrderTag过滤+forceExchangeCode=US — 3.8%</t>
+        </is>
+      </c>
       <c r="G898" s="3" t="n"/>
     </row>
-    <row r="899">
+    <row r="899" ht="80" customHeight="1">
       <c r="A899" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25580,10 +25749,18 @@
         </is>
       </c>
       <c r="E899" s="3" t="n"/>
-      <c r="F899" s="3" t="n"/>
+      <c r="F899" s="6" t="inlineStr">
+        <is>
+          <t>不传OrderTagIds+forceExchangeCode=US — 61.6%
+不传OrderTagIds+forceExchangeCode=MX — 14.0%
+不传OrderTagIds+forceExchangeCode=CA — 11.6%
+按OrderTag过滤+forceExchangeCode=US — 8.8%
+不传OrderTagIds+forceExchangeCode=AU — 2.8%</t>
+        </is>
+      </c>
       <c r="G899" s="3" t="n"/>
     </row>
-    <row r="900">
+    <row r="900" ht="96" customHeight="1">
       <c r="A900" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25605,10 +25782,19 @@
         </is>
       </c>
       <c r="E900" s="3" t="n"/>
-      <c r="F900" s="3" t="n"/>
+      <c r="F900" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无Order过滤+不含CompareStart — 49.8%
+无Advertiser过滤+无Order过滤+含CompareStart — 21.2%
+按Advertiser过滤+无Order过滤+不含CompareStart — 18.0%
+按Advertiser过滤+按Order过滤+不含CompareStart — 5.2%
+无Advertiser过滤+按Order过滤+不含CompareStart — 3.8%
+按Advertiser过滤+无Order过滤+含CompareStart — 1.6%</t>
+        </is>
+      </c>
       <c r="G900" s="3" t="n"/>
     </row>
-    <row r="901">
+    <row r="901" ht="96" customHeight="1">
       <c r="A901" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25630,10 +25816,19 @@
         </is>
       </c>
       <c r="E901" s="3" t="n"/>
-      <c r="F901" s="3" t="n"/>
+      <c r="F901" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无Order过滤+不含CompareStart — 46.6%
+无Advertiser过滤+无Order过滤+含CompareStart — 24.6%
+按Advertiser过滤+无Order过滤+不含CompareStart — 15.8%
+按Advertiser过滤+按Order过滤+不含CompareStart — 7.4%
+无Advertiser过滤+按Order过滤+不含CompareStart — 3.6%
+按Advertiser过滤+无Order过滤+含CompareStart — 1.4%</t>
+        </is>
+      </c>
       <c r="G901" s="3" t="n"/>
     </row>
-    <row r="902">
+    <row r="902" ht="96" customHeight="1">
       <c r="A902" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25655,10 +25850,19 @@
         </is>
       </c>
       <c r="E902" s="3" t="n"/>
-      <c r="F902" s="3" t="n"/>
+      <c r="F902" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无Order过滤+不含CompareStart — 50.6%
+无Advertiser过滤+无Order过滤+含CompareStart — 19.6%
+按Advertiser过滤+无Order过滤+不含CompareStart — 17.2%
+按Advertiser过滤+按Order过滤+不含CompareStart — 6.8%
+无Advertiser过滤+按Order过滤+不含CompareStart — 3.4%
+按Advertiser过滤+无Order过滤+含CompareStart — 1.8%</t>
+        </is>
+      </c>
       <c r="G902" s="3" t="n"/>
     </row>
-    <row r="903">
+    <row r="903" ht="16" customHeight="1">
       <c r="A903" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25680,10 +25884,14 @@
         </is>
       </c>
       <c r="E903" s="3" t="n"/>
-      <c r="F903" s="3" t="n"/>
+      <c r="F903" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G903" s="3" t="n"/>
     </row>
-    <row r="904">
+    <row r="904" ht="16" customHeight="1">
       <c r="A904" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25705,10 +25913,14 @@
         </is>
       </c>
       <c r="E904" s="3" t="n"/>
-      <c r="F904" s="3" t="n"/>
+      <c r="F904" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G904" s="3" t="n"/>
     </row>
-    <row r="905">
+    <row r="905" ht="16" customHeight="1">
       <c r="A905" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25730,10 +25942,14 @@
         </is>
       </c>
       <c r="E905" s="3" t="n"/>
-      <c r="F905" s="3" t="n"/>
+      <c r="F905" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G905" s="3" t="n"/>
     </row>
-    <row r="906">
+    <row r="906" ht="16" customHeight="1">
       <c r="A906" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25755,10 +25971,14 @@
         </is>
       </c>
       <c r="E906" s="3" t="n"/>
-      <c r="F906" s="3" t="n"/>
+      <c r="F906" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G906" s="3" t="n"/>
     </row>
-    <row r="907">
+    <row r="907" ht="16" customHeight="1">
       <c r="A907" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25780,10 +26000,14 @@
         </is>
       </c>
       <c r="E907" s="3" t="n"/>
-      <c r="F907" s="3" t="n"/>
+      <c r="F907" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G907" s="3" t="n"/>
     </row>
-    <row r="908">
+    <row r="908" ht="16" customHeight="1">
       <c r="A908" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25805,10 +26029,14 @@
         </is>
       </c>
       <c r="E908" s="3" t="n"/>
-      <c r="F908" s="3" t="n"/>
+      <c r="F908" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G908" s="3" t="n"/>
     </row>
-    <row r="909">
+    <row r="909" ht="16" customHeight="1">
       <c r="A909" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25830,7 +26058,11 @@
         </is>
       </c>
       <c r="E909" s="3" t="n"/>
-      <c r="F909" s="3" t="n"/>
+      <c r="F909" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G909" s="3" t="n"/>
     </row>
     <row r="910">
@@ -25855,8 +26087,16 @@
         </is>
       </c>
       <c r="E910" s="3" t="n"/>
-      <c r="F910" s="3" t="n"/>
-      <c r="G910" s="3" t="n"/>
+      <c r="F910" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G910" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="911">
       <c r="A911" s="2" t="inlineStr">
@@ -25880,10 +26120,18 @@
         </is>
       </c>
       <c r="E911" s="3" t="n"/>
-      <c r="F911" s="3" t="n"/>
-      <c r="G911" s="3" t="n"/>
-    </row>
-    <row r="912">
+      <c r="F911" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G911" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="912" ht="80" customHeight="1">
       <c r="A912" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25905,10 +26153,18 @@
         </is>
       </c>
       <c r="E912" s="3" t="n"/>
-      <c r="F912" s="3" t="n"/>
+      <c r="F912" s="6" t="inlineStr">
+        <is>
+          <t>不传OrderTagIds+forceExchangeCode=US — 63.0%
+不传OrderTagIds+forceExchangeCode=MX — 15.4%
+不传OrderTagIds+forceExchangeCode=CA — 12.8%
+按OrderTag过滤+forceExchangeCode=US — 5.8%
+不传OrderTagIds+forceExchangeCode=AU — 2.0%</t>
+        </is>
+      </c>
       <c r="G912" s="3" t="n"/>
     </row>
-    <row r="913">
+    <row r="913" ht="80" customHeight="1">
       <c r="A913" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25930,10 +26186,18 @@
         </is>
       </c>
       <c r="E913" s="3" t="n"/>
-      <c r="F913" s="3" t="n"/>
+      <c r="F913" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不传OrderIds+按LineItem过滤 — 40.8%
+按Advertiser过滤+按Order过滤+不传lineItemIds — 28.4%
+按Advertiser过滤+不传OrderIds+不传lineItemIds — 26.2%
+无Advertiser过滤+不传OrderIds+不传lineItemIds — 3.0%
+无Advertiser过滤+不传OrderIds+无LineItem过滤 — 1.4%</t>
+        </is>
+      </c>
       <c r="G913" s="3" t="n"/>
     </row>
-    <row r="914">
+    <row r="914" ht="64" customHeight="1">
       <c r="A914" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25955,10 +26219,17 @@
         </is>
       </c>
       <c r="E914" s="3" t="n"/>
-      <c r="F914" s="3" t="n"/>
+      <c r="F914" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不传OrderIds+按LineItem过滤 — 44.2%
+按Advertiser过滤+按Order过滤+不传lineItemIds — 27.6%
+按Advertiser过滤+不传OrderIds+不传lineItemIds — 25.0%
+无Advertiser过滤+不传OrderIds+不传lineItemIds — 2.2%</t>
+        </is>
+      </c>
       <c r="G914" s="3" t="n"/>
     </row>
-    <row r="915">
+    <row r="915" ht="64" customHeight="1">
       <c r="A915" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25980,7 +26251,14 @@
         </is>
       </c>
       <c r="E915" s="3" t="n"/>
-      <c r="F915" s="3" t="n"/>
+      <c r="F915" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不传OrderIds+按LineItem过滤 — 35.4%
+按Advertiser过滤+不传OrderIds+不传lineItemIds — 31.2%
+按Advertiser过滤+按Order过滤+不传lineItemIds — 30.8%
+无Advertiser过滤+不传OrderIds+不传lineItemIds — 2.2%</t>
+        </is>
+      </c>
       <c r="G915" s="3" t="n"/>
     </row>
     <row r="916">
@@ -26005,10 +26283,18 @@
         </is>
       </c>
       <c r="E916" s="3" t="n"/>
-      <c r="F916" s="3" t="n"/>
-      <c r="G916" s="3" t="n"/>
-    </row>
-    <row r="917">
+      <c r="F916" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G916" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="917" ht="128" customHeight="1">
       <c r="A917" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26030,10 +26316,21 @@
         </is>
       </c>
       <c r="E917" s="3" t="n"/>
-      <c r="F917" s="3" t="n"/>
+      <c r="F917" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+按Order过滤+不含CompareStart — 27.2%
+按Advertiser过滤+无Order过滤+不含CompareStart — 27.0%
+无Advertiser过滤+无Order过滤+不含CompareStart — 22.6%
+按Advertiser过滤+按Order过滤+不含CompareStart — 14.2%
+无Advertiser过滤+按Order过滤+含CompareStart — 2.2%
+无Advertiser过滤+无Order过滤+含CompareStart — 2.2%
+按Advertiser过滤+无Order过滤+含CompareStart — 1.8%
+按Advertiser过滤+不传OrderIds+含CompareStart — 1.0%</t>
+        </is>
+      </c>
       <c r="G917" s="3" t="n"/>
     </row>
-    <row r="918">
+    <row r="918" ht="128" customHeight="1">
       <c r="A918" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26055,10 +26352,21 @@
         </is>
       </c>
       <c r="E918" s="3" t="n"/>
-      <c r="F918" s="3" t="n"/>
+      <c r="F918" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含CompareStart — 26.6%
+无Advertiser过滤+无Order过滤+不含CompareStart — 25.6%
+无Advertiser过滤+按Order过滤+不含CompareStart — 25.6%
+按Advertiser过滤+按Order过滤+不含CompareStart — 13.6%
+按Advertiser过滤+无Order过滤+含CompareStart — 2.6%
+无Advertiser过滤+按Order过滤+含CompareStart — 1.8%
+按Advertiser过滤+按Order过滤+含CompareStart — 1.8%
+无Advertiser过滤+无Order过滤+含CompareStart — 1.6%</t>
+        </is>
+      </c>
       <c r="G918" s="3" t="n"/>
     </row>
-    <row r="919">
+    <row r="919" ht="128" customHeight="1">
       <c r="A919" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26080,10 +26388,21 @@
         </is>
       </c>
       <c r="E919" s="3" t="n"/>
-      <c r="F919" s="3" t="n"/>
+      <c r="F919" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+按Order过滤+不含CompareStart — 30.2%
+按Advertiser过滤+无Order过滤+不含CompareStart — 24.0%
+无Advertiser过滤+无Order过滤+不含CompareStart — 22.8%
+按Advertiser过滤+按Order过滤+不含CompareStart — 9.2%
+按Advertiser过滤+不传OrderIds+含CompareStart — 4.2%
+按Advertiser过滤+无Order过滤+含CompareStart — 3.2%
+无Advertiser过滤+按Order过滤+含CompareStart — 2.4%
+无Advertiser过滤+无Order过滤+含CompareStart — 2.4%</t>
+        </is>
+      </c>
       <c r="G919" s="3" t="n"/>
     </row>
-    <row r="920">
+    <row r="920" ht="144" customHeight="1">
       <c r="A920" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26105,10 +26424,22 @@
         </is>
       </c>
       <c r="E920" s="3" t="n"/>
-      <c r="F920" s="3" t="n"/>
+      <c r="F920" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含CompareStart — 32.4%
+无Advertiser过滤+无Order过滤+不含CompareStart — 23.0%
+按Advertiser过滤+按Order过滤+不含CompareStart — 18.6%
+按Advertiser过滤+无Order过滤+含CompareStart — 8.2%
+无Advertiser过滤+按Order过滤+不含CompareStart — 4.8%
+无Advertiser过滤+无Order过滤+含CompareStart — 4.2%
+按Advertiser过滤+不传OrderIds+不含CompareStart — 3.2%
+按Advertiser过滤+按Order过滤+含CompareStart — 2.4%
+无Advertiser过滤+按Order过滤+含CompareStart — 1.8%</t>
+        </is>
+      </c>
       <c r="G920" s="3" t="n"/>
     </row>
-    <row r="921">
+    <row r="921" ht="144" customHeight="1">
       <c r="A921" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26130,10 +26461,22 @@
         </is>
       </c>
       <c r="E921" s="3" t="n"/>
-      <c r="F921" s="3" t="n"/>
+      <c r="F921" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含CompareStart — 36.6%
+无Advertiser过滤+无Order过滤+不含CompareStart — 20.4%
+按Advertiser过滤+不传OrderIds+不含CompareStart — 13.4%
+按Advertiser过滤+按Order过滤+不含CompareStart — 11.4%
+按Advertiser过滤+无Order过滤+含CompareStart — 6.4%
+无Advertiser过滤+按Order过滤+不含CompareStart — 5.8%
+按Advertiser过滤+按Order过滤+含CompareStart — 3.0%
+无Advertiser过滤+无Order过滤+含CompareStart — 1.6%
+无Advertiser过滤+按Order过滤+含CompareStart — 1.2%</t>
+        </is>
+      </c>
       <c r="G921" s="3" t="n"/>
     </row>
-    <row r="922">
+    <row r="922" ht="160" customHeight="1">
       <c r="A922" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26155,10 +26498,23 @@
         </is>
       </c>
       <c r="E922" s="3" t="n"/>
-      <c r="F922" s="3" t="n"/>
+      <c r="F922" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含CompareStart — 27.8%
+无Advertiser过滤+无Order过滤+不含CompareStart — 18.6%
+按Advertiser过滤+按Order过滤+含CompareStart — 16.6%
+按Advertiser过滤+不传OrderIds+含CompareStart — 10.2%
+按Advertiser过滤+按Order过滤+不含CompareStart — 8.2%
+按Advertiser过滤+无Order过滤+含CompareStart — 4.8%
+按Advertiser过滤+不传OrderIds+不含CompareStart — 4.8%
+无Advertiser过滤+按Order过滤+不含CompareStart — 4.0%
+无Advertiser过滤+无Order过滤+含CompareStart — 3.0%
+无Advertiser过滤+按Order过滤+含CompareStart — 1.0%</t>
+        </is>
+      </c>
       <c r="G922" s="3" t="n"/>
     </row>
-    <row r="923">
+    <row r="923" ht="144" customHeight="1">
       <c r="A923" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26180,10 +26536,22 @@
         </is>
       </c>
       <c r="E923" s="3" t="n"/>
-      <c r="F923" s="3" t="n"/>
+      <c r="F923" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含CompareStart — 39.6%
+无Advertiser过滤+无Order过滤+不含CompareStart — 32.2%
+按Advertiser过滤+按Order过滤+不含CompareStart — 10.4%
+无Advertiser过滤+按Order过滤+不含CompareStart — 3.6%
+不传AdvertiserIds+不传OrderIds+不含CompareStart — 3.6%
+按Advertiser过滤+无Order过滤+含CompareStart — 3.6%
+无Advertiser过滤+无Order过滤+含CompareStart — 2.6%
+按Advertiser过滤+按Order过滤+含CompareStart — 2.4%
+按Advertiser过滤+不传OrderIds+不含CompareStart — 1.2%</t>
+        </is>
+      </c>
       <c r="G923" s="3" t="n"/>
     </row>
-    <row r="924">
+    <row r="924" ht="128" customHeight="1">
       <c r="A924" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26205,10 +26573,21 @@
         </is>
       </c>
       <c r="E924" s="3" t="n"/>
-      <c r="F924" s="3" t="n"/>
+      <c r="F924" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含CompareStart — 40.8%
+无Advertiser过滤+无Order过滤+不含CompareStart — 27.2%
+按Advertiser过滤+按Order过滤+不含CompareStart — 11.2%
+按Advertiser过滤+无Order过滤+含CompareStart — 6.0%
+无Advertiser过滤+按Order过滤+不含CompareStart — 5.0%
+不传AdvertiserIds+不传OrderIds+不含CompareStart — 3.8%
+无Advertiser过滤+无Order过滤+含CompareStart — 2.8%
+按Advertiser过滤+按Order过滤+含CompareStart — 2.2%</t>
+        </is>
+      </c>
       <c r="G924" s="3" t="n"/>
     </row>
-    <row r="925">
+    <row r="925" ht="144" customHeight="1">
       <c r="A925" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26230,10 +26609,22 @@
         </is>
       </c>
       <c r="E925" s="3" t="n"/>
-      <c r="F925" s="3" t="n"/>
+      <c r="F925" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含CompareStart — 36.4%
+无Advertiser过滤+无Order过滤+不含CompareStart — 29.0%
+按Advertiser过滤+按Order过滤+不含CompareStart — 8.4%
+按Advertiser过滤+不传OrderIds+不含CompareStart — 6.2%
+不传AdvertiserIds+不传OrderIds+不含CompareStart — 5.2%
+按Advertiser过滤+无Order过滤+含CompareStart — 5.0%
+无Advertiser过滤+按Order过滤+不含CompareStart — 4.6%
+无Advertiser过滤+无Order过滤+含CompareStart — 2.6%
+按Advertiser过滤+按Order过滤+含CompareStart — 1.0%</t>
+        </is>
+      </c>
       <c r="G925" s="3" t="n"/>
     </row>
-    <row r="926">
+    <row r="926" ht="176" customHeight="1">
       <c r="A926" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26255,10 +26646,24 @@
         </is>
       </c>
       <c r="E926" s="3" t="n"/>
-      <c r="F926" s="3" t="n"/>
+      <c r="F926" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含CompareStart — 35.6%
+按Advertiser过滤+按Order过滤+不含CompareStart — 15.8%
+无Advertiser过滤+无Order过滤+不含CompareStart — 15.0%
+按Advertiser过滤+不传OrderIds+不含CompareStart — 8.8%
+无Advertiser过滤+无Order过滤+含CompareStart — 7.4%
+按Advertiser过滤+无Order过滤+含CompareStart — 5.2%
+无Advertiser过滤+按Order过滤+不含CompareStart — 5.0%
+无Advertiser过滤+不传OrderIds+不含CompareStart — 2.0%
+按Advertiser过滤+不传OrderIds+含CompareStart — 1.6%
+无Advertiser过滤+不传OrderIds+含CompareStart — 1.6%
+无Advertiser过滤+按Order过滤+含CompareStart — 1.6%</t>
+        </is>
+      </c>
       <c r="G926" s="3" t="n"/>
     </row>
-    <row r="927">
+    <row r="927" ht="192" customHeight="1">
       <c r="A927" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26280,10 +26685,25 @@
         </is>
       </c>
       <c r="E927" s="3" t="n"/>
-      <c r="F927" s="3" t="n"/>
+      <c r="F927" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含CompareStart — 29.6%
+按Advertiser过滤+按Order过滤+不含CompareStart — 20.6%
+无Advertiser过滤+无Order过滤+不含CompareStart — 15.2%
+无Advertiser过滤+无Order过滤+含CompareStart — 7.4%
+按Advertiser过滤+不传OrderIds+不含CompareStart — 7.0%
+无Advertiser过滤+按Order过滤+不含CompareStart — 5.8%
+按Advertiser过滤+无Order过滤+含CompareStart — 4.6%
+无Advertiser过滤+不传OrderIds+不含CompareStart — 2.6%
+无Advertiser过滤+不传OrderIds+含CompareStart — 2.2%
+无Advertiser过滤+按Order过滤+含CompareStart — 2.0%
+按Advertiser过滤+不传OrderIds+含CompareStart — 1.8%
+按Advertiser过滤+按Order过滤+含CompareStart — 1.0%</t>
+        </is>
+      </c>
       <c r="G927" s="3" t="n"/>
     </row>
-    <row r="928">
+    <row r="928" ht="176" customHeight="1">
       <c r="A928" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26305,7 +26725,21 @@
         </is>
       </c>
       <c r="E928" s="3" t="n"/>
-      <c r="F928" s="3" t="n"/>
+      <c r="F928" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含CompareStart — 33.2%
+按Advertiser过滤+按Order过滤+不含CompareStart — 17.0%
+无Advertiser过滤+无Order过滤+不含CompareStart — 14.6%
+无Advertiser过滤+无Order过滤+含CompareStart — 7.0%
+按Advertiser过滤+不传OrderIds+不含CompareStart — 6.2%
+按Advertiser过滤+无Order过滤+含CompareStart — 6.0%
+无Advertiser过滤+按Order过滤+不含CompareStart — 5.2%
+无Advertiser过滤+不传OrderIds+不含CompareStart — 3.6%
+无Advertiser过滤+不传OrderIds+含CompareStart — 2.8%
+按Advertiser过滤+不传OrderIds+含CompareStart — 2.0%
+无Advertiser过滤+按Order过滤+含CompareStart — 1.4%</t>
+        </is>
+      </c>
       <c r="G928" s="3" t="n"/>
     </row>
     <row r="929">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -818,9 +818,19 @@
       </c>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="F14" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>54% (32/59)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1890,9 +1900,19 @@
       </c>
       <c r="D60" s="3" t="n"/>
       <c r="E60" s="3" t="n"/>
-      <c r="F60" s="2" t="n"/>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="n"/>
+      <c r="F60" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>64% (37/58)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11286,7 +11306,11 @@
       </c>
       <c r="E349" s="3" t="n"/>
       <c r="F349" s="3" t="n"/>
-      <c r="G349" s="3" t="n"/>
+      <c r="G349" s="5" t="inlineStr">
+        <is>
+          <t>写操作(授权AMC实例)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -11311,7 +11335,11 @@
       </c>
       <c r="E350" s="3" t="n"/>
       <c r="F350" s="3" t="n"/>
-      <c r="G350" s="3" t="n"/>
+      <c r="G350" s="5" t="inlineStr">
+        <is>
+          <t>写操作(绑定用户实例)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -11336,7 +11364,11 @@
       </c>
       <c r="E351" s="3" t="n"/>
       <c r="F351" s="3" t="n"/>
-      <c r="G351" s="3" t="n"/>
+      <c r="G351" s="5" t="inlineStr">
+        <is>
+          <t>写操作(批量创建AMC实例)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -11361,7 +11393,11 @@
       </c>
       <c r="E352" s="3" t="n"/>
       <c r="F352" s="3" t="n"/>
-      <c r="G352" s="3" t="n"/>
+      <c r="G352" s="5" t="inlineStr">
+        <is>
+          <t>写操作(批量解绑)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -11386,7 +11422,11 @@
       </c>
       <c r="E353" s="3" t="n"/>
       <c r="F353" s="3" t="n"/>
-      <c r="G353" s="3" t="n"/>
+      <c r="G353" s="5" t="inlineStr">
+        <is>
+          <t>写操作(取消付费订阅)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -11411,9 +11451,13 @@
       </c>
       <c r="E354" s="3" t="n"/>
       <c r="F354" s="3" t="n"/>
-      <c r="G354" s="3" t="n"/>
-    </row>
-    <row r="355">
+      <c r="G354" s="5" t="inlineStr">
+        <is>
+          <t>写操作(变更实例状态)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="48" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11435,10 +11479,16 @@
         </is>
       </c>
       <c r="E355" s="3" t="n"/>
-      <c r="F355" s="3" t="n"/>
+      <c r="F355" s="6" t="inlineStr">
+        <is>
+          <t>s3RegionEndpoint=USWest2 — 63.4%
+s3RegionEndpoint=USEast1 — 24.4%
+s3RegionEndpoint=APNortheast1 — 12.2%</t>
+        </is>
+      </c>
       <c r="G355" s="3" t="n"/>
     </row>
-    <row r="356">
+    <row r="356" ht="16" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11460,10 +11510,14 @@
         </is>
       </c>
       <c r="E356" s="3" t="n"/>
-      <c r="F356" s="3" t="n"/>
+      <c r="F356" s="6" t="inlineStr">
+        <is>
+          <t>无参调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G356" s="3" t="n"/>
     </row>
-    <row r="357">
+    <row r="357" ht="160" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11485,7 +11539,20 @@
         </is>
       </c>
       <c r="E357" s="3" t="n"/>
-      <c r="F357" s="3" t="n"/>
+      <c r="F357" s="6" t="inlineStr">
+        <is>
+          <t>dataSourceId=amazon retail purchases+不含paidFeatureType — 42.0%
+dataSourceId=conversions asm bundle+不含paidFeatureType — 26.6%
+dataSourceId=amazon brand store page views+不含paidFeatureType — 6.9%
+dataSourceId=brand store conversions+不含paidFeatureType — 6.2%
+dataSourceId=conversions all+不含paidFeatureType — 6.0%
+dataSourceId=streaming insights+不含paidFeatureType — 4.0%
+dataSourceId=amazon your garage+不含paidFeatureType — 2.9%
+dataSourceId=experian vehicle purchases+不含paidFeatureType — 2.1%
+dataSourceId=audience segment membership+不含paidFeatureType — 1.7%
+不传dataSourceId+含paidFeatureType — 1.7%</t>
+        </is>
+      </c>
       <c r="G357" s="3" t="n"/>
     </row>
     <row r="358">
@@ -11511,7 +11578,11 @@
       </c>
       <c r="E358" s="3" t="n"/>
       <c r="F358" s="3" t="n"/>
-      <c r="G358" s="3" t="n"/>
+      <c r="G358" s="5" t="inlineStr">
+        <is>
+          <t>写操作(创建AMC实例)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -11536,7 +11607,11 @@
       </c>
       <c r="E359" s="3" t="n"/>
       <c r="F359" s="3" t="n"/>
-      <c r="G359" s="3" t="n"/>
+      <c r="G359" s="5" t="inlineStr">
+        <is>
+          <t>写操作(创建数据集)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -11561,7 +11636,11 @@
       </c>
       <c r="E360" s="3" t="n"/>
       <c r="F360" s="3" t="n"/>
-      <c r="G360" s="3" t="n"/>
+      <c r="G360" s="5" t="inlineStr">
+        <is>
+          <t>写操作(创建数据上传)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -11586,7 +11665,11 @@
       </c>
       <c r="E361" s="3" t="n"/>
       <c r="F361" s="3" t="n"/>
-      <c r="G361" s="3" t="n"/>
+      <c r="G361" s="5" t="inlineStr">
+        <is>
+          <t>写操作(删除AMC实例)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -11611,7 +11694,11 @@
       </c>
       <c r="E362" s="3" t="n"/>
       <c r="F362" s="3" t="n"/>
-      <c r="G362" s="3" t="n"/>
+      <c r="G362" s="5" t="inlineStr">
+        <is>
+          <t>写操作(删除实例创建记录)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -11635,10 +11722,18 @@
         </is>
       </c>
       <c r="E363" s="3" t="n"/>
-      <c r="F363" s="3" t="n"/>
-      <c r="G363" s="3" t="n"/>
-    </row>
-    <row r="364">
+      <c r="F363" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G363" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="16" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11660,10 +11755,14 @@
         </is>
       </c>
       <c r="E364" s="3" t="n"/>
-      <c r="F364" s="3" t="n"/>
+      <c r="F364" s="6" t="inlineStr">
+        <is>
+          <t>无参调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G364" s="3" t="n"/>
     </row>
-    <row r="365">
+    <row r="365" ht="16" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11685,10 +11784,14 @@
         </is>
       </c>
       <c r="E365" s="3" t="n"/>
-      <c r="F365" s="3" t="n"/>
+      <c r="F365" s="6" t="inlineStr">
+        <is>
+          <t>无参调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G365" s="3" t="n"/>
     </row>
-    <row r="366">
+    <row r="366" ht="16" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11710,7 +11813,11 @@
         </is>
       </c>
       <c r="E366" s="3" t="n"/>
-      <c r="F366" s="3" t="n"/>
+      <c r="F366" s="6" t="inlineStr">
+        <is>
+          <t>按实例下载(最常见组合) — 100.0%</t>
+        </is>
+      </c>
       <c r="G366" s="3" t="n"/>
     </row>
     <row r="367">
@@ -11735,10 +11842,18 @@
         </is>
       </c>
       <c r="E367" s="3" t="n"/>
-      <c r="F367" s="3" t="n"/>
-      <c r="G367" s="3" t="n"/>
-    </row>
-    <row r="368">
+      <c r="F367" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G367" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="16" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11760,10 +11875,14 @@
         </is>
       </c>
       <c r="E368" s="3" t="n"/>
-      <c r="F368" s="3" t="n"/>
+      <c r="F368" s="6" t="inlineStr">
+        <is>
+          <t>无参调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G368" s="3" t="n"/>
     </row>
-    <row r="369">
+    <row r="369" ht="48" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11785,7 +11904,13 @@
         </is>
       </c>
       <c r="E369" s="3" t="n"/>
-      <c r="F369" s="3" t="n"/>
+      <c r="F369" s="6" t="inlineStr">
+        <is>
+          <t>SqlType=report sql — 74.4%
+SqlType=audience sql — 21.8%
+不传SqlType — 3.8%</t>
+        </is>
+      </c>
       <c r="G369" s="3" t="n"/>
     </row>
     <row r="370">
@@ -11810,10 +11935,18 @@
         </is>
       </c>
       <c r="E370" s="3" t="n"/>
-      <c r="F370" s="3" t="n"/>
-      <c r="G370" s="3" t="n"/>
-    </row>
-    <row r="371">
+      <c r="F370" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G370" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="16" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11835,7 +11968,11 @@
         </is>
       </c>
       <c r="E371" s="3" t="n"/>
-      <c r="F371" s="3" t="n"/>
+      <c r="F371" s="6" t="inlineStr">
+        <is>
+          <t>无参调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G371" s="3" t="n"/>
     </row>
     <row r="372">
@@ -11860,10 +11997,18 @@
         </is>
       </c>
       <c r="E372" s="3" t="n"/>
-      <c r="F372" s="3" t="n"/>
-      <c r="G372" s="3" t="n"/>
-    </row>
-    <row r="373">
+      <c r="F372" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G372" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="16" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11885,10 +12030,14 @@
         </is>
       </c>
       <c r="E373" s="3" t="n"/>
-      <c r="F373" s="3" t="n"/>
+      <c r="F373" s="6" t="inlineStr">
+        <is>
+          <t>无参调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G373" s="3" t="n"/>
     </row>
-    <row r="374">
+    <row r="374" ht="16" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11910,10 +12059,14 @@
         </is>
       </c>
       <c r="E374" s="3" t="n"/>
-      <c r="F374" s="3" t="n"/>
+      <c r="F374" s="6" t="inlineStr">
+        <is>
+          <t>按创建记录id查询(最常见) — 100.0%</t>
+        </is>
+      </c>
       <c r="G374" s="3" t="n"/>
     </row>
-    <row r="375">
+    <row r="375" ht="32" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11935,10 +12088,15 @@
         </is>
       </c>
       <c r="E375" s="3" t="n"/>
-      <c r="F375" s="3" t="n"/>
+      <c r="F375" s="6" t="inlineStr">
+        <is>
+          <t>含instanceName+含userIds+含status+首页 — 98.6%
+含instanceName+含userIds+含status+翻页(pageIndex&gt;1) — 1.2%</t>
+        </is>
+      </c>
       <c r="G375" s="3" t="n"/>
     </row>
-    <row r="376">
+    <row r="376" ht="48" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11960,10 +12118,16 @@
         </is>
       </c>
       <c r="E376" s="3" t="n"/>
-      <c r="F376" s="3" t="n"/>
+      <c r="F376" s="6" t="inlineStr">
+        <is>
+          <t>含instanceName+按InstanceName排序+首页 — 96.2%
+含instanceName+按AdvertiserName排序+首页 — 1.0%
+含instanceName+按InstanceName排序+翻页(pageIndex&gt;1) — 1.0%</t>
+        </is>
+      </c>
       <c r="G376" s="3" t="n"/>
     </row>
-    <row r="377">
+    <row r="377" ht="16" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11985,10 +12149,14 @@
         </is>
       </c>
       <c r="E377" s="3" t="n"/>
-      <c r="F377" s="3" t="n"/>
+      <c r="F377" s="6" t="inlineStr">
+        <is>
+          <t>无参调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G377" s="3" t="n"/>
     </row>
-    <row r="378">
+    <row r="378" ht="16" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12010,10 +12178,14 @@
         </is>
       </c>
       <c r="E378" s="3" t="n"/>
-      <c r="F378" s="3" t="n"/>
+      <c r="F378" s="6" t="inlineStr">
+        <is>
+          <t>无参调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G378" s="3" t="n"/>
     </row>
-    <row r="379">
+    <row r="379" ht="16" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12035,10 +12207,14 @@
         </is>
       </c>
       <c r="E379" s="3" t="n"/>
-      <c r="F379" s="3" t="n"/>
+      <c r="F379" s="6" t="inlineStr">
+        <is>
+          <t>按实例查询绑定用户(最常见) — 100.0%</t>
+        </is>
+      </c>
       <c r="G379" s="3" t="n"/>
     </row>
-    <row r="380">
+    <row r="380" ht="16" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12060,10 +12236,14 @@
         </is>
       </c>
       <c r="E380" s="3" t="n"/>
-      <c r="F380" s="3" t="n"/>
+      <c r="F380" s="6" t="inlineStr">
+        <is>
+          <t>无参调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G380" s="3" t="n"/>
     </row>
-    <row r="381">
+    <row r="381" ht="32" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12085,10 +12265,15 @@
         </is>
       </c>
       <c r="E381" s="3" t="n"/>
-      <c r="F381" s="3" t="n"/>
+      <c r="F381" s="6" t="inlineStr">
+        <is>
+          <t>首页 — 87.5%
+翻页(pageIndex&gt;1) — 12.5%</t>
+        </is>
+      </c>
       <c r="G381" s="3" t="n"/>
     </row>
-    <row r="382">
+    <row r="382" ht="16" customHeight="1">
       <c r="A382" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12110,10 +12295,14 @@
         </is>
       </c>
       <c r="E382" s="3" t="n"/>
-      <c r="F382" s="3" t="n"/>
+      <c r="F382" s="6" t="inlineStr">
+        <is>
+          <t>含instanceIds — 100.0%</t>
+        </is>
+      </c>
       <c r="G382" s="3" t="n"/>
     </row>
-    <row r="383">
+    <row r="383" ht="16" customHeight="1">
       <c r="A383" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12135,10 +12324,14 @@
         </is>
       </c>
       <c r="E383" s="3" t="n"/>
-      <c r="F383" s="3" t="n"/>
+      <c r="F383" s="6" t="inlineStr">
+        <is>
+          <t>按Id查询数据集详情(最常见) — 100.0%</t>
+        </is>
+      </c>
       <c r="G383" s="3" t="n"/>
     </row>
-    <row r="384">
+    <row r="384" ht="16" customHeight="1">
       <c r="A384" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12160,10 +12353,14 @@
         </is>
       </c>
       <c r="E384" s="3" t="n"/>
-      <c r="F384" s="3" t="n"/>
+      <c r="F384" s="6" t="inlineStr">
+        <is>
+          <t>按实例查询数据上传记录(最常见) — 100.0%</t>
+        </is>
+      </c>
       <c r="G384" s="3" t="n"/>
     </row>
-    <row r="385">
+    <row r="385" ht="16" customHeight="1">
       <c r="A385" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12185,10 +12382,14 @@
         </is>
       </c>
       <c r="E385" s="3" t="n"/>
-      <c r="F385" s="3" t="n"/>
+      <c r="F385" s="6" t="inlineStr">
+        <is>
+          <t>按实例查询实体列表(最常见) — 100.0%</t>
+        </is>
+      </c>
       <c r="G385" s="3" t="n"/>
     </row>
-    <row r="386">
+    <row r="386" ht="16" customHeight="1">
       <c r="A386" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12210,10 +12411,14 @@
         </is>
       </c>
       <c r="E386" s="3" t="n"/>
-      <c r="F386" s="3" t="n"/>
+      <c r="F386" s="6" t="inlineStr">
+        <is>
+          <t>无参调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G386" s="3" t="n"/>
     </row>
-    <row r="387">
+    <row r="387" ht="16" customHeight="1">
       <c r="A387" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12235,10 +12440,14 @@
         </is>
       </c>
       <c r="E387" s="3" t="n"/>
-      <c r="F387" s="3" t="n"/>
+      <c r="F387" s="6" t="inlineStr">
+        <is>
+          <t>按实例查询详情(最常见) — 100.0%</t>
+        </is>
+      </c>
       <c r="G387" s="3" t="n"/>
     </row>
-    <row r="388">
+    <row r="388" ht="16" customHeight="1">
       <c r="A388" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12260,10 +12469,14 @@
         </is>
       </c>
       <c r="E388" s="3" t="n"/>
-      <c r="F388" s="3" t="n"/>
+      <c r="F388" s="6" t="inlineStr">
+        <is>
+          <t>按实例查询已开通付费功能(最常见) — 100.0%</t>
+        </is>
+      </c>
       <c r="G388" s="3" t="n"/>
     </row>
-    <row r="389">
+    <row r="389" ht="16" customHeight="1">
       <c r="A389" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12285,10 +12498,14 @@
         </is>
       </c>
       <c r="E389" s="3" t="n"/>
-      <c r="F389" s="3" t="n"/>
+      <c r="F389" s="6" t="inlineStr">
+        <is>
+          <t>按实例查询最近S3配置(最常见) — 100.0%</t>
+        </is>
+      </c>
       <c r="G389" s="3" t="n"/>
     </row>
-    <row r="390">
+    <row r="390" ht="112" customHeight="1">
       <c r="A390" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12310,10 +12527,20 @@
         </is>
       </c>
       <c r="E390" s="3" t="n"/>
-      <c r="F390" s="3" t="n"/>
+      <c r="F390" s="6" t="inlineStr">
+        <is>
+          <t>catalogItemIds=[amazon retail purchases] — 41.9%
+catalogItemIds=[conversions asm bundle] — 33.2%
+catalogItemIds=[brand store conversions] — 9.8%
+catalogItemIds=[streaming insights] — 6.4%
+catalogItemIds=[amazon your garage] — 4.5%
+catalogItemIds=[audience segment membership] — 2.6%
+catalogItemIds=[conversions all] — 1.5%</t>
+        </is>
+      </c>
       <c r="G390" s="3" t="n"/>
     </row>
-    <row r="391">
+    <row r="391" ht="64" customHeight="1">
       <c r="A391" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12335,10 +12562,17 @@
         </is>
       </c>
       <c r="E391" s="3" t="n"/>
-      <c r="F391" s="3" t="n"/>
+      <c r="F391" s="6" t="inlineStr">
+        <is>
+          <t>isMyFavorite=true+IsAudience=false — 50.6%
+isMyFavorite=false+IsAudience=false — 30.6%
+isMyFavorite=true+IsAudience=true — 13.4%
+isMyFavorite=false+IsAudience=true — 5.4%</t>
+        </is>
+      </c>
       <c r="G391" s="3" t="n"/>
     </row>
-    <row r="392">
+    <row r="392" ht="16" customHeight="1">
       <c r="A392" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12360,10 +12594,14 @@
         </is>
       </c>
       <c r="E392" s="3" t="n"/>
-      <c r="F392" s="3" t="n"/>
+      <c r="F392" s="6" t="inlineStr">
+        <is>
+          <t>按reportId查询分享Id(最常见) — 100.0%</t>
+        </is>
+      </c>
       <c r="G392" s="3" t="n"/>
     </row>
-    <row r="393">
+    <row r="393" ht="16" customHeight="1">
       <c r="A393" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12385,10 +12623,14 @@
         </is>
       </c>
       <c r="E393" s="3" t="n"/>
-      <c r="F393" s="3" t="n"/>
+      <c r="F393" s="6" t="inlineStr">
+        <is>
+          <t>按shareId查询分享Token(最常见) — 100.0%</t>
+        </is>
+      </c>
       <c r="G393" s="3" t="n"/>
     </row>
-    <row r="394">
+    <row r="394" ht="16" customHeight="1">
       <c r="A394" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12410,10 +12652,14 @@
         </is>
       </c>
       <c r="E394" s="3" t="n"/>
-      <c r="F394" s="3" t="n"/>
+      <c r="F394" s="6" t="inlineStr">
+        <is>
+          <t>按订阅类型查询(最常见) — 100.0%</t>
+        </is>
+      </c>
       <c r="G394" s="3" t="n"/>
     </row>
-    <row r="395">
+    <row r="395" ht="32" customHeight="1">
       <c r="A395" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12435,7 +12681,12 @@
         </is>
       </c>
       <c r="E395" s="3" t="n"/>
-      <c r="F395" s="3" t="n"/>
+      <c r="F395" s="6" t="inlineStr">
+        <is>
+          <t>不含clintIds — 84.2%
+含clintIds — 15.8%</t>
+        </is>
+      </c>
       <c r="G395" s="3" t="n"/>
     </row>
     <row r="396">
@@ -12461,7 +12712,11 @@
       </c>
       <c r="E396" s="3" t="n"/>
       <c r="F396" s="3" t="n"/>
-      <c r="G396" s="3" t="n"/>
+      <c r="G396" s="5" t="inlineStr">
+        <is>
+          <t>写操作(导入AMC实例)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -12486,7 +12741,11 @@
       </c>
       <c r="E397" s="3" t="n"/>
       <c r="F397" s="3" t="n"/>
-      <c r="G397" s="3" t="n"/>
+      <c r="G397" s="5" t="inlineStr">
+        <is>
+          <t>写操作(刷新实例，路径含refresh)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -12511,7 +12770,11 @@
       </c>
       <c r="E398" s="3" t="n"/>
       <c r="F398" s="3" t="n"/>
-      <c r="G398" s="3" t="n"/>
+      <c r="G398" s="5" t="inlineStr">
+        <is>
+          <t>写操作(保存收藏查询)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -12536,7 +12799,11 @@
       </c>
       <c r="E399" s="3" t="n"/>
       <c r="F399" s="3" t="n"/>
-      <c r="G399" s="3" t="n"/>
+      <c r="G399" s="5" t="inlineStr">
+        <is>
+          <t>写操作(订阅付费功能)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -12560,8 +12827,16 @@
         </is>
       </c>
       <c r="E400" s="3" t="n"/>
-      <c r="F400" s="3" t="n"/>
-      <c r="G400" s="3" t="n"/>
+      <c r="F400" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G400" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -12585,8 +12860,16 @@
         </is>
       </c>
       <c r="E401" s="3" t="n"/>
-      <c r="F401" s="3" t="n"/>
-      <c r="G401" s="3" t="n"/>
+      <c r="F401" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G401" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -12611,7 +12894,11 @@
       </c>
       <c r="E402" s="3" t="n"/>
       <c r="F402" s="3" t="n"/>
-      <c r="G402" s="3" t="n"/>
+      <c r="G402" s="5" t="inlineStr">
+        <is>
+          <t>写操作(解绑实例)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -12636,7 +12923,11 @@
       </c>
       <c r="E403" s="3" t="n"/>
       <c r="F403" s="3" t="n"/>
-      <c r="G403" s="3" t="n"/>
+      <c r="G403" s="5" t="inlineStr">
+        <is>
+          <t>写操作(更新AMC实例)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -12661,7 +12952,11 @@
       </c>
       <c r="E404" s="3" t="n"/>
       <c r="F404" s="3" t="n"/>
-      <c r="G404" s="3" t="n"/>
+      <c r="G404" s="5" t="inlineStr">
+        <is>
+          <t>写操作(更新实例名称)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -12686,7 +12981,11 @@
       </c>
       <c r="E405" s="3" t="n"/>
       <c r="F405" s="3" t="n"/>
-      <c r="G405" s="3" t="n"/>
+      <c r="G405" s="5" t="inlineStr">
+        <is>
+          <t>写操作(更新数据集)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -12711,7 +13010,11 @@
       </c>
       <c r="E406" s="3" t="n"/>
       <c r="F406" s="3" t="n"/>
-      <c r="G406" s="3" t="n"/>
+      <c r="G406" s="5" t="inlineStr">
+        <is>
+          <t>写操作(更新实例详情)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -12736,7 +13039,11 @@
       </c>
       <c r="E407" s="3" t="n"/>
       <c r="F407" s="3" t="n"/>
-      <c r="G407" s="3" t="n"/>
+      <c r="G407" s="5" t="inlineStr">
+        <is>
+          <t>写操作(上传自定义campaign)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -35795,7 +36102,7 @@
       <c r="F1277" s="3" t="n"/>
       <c r="G1277" s="3" t="n"/>
     </row>
-    <row r="1278">
+    <row r="1278" ht="96" customHeight="1">
       <c r="A1278" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35817,10 +36124,19 @@
         </is>
       </c>
       <c r="E1278" s="3" t="n"/>
-      <c r="F1278" s="3" t="n"/>
+      <c r="F1278" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+无Creative过滤 — 49.5%
+timeType=3+按Creative过滤 — 24.3%
+timeType=3+不传creativeIds — 8.7%
+timeType=1+无Creative过滤 — 7.5%
+timeType=1+按Creative过滤 — 6.2%
+timeType=2+按Creative过滤 — 1.9%</t>
+        </is>
+      </c>
       <c r="G1278" s="3" t="n"/>
     </row>
-    <row r="1279">
+    <row r="1279" ht="96" customHeight="1">
       <c r="A1279" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35842,7 +36158,16 @@
         </is>
       </c>
       <c r="E1279" s="3" t="n"/>
-      <c r="F1279" s="3" t="n"/>
+      <c r="F1279" s="6" t="inlineStr">
+        <is>
+          <t>无Order过滤+comparisonSetting=0 — 47.2%
+不传orderIds+comparisonSetting=0 — 25.0%
+按Order过滤+comparisonSetting=0 — 20.4%
+不传orderIds+comparisonSetting=1 — 2.8%
+按Order过滤+comparisonSetting=1 — 2.2%
+无Order过滤+不传comparisonSetting — 1.6%</t>
+        </is>
+      </c>
       <c r="G1279" s="3" t="n"/>
     </row>
     <row r="1280">
@@ -35867,10 +36192,18 @@
         </is>
       </c>
       <c r="E1280" s="3" t="n"/>
-      <c r="F1280" s="3" t="n"/>
-      <c r="G1280" s="3" t="n"/>
-    </row>
-    <row r="1281">
+      <c r="F1280" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1280" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281" ht="96" customHeight="1">
       <c r="A1281" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35892,10 +36225,19 @@
         </is>
       </c>
       <c r="E1281" s="3" t="n"/>
-      <c r="F1281" s="3" t="n"/>
+      <c r="F1281" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤+valueParam=sales — 61.0%
+timeType=3+无Order过滤+valueParam=sales — 22.8%
+timeType=1+按Order过滤+valueParam=sales — 9.8%
+timeType=2+按Order过滤+valueParam=sales — 2.0%
+timeType=1+无Order过滤+valueParam=sales — 1.8%
+timeType=3+不传orderIds+valueParam=sales — 1.4%</t>
+        </is>
+      </c>
       <c r="G1281" s="3" t="n"/>
     </row>
-    <row r="1282">
+    <row r="1282" ht="80" customHeight="1">
       <c r="A1282" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35917,10 +36259,18 @@
         </is>
       </c>
       <c r="E1282" s="3" t="n"/>
-      <c r="F1282" s="3" t="n"/>
+      <c r="F1282" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤 — 63.0%
+timeType=3+无Order过滤 — 22.6%
+timeType=1+按Order过滤 — 11.0%
+timeType=1+无Order过滤 — 1.4%
+timeType=2+按Order过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G1282" s="3" t="n"/>
     </row>
-    <row r="1283">
+    <row r="1283" ht="96" customHeight="1">
       <c r="A1283" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35942,7 +36292,16 @@
         </is>
       </c>
       <c r="E1283" s="3" t="n"/>
-      <c r="F1283" s="3" t="n"/>
+      <c r="F1283" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤 — 60.8%
+timeType=3+无Order过滤 — 23.4%
+timeType=1+按Order过滤 — 10.4%
+timeType=1+无Order过滤 — 2.2%
+timeType=2+按Order过滤 — 1.2%
+timeType=3+不传orderIds — 1.2%</t>
+        </is>
+      </c>
       <c r="G1283" s="3" t="n"/>
     </row>
     <row r="1284">
@@ -35967,10 +36326,18 @@
         </is>
       </c>
       <c r="E1284" s="3" t="n"/>
-      <c r="F1284" s="3" t="n"/>
-      <c r="G1284" s="3" t="n"/>
-    </row>
-    <row r="1285">
+      <c r="F1284" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1284" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285" ht="96" customHeight="1">
       <c r="A1285" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35992,10 +36359,19 @@
         </is>
       </c>
       <c r="E1285" s="3" t="n"/>
-      <c r="F1285" s="3" t="n"/>
+      <c r="F1285" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+无Order过滤 — 30.3%
+timeType=3+按Order过滤 — 30.3%
+timeType=1+按Order过滤 — 21.2%
+timeType=1+无Order过滤 — 12.0%
+timeType=2+按Order过滤 — 2.9%
+timeType=3+不传orderIds — 2.5%</t>
+        </is>
+      </c>
       <c r="G1285" s="3" t="n"/>
     </row>
-    <row r="1286">
+    <row r="1286" ht="96" customHeight="1">
       <c r="A1286" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36017,10 +36393,19 @@
         </is>
       </c>
       <c r="E1286" s="3" t="n"/>
-      <c r="F1286" s="3" t="n"/>
+      <c r="F1286" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+无Creative过滤 — 49.5%
+timeType=3+按Creative过滤 — 24.3%
+timeType=3+不传creativeIds — 8.7%
+timeType=1+无Creative过滤 — 7.5%
+timeType=1+按Creative过滤 — 6.2%
+timeType=2+按Creative过滤 — 1.9%</t>
+        </is>
+      </c>
       <c r="G1286" s="3" t="n"/>
     </row>
-    <row r="1287">
+    <row r="1287" ht="192" customHeight="1">
       <c r="A1287" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36042,10 +36427,25 @@
         </is>
       </c>
       <c r="E1287" s="3" t="n"/>
-      <c r="F1287" s="3" t="n"/>
+      <c r="F1287" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+无Order过滤+无LineItem过滤 — 24.8%
+timeType=3+按Order过滤+无LineItem过滤 — 24.6%
+timeType=3+按Order过滤+按LineItem过滤 — 14.8%
+timeType=1+按Order过滤+无LineItem过滤 — 9.6%
+timeType=3+无Order过滤+按LineItem过滤(含非数字ID) — 5.4%
+timeType=3+按Order过滤+不传lineItemIds — 4.2%
+timeType=3+无Order过滤+不传lineItemIds — 4.0%
+timeType=1+无Order过滤+无LineItem过滤 — 2.8%
+timeType=1+按Order过滤+按LineItem过滤 — 2.2%
+timeType=1+无Order过滤+不传lineItemIds — 1.4%
+timeType=2+按Order过滤+无LineItem过滤 — 1.2%
+timeType=1+按Order过滤+不传lineItemIds — 1.0%</t>
+        </is>
+      </c>
       <c r="G1287" s="3" t="n"/>
     </row>
-    <row r="1288">
+    <row r="1288" ht="96" customHeight="1">
       <c r="A1288" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36067,10 +36467,19 @@
         </is>
       </c>
       <c r="E1288" s="3" t="n"/>
-      <c r="F1288" s="3" t="n"/>
+      <c r="F1288" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+无Creative过滤 — 49.5%
+timeType=3+按Creative过滤 — 24.3%
+timeType=3+不传creativeIds — 8.7%
+timeType=1+无Creative过滤 — 7.5%
+timeType=1+按Creative过滤 — 6.2%
+timeType=2+按Creative过滤 — 1.9%</t>
+        </is>
+      </c>
       <c r="G1288" s="3" t="n"/>
     </row>
-    <row r="1289">
+    <row r="1289" ht="96" customHeight="1">
       <c r="A1289" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36092,10 +36501,19 @@
         </is>
       </c>
       <c r="E1289" s="3" t="n"/>
-      <c r="F1289" s="3" t="n"/>
+      <c r="F1289" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤 — 30.3%
+timeType=3+无Order过滤 — 30.3%
+timeType=1+按Order过滤 — 21.2%
+timeType=1+无Order过滤 — 12.0%
+timeType=2+按Order过滤 — 2.9%
+timeType=3+不传orderIds — 2.5%</t>
+        </is>
+      </c>
       <c r="G1289" s="3" t="n"/>
     </row>
-    <row r="1290">
+    <row r="1290" ht="96" customHeight="1">
       <c r="A1290" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36117,7 +36535,16 @@
         </is>
       </c>
       <c r="E1290" s="3" t="n"/>
-      <c r="F1290" s="3" t="n"/>
+      <c r="F1290" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤 — 62.8%
+timeType=3+无Order过滤 — 23.6%
+timeType=1+按Order过滤 — 9.2%
+timeType=1+无Order过滤 — 1.4%
+timeType=2+按Order过滤 — 1.4%
+timeType=3+不传orderIds — 1.0%</t>
+        </is>
+      </c>
       <c r="G1290" s="3" t="n"/>
     </row>
     <row r="1291">
@@ -36142,8 +36569,16 @@
         </is>
       </c>
       <c r="E1291" s="3" t="n"/>
-      <c r="F1291" s="3" t="n"/>
-      <c r="G1291" s="3" t="n"/>
+      <c r="F1291" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1291" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1292">
       <c r="A1292" s="2" t="inlineStr">
@@ -36167,8 +36602,16 @@
         </is>
       </c>
       <c r="E1292" s="3" t="n"/>
-      <c r="F1292" s="3" t="n"/>
-      <c r="G1292" s="3" t="n"/>
+      <c r="F1292" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1292" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1293">
       <c r="A1293" s="2" t="inlineStr">
@@ -36192,8 +36635,16 @@
         </is>
       </c>
       <c r="E1293" s="3" t="n"/>
-      <c r="F1293" s="3" t="n"/>
-      <c r="G1293" s="3" t="n"/>
+      <c r="F1293" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1293" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1294">
       <c r="A1294" s="2" t="inlineStr">
@@ -36217,8 +36668,16 @@
         </is>
       </c>
       <c r="E1294" s="3" t="n"/>
-      <c r="F1294" s="3" t="n"/>
-      <c r="G1294" s="3" t="n"/>
+      <c r="F1294" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1294" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1295">
       <c r="A1295" s="2" t="inlineStr">
@@ -36242,8 +36701,16 @@
         </is>
       </c>
       <c r="E1295" s="3" t="n"/>
-      <c r="F1295" s="3" t="n"/>
-      <c r="G1295" s="3" t="n"/>
+      <c r="F1295" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1295" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1296">
       <c r="A1296" s="2" t="inlineStr">
@@ -36267,8 +36734,16 @@
         </is>
       </c>
       <c r="E1296" s="3" t="n"/>
-      <c r="F1296" s="3" t="n"/>
-      <c r="G1296" s="3" t="n"/>
+      <c r="F1296" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1296" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1297">
       <c r="A1297" s="2" t="inlineStr">
@@ -36292,8 +36767,16 @@
         </is>
       </c>
       <c r="E1297" s="3" t="n"/>
-      <c r="F1297" s="3" t="n"/>
-      <c r="G1297" s="3" t="n"/>
+      <c r="F1297" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1297" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1298">
       <c r="A1298" s="2" t="inlineStr">
@@ -36317,8 +36800,16 @@
         </is>
       </c>
       <c r="E1298" s="3" t="n"/>
-      <c r="F1298" s="3" t="n"/>
-      <c r="G1298" s="3" t="n"/>
+      <c r="F1298" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1298" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1299">
       <c r="A1299" s="2" t="inlineStr">
@@ -36342,8 +36833,16 @@
         </is>
       </c>
       <c r="E1299" s="3" t="n"/>
-      <c r="F1299" s="3" t="n"/>
-      <c r="G1299" s="3" t="n"/>
+      <c r="F1299" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1299" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1300">
       <c r="A1300" s="2" t="inlineStr">
@@ -36367,8 +36866,16 @@
         </is>
       </c>
       <c r="E1300" s="3" t="n"/>
-      <c r="F1300" s="3" t="n"/>
-      <c r="G1300" s="3" t="n"/>
+      <c r="F1300" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1300" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1301">
       <c r="A1301" s="2" t="inlineStr">
@@ -36392,10 +36899,18 @@
         </is>
       </c>
       <c r="E1301" s="3" t="n"/>
-      <c r="F1301" s="3" t="n"/>
-      <c r="G1301" s="3" t="n"/>
-    </row>
-    <row r="1302">
+      <c r="F1301" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1301" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302" ht="32" customHeight="1">
       <c r="A1302" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36417,7 +36932,12 @@
         </is>
       </c>
       <c r="E1302" s="3" t="n"/>
-      <c r="F1302" s="3" t="n"/>
+      <c r="F1302" s="6" t="inlineStr">
+        <is>
+          <t>reportType=0 — 88.9%
+reportType=1 — 11.1%</t>
+        </is>
+      </c>
       <c r="G1302" s="3" t="n"/>
     </row>
     <row r="1303">
@@ -36442,8 +36962,16 @@
         </is>
       </c>
       <c r="E1303" s="3" t="n"/>
-      <c r="F1303" s="3" t="n"/>
-      <c r="G1303" s="3" t="n"/>
+      <c r="F1303" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1303" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1304">
       <c r="A1304" s="2" t="inlineStr">
@@ -36467,10 +36995,18 @@
         </is>
       </c>
       <c r="E1304" s="3" t="n"/>
-      <c r="F1304" s="3" t="n"/>
-      <c r="G1304" s="3" t="n"/>
-    </row>
-    <row r="1305">
+      <c r="F1304" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1304" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305" ht="208" customHeight="1">
       <c r="A1305" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36492,7 +37028,23 @@
         </is>
       </c>
       <c r="E1305" s="3" t="n"/>
-      <c r="F1305" s="3" t="n"/>
+      <c r="F1305" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+无Order过滤+无LineItem过滤 — 24.2%
+timeType=3+按Order过滤+无LineItem过滤 — 23.0%
+timeType=3+按Order过滤+按LineItem过滤 — 15.6%
+timeType=1+按Order过滤+无LineItem过滤 — 9.6%
+timeType=3+无Order过滤+按LineItem过滤(含非数字ID) — 5.4%
+timeType=3+无Order过滤+不传lineItemIds — 4.8%
+timeType=3+按Order过滤+不传lineItemIds — 3.8%
+timeType=1+无Order过滤+无LineItem过滤 — 3.6%
+timeType=1+按Order过滤+按LineItem过滤 — 2.4%
+timeType=2+按Order过滤+无LineItem过滤 — 1.4%
+timeType=1+无Order过滤+不传lineItemIds — 1.2%
+timeType=1+按Order过滤+不传lineItemIds — 1.0%
+timeType=3+不传orderIds+无LineItem过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G1305" s="3" t="n"/>
     </row>
     <row r="1306">
@@ -36517,10 +37069,18 @@
         </is>
       </c>
       <c r="E1306" s="3" t="n"/>
-      <c r="F1306" s="3" t="n"/>
-      <c r="G1306" s="3" t="n"/>
-    </row>
-    <row r="1307">
+      <c r="F1306" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1306" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307" ht="96" customHeight="1">
       <c r="A1307" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36542,10 +37102,19 @@
         </is>
       </c>
       <c r="E1307" s="3" t="n"/>
-      <c r="F1307" s="3" t="n"/>
+      <c r="F1307" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+comparisonSetting=0 — 48.6%
+timeType=1+comparisonSetting=0 — 40.4%
+timeType=3+comparisonSetting=1 — 4.0%
+timeType=2+comparisonSetting=0 — 3.8%
+timeType=3+不传comparisonSetting — 1.4%
+timeType=1+comparisonSetting=1 — 1.2%</t>
+        </is>
+      </c>
       <c r="G1307" s="3" t="n"/>
     </row>
-    <row r="1308">
+    <row r="1308" ht="112" customHeight="1">
       <c r="A1308" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36567,10 +37136,20 @@
         </is>
       </c>
       <c r="E1308" s="3" t="n"/>
-      <c r="F1308" s="3" t="n"/>
+      <c r="F1308" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤+targetType=0 — 43.4%
+timeType=3+无Order过滤+targetType=0 — 32.2%
+timeType=1+按Order过滤+targetType=0 — 12.4%
+timeType=1+无Order过滤+targetType=0 — 5.0%
+timeType=2+按Order过滤+targetType=0 — 1.6%
+timeType=3+不传orderIds+targetType=0 — 1.4%
+timeType=3+按Order过滤+targetType=1 — 1.4%</t>
+        </is>
+      </c>
       <c r="G1308" s="3" t="n"/>
     </row>
-    <row r="1309">
+    <row r="1309" ht="80" customHeight="1">
       <c r="A1309" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36592,7 +37171,15 @@
         </is>
       </c>
       <c r="E1309" s="3" t="n"/>
-      <c r="F1309" s="3" t="n"/>
+      <c r="F1309" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+comparisonSetting=0 — 77.2%
+timeType=3+comparisonSetting=1 — 11.2%
+timeType=2+comparisonSetting=0 — 8.4%
+timeType=3+不传comparisonSetting — 1.9%
+timeType=2+comparisonSetting=1 — 1.4%</t>
+        </is>
+      </c>
       <c r="G1309" s="3" t="n"/>
     </row>
     <row r="1310">
@@ -36617,10 +37204,18 @@
         </is>
       </c>
       <c r="E1310" s="3" t="n"/>
-      <c r="F1310" s="3" t="n"/>
-      <c r="G1310" s="3" t="n"/>
-    </row>
-    <row r="1311">
+      <c r="F1310" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1310" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311" ht="176" customHeight="1">
       <c r="A1311" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36642,10 +37237,24 @@
         </is>
       </c>
       <c r="E1311" s="3" t="n"/>
-      <c r="F1311" s="3" t="n"/>
+      <c r="F1311" s="6" t="inlineStr">
+        <is>
+          <t>timeType=1+无Order过滤+含advertiserIds — 30.2%
+timeType=3+无Order过滤+含advertiserIds — 16.2%
+timeType=3+按Order过滤+含advertiserIds — 10.2%
+timeType=1+按Order过滤+含advertiserIds — 10.0%
+timeType=3+无Order过滤+不含advertiserIds — 8.6%
+timeType=3+按Order过滤+不含advertiserIds — 7.8%
+timeType=1+按Order过滤+不含advertiserIds — 6.6%
+timeType=1+无Order过滤+不含advertiserIds — 3.8%
+timeType=1+不传orderIds+含advertiserIds — 2.0%
+timeType=2+无Order过滤+含advertiserIds — 1.2%
+timeType=2+按Order过滤+不含advertiserIds — 1.2%</t>
+        </is>
+      </c>
       <c r="G1311" s="3" t="n"/>
     </row>
-    <row r="1312">
+    <row r="1312" ht="96" customHeight="1">
       <c r="A1312" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36667,10 +37276,19 @@
         </is>
       </c>
       <c r="E1312" s="3" t="n"/>
-      <c r="F1312" s="3" t="n"/>
+      <c r="F1312" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+无Creative过滤 — 49.5%
+timeType=3+按Creative过滤 — 24.3%
+timeType=3+不传creativeIds — 8.7%
+timeType=1+无Creative过滤 — 7.5%
+timeType=1+按Creative过滤 — 6.2%
+timeType=2+按Creative过滤 — 1.9%</t>
+        </is>
+      </c>
       <c r="G1312" s="3" t="n"/>
     </row>
-    <row r="1313">
+    <row r="1313" ht="96" customHeight="1">
       <c r="A1313" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36692,10 +37310,19 @@
         </is>
       </c>
       <c r="E1313" s="3" t="n"/>
-      <c r="F1313" s="3" t="n"/>
+      <c r="F1313" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤 — 30.3%
+timeType=3+无Order过滤 — 30.3%
+timeType=1+按Order过滤 — 21.2%
+timeType=1+无Order过滤 — 12.0%
+timeType=2+按Order过滤 — 2.9%
+timeType=3+不传orderIds — 2.5%</t>
+        </is>
+      </c>
       <c r="G1313" s="3" t="n"/>
     </row>
-    <row r="1314">
+    <row r="1314" ht="96" customHeight="1">
       <c r="A1314" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36717,10 +37344,19 @@
         </is>
       </c>
       <c r="E1314" s="3" t="n"/>
-      <c r="F1314" s="3" t="n"/>
+      <c r="F1314" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+comparisonSetting=0 — 48.0%
+timeType=1+comparisonSetting=0 — 41.2%
+timeType=3+comparisonSetting=1 — 4.8%
+timeType=2+comparisonSetting=0 — 2.8%
+timeType=1+comparisonSetting=1 — 1.4%
+timeType=3+不传comparisonSetting — 1.2%</t>
+        </is>
+      </c>
       <c r="G1314" s="3" t="n"/>
     </row>
-    <row r="1315">
+    <row r="1315" ht="112" customHeight="1">
       <c r="A1315" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36742,10 +37378,20 @@
         </is>
       </c>
       <c r="E1315" s="3" t="n"/>
-      <c r="F1315" s="3" t="n"/>
+      <c r="F1315" s="6" t="inlineStr">
+        <is>
+          <t>timeType=1+无Order过滤 — 42.6%
+timeType=3+无Order过滤 — 21.6%
+timeType=3+按Order过滤 — 16.4%
+timeType=1+按Order过滤 — 13.6%
+timeType=1+不传orderIds — 2.4%
+timeType=2+无Order过滤 — 1.6%
+timeType=3+不传orderIds — 1.4%</t>
+        </is>
+      </c>
       <c r="G1315" s="3" t="n"/>
     </row>
-    <row r="1316">
+    <row r="1316" ht="96" customHeight="1">
       <c r="A1316" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36767,10 +37413,19 @@
         </is>
       </c>
       <c r="E1316" s="3" t="n"/>
-      <c r="F1316" s="3" t="n"/>
+      <c r="F1316" s="6" t="inlineStr">
+        <is>
+          <t>timeType=1+conversionType=0 — 55.0%
+timeType=3+conversionType=0 — 37.4%
+timeType=2+conversionType=0 — 2.2%
+timeType=1+conversionType=1 — 1.4%
+timeType=3+conversionType=3 — 1.2%
+timeType=1+conversionType=3 — 1.0%</t>
+        </is>
+      </c>
       <c r="G1316" s="3" t="n"/>
     </row>
-    <row r="1317">
+    <row r="1317" ht="80" customHeight="1">
       <c r="A1317" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36792,10 +37447,18 @@
         </is>
       </c>
       <c r="E1317" s="3" t="n"/>
-      <c r="F1317" s="3" t="n"/>
+      <c r="F1317" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤 — 62.8%
+timeType=3+无Order过滤 — 21.8%
+timeType=1+按Order过滤 — 10.6%
+timeType=1+无Order过滤 — 1.6%
+timeType=2+按Order过滤 — 1.4%</t>
+        </is>
+      </c>
       <c r="G1317" s="3" t="n"/>
     </row>
-    <row r="1318">
+    <row r="1318" ht="96" customHeight="1">
       <c r="A1318" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36817,10 +37480,19 @@
         </is>
       </c>
       <c r="E1318" s="3" t="n"/>
-      <c r="F1318" s="3" t="n"/>
+      <c r="F1318" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤 — 61.8%
+timeType=3+无Order过滤 — 23.2%
+timeType=1+按Order过滤 — 10.2%
+timeType=2+按Order过滤 — 1.8%
+timeType=1+无Order过滤 — 1.4%
+timeType=3+不传orderIds — 1.0%</t>
+        </is>
+      </c>
       <c r="G1318" s="3" t="n"/>
     </row>
-    <row r="1319">
+    <row r="1319" ht="80" customHeight="1">
       <c r="A1319" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36842,10 +37514,18 @@
         </is>
       </c>
       <c r="E1319" s="3" t="n"/>
-      <c r="F1319" s="3" t="n"/>
+      <c r="F1319" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤 — 61.8%
+timeType=3+无Order过滤 — 24.6%
+timeType=1+按Order过滤 — 8.8%
+timeType=2+按Order过滤 — 1.6%
+timeType=1+无Order过滤 — 1.4%</t>
+        </is>
+      </c>
       <c r="G1319" s="3" t="n"/>
     </row>
-    <row r="1320">
+    <row r="1320" ht="96" customHeight="1">
       <c r="A1320" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36867,10 +37547,19 @@
         </is>
       </c>
       <c r="E1320" s="3" t="n"/>
-      <c r="F1320" s="3" t="n"/>
+      <c r="F1320" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤 — 30.3%
+timeType=3+无Order过滤 — 30.3%
+timeType=1+按Order过滤 — 21.2%
+timeType=1+无Order过滤 — 12.0%
+timeType=2+按Order过滤 — 2.9%
+timeType=3+不传orderIds — 2.5%</t>
+        </is>
+      </c>
       <c r="G1320" s="3" t="n"/>
     </row>
-    <row r="1321">
+    <row r="1321" ht="64" customHeight="1">
       <c r="A1321" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36892,7 +37581,14 @@
         </is>
       </c>
       <c r="E1321" s="3" t="n"/>
-      <c r="F1321" s="3" t="n"/>
+      <c r="F1321" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤 — 62.8%
+timeType=3+无Order过滤 — 23.4%
+timeType=1+按Order过滤 — 9.6%
+timeType=1+无Order过滤 — 1.6%</t>
+        </is>
+      </c>
       <c r="G1321" s="3" t="n"/>
     </row>
     <row r="1322">
@@ -36917,10 +37613,18 @@
         </is>
       </c>
       <c r="E1322" s="3" t="n"/>
-      <c r="F1322" s="3" t="n"/>
-      <c r="G1322" s="3" t="n"/>
-    </row>
-    <row r="1323">
+      <c r="F1322" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1322" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323" ht="96" customHeight="1">
       <c r="A1323" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36942,10 +37646,19 @@
         </is>
       </c>
       <c r="E1323" s="3" t="n"/>
-      <c r="F1323" s="3" t="n"/>
+      <c r="F1323" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+无Creative过滤 — 49.5%
+timeType=3+按Creative过滤 — 24.3%
+timeType=3+不传creativeIds — 8.7%
+timeType=1+无Creative过滤 — 7.5%
+timeType=1+按Creative过滤 — 6.2%
+timeType=2+按Creative过滤 — 1.9%</t>
+        </is>
+      </c>
       <c r="G1323" s="3" t="n"/>
     </row>
-    <row r="1324">
+    <row r="1324" ht="96" customHeight="1">
       <c r="A1324" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36967,10 +37680,19 @@
         </is>
       </c>
       <c r="E1324" s="3" t="n"/>
-      <c r="F1324" s="3" t="n"/>
+      <c r="F1324" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+无Creative过滤 — 49.5%
+timeType=3+按Creative过滤 — 24.3%
+timeType=3+不传creativeIds — 8.7%
+timeType=1+无Creative过滤 — 7.5%
+timeType=1+按Creative过滤 — 6.2%
+timeType=2+按Creative过滤 — 1.9%</t>
+        </is>
+      </c>
       <c r="G1324" s="3" t="n"/>
     </row>
-    <row r="1325">
+    <row r="1325" ht="96" customHeight="1">
       <c r="A1325" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36992,10 +37714,19 @@
         </is>
       </c>
       <c r="E1325" s="3" t="n"/>
-      <c r="F1325" s="3" t="n"/>
+      <c r="F1325" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+无Creative过滤 — 49.5%
+timeType=3+按Creative过滤 — 24.3%
+timeType=3+不传creativeIds — 8.7%
+timeType=1+无Creative过滤 — 7.5%
+timeType=1+按Creative过滤 — 6.2%
+timeType=2+按Creative过滤 — 1.9%</t>
+        </is>
+      </c>
       <c r="G1325" s="3" t="n"/>
     </row>
-    <row r="1326">
+    <row r="1326" ht="96" customHeight="1">
       <c r="A1326" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -37017,10 +37748,19 @@
         </is>
       </c>
       <c r="E1326" s="3" t="n"/>
-      <c r="F1326" s="3" t="n"/>
+      <c r="F1326" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+无Creative过滤 — 49.5%
+timeType=3+按Creative过滤 — 24.3%
+timeType=3+不传creativeIds — 8.7%
+timeType=1+无Creative过滤 — 7.5%
+timeType=1+按Creative过滤 — 6.2%
+timeType=2+按Creative过滤 — 1.9%</t>
+        </is>
+      </c>
       <c r="G1326" s="3" t="n"/>
     </row>
-    <row r="1327">
+    <row r="1327" ht="96" customHeight="1">
       <c r="A1327" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -37042,10 +37782,19 @@
         </is>
       </c>
       <c r="E1327" s="3" t="n"/>
-      <c r="F1327" s="3" t="n"/>
+      <c r="F1327" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+无Order过滤 — 30.4%
+timeType=3+按Order过滤 — 30.4%
+timeType=1+按Order过滤 — 20.8%
+timeType=1+无Order过滤 — 12.1%
+timeType=2+按Order过滤 — 2.9%
+timeType=3+不传orderIds — 2.5%</t>
+        </is>
+      </c>
       <c r="G1327" s="3" t="n"/>
     </row>
-    <row r="1328">
+    <row r="1328" ht="80" customHeight="1">
       <c r="A1328" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -37067,10 +37816,18 @@
         </is>
       </c>
       <c r="E1328" s="3" t="n"/>
-      <c r="F1328" s="3" t="n"/>
+      <c r="F1328" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤+isBrandHalo=false — 59.6%
+timeType=3+无Order过滤+isBrandHalo=false — 24.6%
+timeType=1+按Order过滤+isBrandHalo=false — 9.4%
+timeType=1+无Order过滤+isBrandHalo=false — 1.8%
+timeType=2+按Order过滤+isBrandHalo=false — 1.6%</t>
+        </is>
+      </c>
       <c r="G1328" s="3" t="n"/>
     </row>
-    <row r="1329">
+    <row r="1329" ht="112" customHeight="1">
       <c r="A1329" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -37092,10 +37849,20 @@
         </is>
       </c>
       <c r="E1329" s="3" t="n"/>
-      <c r="F1329" s="3" t="n"/>
+      <c r="F1329" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+targetType=0+不含top — 41.6%
+timeType=3+targetType=0+含top — 18.6%
+timeType=3+targetType=1+含top — 17.6%
+timeType=1+targetType=0+不含top — 7.6%
+timeType=1+targetType=0+含top — 4.8%
+timeType=1+targetType=1+含top — 4.6%
+timeType=3+targetType=2+不含top — 1.4%</t>
+        </is>
+      </c>
       <c r="G1329" s="3" t="n"/>
     </row>
-    <row r="1330">
+    <row r="1330" ht="96" customHeight="1">
       <c r="A1330" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -37117,10 +37884,19 @@
         </is>
       </c>
       <c r="E1330" s="3" t="n"/>
-      <c r="F1330" s="3" t="n"/>
+      <c r="F1330" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+按Order过滤 — 30.4%
+timeType=3+无Order过滤 — 30.4%
+timeType=1+按Order过滤 — 20.8%
+timeType=1+无Order过滤 — 12.1%
+timeType=2+按Order过滤 — 2.9%
+timeType=3+不传orderIds — 2.5%</t>
+        </is>
+      </c>
       <c r="G1330" s="3" t="n"/>
     </row>
-    <row r="1331">
+    <row r="1331" ht="96" customHeight="1">
       <c r="A1331" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -37142,7 +37918,16 @@
         </is>
       </c>
       <c r="E1331" s="3" t="n"/>
-      <c r="F1331" s="3" t="n"/>
+      <c r="F1331" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+comparisonSetting=0 — 47.2%
+timeType=1+comparisonSetting=0 — 40.4%
+timeType=3+comparisonSetting=1 — 4.6%
+timeType=2+comparisonSetting=0 — 4.2%
+timeType=1+comparisonSetting=1 — 1.4%
+timeType=3+不传comparisonSetting — 1.4%</t>
+        </is>
+      </c>
       <c r="G1331" s="3" t="n"/>
     </row>
     <row r="1332">
@@ -37167,8 +37952,16 @@
         </is>
       </c>
       <c r="E1332" s="3" t="n"/>
-      <c r="F1332" s="3" t="n"/>
-      <c r="G1332" s="3" t="n"/>
+      <c r="F1332" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1332" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1333">
       <c r="A1333" s="2" t="inlineStr">
@@ -37192,10 +37985,18 @@
         </is>
       </c>
       <c r="E1333" s="3" t="n"/>
-      <c r="F1333" s="3" t="n"/>
-      <c r="G1333" s="3" t="n"/>
-    </row>
-    <row r="1334">
+      <c r="F1333" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1333" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334" ht="112" customHeight="1">
       <c r="A1334" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -37217,7 +38018,17 @@
         </is>
       </c>
       <c r="E1334" s="3" t="n"/>
-      <c r="F1334" s="3" t="n"/>
+      <c r="F1334" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+conversionType=0 — 58.4%
+timeType=1+conversionType=0 — 30.9%
+timeType=2+conversionType=0 — 3.4%
+timeType=1+conversionType=4 — 2.7%
+timeType=1+conversionType=1 — 1.5%
+timeType=3+conversionType=3 — 1.1%
+timeType=3+conversionType=4 — 1.1%</t>
+        </is>
+      </c>
       <c r="G1334" s="3" t="n"/>
     </row>
     <row r="1335">
@@ -37242,8 +38053,16 @@
         </is>
       </c>
       <c r="E1335" s="3" t="n"/>
-      <c r="F1335" s="3" t="n"/>
-      <c r="G1335" s="3" t="n"/>
+      <c r="F1335" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1335" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用；接口名疑似写操作(更新设置)，未来出现流量需人工先确认读写属性再纳入流程</t>
+        </is>
+      </c>
     </row>
     <row r="1336">
       <c r="A1336" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -796,9 +796,19 @@
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
+      <c r="F13" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>76% (120/157)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -7380,8 +7390,16 @@
         </is>
       </c>
       <c r="E192" s="3" t="n"/>
-      <c r="F192" s="3" t="n"/>
-      <c r="G192" s="3" t="n"/>
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G192" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -7405,8 +7423,16 @@
         </is>
       </c>
       <c r="E193" s="3" t="n"/>
-      <c r="F193" s="3" t="n"/>
-      <c r="G193" s="3" t="n"/>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -7430,10 +7456,18 @@
         </is>
       </c>
       <c r="E194" s="3" t="n"/>
-      <c r="F194" s="3" t="n"/>
-      <c r="G194" s="3" t="n"/>
-    </row>
-    <row r="195">
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="16" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7455,7 +7489,11 @@
         </is>
       </c>
       <c r="E195" s="3" t="n"/>
-      <c r="F195" s="3" t="n"/>
+      <c r="F195" s="6" t="inlineStr">
+        <is>
+          <t>默认调用</t>
+        </is>
+      </c>
       <c r="G195" s="3" t="n"/>
     </row>
     <row r="196">
@@ -7480,8 +7518,16 @@
         </is>
       </c>
       <c r="E196" s="3" t="n"/>
-      <c r="F196" s="3" t="n"/>
-      <c r="G196" s="3" t="n"/>
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -7505,8 +7551,16 @@
         </is>
       </c>
       <c r="E197" s="3" t="n"/>
-      <c r="F197" s="3" t="n"/>
-      <c r="G197" s="3" t="n"/>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G197" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -7530,8 +7584,16 @@
         </is>
       </c>
       <c r="E198" s="3" t="n"/>
-      <c r="F198" s="3" t="n"/>
-      <c r="G198" s="3" t="n"/>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -7555,8 +7617,16 @@
         </is>
       </c>
       <c r="E199" s="3" t="n"/>
-      <c r="F199" s="3" t="n"/>
-      <c r="G199" s="3" t="n"/>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -7580,8 +7650,16 @@
         </is>
       </c>
       <c r="E200" s="3" t="n"/>
-      <c r="F200" s="3" t="n"/>
-      <c r="G200" s="3" t="n"/>
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G200" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -7605,8 +7683,16 @@
         </is>
       </c>
       <c r="E201" s="3" t="n"/>
-      <c r="F201" s="3" t="n"/>
-      <c r="G201" s="3" t="n"/>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G201" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -7631,7 +7717,11 @@
       </c>
       <c r="E202" s="3" t="n"/>
       <c r="F202" s="3" t="n"/>
-      <c r="G202" s="3" t="n"/>
+      <c r="G202" s="5" t="inlineStr">
+        <is>
+          <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -7656,9 +7746,13 @@
       </c>
       <c r="E203" s="3" t="n"/>
       <c r="F203" s="3" t="n"/>
-      <c r="G203" s="3" t="n"/>
-    </row>
-    <row r="204">
+      <c r="G203" s="5" t="inlineStr">
+        <is>
+          <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="112" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7680,7 +7774,17 @@
         </is>
       </c>
       <c r="E204" s="3" t="n"/>
-      <c r="F204" s="3" t="n"/>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>instanceId=amcgd4jvzeh+dataSourceId=amazon retail purchases — 28.4%
+instanceId=amcgd4jvzeh+dataSourceId=conversions all — 16.6%
+instanceId=amcgd4jvzeh+dataSourceId=conversions all for audiences — 16.4%
+instanceId=amcgd4jvzeh+dataSourceId=amazon retail purchases for audiences — 12.4%
+instanceId=amcgd4jvzeh+dataSourceId=amazon brand store page views — 10.9%
+instanceId=amc5e96cnci+dataSourceId=conversions all — 5.7%
+instanceId=amckgvjhven+dataSourceId=conversions all — 1.3%</t>
+        </is>
+      </c>
       <c r="G204" s="3" t="n"/>
     </row>
     <row r="205">
@@ -7706,7 +7810,11 @@
       </c>
       <c r="E205" s="3" t="n"/>
       <c r="F205" s="3" t="n"/>
-      <c r="G205" s="3" t="n"/>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -7731,7 +7839,11 @@
       </c>
       <c r="E206" s="3" t="n"/>
       <c r="F206" s="3" t="n"/>
-      <c r="G206" s="3" t="n"/>
+      <c r="G206" s="5" t="inlineStr">
+        <is>
+          <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -7756,7 +7868,11 @@
       </c>
       <c r="E207" s="3" t="n"/>
       <c r="F207" s="3" t="n"/>
-      <c r="G207" s="3" t="n"/>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -7780,10 +7896,18 @@
         </is>
       </c>
       <c r="E208" s="3" t="n"/>
-      <c r="F208" s="3" t="n"/>
-      <c r="G208" s="3" t="n"/>
-    </row>
-    <row r="209">
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="16" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7805,7 +7929,11 @@
         </is>
       </c>
       <c r="E209" s="3" t="n"/>
-      <c r="F209" s="3" t="n"/>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G209" s="3" t="n"/>
     </row>
     <row r="210">
@@ -7831,9 +7959,13 @@
       </c>
       <c r="E210" s="3" t="n"/>
       <c r="F210" s="3" t="n"/>
-      <c r="G210" s="3" t="n"/>
-    </row>
-    <row r="211">
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="16" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7855,10 +7987,14 @@
         </is>
       </c>
       <c r="E211" s="3" t="n"/>
-      <c r="F211" s="3" t="n"/>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>按id查询</t>
+        </is>
+      </c>
       <c r="G211" s="3" t="n"/>
     </row>
-    <row r="212">
+    <row r="212" ht="16" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7880,7 +8016,11 @@
         </is>
       </c>
       <c r="E212" s="3" t="n"/>
-      <c r="F212" s="3" t="n"/>
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>含tagId — 100.0%</t>
+        </is>
+      </c>
       <c r="G212" s="3" t="n"/>
     </row>
     <row r="213">
@@ -7905,8 +8045,16 @@
         </is>
       </c>
       <c r="E213" s="3" t="n"/>
-      <c r="F213" s="3" t="n"/>
-      <c r="G213" s="3" t="n"/>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -7930,10 +8078,18 @@
         </is>
       </c>
       <c r="E214" s="3" t="n"/>
-      <c r="F214" s="3" t="n"/>
-      <c r="G214" s="3" t="n"/>
-    </row>
-    <row r="215">
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="48" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7955,7 +8111,13 @@
         </is>
       </c>
       <c r="E215" s="3" t="n"/>
-      <c r="F215" s="3" t="n"/>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>含historyId+不含CrossPurchaseGroupBy — 70.6%
+含historyId+含CrossPurchaseGroupBy — 23.8%
+不含historyId+不含CrossPurchaseGroupBy — 5.6%</t>
+        </is>
+      </c>
       <c r="G215" s="3" t="n"/>
     </row>
     <row r="216">
@@ -7980,8 +8142,16 @@
         </is>
       </c>
       <c r="E216" s="3" t="n"/>
-      <c r="F216" s="3" t="n"/>
-      <c r="G216" s="3" t="n"/>
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -8006,7 +8176,11 @@
       </c>
       <c r="E217" s="3" t="n"/>
       <c r="F217" s="3" t="n"/>
-      <c r="G217" s="3" t="n"/>
+      <c r="G217" s="5" t="inlineStr">
+        <is>
+          <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -8031,7 +8205,11 @@
       </c>
       <c r="E218" s="3" t="n"/>
       <c r="F218" s="3" t="n"/>
-      <c r="G218" s="3" t="n"/>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -8056,9 +8234,13 @@
       </c>
       <c r="E219" s="3" t="n"/>
       <c r="F219" s="3" t="n"/>
-      <c r="G219" s="3" t="n"/>
-    </row>
-    <row r="220">
+      <c r="G219" s="5" t="inlineStr">
+        <is>
+          <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="96" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8080,10 +8262,19 @@
         </is>
       </c>
       <c r="E220" s="3" t="n"/>
-      <c r="F220" s="3" t="n"/>
+      <c r="F220" s="6" t="inlineStr">
+        <is>
+          <t>reportTypes=[All] — 59.6%
+reportTypes=[SP] — 12.4%
+reportTypes=[DSP] — 9.0%
+reportTypes=[SD] — 9.0%
+reportTypes=[SB] — 7.9%
+reportTypes=[STV] — 2.2%</t>
+        </is>
+      </c>
       <c r="G220" s="3" t="n"/>
     </row>
-    <row r="221">
+    <row r="221" ht="16" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8105,10 +8296,14 @@
         </is>
       </c>
       <c r="E221" s="3" t="n"/>
-      <c r="F221" s="3" t="n"/>
+      <c r="F221" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G221" s="3" t="n"/>
     </row>
-    <row r="222">
+    <row r="222" ht="16" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8130,10 +8325,14 @@
         </is>
       </c>
       <c r="E222" s="3" t="n"/>
-      <c r="F222" s="3" t="n"/>
+      <c r="F222" s="6" t="inlineStr">
+        <is>
+          <t>含instanceIds — 100.0%</t>
+        </is>
+      </c>
       <c r="G222" s="3" t="n"/>
     </row>
-    <row r="223">
+    <row r="223" ht="32" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8155,10 +8354,15 @@
         </is>
       </c>
       <c r="E223" s="3" t="n"/>
-      <c r="F223" s="3" t="n"/>
+      <c r="F223" s="6" t="inlineStr">
+        <is>
+          <t>category=MCF14 — 70.3%
+category=TagMCF14 — 29.7%</t>
+        </is>
+      </c>
       <c r="G223" s="3" t="n"/>
     </row>
-    <row r="224">
+    <row r="224" ht="16" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8180,10 +8384,14 @@
         </is>
       </c>
       <c r="E224" s="3" t="n"/>
-      <c r="F224" s="3" t="n"/>
+      <c r="F224" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G224" s="3" t="n"/>
     </row>
-    <row r="225">
+    <row r="225" ht="16" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8205,10 +8413,14 @@
         </is>
       </c>
       <c r="E225" s="3" t="n"/>
-      <c r="F225" s="3" t="n"/>
+      <c r="F225" s="6" t="inlineStr">
+        <is>
+          <t>含tagId — 100.0%</t>
+        </is>
+      </c>
       <c r="G225" s="3" t="n"/>
     </row>
-    <row r="226">
+    <row r="226" ht="16" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8230,10 +8442,14 @@
         </is>
       </c>
       <c r="E226" s="3" t="n"/>
-      <c r="F226" s="3" t="n"/>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>含tagId — 100.0%</t>
+        </is>
+      </c>
       <c r="G226" s="3" t="n"/>
     </row>
-    <row r="227">
+    <row r="227" ht="32" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8255,10 +8471,15 @@
         </is>
       </c>
       <c r="E227" s="3" t="n"/>
-      <c r="F227" s="3" t="n"/>
+      <c r="F227" s="6" t="inlineStr">
+        <is>
+          <t>category=Consideration — 86.2%
+category=ConsiderationTotal — 13.6%</t>
+        </is>
+      </c>
       <c r="G227" s="3" t="n"/>
     </row>
-    <row r="228">
+    <row r="228" ht="16" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8280,10 +8501,14 @@
         </is>
       </c>
       <c r="E228" s="3" t="n"/>
-      <c r="F228" s="3" t="n"/>
+      <c r="F228" s="6" t="inlineStr">
+        <is>
+          <t>默认调用</t>
+        </is>
+      </c>
       <c r="G228" s="3" t="n"/>
     </row>
-    <row r="229">
+    <row r="229" ht="32" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8305,10 +8530,15 @@
         </is>
       </c>
       <c r="E229" s="3" t="n"/>
-      <c r="F229" s="3" t="n"/>
+      <c r="F229" s="6" t="inlineStr">
+        <is>
+          <t>type=Off-Amazon conversion events — 57.4%
+type=Additional product metadata — 42.6%</t>
+        </is>
+      </c>
       <c r="G229" s="3" t="n"/>
     </row>
-    <row r="230">
+    <row r="230" ht="48" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8330,10 +8560,16 @@
         </is>
       </c>
       <c r="E230" s="3" t="n"/>
-      <c r="F230" s="3" t="n"/>
+      <c r="F230" s="6" t="inlineStr">
+        <is>
+          <t>reportTypes=[SP]+不含tagId — 50.0%
+reportTypes=[DSP]+含tagId — 27.5%
+reportTypes=[AMS]+含tagId — 22.5%</t>
+        </is>
+      </c>
       <c r="G230" s="3" t="n"/>
     </row>
-    <row r="231">
+    <row r="231" ht="16" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8355,10 +8591,14 @@
         </is>
       </c>
       <c r="E231" s="3" t="n"/>
-      <c r="F231" s="3" t="n"/>
+      <c r="F231" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G231" s="3" t="n"/>
     </row>
-    <row r="232">
+    <row r="232" ht="112" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8380,10 +8620,20 @@
         </is>
       </c>
       <c r="E232" s="3" t="n"/>
-      <c r="F232" s="3" t="n"/>
+      <c r="F232" s="6" t="inlineStr">
+        <is>
+          <t>category=DemoGraphicRelationship — 15.0%
+category=DemoGraphicAge — 15.0%
+category=DemoGraphicIncome — 15.0%
+category=DemoGraphicEducation — 15.0%
+category=DemoGraphicDevice — 15.0%
+category=DemoGraphicGender — 15.0%
+category=DemoGraphicGenderByAge — 10.0%</t>
+        </is>
+      </c>
       <c r="G232" s="3" t="n"/>
     </row>
-    <row r="233">
+    <row r="233" ht="32" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8405,10 +8655,15 @@
         </is>
       </c>
       <c r="E233" s="3" t="n"/>
-      <c r="F233" s="3" t="n"/>
+      <c r="F233" s="6" t="inlineStr">
+        <is>
+          <t>keyWord=State+category=DemoGraphicLocationUser — 85.7%
+keyWord=State+category=DemoGraphicLocationNTBUser — 14.3%</t>
+        </is>
+      </c>
       <c r="G233" s="3" t="n"/>
     </row>
-    <row r="234">
+    <row r="234" ht="48" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8430,10 +8685,16 @@
         </is>
       </c>
       <c r="E234" s="3" t="n"/>
-      <c r="F234" s="3" t="n"/>
+      <c r="F234" s="6" t="inlineStr">
+        <is>
+          <t>includeCleanRoom=true — 68.8%
+不传includeCleanRoom — 26.2%
+includeCleanRoom=false — 5.0%</t>
+        </is>
+      </c>
       <c r="G234" s="3" t="n"/>
     </row>
-    <row r="235">
+    <row r="235" ht="16" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8455,10 +8716,14 @@
         </is>
       </c>
       <c r="E235" s="3" t="n"/>
-      <c r="F235" s="3" t="n"/>
+      <c r="F235" s="6" t="inlineStr">
+        <is>
+          <t>按advertiserId查询</t>
+        </is>
+      </c>
       <c r="G235" s="3" t="n"/>
     </row>
-    <row r="236">
+    <row r="236" ht="16" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8480,7 +8745,11 @@
         </is>
       </c>
       <c r="E236" s="3" t="n"/>
-      <c r="F236" s="3" t="n"/>
+      <c r="F236" s="6" t="inlineStr">
+        <is>
+          <t>含keyword+不含tagId — 100.0%</t>
+        </is>
+      </c>
       <c r="G236" s="3" t="n"/>
     </row>
     <row r="237">
@@ -8505,10 +8774,18 @@
         </is>
       </c>
       <c r="E237" s="3" t="n"/>
-      <c r="F237" s="3" t="n"/>
-      <c r="G237" s="3" t="n"/>
-    </row>
-    <row r="238">
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="16" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8530,10 +8807,14 @@
         </is>
       </c>
       <c r="E238" s="3" t="n"/>
-      <c r="F238" s="3" t="n"/>
+      <c r="F238" s="6" t="inlineStr">
+        <is>
+          <t>tagTypes=[]+首页 — 100.0%</t>
+        </is>
+      </c>
       <c r="G238" s="3" t="n"/>
     </row>
-    <row r="239">
+    <row r="239" ht="16" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8555,10 +8836,14 @@
         </is>
       </c>
       <c r="E239" s="3" t="n"/>
-      <c r="F239" s="3" t="n"/>
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>tagTypes=[]+首页 — 100.0%</t>
+        </is>
+      </c>
       <c r="G239" s="3" t="n"/>
     </row>
-    <row r="240">
+    <row r="240" ht="16" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8580,10 +8865,14 @@
         </is>
       </c>
       <c r="E240" s="3" t="n"/>
-      <c r="F240" s="3" t="n"/>
+      <c r="F240" s="6" t="inlineStr">
+        <is>
+          <t>按historyId查询</t>
+        </is>
+      </c>
       <c r="G240" s="3" t="n"/>
     </row>
-    <row r="241">
+    <row r="241" ht="16" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8605,10 +8894,14 @@
         </is>
       </c>
       <c r="E241" s="3" t="n"/>
-      <c r="F241" s="3" t="n"/>
+      <c r="F241" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G241" s="3" t="n"/>
     </row>
-    <row r="242">
+    <row r="242" ht="48" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8630,10 +8923,16 @@
         </is>
       </c>
       <c r="E242" s="3" t="n"/>
-      <c r="F242" s="3" t="n"/>
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>category=PersonaUserSegmentInterest — 64.3%
+category=PersonaUserSegmentLifestyle — 28.6%
+category=PersonaUserSegmentInmarket — 7.1%</t>
+        </is>
+      </c>
       <c r="G242" s="3" t="n"/>
     </row>
-    <row r="243">
+    <row r="243" ht="32" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8655,10 +8954,15 @@
         </is>
       </c>
       <c r="E243" s="3" t="n"/>
-      <c r="F243" s="3" t="n"/>
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>category=Repurchased — 89.6%
+category=RepurchasedTotal — 10.4%</t>
+        </is>
+      </c>
       <c r="G243" s="3" t="n"/>
     </row>
-    <row r="244">
+    <row r="244" ht="16" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8680,10 +8984,14 @@
         </is>
       </c>
       <c r="E244" s="3" t="n"/>
-      <c r="F244" s="3" t="n"/>
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>不含subReportId — 100.0%</t>
+        </is>
+      </c>
       <c r="G244" s="3" t="n"/>
     </row>
-    <row r="245">
+    <row r="245" ht="32" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8705,10 +9013,15 @@
         </is>
       </c>
       <c r="E245" s="3" t="n"/>
-      <c r="F245" s="3" t="n"/>
+      <c r="F245" s="6" t="inlineStr">
+        <is>
+          <t>不含category+不含subReportId — 55.0%
+含category+不含subReportId — 45.0%</t>
+        </is>
+      </c>
       <c r="G245" s="3" t="n"/>
     </row>
-    <row r="246">
+    <row r="246" ht="16" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8730,10 +9043,14 @@
         </is>
       </c>
       <c r="E246" s="3" t="n"/>
-      <c r="F246" s="3" t="n"/>
+      <c r="F246" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G246" s="3" t="n"/>
     </row>
-    <row r="247">
+    <row r="247" ht="16" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8755,7 +9072,11 @@
         </is>
       </c>
       <c r="E247" s="3" t="n"/>
-      <c r="F247" s="3" t="n"/>
+      <c r="F247" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G247" s="3" t="n"/>
     </row>
     <row r="248">
@@ -8780,10 +9101,18 @@
         </is>
       </c>
       <c r="E248" s="3" t="n"/>
-      <c r="F248" s="3" t="n"/>
-      <c r="G248" s="3" t="n"/>
-    </row>
-    <row r="249">
+      <c r="F248" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G248" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="32" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8805,10 +9134,15 @@
         </is>
       </c>
       <c r="E249" s="3" t="n"/>
-      <c r="F249" s="3" t="n"/>
+      <c r="F249" s="6" t="inlineStr">
+        <is>
+          <t>按Profile过滤 — 66.4%
+无Profile过滤 — 33.0%</t>
+        </is>
+      </c>
       <c r="G249" s="3" t="n"/>
     </row>
-    <row r="250">
+    <row r="250" ht="32" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8830,10 +9164,15 @@
         </is>
       </c>
       <c r="E250" s="3" t="n"/>
-      <c r="F250" s="3" t="n"/>
+      <c r="F250" s="6" t="inlineStr">
+        <is>
+          <t>按Profile过滤 — 97.8%
+无Profile过滤 — 2.2%</t>
+        </is>
+      </c>
       <c r="G250" s="3" t="n"/>
     </row>
-    <row r="251">
+    <row r="251" ht="16" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8855,10 +9194,14 @@
         </is>
       </c>
       <c r="E251" s="3" t="n"/>
-      <c r="F251" s="3" t="n"/>
+      <c r="F251" s="6" t="inlineStr">
+        <is>
+          <t>按InstanceId查询</t>
+        </is>
+      </c>
       <c r="G251" s="3" t="n"/>
     </row>
-    <row r="252">
+    <row r="252" ht="32" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8880,10 +9223,15 @@
         </is>
       </c>
       <c r="E252" s="3" t="n"/>
-      <c r="F252" s="3" t="n"/>
+      <c r="F252" s="6" t="inlineStr">
+        <is>
+          <t>不含reportId — 98.5%
+含reportId — 1.5%</t>
+        </is>
+      </c>
       <c r="G252" s="3" t="n"/>
     </row>
-    <row r="253">
+    <row r="253" ht="16" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8905,7 +9253,11 @@
         </is>
       </c>
       <c r="E253" s="3" t="n"/>
-      <c r="F253" s="3" t="n"/>
+      <c r="F253" s="6" t="inlineStr">
+        <is>
+          <t>groupBy=Daily — 100.0%</t>
+        </is>
+      </c>
       <c r="G253" s="3" t="n"/>
     </row>
     <row r="254">
@@ -8930,10 +9282,18 @@
         </is>
       </c>
       <c r="E254" s="3" t="n"/>
-      <c r="F254" s="3" t="n"/>
-      <c r="G254" s="3" t="n"/>
-    </row>
-    <row r="255">
+      <c r="F254" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G254" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="32" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8955,10 +9315,15 @@
         </is>
       </c>
       <c r="E255" s="3" t="n"/>
-      <c r="F255" s="3" t="n"/>
+      <c r="F255" s="6" t="inlineStr">
+        <is>
+          <t>不含reportId — 98.5%
+含reportId — 1.5%</t>
+        </is>
+      </c>
       <c r="G255" s="3" t="n"/>
     </row>
-    <row r="256">
+    <row r="256" ht="32" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8980,10 +9345,15 @@
         </is>
       </c>
       <c r="E256" s="3" t="n"/>
-      <c r="F256" s="3" t="n"/>
+      <c r="F256" s="6" t="inlineStr">
+        <is>
+          <t>不含reportId — 98.5%
+含reportId — 1.5%</t>
+        </is>
+      </c>
       <c r="G256" s="3" t="n"/>
     </row>
-    <row r="257">
+    <row r="257" ht="16" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9005,10 +9375,14 @@
         </is>
       </c>
       <c r="E257" s="3" t="n"/>
-      <c r="F257" s="3" t="n"/>
+      <c r="F257" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G257" s="3" t="n"/>
     </row>
-    <row r="258">
+    <row r="258" ht="16" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9030,10 +9404,14 @@
         </is>
       </c>
       <c r="E258" s="3" t="n"/>
-      <c r="F258" s="3" t="n"/>
+      <c r="F258" s="6" t="inlineStr">
+        <is>
+          <t>exposure type=[ad-exposed,non-ad-exposed] — 100.0%</t>
+        </is>
+      </c>
       <c r="G258" s="3" t="n"/>
     </row>
-    <row r="259">
+    <row r="259" ht="48" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9055,10 +9433,16 @@
         </is>
       </c>
       <c r="E259" s="3" t="n"/>
-      <c r="F259" s="3" t="n"/>
+      <c r="F259" s="6" t="inlineStr">
+        <is>
+          <t>customerType=Business — 82.4%
+customerType= — 9.6%
+customerType=Non-Business — 7.3%</t>
+        </is>
+      </c>
       <c r="G259" s="3" t="n"/>
     </row>
-    <row r="260">
+    <row r="260" ht="16" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9080,10 +9464,14 @@
         </is>
       </c>
       <c r="E260" s="3" t="n"/>
-      <c r="F260" s="3" t="n"/>
+      <c r="F260" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G260" s="3" t="n"/>
     </row>
-    <row r="261">
+    <row r="261" ht="96" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9105,10 +9493,19 @@
         </is>
       </c>
       <c r="E261" s="3" t="n"/>
-      <c r="F261" s="3" t="n"/>
+      <c r="F261" s="6" t="inlineStr">
+        <is>
+          <t>customerType=Business+groupBy=ASIN — 61.2%
+customerType=+groupBy=AdType — 12.2%
+customerType=+groupBy=ASIN — 10.2%
+customerType=Non-Business+groupBy=ASIN — 6.2%
+customerType=Non-Business+groupBy=AdType — 5.0%
+customerType=Business+groupBy=AdType — 4.4%</t>
+        </is>
+      </c>
       <c r="G261" s="3" t="n"/>
     </row>
-    <row r="262">
+    <row r="262" ht="48" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9130,10 +9527,16 @@
         </is>
       </c>
       <c r="E262" s="3" t="n"/>
-      <c r="F262" s="3" t="n"/>
+      <c r="F262" s="6" t="inlineStr">
+        <is>
+          <t>customerType=Business+含matchTypes — 83.6%
+customerType=+含matchTypes — 12.2%
+customerType=Non-Business+含matchTypes — 3.8%</t>
+        </is>
+      </c>
       <c r="G262" s="3" t="n"/>
     </row>
-    <row r="263">
+    <row r="263" ht="16" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9155,10 +9558,14 @@
         </is>
       </c>
       <c r="E263" s="3" t="n"/>
-      <c r="F263" s="3" t="n"/>
+      <c r="F263" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G263" s="3" t="n"/>
     </row>
-    <row r="264">
+    <row r="264" ht="16" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9180,10 +9587,14 @@
         </is>
       </c>
       <c r="E264" s="3" t="n"/>
-      <c r="F264" s="3" t="n"/>
+      <c r="F264" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G264" s="3" t="n"/>
     </row>
-    <row r="265">
+    <row r="265" ht="16" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9205,10 +9616,14 @@
         </is>
       </c>
       <c r="E265" s="3" t="n"/>
-      <c r="F265" s="3" t="n"/>
+      <c r="F265" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G265" s="3" t="n"/>
     </row>
-    <row r="266">
+    <row r="266" ht="16" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9230,10 +9645,14 @@
         </is>
       </c>
       <c r="E266" s="3" t="n"/>
-      <c r="F266" s="3" t="n"/>
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G266" s="3" t="n"/>
     </row>
-    <row r="267">
+    <row r="267" ht="16" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9255,10 +9674,14 @@
         </is>
       </c>
       <c r="E267" s="3" t="n"/>
-      <c r="F267" s="3" t="n"/>
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G267" s="3" t="n"/>
     </row>
-    <row r="268">
+    <row r="268" ht="64" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9280,10 +9703,17 @@
         </is>
       </c>
       <c r="E268" s="3" t="n"/>
-      <c r="F268" s="3" t="n"/>
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>category=AudienceLabelAnalysis — 37.2%
+category=CLTVOfASIN — 34.9%
+category=CLTVOfCustomerSegments — 14.0%
+category=NTBUserCLTVOfASIN — 14.0%</t>
+        </is>
+      </c>
       <c r="G268" s="3" t="n"/>
     </row>
-    <row r="269">
+    <row r="269" ht="32" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9305,10 +9735,15 @@
         </is>
       </c>
       <c r="E269" s="3" t="n"/>
-      <c r="F269" s="3" t="n"/>
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>marketPlaceId=1 — 88.9%
+marketPlaceId= — 11.1%</t>
+        </is>
+      </c>
       <c r="G269" s="3" t="n"/>
     </row>
-    <row r="270">
+    <row r="270" ht="16" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9330,10 +9765,14 @@
         </is>
       </c>
       <c r="E270" s="3" t="n"/>
-      <c r="F270" s="3" t="n"/>
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>默认调用</t>
+        </is>
+      </c>
       <c r="G270" s="3" t="n"/>
     </row>
-    <row r="271">
+    <row r="271" ht="16" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9355,7 +9794,11 @@
         </is>
       </c>
       <c r="E271" s="3" t="n"/>
-      <c r="F271" s="3" t="n"/>
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G271" s="3" t="n"/>
     </row>
     <row r="272">
@@ -9380,10 +9823,18 @@
         </is>
       </c>
       <c r="E272" s="3" t="n"/>
-      <c r="F272" s="3" t="n"/>
-      <c r="G272" s="3" t="n"/>
-    </row>
-    <row r="273">
+      <c r="F272" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G272" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="32" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9405,10 +9856,15 @@
         </is>
       </c>
       <c r="E273" s="3" t="n"/>
-      <c r="F273" s="3" t="n"/>
+      <c r="F273" s="6" t="inlineStr">
+        <is>
+          <t>marketPlaceId=1 — 88.9%
+不传marketPlaceId — 11.1%</t>
+        </is>
+      </c>
       <c r="G273" s="3" t="n"/>
     </row>
-    <row r="274">
+    <row r="274" ht="16" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9430,10 +9886,14 @@
         </is>
       </c>
       <c r="E274" s="3" t="n"/>
-      <c r="F274" s="3" t="n"/>
+      <c r="F274" s="6" t="inlineStr">
+        <is>
+          <t>marketPlaceId= — 100.0%</t>
+        </is>
+      </c>
       <c r="G274" s="3" t="n"/>
     </row>
-    <row r="275">
+    <row r="275" ht="16" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9455,10 +9915,14 @@
         </is>
       </c>
       <c r="E275" s="3" t="n"/>
-      <c r="F275" s="3" t="n"/>
+      <c r="F275" s="6" t="inlineStr">
+        <is>
+          <t>按InstanceId查询</t>
+        </is>
+      </c>
       <c r="G275" s="3" t="n"/>
     </row>
-    <row r="276">
+    <row r="276" ht="32" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9480,10 +9944,15 @@
         </is>
       </c>
       <c r="E276" s="3" t="n"/>
-      <c r="F276" s="3" t="n"/>
+      <c r="F276" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤 — 61.7%
+无Advertiser过滤 — 38.3%</t>
+        </is>
+      </c>
       <c r="G276" s="3" t="n"/>
     </row>
-    <row r="277">
+    <row r="277" ht="32" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9505,10 +9974,15 @@
         </is>
       </c>
       <c r="E277" s="3" t="n"/>
-      <c r="F277" s="3" t="n"/>
+      <c r="F277" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤 — 52.4%
+无Advertiser过滤 — 47.0%</t>
+        </is>
+      </c>
       <c r="G277" s="3" t="n"/>
     </row>
-    <row r="278">
+    <row r="278" ht="32" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9530,10 +10004,15 @@
         </is>
       </c>
       <c r="E278" s="3" t="n"/>
-      <c r="F278" s="3" t="n"/>
+      <c r="F278" s="6" t="inlineStr">
+        <is>
+          <t>不含reportId — 98.5%
+含reportId — 1.5%</t>
+        </is>
+      </c>
       <c r="G278" s="3" t="n"/>
     </row>
-    <row r="279">
+    <row r="279" ht="16" customHeight="1">
       <c r="A279" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9555,10 +10034,14 @@
         </is>
       </c>
       <c r="E279" s="3" t="n"/>
-      <c r="F279" s="3" t="n"/>
+      <c r="F279" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G279" s="3" t="n"/>
     </row>
-    <row r="280">
+    <row r="280" ht="112" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9580,10 +10063,20 @@
         </is>
       </c>
       <c r="E280" s="3" t="n"/>
-      <c r="F280" s="3" t="n"/>
+      <c r="F280" s="6" t="inlineStr">
+        <is>
+          <t>category=DemoGraphicDevice — 14.3%
+category=DemoGraphicGender — 14.3%
+category=DemoGraphicSystem — 14.3%
+category=DemoGraphicIncome — 14.3%
+category=DemoGraphicRelationship — 14.3%
+category=DemoGraphicEducation — 14.3%
+category=DemoGraphicAge — 14.3%</t>
+        </is>
+      </c>
       <c r="G280" s="3" t="n"/>
     </row>
-    <row r="281">
+    <row r="281" ht="16" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9605,10 +10098,14 @@
         </is>
       </c>
       <c r="E281" s="3" t="n"/>
-      <c r="F281" s="3" t="n"/>
+      <c r="F281" s="6" t="inlineStr">
+        <is>
+          <t>exposure type=[ad-exposed,non-ad-exposed] — 100.0%</t>
+        </is>
+      </c>
       <c r="G281" s="3" t="n"/>
     </row>
-    <row r="282">
+    <row r="282" ht="16" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9630,10 +10127,14 @@
         </is>
       </c>
       <c r="E282" s="3" t="n"/>
-      <c r="F282" s="3" t="n"/>
+      <c r="F282" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G282" s="3" t="n"/>
     </row>
-    <row r="283">
+    <row r="283" ht="16" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9655,10 +10156,14 @@
         </is>
       </c>
       <c r="E283" s="3" t="n"/>
-      <c r="F283" s="3" t="n"/>
+      <c r="F283" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G283" s="3" t="n"/>
     </row>
-    <row r="284">
+    <row r="284" ht="16" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9680,10 +10185,14 @@
         </is>
       </c>
       <c r="E284" s="3" t="n"/>
-      <c r="F284" s="3" t="n"/>
+      <c r="F284" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G284" s="3" t="n"/>
     </row>
-    <row r="285">
+    <row r="285" ht="16" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9705,10 +10214,14 @@
         </is>
       </c>
       <c r="E285" s="3" t="n"/>
-      <c r="F285" s="3" t="n"/>
+      <c r="F285" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G285" s="3" t="n"/>
     </row>
-    <row r="286">
+    <row r="286" ht="16" customHeight="1">
       <c r="A286" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9730,10 +10243,14 @@
         </is>
       </c>
       <c r="E286" s="3" t="n"/>
-      <c r="F286" s="3" t="n"/>
+      <c r="F286" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G286" s="3" t="n"/>
     </row>
-    <row r="287">
+    <row r="287" ht="16" customHeight="1">
       <c r="A287" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9755,10 +10272,14 @@
         </is>
       </c>
       <c r="E287" s="3" t="n"/>
-      <c r="F287" s="3" t="n"/>
+      <c r="F287" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G287" s="3" t="n"/>
     </row>
-    <row r="288">
+    <row r="288" ht="16" customHeight="1">
       <c r="A288" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9780,10 +10301,14 @@
         </is>
       </c>
       <c r="E288" s="3" t="n"/>
-      <c r="F288" s="3" t="n"/>
+      <c r="F288" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G288" s="3" t="n"/>
     </row>
-    <row r="289">
+    <row r="289" ht="16" customHeight="1">
       <c r="A289" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9805,10 +10330,14 @@
         </is>
       </c>
       <c r="E289" s="3" t="n"/>
-      <c r="F289" s="3" t="n"/>
+      <c r="F289" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G289" s="3" t="n"/>
     </row>
-    <row r="290">
+    <row r="290" ht="16" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9830,10 +10359,14 @@
         </is>
       </c>
       <c r="E290" s="3" t="n"/>
-      <c r="F290" s="3" t="n"/>
+      <c r="F290" s="6" t="inlineStr">
+        <is>
+          <t>marketPlaceId= — 100.0%</t>
+        </is>
+      </c>
       <c r="G290" s="3" t="n"/>
     </row>
-    <row r="291">
+    <row r="291" ht="32" customHeight="1">
       <c r="A291" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9855,7 +10388,12 @@
         </is>
       </c>
       <c r="E291" s="3" t="n"/>
-      <c r="F291" s="3" t="n"/>
+      <c r="F291" s="6" t="inlineStr">
+        <is>
+          <t>holiday=Christmas+marketPlaceId=1 — 88.9%
+holiday=Christmas+不传marketPlaceId — 11.1%</t>
+        </is>
+      </c>
       <c r="G291" s="3" t="n"/>
     </row>
     <row r="292">
@@ -9880,10 +10418,18 @@
         </is>
       </c>
       <c r="E292" s="3" t="n"/>
-      <c r="F292" s="3" t="n"/>
-      <c r="G292" s="3" t="n"/>
-    </row>
-    <row r="293">
+      <c r="F292" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G292" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="16" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9905,10 +10451,14 @@
         </is>
       </c>
       <c r="E293" s="3" t="n"/>
-      <c r="F293" s="3" t="n"/>
+      <c r="F293" s="6" t="inlineStr">
+        <is>
+          <t>含pathFilters — 100.0%</t>
+        </is>
+      </c>
       <c r="G293" s="3" t="n"/>
     </row>
-    <row r="294">
+    <row r="294" ht="80" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9930,7 +10480,15 @@
         </is>
       </c>
       <c r="E294" s="3" t="n"/>
-      <c r="F294" s="3" t="n"/>
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>adTypes=[All] — 84.5%
+adTypes=[DSP] — 6.8%
+adTypes=[SP] — 6.1%
+adTypes=[SD] — 1.4%
+adTypes=[SB] — 1.4%</t>
+        </is>
+      </c>
       <c r="G294" s="3" t="n"/>
     </row>
     <row r="295">
@@ -9955,10 +10513,18 @@
         </is>
       </c>
       <c r="E295" s="3" t="n"/>
-      <c r="F295" s="3" t="n"/>
-      <c r="G295" s="3" t="n"/>
-    </row>
-    <row r="296">
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="16" customHeight="1">
       <c r="A296" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -9980,10 +10546,14 @@
         </is>
       </c>
       <c r="E296" s="3" t="n"/>
-      <c r="F296" s="3" t="n"/>
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G296" s="3" t="n"/>
     </row>
-    <row r="297">
+    <row r="297" ht="16" customHeight="1">
       <c r="A297" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10005,10 +10575,14 @@
         </is>
       </c>
       <c r="E297" s="3" t="n"/>
-      <c r="F297" s="3" t="n"/>
+      <c r="F297" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G297" s="3" t="n"/>
     </row>
-    <row r="298">
+    <row r="298" ht="16" customHeight="1">
       <c r="A298" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10030,7 +10604,11 @@
         </is>
       </c>
       <c r="E298" s="3" t="n"/>
-      <c r="F298" s="3" t="n"/>
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G298" s="3" t="n"/>
     </row>
     <row r="299">
@@ -10055,10 +10633,18 @@
         </is>
       </c>
       <c r="E299" s="3" t="n"/>
-      <c r="F299" s="3" t="n"/>
-      <c r="G299" s="3" t="n"/>
-    </row>
-    <row r="300">
+      <c r="F299" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G299" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="16" customHeight="1">
       <c r="A300" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10080,10 +10666,14 @@
         </is>
       </c>
       <c r="E300" s="3" t="n"/>
-      <c r="F300" s="3" t="n"/>
+      <c r="F300" s="6" t="inlineStr">
+        <is>
+          <t>按instanceId查询</t>
+        </is>
+      </c>
       <c r="G300" s="3" t="n"/>
     </row>
-    <row r="301">
+    <row r="301" ht="16" customHeight="1">
       <c r="A301" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10105,10 +10695,14 @@
         </is>
       </c>
       <c r="E301" s="3" t="n"/>
-      <c r="F301" s="3" t="n"/>
+      <c r="F301" s="6" t="inlineStr">
+        <is>
+          <t>不传marketPlaceId — 100.0%</t>
+        </is>
+      </c>
       <c r="G301" s="3" t="n"/>
     </row>
-    <row r="302">
+    <row r="302" ht="16" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10130,10 +10724,14 @@
         </is>
       </c>
       <c r="E302" s="3" t="n"/>
-      <c r="F302" s="3" t="n"/>
+      <c r="F302" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G302" s="3" t="n"/>
     </row>
-    <row r="303">
+    <row r="303" ht="16" customHeight="1">
       <c r="A303" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10155,10 +10753,14 @@
         </is>
       </c>
       <c r="E303" s="3" t="n"/>
-      <c r="F303" s="3" t="n"/>
+      <c r="F303" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G303" s="3" t="n"/>
     </row>
-    <row r="304">
+    <row r="304" ht="16" customHeight="1">
       <c r="A304" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10180,10 +10782,14 @@
         </is>
       </c>
       <c r="E304" s="3" t="n"/>
-      <c r="F304" s="3" t="n"/>
+      <c r="F304" s="6" t="inlineStr">
+        <is>
+          <t>按reportId查询</t>
+        </is>
+      </c>
       <c r="G304" s="3" t="n"/>
     </row>
-    <row r="305">
+    <row r="305" ht="16" customHeight="1">
       <c r="A305" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10205,10 +10811,14 @@
         </is>
       </c>
       <c r="E305" s="3" t="n"/>
-      <c r="F305" s="3" t="n"/>
+      <c r="F305" s="6" t="inlineStr">
+        <is>
+          <t>按reportId查询</t>
+        </is>
+      </c>
       <c r="G305" s="3" t="n"/>
     </row>
-    <row r="306">
+    <row r="306" ht="32" customHeight="1">
       <c r="A306" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10230,10 +10840,15 @@
         </is>
       </c>
       <c r="E306" s="3" t="n"/>
-      <c r="F306" s="3" t="n"/>
+      <c r="F306" s="6" t="inlineStr">
+        <is>
+          <t>category=All+不含reportId — 98.5%
+category=All+含reportId — 1.5%</t>
+        </is>
+      </c>
       <c r="G306" s="3" t="n"/>
     </row>
-    <row r="307">
+    <row r="307" ht="48" customHeight="1">
       <c r="A307" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10255,10 +10870,16 @@
         </is>
       </c>
       <c r="E307" s="3" t="n"/>
-      <c r="F307" s="3" t="n"/>
+      <c r="F307" s="6" t="inlineStr">
+        <is>
+          <t>不含reportId+category=All — 95.5%
+不含reportId+category=SP — 3.0%
+含reportId+category=All — 1.5%</t>
+        </is>
+      </c>
       <c r="G307" s="3" t="n"/>
     </row>
-    <row r="308">
+    <row r="308" ht="16" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10280,10 +10901,14 @@
         </is>
       </c>
       <c r="E308" s="3" t="n"/>
-      <c r="F308" s="3" t="n"/>
+      <c r="F308" s="6" t="inlineStr">
+        <is>
+          <t>按historyId查询</t>
+        </is>
+      </c>
       <c r="G308" s="3" t="n"/>
     </row>
-    <row r="309">
+    <row r="309" ht="16" customHeight="1">
       <c r="A309" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10305,10 +10930,14 @@
         </is>
       </c>
       <c r="E309" s="3" t="n"/>
-      <c r="F309" s="3" t="n"/>
+      <c r="F309" s="6" t="inlineStr">
+        <is>
+          <t>按historyId查询</t>
+        </is>
+      </c>
       <c r="G309" s="3" t="n"/>
     </row>
-    <row r="310">
+    <row r="310" ht="32" customHeight="1">
       <c r="A310" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10330,10 +10959,15 @@
         </is>
       </c>
       <c r="E310" s="3" t="n"/>
-      <c r="F310" s="3" t="n"/>
+      <c r="F310" s="6" t="inlineStr">
+        <is>
+          <t>含reportType — 75.6%
+不含reportType — 24.4%</t>
+        </is>
+      </c>
       <c r="G310" s="3" t="n"/>
     </row>
-    <row r="311">
+    <row r="311" ht="16" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10355,10 +10989,14 @@
         </is>
       </c>
       <c r="E311" s="3" t="n"/>
-      <c r="F311" s="3" t="n"/>
+      <c r="F311" s="6" t="inlineStr">
+        <is>
+          <t>按historyId查询</t>
+        </is>
+      </c>
       <c r="G311" s="3" t="n"/>
     </row>
-    <row r="312">
+    <row r="312" ht="16" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10380,10 +11018,14 @@
         </is>
       </c>
       <c r="E312" s="3" t="n"/>
-      <c r="F312" s="3" t="n"/>
+      <c r="F312" s="6" t="inlineStr">
+        <is>
+          <t>按historyId查询</t>
+        </is>
+      </c>
       <c r="G312" s="3" t="n"/>
     </row>
-    <row r="313">
+    <row r="313" ht="32" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10405,10 +11047,15 @@
         </is>
       </c>
       <c r="E313" s="3" t="n"/>
-      <c r="F313" s="3" t="n"/>
+      <c r="F313" s="6" t="inlineStr">
+        <is>
+          <t>按historyId+tabType(on amazon)查询
+按historyId+tabType(off amazon)查询</t>
+        </is>
+      </c>
       <c r="G313" s="3" t="n"/>
     </row>
-    <row r="314">
+    <row r="314" ht="32" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10430,10 +11077,15 @@
         </is>
       </c>
       <c r="E314" s="3" t="n"/>
-      <c r="F314" s="3" t="n"/>
+      <c r="F314" s="6" t="inlineStr">
+        <is>
+          <t>按historyId+tabType(on amazon users)查询
+按historyId+tabType(off amazon users)查询</t>
+        </is>
+      </c>
       <c r="G314" s="3" t="n"/>
     </row>
-    <row r="315">
+    <row r="315" ht="16" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10455,10 +11107,14 @@
         </is>
       </c>
       <c r="E315" s="3" t="n"/>
-      <c r="F315" s="3" t="n"/>
+      <c r="F315" s="6" t="inlineStr">
+        <is>
+          <t>按historyId查询</t>
+        </is>
+      </c>
       <c r="G315" s="3" t="n"/>
     </row>
-    <row r="316">
+    <row r="316" ht="32" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10480,10 +11136,15 @@
         </is>
       </c>
       <c r="E316" s="3" t="n"/>
-      <c r="F316" s="3" t="n"/>
+      <c r="F316" s="6" t="inlineStr">
+        <is>
+          <t>不含reportId — 98.5%
+含reportId — 1.5%</t>
+        </is>
+      </c>
       <c r="G316" s="3" t="n"/>
     </row>
-    <row r="317">
+    <row r="317" ht="32" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10505,10 +11166,15 @@
         </is>
       </c>
       <c r="E317" s="3" t="n"/>
-      <c r="F317" s="3" t="n"/>
+      <c r="F317" s="6" t="inlineStr">
+        <is>
+          <t>marketPlaceId=1 — 88.9%
+不传marketPlaceId — 11.1%</t>
+        </is>
+      </c>
       <c r="G317" s="3" t="n"/>
     </row>
-    <row r="318">
+    <row r="318" ht="16" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10530,10 +11196,14 @@
         </is>
       </c>
       <c r="E318" s="3" t="n"/>
-      <c r="F318" s="3" t="n"/>
+      <c r="F318" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G318" s="3" t="n"/>
     </row>
-    <row r="319">
+    <row r="319" ht="16" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10555,10 +11225,14 @@
         </is>
       </c>
       <c r="E319" s="3" t="n"/>
-      <c r="F319" s="3" t="n"/>
+      <c r="F319" s="6" t="inlineStr">
+        <is>
+          <t>groupBy=Weekly+exposure type=[ad-exposed,non-ad-exposed] — 100.0%</t>
+        </is>
+      </c>
       <c r="G319" s="3" t="n"/>
     </row>
-    <row r="320">
+    <row r="320" ht="32" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10580,10 +11254,15 @@
         </is>
       </c>
       <c r="E320" s="3" t="n"/>
-      <c r="F320" s="3" t="n"/>
+      <c r="F320" s="6" t="inlineStr">
+        <is>
+          <t>不含reportId+category=All — 98.5%
+含reportId+category=All — 1.5%</t>
+        </is>
+      </c>
       <c r="G320" s="3" t="n"/>
     </row>
-    <row r="321">
+    <row r="321" ht="16" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10605,10 +11284,14 @@
         </is>
       </c>
       <c r="E321" s="3" t="n"/>
-      <c r="F321" s="3" t="n"/>
+      <c r="F321" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G321" s="3" t="n"/>
     </row>
-    <row r="322">
+    <row r="322" ht="16" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10630,10 +11313,14 @@
         </is>
       </c>
       <c r="E322" s="3" t="n"/>
-      <c r="F322" s="3" t="n"/>
+      <c r="F322" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G322" s="3" t="n"/>
     </row>
-    <row r="323">
+    <row r="323" ht="16" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10655,10 +11342,14 @@
         </is>
       </c>
       <c r="E323" s="3" t="n"/>
-      <c r="F323" s="3" t="n"/>
+      <c r="F323" s="6" t="inlineStr">
+        <is>
+          <t>按historyId查询</t>
+        </is>
+      </c>
       <c r="G323" s="3" t="n"/>
     </row>
-    <row r="324">
+    <row r="324" ht="16" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10680,10 +11371,14 @@
         </is>
       </c>
       <c r="E324" s="3" t="n"/>
-      <c r="F324" s="3" t="n"/>
+      <c r="F324" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G324" s="3" t="n"/>
     </row>
-    <row r="325">
+    <row r="325" ht="32" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10705,10 +11400,15 @@
         </is>
       </c>
       <c r="E325" s="3" t="n"/>
-      <c r="F325" s="3" t="n"/>
+      <c r="F325" s="6" t="inlineStr">
+        <is>
+          <t>category=AMS+含profileIds+不含advertiserIds — 51.6%
+category=DSP+不含profileIds+含advertiserIds — 48.4%</t>
+        </is>
+      </c>
       <c r="G325" s="3" t="n"/>
     </row>
-    <row r="326">
+    <row r="326" ht="32" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10730,10 +11430,15 @@
         </is>
       </c>
       <c r="E326" s="3" t="n"/>
-      <c r="F326" s="3" t="n"/>
+      <c r="F326" s="6" t="inlineStr">
+        <is>
+          <t>category=AMS+含profileIds+不含advertiserIds — 52.4%
+category=DSP+不含profileIds+含advertiserIds — 47.6%</t>
+        </is>
+      </c>
       <c r="G326" s="3" t="n"/>
     </row>
-    <row r="327">
+    <row r="327" ht="32" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10755,10 +11460,15 @@
         </is>
       </c>
       <c r="E327" s="3" t="n"/>
-      <c r="F327" s="3" t="n"/>
+      <c r="F327" s="6" t="inlineStr">
+        <is>
+          <t>marketPlaceId=1 — 88.9%
+marketPlaceId= — 11.1%</t>
+        </is>
+      </c>
       <c r="G327" s="3" t="n"/>
     </row>
-    <row r="328">
+    <row r="328" ht="16" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10780,7 +11490,11 @@
         </is>
       </c>
       <c r="E328" s="3" t="n"/>
-      <c r="F328" s="3" t="n"/>
+      <c r="F328" s="6" t="inlineStr">
+        <is>
+          <t>exposure type=[ad-exposed,non-ad-exposed]+groupBy=Monthly — 100.0%</t>
+        </is>
+      </c>
       <c r="G328" s="3" t="n"/>
     </row>
     <row r="329">
@@ -10805,8 +11519,16 @@
         </is>
       </c>
       <c r="E329" s="3" t="n"/>
-      <c r="F329" s="3" t="n"/>
-      <c r="G329" s="3" t="n"/>
+      <c r="F329" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G329" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -10830,8 +11552,16 @@
         </is>
       </c>
       <c r="E330" s="3" t="n"/>
-      <c r="F330" s="3" t="n"/>
-      <c r="G330" s="3" t="n"/>
+      <c r="F330" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G330" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -10855,10 +11585,18 @@
         </is>
       </c>
       <c r="E331" s="3" t="n"/>
-      <c r="F331" s="3" t="n"/>
-      <c r="G331" s="3" t="n"/>
-    </row>
-    <row r="332">
+      <c r="F331" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G331" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="32" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10880,10 +11618,15 @@
         </is>
       </c>
       <c r="E332" s="3" t="n"/>
-      <c r="F332" s="3" t="n"/>
+      <c r="F332" s="6" t="inlineStr">
+        <is>
+          <t>不含reportId+category=Path Occurrences — 98.5%
+含reportId+category=Path Occurrences — 1.5%</t>
+        </is>
+      </c>
       <c r="G332" s="3" t="n"/>
     </row>
-    <row r="333">
+    <row r="333" ht="16" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10905,10 +11648,14 @@
         </is>
       </c>
       <c r="E333" s="3" t="n"/>
-      <c r="F333" s="3" t="n"/>
+      <c r="F333" s="6" t="inlineStr">
+        <is>
+          <t>按historyId查询</t>
+        </is>
+      </c>
       <c r="G333" s="3" t="n"/>
     </row>
-    <row r="334">
+    <row r="334" ht="16" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10930,7 +11677,11 @@
         </is>
       </c>
       <c r="E334" s="3" t="n"/>
-      <c r="F334" s="3" t="n"/>
+      <c r="F334" s="6" t="inlineStr">
+        <is>
+          <t>exposure type=[ad-exposed,non-ad-exposed] — 100.0%</t>
+        </is>
+      </c>
       <c r="G334" s="3" t="n"/>
     </row>
     <row r="335">
@@ -10955,10 +11706,18 @@
         </is>
       </c>
       <c r="E335" s="3" t="n"/>
-      <c r="F335" s="3" t="n"/>
-      <c r="G335" s="3" t="n"/>
-    </row>
-    <row r="336">
+      <c r="F335" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G335" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="16" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -10980,10 +11739,14 @@
         </is>
       </c>
       <c r="E336" s="3" t="n"/>
-      <c r="F336" s="3" t="n"/>
+      <c r="F336" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G336" s="3" t="n"/>
     </row>
-    <row r="337">
+    <row r="337" ht="16" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11005,10 +11768,14 @@
         </is>
       </c>
       <c r="E337" s="3" t="n"/>
-      <c r="F337" s="3" t="n"/>
+      <c r="F337" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G337" s="3" t="n"/>
     </row>
-    <row r="338">
+    <row r="338" ht="32" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11030,10 +11797,15 @@
         </is>
       </c>
       <c r="E338" s="3" t="n"/>
-      <c r="F338" s="3" t="n"/>
+      <c r="F338" s="6" t="inlineStr">
+        <is>
+          <t>按HistoryId+isOneClick查询
+仅按HistoryId查询(不含isOneClick)</t>
+        </is>
+      </c>
       <c r="G338" s="3" t="n"/>
     </row>
-    <row r="339">
+    <row r="339" ht="16" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11055,10 +11827,14 @@
         </is>
       </c>
       <c r="E339" s="3" t="n"/>
-      <c r="F339" s="3" t="n"/>
+      <c r="F339" s="6" t="inlineStr">
+        <is>
+          <t>按id查询</t>
+        </is>
+      </c>
       <c r="G339" s="3" t="n"/>
     </row>
-    <row r="340">
+    <row r="340" ht="32" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11080,10 +11856,15 @@
         </is>
       </c>
       <c r="E340" s="3" t="n"/>
-      <c r="F340" s="3" t="n"/>
+      <c r="F340" s="6" t="inlineStr">
+        <is>
+          <t>不含reportId — 95.8%
+含reportId — 4.2%</t>
+        </is>
+      </c>
       <c r="G340" s="3" t="n"/>
     </row>
-    <row r="341">
+    <row r="341" ht="48" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11105,10 +11886,16 @@
         </is>
       </c>
       <c r="E341" s="3" t="n"/>
-      <c r="F341" s="3" t="n"/>
+      <c r="F341" s="6" t="inlineStr">
+        <is>
+          <t>按&lt;MISSING&gt;排序+含status — 80.6%
+按LastRunTimeUTC排序+不含status — 11.2%
+按CreateTimeUTC排序+不含status — 8.2%</t>
+        </is>
+      </c>
       <c r="G341" s="3" t="n"/>
     </row>
-    <row r="342">
+    <row r="342" ht="16" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11130,10 +11917,14 @@
         </is>
       </c>
       <c r="E342" s="3" t="n"/>
-      <c r="F342" s="3" t="n"/>
+      <c r="F342" s="6" t="inlineStr">
+        <is>
+          <t>含instanceIds+含reportIds — 100.0%</t>
+        </is>
+      </c>
       <c r="G342" s="3" t="n"/>
     </row>
-    <row r="343">
+    <row r="343" ht="16" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11155,7 +11946,11 @@
         </is>
       </c>
       <c r="E343" s="3" t="n"/>
-      <c r="F343" s="3" t="n"/>
+      <c r="F343" s="6" t="inlineStr">
+        <is>
+          <t>含instanceIds — 100.0%</t>
+        </is>
+      </c>
       <c r="G343" s="3" t="n"/>
     </row>
     <row r="344">
@@ -11181,7 +11976,11 @@
       </c>
       <c r="E344" s="3" t="n"/>
       <c r="F344" s="3" t="n"/>
-      <c r="G344" s="3" t="n"/>
+      <c r="G344" s="5" t="inlineStr">
+        <is>
+          <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -11206,7 +12005,11 @@
       </c>
       <c r="E345" s="3" t="n"/>
       <c r="F345" s="3" t="n"/>
-      <c r="G345" s="3" t="n"/>
+      <c r="G345" s="5" t="inlineStr">
+        <is>
+          <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -11230,8 +12033,16 @@
         </is>
       </c>
       <c r="E346" s="3" t="n"/>
-      <c r="F346" s="3" t="n"/>
-      <c r="G346" s="3" t="n"/>
+      <c r="F346" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G346" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -11256,9 +12067,13 @@
       </c>
       <c r="E347" s="3" t="n"/>
       <c r="F347" s="3" t="n"/>
-      <c r="G347" s="3" t="n"/>
-    </row>
-    <row r="348">
+      <c r="G347" s="5" t="inlineStr">
+        <is>
+          <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="64" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -11280,7 +12095,14 @@
         </is>
       </c>
       <c r="E348" s="3" t="n"/>
-      <c r="F348" s="3" t="n"/>
+      <c r="F348" s="6" t="inlineStr">
+        <is>
+          <t>conversionMetric=Total+含dspAdvertisers — 33.3%
+conversionMetric=Total+不含dspAdvertisers — 33.3%
+不传conversionMetric+含dspAdvertisers — 18.5%
+conversionMetric=Promoted+含dspAdvertisers — 14.8%</t>
+        </is>
+      </c>
       <c r="G348" s="3" t="n"/>
     </row>
     <row r="349">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1332,9 +1332,19 @@
       </c>
       <c r="D36" s="3" t="n"/>
       <c r="E36" s="3" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
+      <c r="F36" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>86% (36/42)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -23947,7 +23957,7 @@
       <c r="F788" s="3" t="n"/>
       <c r="G788" s="3" t="n"/>
     </row>
-    <row r="789">
+    <row r="789" ht="64" customHeight="1">
       <c r="A789" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -23969,10 +23979,17 @@
         </is>
       </c>
       <c r="E789" s="3" t="n"/>
-      <c r="F789" s="3" t="n"/>
+      <c r="F789" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不含CompareStart — 41.8%
+按Advertiser过滤+含CompareStart — 27.6%
+无Advertiser过滤+不含CompareStart — 16.8%
+无Advertiser过滤+含CompareStart — 13.8%</t>
+        </is>
+      </c>
       <c r="G789" s="3" t="n"/>
     </row>
-    <row r="790">
+    <row r="790" ht="64" customHeight="1">
       <c r="A790" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -23994,10 +24011,17 @@
         </is>
       </c>
       <c r="E790" s="3" t="n"/>
-      <c r="F790" s="3" t="n"/>
+      <c r="F790" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不含CompareStart — 39.0%
+按Advertiser过滤+含CompareStart — 27.0%
+无Advertiser过滤+不含CompareStart — 18.2%
+无Advertiser过滤+含CompareStart — 15.8%</t>
+        </is>
+      </c>
       <c r="G790" s="3" t="n"/>
     </row>
-    <row r="791">
+    <row r="791" ht="16" customHeight="1">
       <c r="A791" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24019,10 +24043,14 @@
         </is>
       </c>
       <c r="E791" s="3" t="n"/>
-      <c r="F791" s="3" t="n"/>
+      <c r="F791" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G791" s="3" t="n"/>
     </row>
-    <row r="792">
+    <row r="792" ht="96" customHeight="1">
       <c r="A792" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24044,10 +24072,19 @@
         </is>
       </c>
       <c r="E792" s="3" t="n"/>
-      <c r="F792" s="3" t="n"/>
+      <c r="F792" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+无OrderTag过滤 — 37.8%
+按Advertiser过滤+按Order过滤+无OrderTag过滤 — 19.8%
+无Advertiser过滤+无Order过滤+无OrderTag过滤 — 16.4%
+无Advertiser过滤+无Order过滤+按OrderTag过滤 — 11.8%
+按Advertiser过滤+无Order过滤+按OrderTag过滤 — 7.2%
+无Advertiser过滤+按Order过滤+无OrderTag过滤 — 6.4%</t>
+        </is>
+      </c>
       <c r="G792" s="3" t="n"/>
     </row>
-    <row r="793">
+    <row r="793" ht="96" customHeight="1">
       <c r="A793" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24069,10 +24106,19 @@
         </is>
       </c>
       <c r="E793" s="3" t="n"/>
-      <c r="F793" s="3" t="n"/>
+      <c r="F793" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+无OrderTag过滤 — 32.8%
+按Advertiser过滤+按Order过滤+无OrderTag过滤 — 21.6%
+无Advertiser过滤+无Order过滤+无OrderTag过滤 — 18.6%
+无Advertiser过滤+无Order过滤+按OrderTag过滤 — 10.4%
+按Advertiser过滤+无Order过滤+按OrderTag过滤 — 8.6%
+无Advertiser过滤+按Order过滤+无OrderTag过滤 — 7.0%</t>
+        </is>
+      </c>
       <c r="G793" s="3" t="n"/>
     </row>
-    <row r="794">
+    <row r="794" ht="16" customHeight="1">
       <c r="A794" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24094,10 +24140,14 @@
         </is>
       </c>
       <c r="E794" s="3" t="n"/>
-      <c r="F794" s="3" t="n"/>
+      <c r="F794" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G794" s="3" t="n"/>
     </row>
-    <row r="795">
+    <row r="795" ht="16" customHeight="1">
       <c r="A795" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24119,10 +24169,14 @@
         </is>
       </c>
       <c r="E795" s="3" t="n"/>
-      <c r="F795" s="3" t="n"/>
+      <c r="F795" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G795" s="3" t="n"/>
     </row>
-    <row r="796">
+    <row r="796" ht="16" customHeight="1">
       <c r="A796" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24144,10 +24198,14 @@
         </is>
       </c>
       <c r="E796" s="3" t="n"/>
-      <c r="F796" s="3" t="n"/>
+      <c r="F796" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G796" s="3" t="n"/>
     </row>
-    <row r="797">
+    <row r="797" ht="112" customHeight="1">
       <c r="A797" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24169,10 +24227,20 @@
         </is>
       </c>
       <c r="E797" s="3" t="n"/>
-      <c r="F797" s="3" t="n"/>
+      <c r="F797" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+CreativeIds=[]+无Order过滤 — 39.6%
+无Advertiser过滤+CreativeIds=[]+无Order过滤 — 29.0%
+按Advertiser过滤+CreativeIds=[]+按Order过滤 — 14.6%
+按Advertiser过滤+CreativeIds=[ids+]+无Order过滤 — 6.4%
+无Advertiser过滤+CreativeIds=[]+按Order过滤 — 4.8%
+按Advertiser过滤+CreativeIds=[ids+]+按Order过滤 — 2.6%
+无Advertiser过滤+CreativeIds=[ids+]+无Order过滤 — 1.8%</t>
+        </is>
+      </c>
       <c r="G797" s="3" t="n"/>
     </row>
-    <row r="798">
+    <row r="798" ht="48" customHeight="1">
       <c r="A798" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24194,10 +24262,16 @@
         </is>
       </c>
       <c r="E798" s="3" t="n"/>
-      <c r="F798" s="3" t="n"/>
+      <c r="F798" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤 — 61.3%
+按Advertiser过滤 — 35.5%
+不传advertiserIds — 3.2%</t>
+        </is>
+      </c>
       <c r="G798" s="3" t="n"/>
     </row>
-    <row r="799">
+    <row r="799" ht="48" customHeight="1">
       <c r="A799" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24219,10 +24293,16 @@
         </is>
       </c>
       <c r="E799" s="3" t="n"/>
-      <c r="F799" s="3" t="n"/>
+      <c r="F799" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+CreativeIds=[] — 61.3%
+按Advertiser过滤+CreativeIds=[] — 35.5%
+不传AdvertiserIds+不传CreativeIds — 3.2%</t>
+        </is>
+      </c>
       <c r="G799" s="3" t="n"/>
     </row>
-    <row r="800">
+    <row r="800" ht="128" customHeight="1">
       <c r="A800" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24244,7 +24324,18 @@
         </is>
       </c>
       <c r="E800" s="3" t="n"/>
-      <c r="F800" s="3" t="n"/>
+      <c r="F800" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+CreativeIds=[]+无Order过滤 — 43.8%
+无Advertiser过滤+CreativeIds=[]+无Order过滤 — 27.2%
+按Advertiser过滤+CreativeIds=[]+按Order过滤 — 15.4%
+按Advertiser过滤+CreativeIds=[ids+]+无Order过滤 — 5.0%
+按Advertiser过滤+CreativeIds=[ids+]+按Order过滤 — 2.6%
+无Advertiser过滤+CreativeIds=[]+按Order过滤 — 2.4%
+无Advertiser过滤+CreativeIds=[ids+]+无Order过滤 — 2.0%
+无Advertiser过滤+CreativeIds=[ids+]+按Order过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G800" s="3" t="n"/>
     </row>
     <row r="801">
@@ -24269,10 +24360,18 @@
         </is>
       </c>
       <c r="E801" s="3" t="n"/>
-      <c r="F801" s="3" t="n"/>
-      <c r="G801" s="3" t="n"/>
-    </row>
-    <row r="802">
+      <c r="F801" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G801" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="802" ht="16" customHeight="1">
       <c r="A802" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24294,10 +24393,14 @@
         </is>
       </c>
       <c r="E802" s="3" t="n"/>
-      <c r="F802" s="3" t="n"/>
+      <c r="F802" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G802" s="3" t="n"/>
     </row>
-    <row r="803">
+    <row r="803" ht="64" customHeight="1">
       <c r="A803" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24319,10 +24422,17 @@
         </is>
       </c>
       <c r="E803" s="3" t="n"/>
-      <c r="F803" s="3" t="n"/>
+      <c r="F803" s="6" t="inlineStr">
+        <is>
+          <t>CreativeTagIds=[ids+]+按Advertiser过滤 — 37.8%
+CreativeTagIds=[ids+]+无Advertiser过滤 — 32.4%
+CreativeTagIds=[]+无Advertiser过滤 — 27.0%
+CreativeTagIds=[]+按Advertiser过滤 — 2.7%</t>
+        </is>
+      </c>
       <c r="G803" s="3" t="n"/>
     </row>
-    <row r="804">
+    <row r="804" ht="64" customHeight="1">
       <c r="A804" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24344,10 +24454,17 @@
         </is>
       </c>
       <c r="E804" s="3" t="n"/>
-      <c r="F804" s="3" t="n"/>
+      <c r="F804" s="6" t="inlineStr">
+        <is>
+          <t>CreativeTagIds=[ids+]+按Advertiser过滤 — 55.6%
+CreativeTagIds=[]+按Advertiser过滤 — 18.1%
+CreativeTagIds=[ids+]+无Advertiser过滤 — 16.7%
+CreativeTagIds=[]+无Advertiser过滤 — 9.7%</t>
+        </is>
+      </c>
       <c r="G804" s="3" t="n"/>
     </row>
-    <row r="805">
+    <row r="805" ht="64" customHeight="1">
       <c r="A805" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24369,10 +24486,17 @@
         </is>
       </c>
       <c r="E805" s="3" t="n"/>
-      <c r="F805" s="3" t="n"/>
+      <c r="F805" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无Order过滤+含CompareStart — 45.8%
+按Advertiser过滤+无Order过滤+含CompareStart — 25.0%
+无Advertiser过滤+无Order过滤+不含CompareStart — 16.7%
+按Advertiser过滤+按Order过滤+含CompareStart — 12.5%</t>
+        </is>
+      </c>
       <c r="G805" s="3" t="n"/>
     </row>
-    <row r="806">
+    <row r="806" ht="64" customHeight="1">
       <c r="A806" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24394,10 +24518,17 @@
         </is>
       </c>
       <c r="E806" s="3" t="n"/>
-      <c r="F806" s="3" t="n"/>
+      <c r="F806" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无Order过滤+含CompareStart — 48.0%
+按Advertiser过滤+无Order过滤+含CompareStart — 24.0%
+无Advertiser过滤+无Order过滤+不含CompareStart — 16.0%
+按Advertiser过滤+按Order过滤+含CompareStart — 12.0%</t>
+        </is>
+      </c>
       <c r="G806" s="3" t="n"/>
     </row>
-    <row r="807">
+    <row r="807" ht="48" customHeight="1">
       <c r="A807" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24419,10 +24550,16 @@
         </is>
       </c>
       <c r="E807" s="3" t="n"/>
-      <c r="F807" s="3" t="n"/>
+      <c r="F807" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不传OrderIds — 60.4%
+按Advertiser过滤+按Order过滤 — 34.0%
+无Advertiser过滤+不传OrderIds — 5.7%</t>
+        </is>
+      </c>
       <c r="G807" s="3" t="n"/>
     </row>
-    <row r="808">
+    <row r="808" ht="48" customHeight="1">
       <c r="A808" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24444,10 +24581,16 @@
         </is>
       </c>
       <c r="E808" s="3" t="n"/>
-      <c r="F808" s="3" t="n"/>
+      <c r="F808" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+不传OrderIds — 60.4%
+按Advertiser过滤+按Order过滤 — 34.0%
+无Advertiser过滤+不传OrderIds — 5.7%</t>
+        </is>
+      </c>
       <c r="G808" s="3" t="n"/>
     </row>
-    <row r="809">
+    <row r="809" ht="112" customHeight="1">
       <c r="A809" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24469,10 +24612,20 @@
         </is>
       </c>
       <c r="E809" s="3" t="n"/>
-      <c r="F809" s="3" t="n"/>
+      <c r="F809" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+含CompareStart — 35.4%
+无Advertiser过滤+无Order过滤+含CompareStart — 29.4%
+无Advertiser过滤+按Order过滤+含CompareStart — 12.8%
+按Advertiser过滤+按Order过滤+含CompareStart — 8.4%
+无Advertiser过滤+无Order过滤+不含CompareStart — 6.6%
+按Advertiser过滤+无Order过滤+不含CompareStart — 5.2%
+无Advertiser过滤+按Order过滤+不含CompareStart — 1.2%</t>
+        </is>
+      </c>
       <c r="G809" s="3" t="n"/>
     </row>
-    <row r="810">
+    <row r="810" ht="128" customHeight="1">
       <c r="A810" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24494,7 +24647,18 @@
         </is>
       </c>
       <c r="E810" s="3" t="n"/>
-      <c r="F810" s="3" t="n"/>
+      <c r="F810" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+含CompareStart — 35.4%
+无Advertiser过滤+无Order过滤+含CompareStart — 30.8%
+无Advertiser过滤+按Order过滤+含CompareStart — 13.8%
+无Advertiser过滤+无Order过滤+不含CompareStart — 6.4%
+按Advertiser过滤+按Order过滤+含CompareStart — 5.6%
+按Advertiser过滤+无Order过滤+不含CompareStart — 5.4%
+按Advertiser过滤+按Order过滤+不含CompareStart — 1.2%
+无Advertiser过滤+按Order过滤+不含CompareStart — 1.0%</t>
+        </is>
+      </c>
       <c r="G810" s="3" t="n"/>
     </row>
     <row r="811">
@@ -24519,10 +24683,18 @@
         </is>
       </c>
       <c r="E811" s="3" t="n"/>
-      <c r="F811" s="3" t="n"/>
-      <c r="G811" s="3" t="n"/>
-    </row>
-    <row r="812">
+      <c r="F811" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G811" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="812" ht="16" customHeight="1">
       <c r="A812" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24544,10 +24716,14 @@
         </is>
       </c>
       <c r="E812" s="3" t="n"/>
-      <c r="F812" s="3" t="n"/>
+      <c r="F812" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G812" s="3" t="n"/>
     </row>
-    <row r="813">
+    <row r="813" ht="64" customHeight="1">
       <c r="A813" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24569,10 +24745,17 @@
         </is>
       </c>
       <c r="E813" s="3" t="n"/>
-      <c r="F813" s="3" t="n"/>
+      <c r="F813" s="6" t="inlineStr">
+        <is>
+          <t>按LineItemTag过滤+按Advertiser过滤 — 54.7%
+按LineItemTag过滤+无Advertiser过滤 — 20.9%
+无LineItemTag过滤+按Advertiser过滤 — 16.2%
+无LineItemTag过滤+无Advertiser过滤 — 7.4%</t>
+        </is>
+      </c>
       <c r="G813" s="3" t="n"/>
     </row>
-    <row r="814">
+    <row r="814" ht="64" customHeight="1">
       <c r="A814" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24594,7 +24777,14 @@
         </is>
       </c>
       <c r="E814" s="3" t="n"/>
-      <c r="F814" s="3" t="n"/>
+      <c r="F814" s="6" t="inlineStr">
+        <is>
+          <t>LineItemTagIds=[ids+]+按Advertiser过滤 — 61.9%
+LineItemTagIds=[]+按Advertiser过滤 — 21.1%
+LineItemTagIds=[ids+]+无Advertiser过滤 — 14.3%
+LineItemTagIds=[]+无Advertiser过滤 — 2.7%</t>
+        </is>
+      </c>
       <c r="G814" s="3" t="n"/>
     </row>
     <row r="815">
@@ -24619,10 +24809,18 @@
         </is>
       </c>
       <c r="E815" s="3" t="n"/>
-      <c r="F815" s="3" t="n"/>
-      <c r="G815" s="3" t="n"/>
-    </row>
-    <row r="816">
+      <c r="F815" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G815" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="816" ht="128" customHeight="1">
       <c r="A816" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24644,10 +24842,21 @@
         </is>
       </c>
       <c r="E816" s="3" t="n"/>
-      <c r="F816" s="3" t="n"/>
+      <c r="F816" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+含CompareStart — 39.6%
+无Advertiser过滤+无Order过滤+含CompareStart — 24.6%
+按Advertiser过滤+无Order过滤+不含CompareStart — 13.6%
+无Advertiser过滤+无Order过滤+不含CompareStart — 9.2%
+按Advertiser过滤+按Order过滤+含CompareStart — 6.4%
+无Advertiser过滤+按Order过滤+含CompareStart — 3.6%
+无Advertiser过滤+按Order过滤+不含CompareStart — 1.6%
+按Advertiser过滤+按Order过滤+不含CompareStart — 1.4%</t>
+        </is>
+      </c>
       <c r="G816" s="3" t="n"/>
     </row>
-    <row r="817">
+    <row r="817" ht="128" customHeight="1">
       <c r="A817" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24669,7 +24878,18 @@
         </is>
       </c>
       <c r="E817" s="3" t="n"/>
-      <c r="F817" s="3" t="n"/>
+      <c r="F817" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+含CompareStart — 42.6%
+无Advertiser过滤+无Order过滤+含CompareStart — 22.6%
+按Advertiser过滤+无Order过滤+不含CompareStart — 13.6%
+按Advertiser过滤+按Order过滤+含CompareStart — 7.6%
+无Advertiser过滤+无Order过滤+不含CompareStart — 6.6%
+无Advertiser过滤+按Order过滤+含CompareStart — 3.2%
+按Advertiser过滤+按Order过滤+不含CompareStart — 2.0%
+无Advertiser过滤+按Order过滤+不含CompareStart — 1.6%</t>
+        </is>
+      </c>
       <c r="G817" s="3" t="n"/>
     </row>
     <row r="818">
@@ -24694,10 +24914,18 @@
         </is>
       </c>
       <c r="E818" s="3" t="n"/>
-      <c r="F818" s="3" t="n"/>
-      <c r="G818" s="3" t="n"/>
-    </row>
-    <row r="819">
+      <c r="F818" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G818" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="819" ht="16" customHeight="1">
       <c r="A819" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24719,10 +24947,14 @@
         </is>
       </c>
       <c r="E819" s="3" t="n"/>
-      <c r="F819" s="3" t="n"/>
+      <c r="F819" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G819" s="3" t="n"/>
     </row>
-    <row r="820">
+    <row r="820" ht="64" customHeight="1">
       <c r="A820" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24744,10 +24976,17 @@
         </is>
       </c>
       <c r="E820" s="3" t="n"/>
-      <c r="F820" s="3" t="n"/>
+      <c r="F820" s="6" t="inlineStr">
+        <is>
+          <t>按OrderTag过滤+无Advertiser过滤 — 46.4%
+按OrderTag过滤+按Advertiser过滤 — 42.4%
+无OrderTag过滤+按Advertiser过滤 — 6.0%
+无OrderTag过滤+无Advertiser过滤 — 5.2%</t>
+        </is>
+      </c>
       <c r="G820" s="3" t="n"/>
     </row>
-    <row r="821">
+    <row r="821" ht="32" customHeight="1">
       <c r="A821" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24769,10 +25008,15 @@
         </is>
       </c>
       <c r="E821" s="3" t="n"/>
-      <c r="F821" s="3" t="n"/>
+      <c r="F821" s="6" t="inlineStr">
+        <is>
+          <t>按OrderTag过滤+按Advertiser过滤 — 89.6%
+无OrderTag过滤+按Advertiser过滤 — 10.4%</t>
+        </is>
+      </c>
       <c r="G821" s="3" t="n"/>
     </row>
-    <row r="822">
+    <row r="822" ht="112" customHeight="1">
       <c r="A822" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24794,10 +25038,20 @@
         </is>
       </c>
       <c r="E822" s="3" t="n"/>
-      <c r="F822" s="3" t="n"/>
+      <c r="F822" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+含CompareStart — 47.6%
+无Advertiser过滤+无Order过滤+含CompareStart — 17.4%
+按Advertiser过滤+无Order过滤+不含CompareStart — 10.0%
+按Advertiser过滤+按Order过滤+含CompareStart — 9.8%
+无Advertiser过滤+按Order过滤+含CompareStart — 7.0%
+无Advertiser过滤+无Order过滤+不含CompareStart — 4.0%
+按Advertiser过滤+按Order过滤+不含CompareStart — 3.6%</t>
+        </is>
+      </c>
       <c r="G822" s="3" t="n"/>
     </row>
-    <row r="823">
+    <row r="823" ht="112" customHeight="1">
       <c r="A823" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24819,10 +25073,20 @@
         </is>
       </c>
       <c r="E823" s="3" t="n"/>
-      <c r="F823" s="3" t="n"/>
+      <c r="F823" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+含CompareStart — 48.0%
+无Advertiser过滤+无Order过滤+含CompareStart — 18.4%
+按Advertiser过滤+按Order过滤+含CompareStart — 10.6%
+按Advertiser过滤+无Order过滤+不含CompareStart — 9.6%
+无Advertiser过滤+按Order过滤+含CompareStart — 6.0%
+无Advertiser过滤+无Order过滤+不含CompareStart — 4.4%
+按Advertiser过滤+按Order过滤+不含CompareStart — 2.4%</t>
+        </is>
+      </c>
       <c r="G823" s="3" t="n"/>
     </row>
-    <row r="824">
+    <row r="824" ht="64" customHeight="1">
       <c r="A824" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24844,10 +25108,17 @@
         </is>
       </c>
       <c r="E824" s="3" t="n"/>
-      <c r="F824" s="3" t="n"/>
+      <c r="F824" s="6" t="inlineStr">
+        <is>
+          <t>ProductTagIds=[ids+]+按Advertiser过滤 — 36.4%
+ProductTagIds=[]+按Advertiser过滤 — 36.4%
+ProductTagIds=[]+无Advertiser过滤 — 18.2%
+ProductTagIds=[ids+]+无Advertiser过滤 — 9.1%</t>
+        </is>
+      </c>
       <c r="G824" s="3" t="n"/>
     </row>
-    <row r="825">
+    <row r="825" ht="32" customHeight="1">
       <c r="A825" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24869,10 +25140,15 @@
         </is>
       </c>
       <c r="E825" s="3" t="n"/>
-      <c r="F825" s="3" t="n"/>
+      <c r="F825" s="6" t="inlineStr">
+        <is>
+          <t>ProductTagIds=[]+按Advertiser过滤 — 54.5%
+ProductTagIds=[ids+]+按Advertiser过滤 — 45.5%</t>
+        </is>
+      </c>
       <c r="G825" s="3" t="n"/>
     </row>
-    <row r="826">
+    <row r="826" ht="160" customHeight="1">
       <c r="A826" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24894,10 +25170,23 @@
         </is>
       </c>
       <c r="E826" s="3" t="n"/>
-      <c r="F826" s="3" t="n"/>
+      <c r="F826" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含CompareStart — 48.4%
+无Advertiser过滤+无Order过滤+不含CompareStart — 9.8%
+无Advertiser过滤+无Order过滤+含CompareStart — 9.2%
+按Advertiser过滤+不传OrderIds+不含CompareStart — 8.5%
+按Advertiser过滤+按Order过滤+不含CompareStart — 5.2%
+按Advertiser过滤+按Order过滤+含CompareStart — 5.2%
+无Advertiser过滤+不传OrderIds+不含CompareStart — 3.9%
+无Advertiser过滤+按Order过滤+不含CompareStart — 3.9%
+按Advertiser过滤+无Order过滤+含CompareStart — 3.3%
+无Advertiser过滤+按Order过滤+含CompareStart — 2.6%</t>
+        </is>
+      </c>
       <c r="G826" s="3" t="n"/>
     </row>
-    <row r="827">
+    <row r="827" ht="112" customHeight="1">
       <c r="A827" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24919,7 +25208,17 @@
         </is>
       </c>
       <c r="E827" s="3" t="n"/>
-      <c r="F827" s="3" t="n"/>
+      <c r="F827" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含CompareStart — 37.2%
+无Advertiser过滤+无Order过滤+不含CompareStart — 18.0%
+按Advertiser过滤+不传OrderIds+不含CompareStart — 12.8%
+无Advertiser过滤+无Order过滤+含CompareStart — 11.2%
+按Advertiser过滤+按Order过滤+不含CompareStart — 7.6%
+无Advertiser过滤+按Order过滤+不含CompareStart — 7.0%
+无Advertiser过滤+不传OrderIds+不含CompareStart — 4.6%</t>
+        </is>
+      </c>
       <c r="G827" s="3" t="n"/>
     </row>
     <row r="828">
@@ -24944,8 +25243,16 @@
         </is>
       </c>
       <c r="E828" s="3" t="n"/>
-      <c r="F828" s="3" t="n"/>
-      <c r="G828" s="3" t="n"/>
+      <c r="F828" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G828" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="829">
       <c r="A829" s="2" t="inlineStr">
@@ -24969,10 +25276,18 @@
         </is>
       </c>
       <c r="E829" s="3" t="n"/>
-      <c r="F829" s="3" t="n"/>
-      <c r="G829" s="3" t="n"/>
-    </row>
-    <row r="830">
+      <c r="F829" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G829" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="830" ht="48" customHeight="1">
       <c r="A830" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24994,7 +25309,13 @@
         </is>
       </c>
       <c r="E830" s="3" t="n"/>
-      <c r="F830" s="3" t="n"/>
+      <c r="F830" s="6" t="inlineStr">
+        <is>
+          <t>无OrderTag过滤 — 87.6%
+按OrderTag过滤 — 10.6%
+不传orderTagIds — 1.8%</t>
+        </is>
+      </c>
       <c r="G830" s="3" t="n"/>
     </row>
     <row r="831">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -2276,9 +2276,19 @@
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="3" t="n"/>
-      <c r="F73" s="2" t="n"/>
-      <c r="G73" s="2" t="n"/>
-      <c r="H73" s="2" t="n"/>
+      <c r="F73" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>79% (27/34)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -44048,7 +44058,7 @@
       <c r="F1512" s="3" t="n"/>
       <c r="G1512" s="3" t="n"/>
     </row>
-    <row r="1513">
+    <row r="1513" ht="64" customHeight="1">
       <c r="A1513" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44070,10 +44080,17 @@
         </is>
       </c>
       <c r="E1513" s="3" t="n"/>
-      <c r="F1513" s="3" t="n"/>
+      <c r="F1513" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+CreativeTagIds=[] — 47.4%
+按Advertiser过滤+CreativeTagIds=[ids+] — 21.6%
+按Advertiser过滤+CreativeTagIds=[] — 19.6%
+无Advertiser过滤+CreativeTagIds=[ids+] — 10.6%</t>
+        </is>
+      </c>
       <c r="G1513" s="3" t="n"/>
     </row>
-    <row r="1514">
+    <row r="1514" ht="112" customHeight="1">
       <c r="A1514" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44095,10 +44112,20 @@
         </is>
       </c>
       <c r="E1514" s="3" t="n"/>
-      <c r="F1514" s="3" t="n"/>
+      <c r="F1514" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+CreativeTagIds=[]+不含parentTagId — 38.2%
+按Advertiser过滤+CreativeTagIds=[]+不含parentTagId — 17.8%
+按Advertiser过滤+CreativeTagIds=[ids+]+不含parentTagId — 15.6%
+无Advertiser过滤+CreativeTagIds=[ids+]+不含parentTagId — 11.0%
+无Advertiser过滤+CreativeTagIds=[]+含parentTagId — 10.6%
+按Advertiser过滤+CreativeTagIds=[ids+]+含parentTagId — 5.2%
+无Advertiser过滤+CreativeTagIds=[ids+]+含parentTagId — 1.0%</t>
+        </is>
+      </c>
       <c r="G1514" s="3" t="n"/>
     </row>
-    <row r="1515">
+    <row r="1515" ht="16" customHeight="1">
       <c r="A1515" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44120,10 +44147,14 @@
         </is>
       </c>
       <c r="E1515" s="3" t="n"/>
-      <c r="F1515" s="3" t="n"/>
+      <c r="F1515" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+timeType=ytd — 98.5%</t>
+        </is>
+      </c>
       <c r="G1515" s="3" t="n"/>
     </row>
-    <row r="1516">
+    <row r="1516" ht="48" customHeight="1">
       <c r="A1516" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44145,10 +44176,16 @@
         </is>
       </c>
       <c r="E1516" s="3" t="n"/>
-      <c r="F1516" s="3" t="n"/>
+      <c r="F1516" s="6" t="inlineStr">
+        <is>
+          <t>forceExchangeCode=US+不含CompareStart — 47.6%
+forceExchangeCode=US+含CompareStart — 44.2%
+forceExchangeCode=DE+含CompareStart — 7.6%</t>
+        </is>
+      </c>
       <c r="G1516" s="3" t="n"/>
     </row>
-    <row r="1517">
+    <row r="1517" ht="64" customHeight="1">
       <c r="A1517" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44170,10 +44207,17 @@
         </is>
       </c>
       <c r="E1517" s="3" t="n"/>
-      <c r="F1517" s="3" t="n"/>
+      <c r="F1517" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+CreativeTagIds=[] — 50.4%
+按Advertiser过滤+CreativeTagIds=[] — 21.0%
+按Advertiser过滤+CreativeTagIds=[ids+] — 16.6%
+无Advertiser过滤+CreativeTagIds=[ids+] — 12.0%</t>
+        </is>
+      </c>
       <c r="G1517" s="3" t="n"/>
     </row>
-    <row r="1518">
+    <row r="1518" ht="48" customHeight="1">
       <c r="A1518" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44195,10 +44239,16 @@
         </is>
       </c>
       <c r="E1518" s="3" t="n"/>
-      <c r="F1518" s="3" t="n"/>
+      <c r="F1518" s="6" t="inlineStr">
+        <is>
+          <t>forceExchangeCode=US+不含CompareStart — 55.8%
+forceExchangeCode=US+含CompareStart — 36.0%
+forceExchangeCode=DE+含CompareStart — 6.2%</t>
+        </is>
+      </c>
       <c r="G1518" s="3" t="n"/>
     </row>
-    <row r="1519">
+    <row r="1519" ht="48" customHeight="1">
       <c r="A1519" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44220,10 +44270,16 @@
         </is>
       </c>
       <c r="E1519" s="3" t="n"/>
-      <c r="F1519" s="3" t="n"/>
+      <c r="F1519" s="6" t="inlineStr">
+        <is>
+          <t>forceExchangeCode=US+含CompareStart — 55.0%
+forceExchangeCode=US+不含CompareStart — 42.2%
+forceExchangeCode=DE+含CompareStart — 2.4%</t>
+        </is>
+      </c>
       <c r="G1519" s="3" t="n"/>
     </row>
-    <row r="1520">
+    <row r="1520" ht="96" customHeight="1">
       <c r="A1520" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44245,7 +44301,16 @@
         </is>
       </c>
       <c r="E1520" s="3" t="n"/>
-      <c r="F1520" s="3" t="n"/>
+      <c r="F1520" s="6" t="inlineStr">
+        <is>
+          <t>forceExchangeCode=US+含CompareStart+不含performanceOrderTagIds — 58.6%
+forceExchangeCode=US+不含CompareStart+不含performanceOrderTagIds — 22.2%
+forceExchangeCode=US+不含CompareStart+含performanceOrderTagIds — 9.4%
+forceExchangeCode=US+含CompareStart+含performanceOrderTagIds — 4.2%
+forceExchangeCode=MX+含CompareStart+不含performanceOrderTagIds — 2.8%
+forceExchangeCode=CA+含CompareStart+不含performanceOrderTagIds — 1.8%</t>
+        </is>
+      </c>
       <c r="G1520" s="3" t="n"/>
     </row>
     <row r="1521">
@@ -44270,8 +44335,16 @@
         </is>
       </c>
       <c r="E1521" s="3" t="n"/>
-      <c r="F1521" s="3" t="n"/>
-      <c r="G1521" s="3" t="n"/>
+      <c r="F1521" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1521" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1522">
       <c r="A1522" s="2" t="inlineStr">
@@ -44295,8 +44368,16 @@
         </is>
       </c>
       <c r="E1522" s="3" t="n"/>
-      <c r="F1522" s="3" t="n"/>
-      <c r="G1522" s="3" t="n"/>
+      <c r="F1522" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1522" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1523">
       <c r="A1523" s="2" t="inlineStr">
@@ -44320,8 +44401,16 @@
         </is>
       </c>
       <c r="E1523" s="3" t="n"/>
-      <c r="F1523" s="3" t="n"/>
-      <c r="G1523" s="3" t="n"/>
+      <c r="F1523" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1523" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1524">
       <c r="A1524" s="2" t="inlineStr">
@@ -44345,8 +44434,16 @@
         </is>
       </c>
       <c r="E1524" s="3" t="n"/>
-      <c r="F1524" s="3" t="n"/>
-      <c r="G1524" s="3" t="n"/>
+      <c r="F1524" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1524" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1525">
       <c r="A1525" s="2" t="inlineStr">
@@ -44370,10 +44467,18 @@
         </is>
       </c>
       <c r="E1525" s="3" t="n"/>
-      <c r="F1525" s="3" t="n"/>
-      <c r="G1525" s="3" t="n"/>
-    </row>
-    <row r="1526">
+      <c r="F1525" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1525" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526" ht="16" customHeight="1">
       <c r="A1526" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44395,10 +44500,14 @@
         </is>
       </c>
       <c r="E1526" s="3" t="n"/>
-      <c r="F1526" s="3" t="n"/>
+      <c r="F1526" s="6" t="inlineStr">
+        <is>
+          <t>按tagId查询CreativeTag分组</t>
+        </is>
+      </c>
       <c r="G1526" s="3" t="n"/>
     </row>
-    <row r="1527">
+    <row r="1527" ht="16" customHeight="1">
       <c r="A1527" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44420,10 +44529,14 @@
         </is>
       </c>
       <c r="E1527" s="3" t="n"/>
-      <c r="F1527" s="3" t="n"/>
+      <c r="F1527" s="6" t="inlineStr">
+        <is>
+          <t>按tagId查询LineItemTag分组</t>
+        </is>
+      </c>
       <c r="G1527" s="3" t="n"/>
     </row>
-    <row r="1528">
+    <row r="1528" ht="16" customHeight="1">
       <c r="A1528" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44445,7 +44558,11 @@
         </is>
       </c>
       <c r="E1528" s="3" t="n"/>
-      <c r="F1528" s="3" t="n"/>
+      <c r="F1528" s="6" t="inlineStr">
+        <is>
+          <t>按tagId查询OrderTag分组</t>
+        </is>
+      </c>
       <c r="G1528" s="3" t="n"/>
     </row>
     <row r="1529">
@@ -44470,10 +44587,18 @@
         </is>
       </c>
       <c r="E1529" s="3" t="n"/>
-      <c r="F1529" s="3" t="n"/>
-      <c r="G1529" s="3" t="n"/>
-    </row>
-    <row r="1530">
+      <c r="F1529" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1529" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530" ht="16" customHeight="1">
       <c r="A1530" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44495,10 +44620,14 @@
         </is>
       </c>
       <c r="E1530" s="3" t="n"/>
-      <c r="F1530" s="3" t="n"/>
+      <c r="F1530" s="6" t="inlineStr">
+        <is>
+          <t>按tagId查询已选商品</t>
+        </is>
+      </c>
       <c r="G1530" s="3" t="n"/>
     </row>
-    <row r="1531">
+    <row r="1531" ht="16" customHeight="1">
       <c r="A1531" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44520,10 +44649,14 @@
         </is>
       </c>
       <c r="E1531" s="3" t="n"/>
-      <c r="F1531" s="3" t="n"/>
+      <c r="F1531" s="6" t="inlineStr">
+        <is>
+          <t>默认调用(不传参)</t>
+        </is>
+      </c>
       <c r="G1531" s="3" t="n"/>
     </row>
-    <row r="1532">
+    <row r="1532" ht="80" customHeight="1">
       <c r="A1532" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44545,10 +44678,18 @@
         </is>
       </c>
       <c r="E1532" s="3" t="n"/>
-      <c r="F1532" s="3" t="n"/>
+      <c r="F1532" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无LineItemTag过滤 — 50.8%
+按Advertiser过滤+按LineItemTag过滤 — 19.2%
+按Advertiser过滤+无LineItemTag过滤 — 13.2%
+无Advertiser过滤+按LineItemTag过滤 — 13.2%
+无Advertiser过滤+不传lineItemTagIds — 3.4%</t>
+        </is>
+      </c>
       <c r="G1532" s="3" t="n"/>
     </row>
-    <row r="1533">
+    <row r="1533" ht="144" customHeight="1">
       <c r="A1533" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44570,10 +44711,22 @@
         </is>
       </c>
       <c r="E1533" s="3" t="n"/>
-      <c r="F1533" s="3" t="n"/>
+      <c r="F1533" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无LineItemTag过滤+不含parentTagId — 44.2%
+按Advertiser过滤+按LineItemTag过滤+不含parentTagId — 12.8%
+按Advertiser过滤+无LineItemTag过滤+不含parentTagId — 12.2%
+无Advertiser过滤+按LineItemTag过滤+不含parentTagId — 10.0%
+无Advertiser过滤+无LineItemTag过滤+含parentTagId — 8.6%
+按Advertiser过滤+无LineItemTag过滤+含parentTagId — 4.4%
+按Advertiser过滤+按LineItemTag过滤+含parentTagId — 2.6%
+无Advertiser过滤+按LineItemTag过滤+含parentTagId — 2.6%
+无Advertiser过滤+不传lineItemTagIds+不含parentTagId — 1.6%</t>
+        </is>
+      </c>
       <c r="G1533" s="3" t="n"/>
     </row>
-    <row r="1534">
+    <row r="1534" ht="64" customHeight="1">
       <c r="A1534" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44595,10 +44748,17 @@
         </is>
       </c>
       <c r="E1534" s="3" t="n"/>
-      <c r="F1534" s="3" t="n"/>
+      <c r="F1534" s="6" t="inlineStr">
+        <is>
+          <t>forceExchangeCode=US+timeType=month — 63.2%
+forceExchangeCode=US+timeType=week — 25.2%
+forceExchangeCode=US+timeType=ytd — 9.6%
+forceExchangeCode=JP+timeType=month — 1.4%</t>
+        </is>
+      </c>
       <c r="G1534" s="3" t="n"/>
     </row>
-    <row r="1535">
+    <row r="1535" ht="48" customHeight="1">
       <c r="A1535" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44620,10 +44780,16 @@
         </is>
       </c>
       <c r="E1535" s="3" t="n"/>
-      <c r="F1535" s="3" t="n"/>
+      <c r="F1535" s="6" t="inlineStr">
+        <is>
+          <t>forceExchangeCode=US+含CompareStart — 63.6%
+forceExchangeCode=US+不含CompareStart — 35.2%
+forceExchangeCode=DE+含CompareStart — 1.2%</t>
+        </is>
+      </c>
       <c r="G1535" s="3" t="n"/>
     </row>
-    <row r="1536">
+    <row r="1536" ht="80" customHeight="1">
       <c r="A1536" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44645,10 +44811,18 @@
         </is>
       </c>
       <c r="E1536" s="3" t="n"/>
-      <c r="F1536" s="3" t="n"/>
+      <c r="F1536" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无LineItemTag过滤 — 56.4%
+按Advertiser过滤+按LineItemTag过滤 — 15.6%
+按Advertiser过滤+无LineItemTag过滤 — 14.6%
+无Advertiser过滤+按LineItemTag过滤 — 10.2%
+无Advertiser过滤+不传lineItemTagIds — 3.0%</t>
+        </is>
+      </c>
       <c r="G1536" s="3" t="n"/>
     </row>
-    <row r="1537">
+    <row r="1537" ht="64" customHeight="1">
       <c r="A1537" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44670,10 +44844,17 @@
         </is>
       </c>
       <c r="E1537" s="3" t="n"/>
-      <c r="F1537" s="3" t="n"/>
+      <c r="F1537" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+按OrderTag过滤 — 33.8%
+无Advertiser过滤+无OrderTag过滤 — 31.8%
+无Advertiser过滤+按OrderTag过滤 — 25.6%
+按Advertiser过滤+无OrderTag过滤 — 8.8%</t>
+        </is>
+      </c>
       <c r="G1537" s="3" t="n"/>
     </row>
-    <row r="1538">
+    <row r="1538" ht="144" customHeight="1">
       <c r="A1538" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44695,10 +44876,22 @@
         </is>
       </c>
       <c r="E1538" s="3" t="n"/>
-      <c r="F1538" s="3" t="n"/>
+      <c r="F1538" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+无OrderTag过滤+不含parentTagId — 19.2%
+按Advertiser过滤+按OrderTag过滤+不含parentTagId — 18.8%
+不传AdvertiserIds+不传OrderTagIds+不含parentTagId — 18.0%
+无Advertiser过滤+按OrderTag过滤+不含parentTagId — 18.0%
+按Advertiser过滤+无OrderTag过滤+不含parentTagId — 9.4%
+无Advertiser过滤+按OrderTag过滤+含parentTagId — 6.4%
+按Advertiser过滤+按OrderTag过滤+含parentTagId — 5.0%
+无Advertiser过滤+无OrderTag过滤+含parentTagId — 4.2%
+按Advertiser过滤+无OrderTag过滤+含parentTagId — 1.0%</t>
+        </is>
+      </c>
       <c r="G1538" s="3" t="n"/>
     </row>
-    <row r="1539">
+    <row r="1539" ht="96" customHeight="1">
       <c r="A1539" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44720,10 +44913,19 @@
         </is>
       </c>
       <c r="E1539" s="3" t="n"/>
-      <c r="F1539" s="3" t="n"/>
+      <c r="F1539" s="6" t="inlineStr">
+        <is>
+          <t>TimeType=date+不含isShowIRoas — 35.8%
+TimeType=month+不含isShowIRoas — 34.4%
+TimeType=ytd+不含isShowIRoas — 16.0%
+TimeType=date+含isShowIRoas — 6.6%
+TimeType=month+含isShowIRoas — 4.8%
+TimeType=ytd+含isShowIRoas — 2.4%</t>
+        </is>
+      </c>
       <c r="G1539" s="3" t="n"/>
     </row>
-    <row r="1540">
+    <row r="1540" ht="96" customHeight="1">
       <c r="A1540" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44745,10 +44947,19 @@
         </is>
       </c>
       <c r="E1540" s="3" t="n"/>
-      <c r="F1540" s="3" t="n"/>
+      <c r="F1540" s="6" t="inlineStr">
+        <is>
+          <t>forceExchangeCode=US+timeType=ytd — 37.4%
+forceExchangeCode=US+timeType=week — 25.2%
+forceExchangeCode=US+timeType=month — 18.6%
+forceExchangeCode=JP+timeType=month — 9.4%
+forceExchangeCode=MX+timeType=ytd — 5.0%
+forceExchangeCode=CA+timeType=month — 3.0%</t>
+        </is>
+      </c>
       <c r="G1540" s="3" t="n"/>
     </row>
-    <row r="1541">
+    <row r="1541" ht="96" customHeight="1">
       <c r="A1541" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44770,10 +44981,19 @@
         </is>
       </c>
       <c r="E1541" s="3" t="n"/>
-      <c r="F1541" s="3" t="n"/>
+      <c r="F1541" s="6" t="inlineStr">
+        <is>
+          <t>forceExchangeCode=US+含CompareStart+不含performanceOrderTagIds — 70.6%
+forceExchangeCode=US+不含CompareStart+不含performanceOrderTagIds — 14.2%
+forceExchangeCode=US+含CompareStart+含performanceOrderTagIds — 6.2%
+forceExchangeCode=US+不含CompareStart+含performanceOrderTagIds — 3.8%
+forceExchangeCode=MX+含CompareStart+不含performanceOrderTagIds — 2.4%
+forceExchangeCode=DE+含CompareStart+不含performanceOrderTagIds — 1.2%</t>
+        </is>
+      </c>
       <c r="G1541" s="3" t="n"/>
     </row>
-    <row r="1542">
+    <row r="1542" ht="80" customHeight="1">
       <c r="A1542" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44795,10 +45015,18 @@
         </is>
       </c>
       <c r="E1542" s="3" t="n"/>
-      <c r="F1542" s="3" t="n"/>
+      <c r="F1542" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+按OrderTag过滤+不含isDistinct — 29.4%
+无Advertiser过滤+按OrderTag过滤+不含isDistinct — 28.6%
+无Advertiser过滤+无OrderTag过滤+不含isDistinct — 26.0%
+按Advertiser过滤+无OrderTag过滤+不含isDistinct — 10.2%
+无Advertiser过滤+按OrderTag过滤+含isDistinct — 5.8%</t>
+        </is>
+      </c>
       <c r="G1542" s="3" t="n"/>
     </row>
-    <row r="1543">
+    <row r="1543" ht="80" customHeight="1">
       <c r="A1543" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44820,10 +45048,18 @@
         </is>
       </c>
       <c r="E1543" s="3" t="n"/>
-      <c r="F1543" s="3" t="n"/>
+      <c r="F1543" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+ProductTagIds=[]+productVariation=Child products — 41.8%
+按Advertiser过滤+ProductTagIds=[]+productVariation=Child products — 28.8%
+无Advertiser过滤+ProductTagIds=[ids+]+productVariation=Child products — 12.0%
+按Advertiser过滤+ProductTagIds=[ids+]+productVariation=Child products — 11.4%
+无Advertiser过滤+ProductTagIds=[]+productVariation=Parent products — 5.4%</t>
+        </is>
+      </c>
       <c r="G1543" s="3" t="n"/>
     </row>
-    <row r="1544">
+    <row r="1544" ht="96" customHeight="1">
       <c r="A1544" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44845,7 +45081,16 @@
         </is>
       </c>
       <c r="E1544" s="3" t="n"/>
-      <c r="F1544" s="3" t="n"/>
+      <c r="F1544" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+ProductTagIds=[]+productVariation=Child products — 40.1%
+按Advertiser过滤+ProductTagIds=[]+productVariation=Child products — 29.1%
+无Advertiser过滤+ProductTagIds=[ids+]+productVariation=Child products — 11.8%
+按Advertiser过滤+ProductTagIds=[ids+]+productVariation=Child products — 9.4%
+无Advertiser过滤+ProductTagIds=[]+productVariation=Parent products — 8.0%
+按Advertiser过滤+ProductTagIds=[ids+]+productVariation=Parent products — 1.0%</t>
+        </is>
+      </c>
       <c r="G1544" s="3" t="n"/>
     </row>
     <row r="1545">
@@ -44870,10 +45115,18 @@
         </is>
       </c>
       <c r="E1545" s="3" t="n"/>
-      <c r="F1545" s="3" t="n"/>
-      <c r="G1545" s="3" t="n"/>
-    </row>
-    <row r="1546">
+      <c r="F1545" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1545" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546" ht="80" customHeight="1">
       <c r="A1546" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -44895,7 +45148,15 @@
         </is>
       </c>
       <c r="E1546" s="3" t="n"/>
-      <c r="F1546" s="3" t="n"/>
+      <c r="F1546" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+ProductTagIds=[]+productVariation=Child products — 39.0%
+按Advertiser过滤+ProductTagIds=[]+productVariation=Child products — 30.9%
+按Advertiser过滤+ProductTagIds=[ids+]+productVariation=Child products — 13.1%
+无Advertiser过滤+ProductTagIds=[ids+]+productVariation=Child products — 12.2%
+无Advertiser过滤+ProductTagIds=[]+productVariation=Parent products — 3.8%</t>
+        </is>
+      </c>
       <c r="G1546" s="3" t="n"/>
     </row>
     <row r="1547">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -730,9 +730,19 @@
       </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="F10" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>85% (28/33)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5636,9 +5646,13 @@
       </c>
       <c r="E121" s="3" t="n"/>
       <c r="F121" s="3" t="n"/>
-      <c r="G121" s="3" t="n"/>
-    </row>
-    <row r="122">
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>写操作(激活自定义模型)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="16" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5660,10 +5674,14 @@
         </is>
       </c>
       <c r="E122" s="3" t="n"/>
-      <c r="F122" s="3" t="n"/>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G122" s="3" t="n"/>
     </row>
-    <row r="123">
+    <row r="123" ht="16" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5685,10 +5703,14 @@
         </is>
       </c>
       <c r="E123" s="3" t="n"/>
-      <c r="F123" s="3" t="n"/>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G123" s="3" t="n"/>
     </row>
-    <row r="124">
+    <row r="124" ht="16" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5710,10 +5732,14 @@
         </is>
       </c>
       <c r="E124" s="3" t="n"/>
-      <c r="F124" s="3" t="n"/>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G124" s="3" t="n"/>
     </row>
-    <row r="125">
+    <row r="125" ht="16" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5735,10 +5761,14 @@
         </is>
       </c>
       <c r="E125" s="3" t="n"/>
-      <c r="F125" s="3" t="n"/>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G125" s="3" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" ht="16" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5760,7 +5790,11 @@
         </is>
       </c>
       <c r="E126" s="3" t="n"/>
-      <c r="F126" s="3" t="n"/>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G126" s="3" t="n"/>
     </row>
     <row r="127">
@@ -5785,8 +5819,16 @@
         </is>
       </c>
       <c r="E127" s="3" t="n"/>
-      <c r="F127" s="3" t="n"/>
-      <c r="G127" s="3" t="n"/>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -5810,8 +5852,16 @@
         </is>
       </c>
       <c r="E128" s="3" t="n"/>
-      <c r="F128" s="3" t="n"/>
-      <c r="G128" s="3" t="n"/>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5835,10 +5885,18 @@
         </is>
       </c>
       <c r="E129" s="3" t="n"/>
-      <c r="F129" s="3" t="n"/>
-      <c r="G129" s="3" t="n"/>
-    </row>
-    <row r="130">
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="16" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5860,10 +5918,14 @@
         </is>
       </c>
       <c r="E130" s="3" t="n"/>
-      <c r="F130" s="3" t="n"/>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G130" s="3" t="n"/>
     </row>
-    <row r="131">
+    <row r="131" ht="16" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5885,10 +5947,14 @@
         </is>
       </c>
       <c r="E131" s="3" t="n"/>
-      <c r="F131" s="3" t="n"/>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G131" s="3" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" ht="16" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5910,10 +5976,14 @@
         </is>
       </c>
       <c r="E132" s="3" t="n"/>
-      <c r="F132" s="3" t="n"/>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G132" s="3" t="n"/>
     </row>
-    <row r="133">
+    <row r="133" ht="16" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5935,10 +6005,14 @@
         </is>
       </c>
       <c r="E133" s="3" t="n"/>
-      <c r="F133" s="3" t="n"/>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G133" s="3" t="n"/>
     </row>
-    <row r="134">
+    <row r="134" ht="16" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5960,10 +6034,14 @@
         </is>
       </c>
       <c r="E134" s="3" t="n"/>
-      <c r="F134" s="3" t="n"/>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G134" s="3" t="n"/>
     </row>
-    <row r="135">
+    <row r="135" ht="16" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5985,10 +6063,14 @@
         </is>
       </c>
       <c r="E135" s="3" t="n"/>
-      <c r="F135" s="3" t="n"/>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G135" s="3" t="n"/>
     </row>
-    <row r="136">
+    <row r="136" ht="48" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6010,10 +6092,16 @@
         </is>
       </c>
       <c r="E136" s="3" t="n"/>
-      <c r="F136" s="3" t="n"/>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>不含audienceIds+不含AdTypes — 52.8%
+含audienceIds+含AdTypes — 43.3%
+含audienceIds+不含AdTypes — 3.9%</t>
+        </is>
+      </c>
       <c r="G136" s="3" t="n"/>
     </row>
-    <row r="137">
+    <row r="137" ht="32" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6035,10 +6123,15 @@
         </is>
       </c>
       <c r="E137" s="3" t="n"/>
-      <c r="F137" s="3" t="n"/>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>含audienceIds+含AdTypes — 60.4%
+不含audienceIds+不含AdTypes — 39.6%</t>
+        </is>
+      </c>
       <c r="G137" s="3" t="n"/>
     </row>
-    <row r="138">
+    <row r="138" ht="32" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6060,10 +6153,15 @@
         </is>
       </c>
       <c r="E138" s="3" t="n"/>
-      <c r="F138" s="3" t="n"/>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>不含audienceIds — 95.4%
+含audienceIds — 4.6%</t>
+        </is>
+      </c>
       <c r="G138" s="3" t="n"/>
     </row>
-    <row r="139">
+    <row r="139" ht="16" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6085,10 +6183,14 @@
         </is>
       </c>
       <c r="E139" s="3" t="n"/>
-      <c r="F139" s="3" t="n"/>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G139" s="3" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" ht="16" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6110,7 +6212,11 @@
         </is>
       </c>
       <c r="E140" s="3" t="n"/>
-      <c r="F140" s="3" t="n"/>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G140" s="3" t="n"/>
     </row>
     <row r="141">
@@ -6135,10 +6241,18 @@
         </is>
       </c>
       <c r="E141" s="3" t="n"/>
-      <c r="F141" s="3" t="n"/>
-      <c r="G141" s="3" t="n"/>
-    </row>
-    <row r="142">
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="32" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6160,10 +6274,15 @@
         </is>
       </c>
       <c r="E142" s="3" t="n"/>
-      <c r="F142" s="3" t="n"/>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>含instanceIds — 87.4%
+不含instanceIds — 12.6%</t>
+        </is>
+      </c>
       <c r="G142" s="3" t="n"/>
     </row>
-    <row r="143">
+    <row r="143" ht="32" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6185,10 +6304,15 @@
         </is>
       </c>
       <c r="E143" s="3" t="n"/>
-      <c r="F143" s="3" t="n"/>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>含instanceIds — 87.4%
+不含instanceIds — 12.6%</t>
+        </is>
+      </c>
       <c r="G143" s="3" t="n"/>
     </row>
-    <row r="144">
+    <row r="144" ht="32" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6210,10 +6334,15 @@
         </is>
       </c>
       <c r="E144" s="3" t="n"/>
-      <c r="F144" s="3" t="n"/>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>含instanceIds — 87.4%
+不含instanceIds — 12.6%</t>
+        </is>
+      </c>
       <c r="G144" s="3" t="n"/>
     </row>
-    <row r="145">
+    <row r="145" ht="48" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6235,10 +6364,16 @@
         </is>
       </c>
       <c r="E145" s="3" t="n"/>
-      <c r="F145" s="3" t="n"/>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>不含audienceIds+不含AdTypes — 61.5%
+含audienceIds+含AdTypes — 35.3%
+含audienceIds+不含AdTypes — 3.2%</t>
+        </is>
+      </c>
       <c r="G145" s="3" t="n"/>
     </row>
-    <row r="146">
+    <row r="146" ht="16" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6260,10 +6395,14 @@
         </is>
       </c>
       <c r="E146" s="3" t="n"/>
-      <c r="F146" s="3" t="n"/>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G146" s="3" t="n"/>
     </row>
-    <row r="147">
+    <row r="147" ht="32" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6285,10 +6424,15 @@
         </is>
       </c>
       <c r="E147" s="3" t="n"/>
-      <c r="F147" s="3" t="n"/>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>含instanceIds — 87.4%
+不含instanceIds — 12.6%</t>
+        </is>
+      </c>
       <c r="G147" s="3" t="n"/>
     </row>
-    <row r="148">
+    <row r="148" ht="16" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6310,10 +6454,14 @@
         </is>
       </c>
       <c r="E148" s="3" t="n"/>
-      <c r="F148" s="3" t="n"/>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G148" s="3" t="n"/>
     </row>
-    <row r="149">
+    <row r="149" ht="16" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6335,10 +6483,14 @@
         </is>
       </c>
       <c r="E149" s="3" t="n"/>
-      <c r="F149" s="3" t="n"/>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G149" s="3" t="n"/>
     </row>
-    <row r="150">
+    <row r="150" ht="32" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6360,10 +6512,15 @@
         </is>
       </c>
       <c r="E150" s="3" t="n"/>
-      <c r="F150" s="3" t="n"/>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>含amcAdvertiserIds+不含dspAdvertiserIds — 52.3%
+不含amcAdvertiserIds+含dspAdvertiserIds — 47.7%</t>
+        </is>
+      </c>
       <c r="G150" s="3" t="n"/>
     </row>
-    <row r="151">
+    <row r="151" ht="32" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6385,10 +6542,15 @@
         </is>
       </c>
       <c r="E151" s="3" t="n"/>
-      <c r="F151" s="3" t="n"/>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>含amcAdvertiserIds+不含dspAdvertiserIds — 58.5%
+不含amcAdvertiserIds+含dspAdvertiserIds — 40.9%</t>
+        </is>
+      </c>
       <c r="G151" s="3" t="n"/>
     </row>
-    <row r="152">
+    <row r="152" ht="32" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6410,10 +6572,15 @@
         </is>
       </c>
       <c r="E152" s="3" t="n"/>
-      <c r="F152" s="3" t="n"/>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>含amcAdvertiserIds+不含dspAdvertiserIds — 54.7%
+不含amcAdvertiserIds+含dspAdvertiserIds — 45.3%</t>
+        </is>
+      </c>
       <c r="G152" s="3" t="n"/>
     </row>
-    <row r="153">
+    <row r="153" ht="32" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6435,7 +6602,12 @@
         </is>
       </c>
       <c r="E153" s="3" t="n"/>
-      <c r="F153" s="3" t="n"/>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>含sourceInstanceIds — 72.2%
+不含sourceInstanceIds — 27.8%</t>
+        </is>
+      </c>
       <c r="G153" s="3" t="n"/>
     </row>
     <row r="154">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1134,9 +1134,19 @@
       </c>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="F27" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>52% (12/23)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -17659,7 +17669,7 @@
       <c r="F551" s="3" t="n"/>
       <c r="G551" s="3" t="n"/>
     </row>
-    <row r="552">
+    <row r="552" ht="32" customHeight="1">
       <c r="A552" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -17681,10 +17691,15 @@
         </is>
       </c>
       <c r="E552" s="3" t="n"/>
-      <c r="F552" s="3" t="n"/>
+      <c r="F552" s="6" t="inlineStr">
+        <is>
+          <t>filter=[]+groupBy=None — 83.3%
+filter=None+groupBy= — 16.7%</t>
+        </is>
+      </c>
       <c r="G552" s="3" t="n"/>
     </row>
-    <row r="553">
+    <row r="553" ht="16" customHeight="1">
       <c r="A553" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -17706,10 +17721,14 @@
         </is>
       </c>
       <c r="E553" s="3" t="n"/>
-      <c r="F553" s="3" t="n"/>
+      <c r="F553" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G553" s="3" t="n"/>
     </row>
-    <row r="554">
+    <row r="554" ht="48" customHeight="1">
       <c r="A554" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -17731,7 +17750,13 @@
         </is>
       </c>
       <c r="E554" s="3" t="n"/>
-      <c r="F554" s="3" t="n"/>
+      <c r="F554" s="6" t="inlineStr">
+        <is>
+          <t>filter=None+groupBy=None+不传AudienceName — 62.5%
+filter=[]+groupBy=None+AudienceName=Hills CRM Customers 2026 DogOwner — 25.0%
+filter=None+groupBy=+不传AudienceName — 12.5%</t>
+        </is>
+      </c>
       <c r="G554" s="3" t="n"/>
     </row>
     <row r="555">
@@ -17756,10 +17781,18 @@
         </is>
       </c>
       <c r="E555" s="3" t="n"/>
-      <c r="F555" s="3" t="n"/>
-      <c r="G555" s="3" t="n"/>
-    </row>
-    <row r="556">
+      <c r="F555" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G555" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="556" ht="16" customHeight="1">
       <c r="A556" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -17781,10 +17814,14 @@
         </is>
       </c>
       <c r="E556" s="3" t="n"/>
-      <c r="F556" s="3" t="n"/>
+      <c r="F556" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G556" s="3" t="n"/>
     </row>
-    <row r="557">
+    <row r="557" ht="16" customHeight="1">
       <c r="A557" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -17806,7 +17843,11 @@
         </is>
       </c>
       <c r="E557" s="3" t="n"/>
-      <c r="F557" s="3" t="n"/>
+      <c r="F557" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G557" s="3" t="n"/>
     </row>
     <row r="558">
@@ -17831,10 +17872,18 @@
         </is>
       </c>
       <c r="E558" s="3" t="n"/>
-      <c r="F558" s="3" t="n"/>
-      <c r="G558" s="3" t="n"/>
-    </row>
-    <row r="559">
+      <c r="F558" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G558" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="559" ht="64" customHeight="1">
       <c r="A559" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -17856,10 +17905,17 @@
         </is>
       </c>
       <c r="E559" s="3" t="n"/>
-      <c r="F559" s="3" t="n"/>
+      <c r="F559" s="6" t="inlineStr">
+        <is>
+          <t>filter=None+按{"Field": "TotalCostChange", "order": "desc"}排序+count=5+groupBy=None — 25.0%
+filter=[{'Field': 'TotalCostChange', 'Operand': 'Less', 'Value': 0.2]+按{"Field": "TotalCostChange", "order": "asc"}排序+count=1000+groupBy=None — 25.0%
+filter=None+按{"Field": "TotalCost", "order": "desc"}排序+count=1000+groupBy= — 25.0%
+filter=None+按{"Field": "eCPP", "order": "asc"}排序+count=1000+groupBy=None — 25.0%</t>
+        </is>
+      </c>
       <c r="G559" s="3" t="n"/>
     </row>
-    <row r="560">
+    <row r="560" ht="64" customHeight="1">
       <c r="A560" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -17881,7 +17937,14 @@
         </is>
       </c>
       <c r="E560" s="3" t="n"/>
-      <c r="F560" s="3" t="n"/>
+      <c r="F560" s="6" t="inlineStr">
+        <is>
+          <t>按{"Field": "TotalCost", "order": "desc"}排序+count=5 — 40.0%
+按{"Field": "CVR", "order": "desc"}排序+count=5 — 20.0%
+按{"Field": "Purchases", "order": "desc"}排序+count=1000 — 20.0%
+按{"Field": "TotalCost", "order": "desc"}排序+count=1000 — 20.0%</t>
+        </is>
+      </c>
       <c r="G560" s="3" t="n"/>
     </row>
     <row r="561">
@@ -17906,10 +17969,18 @@
         </is>
       </c>
       <c r="E561" s="3" t="n"/>
-      <c r="F561" s="3" t="n"/>
-      <c r="G561" s="3" t="n"/>
-    </row>
-    <row r="562">
+      <c r="F561" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G561" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="562" ht="48" customHeight="1">
       <c r="A562" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -17931,10 +18002,16 @@
         </is>
       </c>
       <c r="E562" s="3" t="n"/>
-      <c r="F562" s="3" t="n"/>
+      <c r="F562" s="6" t="inlineStr">
+        <is>
+          <t>filter=None+按{"Field": "TotalCost", "order": "desc"}排序 — 76.9%
+filter=[{'Field': 'DPVChange', 'Operand': 'Less', 'Value': 0},{'Fiel]+按{"Field": "ImpressionsChange", "order": "desc"}排序 — 15.4%
+filter=None+按{"Field": "eCPP", "order": "asc"}排序 — 7.7%</t>
+        </is>
+      </c>
       <c r="G562" s="3" t="n"/>
     </row>
-    <row r="563">
+    <row r="563" ht="128" customHeight="1">
       <c r="A563" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -17956,10 +18033,21 @@
         </is>
       </c>
       <c r="E563" s="3" t="n"/>
-      <c r="F563" s="3" t="n"/>
+      <c r="F563" s="6" t="inlineStr">
+        <is>
+          <t>filter=None+按{"Field": "TotalROAS", "order": "desc"}排序+count=10+groupBy=None+不传orderIds+不传orderTagIds — 31.8%
+filter=None+按{"Field": "TotalCost", "order": "desc"}排序+count=1000+groupBy=None+不传orderIds+不传orderTagIds — 22.7%
+filter=None+按{"Field": "TotalCost", "order": "desc"}排序+count=1000+groupBy=+不传orderIds+不传orderTagIds — 18.2%
+filter=[]+按{"Field": "TotalCost", "order": "desc"}排序+count=1000+groupBy=None+无Order过滤+不传orderTagIds — 9.1%
+filter=[]+按{"Field": "DPVR", "order": "asc"}排序+count=5+groupBy=None+无Order过滤+不传orderTagIds — 4.5%
+filter=[]+按{"Field": "TotalCost", "order": "desc"}排序+count=1000+groupBy=None+不传orderIds+不传orderTagIds — 4.5%
+filter=None+按{"Field": "TotalROAS", "order": "desc"}排序+count=1000+groupBy=None+不传orderIds+不传orderTagIds — 4.5%
+filter=[]+按{"Field": "TotalCost", "order": "desc"}排序+count=1000+groupBy=None+不传orderIds+按OrderTag过滤 — 4.5%</t>
+        </is>
+      </c>
       <c r="G563" s="3" t="n"/>
     </row>
-    <row r="564">
+    <row r="564" ht="48" customHeight="1">
       <c r="A564" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -17981,7 +18069,13 @@
         </is>
       </c>
       <c r="E564" s="3" t="n"/>
-      <c r="F564" s="3" t="n"/>
+      <c r="F564" s="6" t="inlineStr">
+        <is>
+          <t>filter=None+startCompare=2026-03-22T00:00:00+endCompare=2026-03-29T00:00:00 — 50.0%
+filter=None+startCompare=2025-05-08T00:00:00+endCompare=2025-12-31T00:00:00 — 25.0%
+filter=[]+startCompare=None+endCompare=None — 25.0%</t>
+        </is>
+      </c>
       <c r="G564" s="3" t="n"/>
     </row>
     <row r="565">
@@ -18006,10 +18100,18 @@
         </is>
       </c>
       <c r="E565" s="3" t="n"/>
-      <c r="F565" s="3" t="n"/>
-      <c r="G565" s="3" t="n"/>
-    </row>
-    <row r="566">
+      <c r="F565" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G565" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="64" customHeight="1">
       <c r="A566" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18031,7 +18133,14 @@
         </is>
       </c>
       <c r="E566" s="3" t="n"/>
-      <c r="F566" s="3" t="n"/>
+      <c r="F566" s="6" t="inlineStr">
+        <is>
+          <t>filter=None+按{"Field": "Purchases", "order": "desc"}排序+count=1000+不传orderIds — 66.7%
+filter=[]+按{"Field": "Purchases", "order": "desc"}排序+count=10+按Order过滤 — 11.1%
+filter=None+按{"Field": "NTBSales", "order": "desc"}排序+count=10+不传orderIds — 11.1%
+filter=None+按{"Field": "UnitsSold", "order": "desc"}排序+count=10+不传orderIds — 11.1%</t>
+        </is>
+      </c>
       <c r="G566" s="3" t="n"/>
     </row>
     <row r="567">
@@ -18056,10 +18165,18 @@
         </is>
       </c>
       <c r="E567" s="3" t="n"/>
-      <c r="F567" s="3" t="n"/>
-      <c r="G567" s="3" t="n"/>
-    </row>
-    <row r="568">
+      <c r="F567" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G567" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="16" customHeight="1">
       <c r="A568" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18081,7 +18198,11 @@
         </is>
       </c>
       <c r="E568" s="3" t="n"/>
-      <c r="F568" s="3" t="n"/>
+      <c r="F568" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G568" s="3" t="n"/>
     </row>
     <row r="569">
@@ -18106,8 +18227,16 @@
         </is>
       </c>
       <c r="E569" s="3" t="n"/>
-      <c r="F569" s="3" t="n"/>
-      <c r="G569" s="3" t="n"/>
+      <c r="F569" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G569" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
@@ -18131,8 +18260,16 @@
         </is>
       </c>
       <c r="E570" s="3" t="n"/>
-      <c r="F570" s="3" t="n"/>
-      <c r="G570" s="3" t="n"/>
+      <c r="F570" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G570" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
@@ -18156,8 +18293,16 @@
         </is>
       </c>
       <c r="E571" s="3" t="n"/>
-      <c r="F571" s="3" t="n"/>
-      <c r="G571" s="3" t="n"/>
+      <c r="F571" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G571" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
@@ -18181,8 +18326,16 @@
         </is>
       </c>
       <c r="E572" s="3" t="n"/>
-      <c r="F572" s="3" t="n"/>
-      <c r="G572" s="3" t="n"/>
+      <c r="F572" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G572" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
@@ -18206,8 +18359,16 @@
         </is>
       </c>
       <c r="E573" s="3" t="n"/>
-      <c r="F573" s="3" t="n"/>
-      <c r="G573" s="3" t="n"/>
+      <c r="F573" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G573" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -18231,8 +18392,16 @@
         </is>
       </c>
       <c r="E574" s="3" t="n"/>
-      <c r="F574" s="3" t="n"/>
-      <c r="G574" s="3" t="n"/>
+      <c r="F574" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G574" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -762,9 +762,19 @@
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
+      <c r="F11" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76% (28/37)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -6642,10 +6652,18 @@
         </is>
       </c>
       <c r="E154" s="3" t="n"/>
-      <c r="F154" s="3" t="n"/>
-      <c r="G154" s="3" t="n"/>
-    </row>
-    <row r="155">
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="32" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6667,7 +6685,12 @@
         </is>
       </c>
       <c r="E155" s="3" t="n"/>
-      <c r="F155" s="3" t="n"/>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>不含CrossPurchaseGroupBy — 91.4%
+含CrossPurchaseGroupBy — 8.6%</t>
+        </is>
+      </c>
       <c r="G155" s="3" t="n"/>
     </row>
     <row r="156">
@@ -6693,9 +6716,13 @@
       </c>
       <c r="E156" s="3" t="n"/>
       <c r="F156" s="3" t="n"/>
-      <c r="G156" s="3" t="n"/>
-    </row>
-    <row r="157">
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>写操作(编辑自定义SQL报表列配置)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="80" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6717,7 +6744,15 @@
         </is>
       </c>
       <c r="E157" s="3" t="n"/>
-      <c r="F157" s="3" t="n"/>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>reportTypes=[All] — 82.2%
+reportTypes=[DSP] — 7.0%
+reportTypes=[ids+] — 5.2%
+reportTypes=[SP] — 3.0%
+reportTypes=[SD] — 1.2%</t>
+        </is>
+      </c>
       <c r="G157" s="3" t="n"/>
     </row>
     <row r="158">
@@ -6742,10 +6777,18 @@
         </is>
       </c>
       <c r="E158" s="3" t="n"/>
-      <c r="F158" s="3" t="n"/>
-      <c r="G158" s="3" t="n"/>
-    </row>
-    <row r="159">
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="16" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6767,10 +6810,14 @@
         </is>
       </c>
       <c r="E159" s="3" t="n"/>
-      <c r="F159" s="3" t="n"/>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>含reportTypes — 99.8%</t>
+        </is>
+      </c>
       <c r="G159" s="3" t="n"/>
     </row>
-    <row r="160">
+    <row r="160" ht="16" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6792,10 +6839,14 @@
         </is>
       </c>
       <c r="E160" s="3" t="n"/>
-      <c r="F160" s="3" t="n"/>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G160" s="3" t="n"/>
     </row>
-    <row r="161">
+    <row r="161" ht="16" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6817,7 +6868,11 @@
         </is>
       </c>
       <c r="E161" s="3" t="n"/>
-      <c r="F161" s="3" t="n"/>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G161" s="3" t="n"/>
     </row>
     <row r="162">
@@ -6842,10 +6897,18 @@
         </is>
       </c>
       <c r="E162" s="3" t="n"/>
-      <c r="F162" s="3" t="n"/>
-      <c r="G162" s="3" t="n"/>
-    </row>
-    <row r="163">
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="96" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6867,10 +6930,19 @@
         </is>
       </c>
       <c r="E163" s="3" t="n"/>
-      <c r="F163" s="3" t="n"/>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>reportTypes=[DSP] — 53.0%
+reportTypes=[SP] — 27.0%
+reportTypes=[AMS] — 7.4%
+reportTypes=[SD] — 5.2%
+reportTypes=[SB] — 5.0%
+reportTypes=[STV] — 2.4%</t>
+        </is>
+      </c>
       <c r="G163" s="3" t="n"/>
     </row>
-    <row r="164">
+    <row r="164" ht="32" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6892,7 +6964,12 @@
         </is>
       </c>
       <c r="E164" s="3" t="n"/>
-      <c r="F164" s="3" t="n"/>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>不含historyIdComparison — 97.2%
+含historyIdComparison — 2.8%</t>
+        </is>
+      </c>
       <c r="G164" s="3" t="n"/>
     </row>
     <row r="165">
@@ -6917,10 +6994,18 @@
         </is>
       </c>
       <c r="E165" s="3" t="n"/>
-      <c r="F165" s="3" t="n"/>
-      <c r="G165" s="3" t="n"/>
-    </row>
-    <row r="166">
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="112" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6942,10 +7027,20 @@
         </is>
       </c>
       <c r="E166" s="3" t="n"/>
-      <c r="F166" s="3" t="n"/>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>category=DemoGraphicDevice — 15.8%
+category=DemoGraphicAge — 15.6%
+category=DemoGraphicSystem — 15.4%
+category=DemoGraphicIncome — 13.6%
+category=DemoGraphicEducation — 13.4%
+category=DemoGraphicRelationship — 13.2%
+category=DemoGraphicGender — 13.0%</t>
+        </is>
+      </c>
       <c r="G166" s="3" t="n"/>
     </row>
-    <row r="167">
+    <row r="167" ht="96" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6967,10 +7062,19 @@
         </is>
       </c>
       <c r="E167" s="3" t="n"/>
-      <c r="F167" s="3" t="n"/>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>keyword=All — 76.4%
+keyword=AMS — 8.4%
+keyword=DSP — 8.0%
+keyword=SP — 3.2%
+keyword=SB — 2.2%
+keyword=SD — 1.4%</t>
+        </is>
+      </c>
       <c r="G167" s="3" t="n"/>
     </row>
-    <row r="168">
+    <row r="168" ht="128" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6992,10 +7096,21 @@
         </is>
       </c>
       <c r="E168" s="3" t="n"/>
-      <c r="F168" s="3" t="n"/>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>category=DSP — 43.2%
+category=SP — 22.8%
+category=All — 16.2%
+category=ad-exposed — 12.6%
+category=AMS — 1.4%
+category=non-ad-exposed — 1.2%
+category=SB — 1.2%
+category=SD — 1.0%</t>
+        </is>
+      </c>
       <c r="G168" s="3" t="n"/>
     </row>
-    <row r="169">
+    <row r="169" ht="80" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7017,7 +7132,15 @@
         </is>
       </c>
       <c r="E169" s="3" t="n"/>
-      <c r="F169" s="3" t="n"/>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>category=All — 90.0%
+category=AMS — 3.2%
+category=DSP — 3.2%
+category=SP — 2.4%
+category=SB — 1.0%</t>
+        </is>
+      </c>
       <c r="G169" s="3" t="n"/>
     </row>
     <row r="170">
@@ -7042,8 +7165,16 @@
         </is>
       </c>
       <c r="E170" s="3" t="n"/>
-      <c r="F170" s="3" t="n"/>
-      <c r="G170" s="3" t="n"/>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -7067,10 +7198,18 @@
         </is>
       </c>
       <c r="E171" s="3" t="n"/>
-      <c r="F171" s="3" t="n"/>
-      <c r="G171" s="3" t="n"/>
-    </row>
-    <row r="172">
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="16" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7092,10 +7231,14 @@
         </is>
       </c>
       <c r="E172" s="3" t="n"/>
-      <c r="F172" s="3" t="n"/>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G172" s="3" t="n"/>
     </row>
-    <row r="173">
+    <row r="173" ht="16" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7117,10 +7260,14 @@
         </is>
       </c>
       <c r="E173" s="3" t="n"/>
-      <c r="F173" s="3" t="n"/>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G173" s="3" t="n"/>
     </row>
-    <row r="174">
+    <row r="174" ht="16" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7142,10 +7289,14 @@
         </is>
       </c>
       <c r="E174" s="3" t="n"/>
-      <c r="F174" s="3" t="n"/>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G174" s="3" t="n"/>
     </row>
-    <row r="175">
+    <row r="175" ht="16" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7167,10 +7318,14 @@
         </is>
       </c>
       <c r="E175" s="3" t="n"/>
-      <c r="F175" s="3" t="n"/>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G175" s="3" t="n"/>
     </row>
-    <row r="176">
+    <row r="176" ht="16" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7192,7 +7347,11 @@
         </is>
       </c>
       <c r="E176" s="3" t="n"/>
-      <c r="F176" s="3" t="n"/>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G176" s="3" t="n"/>
     </row>
     <row r="177">
@@ -7217,10 +7376,18 @@
         </is>
       </c>
       <c r="E177" s="3" t="n"/>
-      <c r="F177" s="3" t="n"/>
-      <c r="G177" s="3" t="n"/>
-    </row>
-    <row r="178">
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="32" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7242,7 +7409,12 @@
         </is>
       </c>
       <c r="E178" s="3" t="n"/>
-      <c r="F178" s="3" t="n"/>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>groupBy=ASIN+含leadAsins — 98.2%
+groupBy=AdType+含leadAsins — 1.8%</t>
+        </is>
+      </c>
       <c r="G178" s="3" t="n"/>
     </row>
     <row r="179">
@@ -7267,10 +7439,18 @@
         </is>
       </c>
       <c r="E179" s="3" t="n"/>
-      <c r="F179" s="3" t="n"/>
-      <c r="G179" s="3" t="n"/>
-    </row>
-    <row r="180">
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="16" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7292,10 +7472,14 @@
         </is>
       </c>
       <c r="E180" s="3" t="n"/>
-      <c r="F180" s="3" t="n"/>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G180" s="3" t="n"/>
     </row>
-    <row r="181">
+    <row r="181" ht="112" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7317,10 +7501,20 @@
         </is>
       </c>
       <c r="E181" s="3" t="n"/>
-      <c r="F181" s="3" t="n"/>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>marketPlaceId=1 — 29.4%
+不传marketPlaceId — 27.4%
+marketPlaceId=6 — 25.4%
+marketPlaceId=111172 — 8.2%
+marketPlaceId= — 4.0%
+marketPlaceId=3 — 2.6%
+marketPlaceId=7 — 1.0%</t>
+        </is>
+      </c>
       <c r="G181" s="3" t="n"/>
     </row>
-    <row r="182">
+    <row r="182" ht="32" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7342,10 +7536,15 @@
         </is>
       </c>
       <c r="E182" s="3" t="n"/>
-      <c r="F182" s="3" t="n"/>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>不含subReportId — 56.7%
+含subReportId — 43.3%</t>
+        </is>
+      </c>
       <c r="G182" s="3" t="n"/>
     </row>
-    <row r="183">
+    <row r="183" ht="16" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7367,10 +7566,14 @@
         </is>
       </c>
       <c r="E183" s="3" t="n"/>
-      <c r="F183" s="3" t="n"/>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G183" s="3" t="n"/>
     </row>
-    <row r="184">
+    <row r="184" ht="80" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7392,10 +7595,18 @@
         </is>
       </c>
       <c r="E184" s="3" t="n"/>
-      <c r="F184" s="3" t="n"/>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>reportTypes=[All] — 88.6%
+reportTypes=[DSP] — 4.0%
+reportTypes=[ids+] — 3.0%
+reportTypes=[SP] — 1.8%
+reportTypes=[SD] — 1.2%</t>
+        </is>
+      </c>
       <c r="G184" s="3" t="n"/>
     </row>
-    <row r="185">
+    <row r="185" ht="16" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7417,10 +7628,14 @@
         </is>
       </c>
       <c r="E185" s="3" t="n"/>
-      <c r="F185" s="3" t="n"/>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G185" s="3" t="n"/>
     </row>
-    <row r="186">
+    <row r="186" ht="96" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7442,10 +7657,19 @@
         </is>
       </c>
       <c r="E186" s="3" t="n"/>
-      <c r="F186" s="3" t="n"/>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>marketPlaceId=1 — 46.2%
+marketPlaceId=6 — 43.4%
+marketPlaceId=111172 — 4.8%
+不传marketPlaceId — 3.0%
+marketPlaceId=4 — 1.0%
+marketPlaceId=526970 — 1.0%</t>
+        </is>
+      </c>
       <c r="G186" s="3" t="n"/>
     </row>
-    <row r="187">
+    <row r="187" ht="16" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7467,10 +7691,14 @@
         </is>
       </c>
       <c r="E187" s="3" t="n"/>
-      <c r="F187" s="3" t="n"/>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G187" s="3" t="n"/>
     </row>
-    <row r="188">
+    <row r="188" ht="32" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7492,10 +7720,15 @@
         </is>
       </c>
       <c r="E188" s="3" t="n"/>
-      <c r="F188" s="3" t="n"/>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>首页 — 91.0%
+翻页(pageIndex&gt;1) — 9.0%</t>
+        </is>
+      </c>
       <c r="G188" s="3" t="n"/>
     </row>
-    <row r="189">
+    <row r="189" ht="16" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7517,10 +7750,14 @@
         </is>
       </c>
       <c r="E189" s="3" t="n"/>
-      <c r="F189" s="3" t="n"/>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>含matchTypes+含campaignIds — 100.0%</t>
+        </is>
+      </c>
       <c r="G189" s="3" t="n"/>
     </row>
-    <row r="190">
+    <row r="190" ht="160" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -7542,7 +7779,20 @@
         </is>
       </c>
       <c r="E190" s="3" t="n"/>
-      <c r="F190" s="3" t="n"/>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>marketPlaceId=1 — 45.0%
+marketPlaceId=6 — 29.4%
+marketPlaceId=4 — 7.4%
+marketPlaceId=111172 — 4.2%
+不传marketPlaceId — 4.0%
+marketPlaceId= — 3.0%
+marketPlaceId=3 — 2.2%
+marketPlaceId=338851 — 1.6%
+marketPlaceId=526970 — 1.6%
+marketPlaceId=328451 — 1.0%</t>
+        </is>
+      </c>
       <c r="G190" s="3" t="n"/>
     </row>
     <row r="191">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -990,9 +990,19 @@
       </c>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="F20" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>41% (7/17)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1492,9 +1502,19 @@
       </c>
       <c r="D41" s="3" t="n"/>
       <c r="E41" s="3" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
+      <c r="F41" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>55% (6/11)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1818,9 +1838,19 @@
       </c>
       <c r="D54" s="3" t="n"/>
       <c r="E54" s="3" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
+      <c r="F54" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>92% (11/12)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -16067,7 +16097,11 @@
       </c>
       <c r="E477" s="3" t="n"/>
       <c r="F477" s="3" t="n"/>
-      <c r="G477" s="3" t="n"/>
+      <c r="G477" s="5" t="inlineStr">
+        <is>
+          <t>写操作(应用受众推荐)，本轮只读优先未覆盖，需真实recommendationId，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -16091,8 +16125,16 @@
         </is>
       </c>
       <c r="E478" s="3" t="n"/>
-      <c r="F478" s="3" t="n"/>
-      <c r="G478" s="3" t="n"/>
+      <c r="F478" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G478" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -16117,7 +16159,11 @@
       </c>
       <c r="E479" s="3" t="n"/>
       <c r="F479" s="3" t="n"/>
-      <c r="G479" s="3" t="n"/>
+      <c r="G479" s="5" t="inlineStr">
+        <is>
+          <t>写操作(应用LineItem推荐)，本轮只读优先未覆盖，需真实recommendationId，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -16142,7 +16188,11 @@
       </c>
       <c r="E480" s="3" t="n"/>
       <c r="F480" s="3" t="n"/>
-      <c r="G480" s="3" t="n"/>
+      <c r="G480" s="5" t="inlineStr">
+        <is>
+          <t>写操作(应用Order推荐)，本轮只读优先未覆盖，需真实recommendationId，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -16167,7 +16217,11 @@
       </c>
       <c r="E481" s="3" t="n"/>
       <c r="F481" s="3" t="n"/>
-      <c r="G481" s="3" t="n"/>
+      <c r="G481" s="5" t="inlineStr">
+        <is>
+          <t>写操作(批量应用推荐)，本轮只读优先未覆盖，需真实recommendationId，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -16191,8 +16245,16 @@
         </is>
       </c>
       <c r="E482" s="3" t="n"/>
-      <c r="F482" s="3" t="n"/>
-      <c r="G482" s="3" t="n"/>
+      <c r="F482" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G482" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -16217,9 +16279,13 @@
       </c>
       <c r="E483" s="3" t="n"/>
       <c r="F483" s="3" t="n"/>
-      <c r="G483" s="3" t="n"/>
-    </row>
-    <row r="484">
+      <c r="G483" s="5" t="inlineStr">
+        <is>
+          <t>写操作(排除站点)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="484" ht="48" customHeight="1">
       <c r="A484" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16241,10 +16307,16 @@
         </is>
       </c>
       <c r="E484" s="3" t="n"/>
-      <c r="F484" s="3" t="n"/>
+      <c r="F484" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+含orderIds+state=[PENDING] — 57.0%
+无Advertiser过滤+含orderIds+state=[PENDING] — 38.2%
+无Advertiser过滤+含orderIds+state=[APPLYING,COMPLETED,Expected-failure,FAILED] — 4.0%</t>
+        </is>
+      </c>
       <c r="G484" s="3" t="n"/>
     </row>
-    <row r="485">
+    <row r="485" ht="32" customHeight="1">
       <c r="A485" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16266,10 +16338,15 @@
         </is>
       </c>
       <c r="E485" s="3" t="n"/>
-      <c r="F485" s="3" t="n"/>
+      <c r="F485" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+含orderTagIds — 69.8%
+按Advertiser过滤+含orderTagIds — 30.2%</t>
+        </is>
+      </c>
       <c r="G485" s="3" t="n"/>
     </row>
-    <row r="486">
+    <row r="486" ht="32" customHeight="1">
       <c r="A486" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16291,10 +16368,15 @@
         </is>
       </c>
       <c r="E486" s="3" t="n"/>
-      <c r="F486" s="3" t="n"/>
+      <c r="F486" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+含orderTagIds — 69.6%
+按Advertiser过滤+含orderTagIds — 30.4%</t>
+        </is>
+      </c>
       <c r="G486" s="3" t="n"/>
     </row>
-    <row r="487">
+    <row r="487" ht="32" customHeight="1">
       <c r="A487" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16316,10 +16398,15 @@
         </is>
       </c>
       <c r="E487" s="3" t="n"/>
-      <c r="F487" s="3" t="n"/>
+      <c r="F487" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+含orderTagIds — 75.6%
+按Advertiser过滤+含orderTagIds — 24.2%</t>
+        </is>
+      </c>
       <c r="G487" s="3" t="n"/>
     </row>
-    <row r="488">
+    <row r="488" ht="32" customHeight="1">
       <c r="A488" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16341,10 +16428,15 @@
         </is>
       </c>
       <c r="E488" s="3" t="n"/>
-      <c r="F488" s="3" t="n"/>
+      <c r="F488" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+含orderTagIds — 73.8%
+按Advertiser过滤+含orderTagIds — 26.0%</t>
+        </is>
+      </c>
       <c r="G488" s="3" t="n"/>
     </row>
-    <row r="489">
+    <row r="489" ht="32" customHeight="1">
       <c r="A489" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16366,10 +16458,15 @@
         </is>
       </c>
       <c r="E489" s="3" t="n"/>
-      <c r="F489" s="3" t="n"/>
+      <c r="F489" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+含orderTagIds — 71.8%
+按Advertiser过滤+含orderTagIds — 28.0%</t>
+        </is>
+      </c>
       <c r="G489" s="3" t="n"/>
     </row>
-    <row r="490">
+    <row r="490" ht="32" customHeight="1">
       <c r="A490" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16391,7 +16488,12 @@
         </is>
       </c>
       <c r="E490" s="3" t="n"/>
-      <c r="F490" s="3" t="n"/>
+      <c r="F490" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+含orderTagIds — 59.2%
+按Advertiser过滤+含orderTagIds — 40.8%</t>
+        </is>
+      </c>
       <c r="G490" s="3" t="n"/>
     </row>
     <row r="491">
@@ -16417,7 +16519,11 @@
       </c>
       <c r="E491" s="3" t="n"/>
       <c r="F491" s="3" t="n"/>
-      <c r="G491" s="3" t="n"/>
+      <c r="G491" s="5" t="inlineStr">
+        <is>
+          <t>写操作(更新推荐处理状态)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -16442,7 +16548,11 @@
       </c>
       <c r="E492" s="3" t="n"/>
       <c r="F492" s="3" t="n"/>
-      <c r="G492" s="3" t="n"/>
+      <c r="G492" s="5" t="inlineStr">
+        <is>
+          <t>写操作(更新自定义推荐值)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -16467,7 +16577,11 @@
       </c>
       <c r="E493" s="3" t="n"/>
       <c r="F493" s="3" t="n"/>
-      <c r="G493" s="3" t="n"/>
+      <c r="G493" s="5" t="inlineStr">
+        <is>
+          <t>写操作(更新推荐优先级)，本轮只读优先未覆盖，待补写操作测试</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -29015,8 +29129,16 @@
         </is>
       </c>
       <c r="E937" s="3" t="n"/>
-      <c r="F937" s="3" t="n"/>
-      <c r="G937" s="3" t="n"/>
+      <c r="F937" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G937" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="938">
       <c r="A938" s="2" t="inlineStr">
@@ -29040,8 +29162,16 @@
         </is>
       </c>
       <c r="E938" s="3" t="n"/>
-      <c r="F938" s="3" t="n"/>
-      <c r="G938" s="3" t="n"/>
+      <c r="F938" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G938" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="939">
       <c r="A939" s="2" t="inlineStr">
@@ -29065,10 +29195,18 @@
         </is>
       </c>
       <c r="E939" s="3" t="n"/>
-      <c r="F939" s="3" t="n"/>
-      <c r="G939" s="3" t="n"/>
-    </row>
-    <row r="940">
+      <c r="F939" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G939" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="940" ht="80" customHeight="1">
       <c r="A940" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -29090,10 +29228,18 @@
         </is>
       </c>
       <c r="E940" s="3" t="n"/>
-      <c r="F940" s="3" t="n"/>
+      <c r="F940" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含compareStart — 62.7%
+按Advertiser过滤+无Order过滤+含compareStart — 14.6%
+按Advertiser过滤+按Order过滤+不含compareStart — 12.7%
+无Advertiser过滤+无Order过滤+不含compareStart — 6.7%
+按Advertiser过滤+按Order过滤+含compareStart — 2.2%</t>
+        </is>
+      </c>
       <c r="G940" s="3" t="n"/>
     </row>
-    <row r="941">
+    <row r="941" ht="80" customHeight="1">
       <c r="A941" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -29115,10 +29261,18 @@
         </is>
       </c>
       <c r="E941" s="3" t="n"/>
-      <c r="F941" s="3" t="n"/>
+      <c r="F941" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含compareStart — 70.6%
+按Advertiser过滤+无Order过滤+含compareStart — 15.0%
+无Advertiser过滤+无Order过滤+不含compareStart — 6.4%
+按Advertiser过滤+按Order过滤+不含compareStart — 6.2%
+按Advertiser过滤+按Order过滤+含compareStart — 1.8%</t>
+        </is>
+      </c>
       <c r="G941" s="3" t="n"/>
     </row>
-    <row r="942">
+    <row r="942" ht="80" customHeight="1">
       <c r="A942" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -29140,7 +29294,15 @@
         </is>
       </c>
       <c r="E942" s="3" t="n"/>
-      <c r="F942" s="3" t="n"/>
+      <c r="F942" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+不含compareStart — 67.8%
+按Advertiser过滤+无Order过滤+含compareStart — 18.6%
+无Advertiser过滤+无Order过滤+不含compareStart — 7.0%
+按Advertiser过滤+按Order过滤+不含compareStart — 4.8%
+按Advertiser过滤+按Order过滤+含compareStart — 1.0%</t>
+        </is>
+      </c>
       <c r="G942" s="3" t="n"/>
     </row>
     <row r="943">
@@ -29165,10 +29327,18 @@
         </is>
       </c>
       <c r="E943" s="3" t="n"/>
-      <c r="F943" s="3" t="n"/>
-      <c r="G943" s="3" t="n"/>
-    </row>
-    <row r="944">
+      <c r="F943" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G943" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="944" ht="16" customHeight="1">
       <c r="A944" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -29190,10 +29360,14 @@
         </is>
       </c>
       <c r="E944" s="3" t="n"/>
-      <c r="F944" s="3" t="n"/>
+      <c r="F944" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G944" s="3" t="n"/>
     </row>
-    <row r="945">
+    <row r="945" ht="16" customHeight="1">
       <c r="A945" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -29215,10 +29389,14 @@
         </is>
       </c>
       <c r="E945" s="3" t="n"/>
-      <c r="F945" s="3" t="n"/>
+      <c r="F945" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G945" s="3" t="n"/>
     </row>
-    <row r="946">
+    <row r="946" ht="48" customHeight="1">
       <c r="A946" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -29240,7 +29418,13 @@
         </is>
       </c>
       <c r="E946" s="3" t="n"/>
-      <c r="F946" s="3" t="n"/>
+      <c r="F946" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤+含compareStart — 85.4%
+无Advertiser过滤+无Order过滤+含compareStart — 7.8%
+按Advertiser过滤+按Order过滤+含compareStart — 6.6%</t>
+        </is>
+      </c>
       <c r="G946" s="3" t="n"/>
     </row>
     <row r="947">
@@ -29265,8 +29449,16 @@
         </is>
       </c>
       <c r="E947" s="3" t="n"/>
-      <c r="F947" s="3" t="n"/>
-      <c r="G947" s="3" t="n"/>
+      <c r="F947" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G947" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="948">
       <c r="A948" s="2" t="inlineStr">
@@ -35171,7 +35363,7 @@
         </is>
       </c>
     </row>
-    <row r="1171">
+    <row r="1171" ht="16" customHeight="1">
       <c r="A1171" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35193,10 +35385,14 @@
         </is>
       </c>
       <c r="E1171" s="3" t="n"/>
-      <c r="F1171" s="3" t="n"/>
+      <c r="F1171" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1171" s="3" t="n"/>
     </row>
-    <row r="1172">
+    <row r="1172" ht="16" customHeight="1">
       <c r="A1172" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35218,10 +35414,14 @@
         </is>
       </c>
       <c r="E1172" s="3" t="n"/>
-      <c r="F1172" s="3" t="n"/>
+      <c r="F1172" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1172" s="3" t="n"/>
     </row>
-    <row r="1173">
+    <row r="1173" ht="16" customHeight="1">
       <c r="A1173" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35243,7 +35443,11 @@
         </is>
       </c>
       <c r="E1173" s="3" t="n"/>
-      <c r="F1173" s="3" t="n"/>
+      <c r="F1173" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1173" s="3" t="n"/>
     </row>
     <row r="1174">
@@ -35268,10 +35472,18 @@
         </is>
       </c>
       <c r="E1174" s="3" t="n"/>
-      <c r="F1174" s="3" t="n"/>
-      <c r="G1174" s="3" t="n"/>
-    </row>
-    <row r="1175">
+      <c r="F1174" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1174" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175" ht="16" customHeight="1">
       <c r="A1175" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35293,10 +35505,14 @@
         </is>
       </c>
       <c r="E1175" s="3" t="n"/>
-      <c r="F1175" s="3" t="n"/>
+      <c r="F1175" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1175" s="3" t="n"/>
     </row>
-    <row r="1176">
+    <row r="1176" ht="16" customHeight="1">
       <c r="A1176" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35318,10 +35534,14 @@
         </is>
       </c>
       <c r="E1176" s="3" t="n"/>
-      <c r="F1176" s="3" t="n"/>
+      <c r="F1176" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1176" s="3" t="n"/>
     </row>
-    <row r="1177">
+    <row r="1177" ht="16" customHeight="1">
       <c r="A1177" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35343,10 +35563,14 @@
         </is>
       </c>
       <c r="E1177" s="3" t="n"/>
-      <c r="F1177" s="3" t="n"/>
+      <c r="F1177" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1177" s="3" t="n"/>
     </row>
-    <row r="1178">
+    <row r="1178" ht="16" customHeight="1">
       <c r="A1178" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35368,10 +35592,14 @@
         </is>
       </c>
       <c r="E1178" s="3" t="n"/>
-      <c r="F1178" s="3" t="n"/>
+      <c r="F1178" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1178" s="3" t="n"/>
     </row>
-    <row r="1179">
+    <row r="1179" ht="16" customHeight="1">
       <c r="A1179" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35393,10 +35621,14 @@
         </is>
       </c>
       <c r="E1179" s="3" t="n"/>
-      <c r="F1179" s="3" t="n"/>
+      <c r="F1179" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1179" s="3" t="n"/>
     </row>
-    <row r="1180">
+    <row r="1180" ht="16" customHeight="1">
       <c r="A1180" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35418,10 +35650,14 @@
         </is>
       </c>
       <c r="E1180" s="3" t="n"/>
-      <c r="F1180" s="3" t="n"/>
+      <c r="F1180" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1180" s="3" t="n"/>
     </row>
-    <row r="1181">
+    <row r="1181" ht="16" customHeight="1">
       <c r="A1181" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35443,10 +35679,14 @@
         </is>
       </c>
       <c r="E1181" s="3" t="n"/>
-      <c r="F1181" s="3" t="n"/>
+      <c r="F1181" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1181" s="3" t="n"/>
     </row>
-    <row r="1182">
+    <row r="1182" ht="16" customHeight="1">
       <c r="A1182" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35468,7 +35708,11 @@
         </is>
       </c>
       <c r="E1182" s="3" t="n"/>
-      <c r="F1182" s="3" t="n"/>
+      <c r="F1182" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1182" s="3" t="n"/>
     </row>
     <row r="1183">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1936,9 +1936,19 @@
       </c>
       <c r="D58" s="3" t="n"/>
       <c r="E58" s="3" t="n"/>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="n"/>
+      <c r="F58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>4% (2/56)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -36612,8 +36622,16 @@
         </is>
       </c>
       <c r="E1218" s="3" t="n"/>
-      <c r="F1218" s="3" t="n"/>
-      <c r="G1218" s="3" t="n"/>
+      <c r="F1218" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1218" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1219">
       <c r="A1219" s="2" t="inlineStr">
@@ -36637,8 +36655,16 @@
         </is>
       </c>
       <c r="E1219" s="3" t="n"/>
-      <c r="F1219" s="3" t="n"/>
-      <c r="G1219" s="3" t="n"/>
+      <c r="F1219" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1219" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1220">
       <c r="A1220" s="2" t="inlineStr">
@@ -36662,8 +36688,16 @@
         </is>
       </c>
       <c r="E1220" s="3" t="n"/>
-      <c r="F1220" s="3" t="n"/>
-      <c r="G1220" s="3" t="n"/>
+      <c r="F1220" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1220" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1221">
       <c r="A1221" s="2" t="inlineStr">
@@ -36687,8 +36721,16 @@
         </is>
       </c>
       <c r="E1221" s="3" t="n"/>
-      <c r="F1221" s="3" t="n"/>
-      <c r="G1221" s="3" t="n"/>
+      <c r="F1221" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1221" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1222">
       <c r="A1222" s="2" t="inlineStr">
@@ -36712,8 +36754,16 @@
         </is>
       </c>
       <c r="E1222" s="3" t="n"/>
-      <c r="F1222" s="3" t="n"/>
-      <c r="G1222" s="3" t="n"/>
+      <c r="F1222" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1222" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1223">
       <c r="A1223" s="2" t="inlineStr">
@@ -36737,8 +36787,16 @@
         </is>
       </c>
       <c r="E1223" s="3" t="n"/>
-      <c r="F1223" s="3" t="n"/>
-      <c r="G1223" s="3" t="n"/>
+      <c r="F1223" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1223" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1224">
       <c r="A1224" s="2" t="inlineStr">
@@ -36762,8 +36820,16 @@
         </is>
       </c>
       <c r="E1224" s="3" t="n"/>
-      <c r="F1224" s="3" t="n"/>
-      <c r="G1224" s="3" t="n"/>
+      <c r="F1224" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1224" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1225">
       <c r="A1225" s="2" t="inlineStr">
@@ -36787,8 +36853,16 @@
         </is>
       </c>
       <c r="E1225" s="3" t="n"/>
-      <c r="F1225" s="3" t="n"/>
-      <c r="G1225" s="3" t="n"/>
+      <c r="F1225" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1225" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1226">
       <c r="A1226" s="2" t="inlineStr">
@@ -36812,8 +36886,16 @@
         </is>
       </c>
       <c r="E1226" s="3" t="n"/>
-      <c r="F1226" s="3" t="n"/>
-      <c r="G1226" s="3" t="n"/>
+      <c r="F1226" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1226" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1227">
       <c r="A1227" s="2" t="inlineStr">
@@ -36837,8 +36919,16 @@
         </is>
       </c>
       <c r="E1227" s="3" t="n"/>
-      <c r="F1227" s="3" t="n"/>
-      <c r="G1227" s="3" t="n"/>
+      <c r="F1227" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1227" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1228">
       <c r="A1228" s="2" t="inlineStr">
@@ -36862,8 +36952,16 @@
         </is>
       </c>
       <c r="E1228" s="3" t="n"/>
-      <c r="F1228" s="3" t="n"/>
-      <c r="G1228" s="3" t="n"/>
+      <c r="F1228" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1228" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1229">
       <c r="A1229" s="2" t="inlineStr">
@@ -36887,8 +36985,16 @@
         </is>
       </c>
       <c r="E1229" s="3" t="n"/>
-      <c r="F1229" s="3" t="n"/>
-      <c r="G1229" s="3" t="n"/>
+      <c r="F1229" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1229" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1230">
       <c r="A1230" s="2" t="inlineStr">
@@ -36912,8 +37018,16 @@
         </is>
       </c>
       <c r="E1230" s="3" t="n"/>
-      <c r="F1230" s="3" t="n"/>
-      <c r="G1230" s="3" t="n"/>
+      <c r="F1230" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1230" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1231">
       <c r="A1231" s="2" t="inlineStr">
@@ -36937,8 +37051,16 @@
         </is>
       </c>
       <c r="E1231" s="3" t="n"/>
-      <c r="F1231" s="3" t="n"/>
-      <c r="G1231" s="3" t="n"/>
+      <c r="F1231" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1231" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1232">
       <c r="A1232" s="2" t="inlineStr">
@@ -36962,8 +37084,16 @@
         </is>
       </c>
       <c r="E1232" s="3" t="n"/>
-      <c r="F1232" s="3" t="n"/>
-      <c r="G1232" s="3" t="n"/>
+      <c r="F1232" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1232" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1233">
       <c r="A1233" s="2" t="inlineStr">
@@ -36987,8 +37117,16 @@
         </is>
       </c>
       <c r="E1233" s="3" t="n"/>
-      <c r="F1233" s="3" t="n"/>
-      <c r="G1233" s="3" t="n"/>
+      <c r="F1233" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1233" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1234">
       <c r="A1234" s="2" t="inlineStr">
@@ -37012,8 +37150,16 @@
         </is>
       </c>
       <c r="E1234" s="3" t="n"/>
-      <c r="F1234" s="3" t="n"/>
-      <c r="G1234" s="3" t="n"/>
+      <c r="F1234" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1234" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1235">
       <c r="A1235" s="2" t="inlineStr">
@@ -37037,8 +37183,16 @@
         </is>
       </c>
       <c r="E1235" s="3" t="n"/>
-      <c r="F1235" s="3" t="n"/>
-      <c r="G1235" s="3" t="n"/>
+      <c r="F1235" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1235" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1236">
       <c r="A1236" s="2" t="inlineStr">
@@ -37062,8 +37216,16 @@
         </is>
       </c>
       <c r="E1236" s="3" t="n"/>
-      <c r="F1236" s="3" t="n"/>
-      <c r="G1236" s="3" t="n"/>
+      <c r="F1236" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1236" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1237">
       <c r="A1237" s="2" t="inlineStr">
@@ -37087,8 +37249,16 @@
         </is>
       </c>
       <c r="E1237" s="3" t="n"/>
-      <c r="F1237" s="3" t="n"/>
-      <c r="G1237" s="3" t="n"/>
+      <c r="F1237" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1237" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1238">
       <c r="A1238" s="2" t="inlineStr">
@@ -37112,8 +37282,16 @@
         </is>
       </c>
       <c r="E1238" s="3" t="n"/>
-      <c r="F1238" s="3" t="n"/>
-      <c r="G1238" s="3" t="n"/>
+      <c r="F1238" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1238" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1239">
       <c r="A1239" s="2" t="inlineStr">
@@ -37137,8 +37315,16 @@
         </is>
       </c>
       <c r="E1239" s="3" t="n"/>
-      <c r="F1239" s="3" t="n"/>
-      <c r="G1239" s="3" t="n"/>
+      <c r="F1239" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1239" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1240">
       <c r="A1240" s="2" t="inlineStr">
@@ -37162,8 +37348,16 @@
         </is>
       </c>
       <c r="E1240" s="3" t="n"/>
-      <c r="F1240" s="3" t="n"/>
-      <c r="G1240" s="3" t="n"/>
+      <c r="F1240" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1240" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1241">
       <c r="A1241" s="2" t="inlineStr">
@@ -37187,8 +37381,16 @@
         </is>
       </c>
       <c r="E1241" s="3" t="n"/>
-      <c r="F1241" s="3" t="n"/>
-      <c r="G1241" s="3" t="n"/>
+      <c r="F1241" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1241" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1242">
       <c r="A1242" s="2" t="inlineStr">
@@ -37212,8 +37414,16 @@
         </is>
       </c>
       <c r="E1242" s="3" t="n"/>
-      <c r="F1242" s="3" t="n"/>
-      <c r="G1242" s="3" t="n"/>
+      <c r="F1242" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1242" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1243">
       <c r="A1243" s="2" t="inlineStr">
@@ -37237,8 +37447,16 @@
         </is>
       </c>
       <c r="E1243" s="3" t="n"/>
-      <c r="F1243" s="3" t="n"/>
-      <c r="G1243" s="3" t="n"/>
+      <c r="F1243" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1243" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1244">
       <c r="A1244" s="2" t="inlineStr">
@@ -37262,8 +37480,16 @@
         </is>
       </c>
       <c r="E1244" s="3" t="n"/>
-      <c r="F1244" s="3" t="n"/>
-      <c r="G1244" s="3" t="n"/>
+      <c r="F1244" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1244" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1245">
       <c r="A1245" s="2" t="inlineStr">
@@ -37287,8 +37513,16 @@
         </is>
       </c>
       <c r="E1245" s="3" t="n"/>
-      <c r="F1245" s="3" t="n"/>
-      <c r="G1245" s="3" t="n"/>
+      <c r="F1245" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1245" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1246">
       <c r="A1246" s="2" t="inlineStr">
@@ -37312,8 +37546,16 @@
         </is>
       </c>
       <c r="E1246" s="3" t="n"/>
-      <c r="F1246" s="3" t="n"/>
-      <c r="G1246" s="3" t="n"/>
+      <c r="F1246" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1246" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1247">
       <c r="A1247" s="2" t="inlineStr">
@@ -37337,8 +37579,16 @@
         </is>
       </c>
       <c r="E1247" s="3" t="n"/>
-      <c r="F1247" s="3" t="n"/>
-      <c r="G1247" s="3" t="n"/>
+      <c r="F1247" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1247" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1248">
       <c r="A1248" s="2" t="inlineStr">
@@ -37362,8 +37612,16 @@
         </is>
       </c>
       <c r="E1248" s="3" t="n"/>
-      <c r="F1248" s="3" t="n"/>
-      <c r="G1248" s="3" t="n"/>
+      <c r="F1248" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1248" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1249">
       <c r="A1249" s="2" t="inlineStr">
@@ -37387,8 +37645,16 @@
         </is>
       </c>
       <c r="E1249" s="3" t="n"/>
-      <c r="F1249" s="3" t="n"/>
-      <c r="G1249" s="3" t="n"/>
+      <c r="F1249" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1249" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1250">
       <c r="A1250" s="2" t="inlineStr">
@@ -37412,8 +37678,16 @@
         </is>
       </c>
       <c r="E1250" s="3" t="n"/>
-      <c r="F1250" s="3" t="n"/>
-      <c r="G1250" s="3" t="n"/>
+      <c r="F1250" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1250" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1251">
       <c r="A1251" s="2" t="inlineStr">
@@ -37437,8 +37711,16 @@
         </is>
       </c>
       <c r="E1251" s="3" t="n"/>
-      <c r="F1251" s="3" t="n"/>
-      <c r="G1251" s="3" t="n"/>
+      <c r="F1251" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1251" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1252">
       <c r="A1252" s="2" t="inlineStr">
@@ -37462,8 +37744,16 @@
         </is>
       </c>
       <c r="E1252" s="3" t="n"/>
-      <c r="F1252" s="3" t="n"/>
-      <c r="G1252" s="3" t="n"/>
+      <c r="F1252" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1252" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1253">
       <c r="A1253" s="2" t="inlineStr">
@@ -37487,8 +37777,16 @@
         </is>
       </c>
       <c r="E1253" s="3" t="n"/>
-      <c r="F1253" s="3" t="n"/>
-      <c r="G1253" s="3" t="n"/>
+      <c r="F1253" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1253" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1254">
       <c r="A1254" s="2" t="inlineStr">
@@ -37512,8 +37810,16 @@
         </is>
       </c>
       <c r="E1254" s="3" t="n"/>
-      <c r="F1254" s="3" t="n"/>
-      <c r="G1254" s="3" t="n"/>
+      <c r="F1254" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1254" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1255">
       <c r="A1255" s="2" t="inlineStr">
@@ -37537,8 +37843,16 @@
         </is>
       </c>
       <c r="E1255" s="3" t="n"/>
-      <c r="F1255" s="3" t="n"/>
-      <c r="G1255" s="3" t="n"/>
+      <c r="F1255" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1255" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1256">
       <c r="A1256" s="2" t="inlineStr">
@@ -37562,8 +37876,16 @@
         </is>
       </c>
       <c r="E1256" s="3" t="n"/>
-      <c r="F1256" s="3" t="n"/>
-      <c r="G1256" s="3" t="n"/>
+      <c r="F1256" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1256" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1257">
       <c r="A1257" s="2" t="inlineStr">
@@ -37587,8 +37909,16 @@
         </is>
       </c>
       <c r="E1257" s="3" t="n"/>
-      <c r="F1257" s="3" t="n"/>
-      <c r="G1257" s="3" t="n"/>
+      <c r="F1257" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1257" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1258">
       <c r="A1258" s="2" t="inlineStr">
@@ -37612,8 +37942,16 @@
         </is>
       </c>
       <c r="E1258" s="3" t="n"/>
-      <c r="F1258" s="3" t="n"/>
-      <c r="G1258" s="3" t="n"/>
+      <c r="F1258" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1258" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1259">
       <c r="A1259" s="2" t="inlineStr">
@@ -37637,10 +37975,18 @@
         </is>
       </c>
       <c r="E1259" s="3" t="n"/>
-      <c r="F1259" s="3" t="n"/>
-      <c r="G1259" s="3" t="n"/>
-    </row>
-    <row r="1260">
+      <c r="F1259" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1259" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260" ht="80" customHeight="1">
       <c r="A1260" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -37662,7 +38008,15 @@
         </is>
       </c>
       <c r="E1260" s="3" t="n"/>
-      <c r="F1260" s="3" t="n"/>
+      <c r="F1260" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+comparisonSetting=0 — 77.2%
+timeType=3+comparisonSetting=1 — 11.2%
+timeType=2+comparisonSetting=0 — 8.4%
+timeType=3+不传comparisonSetting — 1.9%
+timeType=2+comparisonSetting=1 — 1.4%</t>
+        </is>
+      </c>
       <c r="G1260" s="3" t="n"/>
     </row>
     <row r="1261">
@@ -37687,8 +38041,16 @@
         </is>
       </c>
       <c r="E1261" s="3" t="n"/>
-      <c r="F1261" s="3" t="n"/>
-      <c r="G1261" s="3" t="n"/>
+      <c r="F1261" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1261" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1262">
       <c r="A1262" s="2" t="inlineStr">
@@ -37712,8 +38074,16 @@
         </is>
       </c>
       <c r="E1262" s="3" t="n"/>
-      <c r="F1262" s="3" t="n"/>
-      <c r="G1262" s="3" t="n"/>
+      <c r="F1262" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1262" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1263">
       <c r="A1263" s="2" t="inlineStr">
@@ -37737,8 +38107,16 @@
         </is>
       </c>
       <c r="E1263" s="3" t="n"/>
-      <c r="F1263" s="3" t="n"/>
-      <c r="G1263" s="3" t="n"/>
+      <c r="F1263" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1263" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1264">
       <c r="A1264" s="2" t="inlineStr">
@@ -37762,8 +38140,16 @@
         </is>
       </c>
       <c r="E1264" s="3" t="n"/>
-      <c r="F1264" s="3" t="n"/>
-      <c r="G1264" s="3" t="n"/>
+      <c r="F1264" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1264" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1265">
       <c r="A1265" s="2" t="inlineStr">
@@ -37787,10 +38173,18 @@
         </is>
       </c>
       <c r="E1265" s="3" t="n"/>
-      <c r="F1265" s="3" t="n"/>
-      <c r="G1265" s="3" t="n"/>
-    </row>
-    <row r="1266">
+      <c r="F1265" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1265" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266" ht="80" customHeight="1">
       <c r="A1266" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -37812,7 +38206,15 @@
         </is>
       </c>
       <c r="E1266" s="3" t="n"/>
-      <c r="F1266" s="3" t="n"/>
+      <c r="F1266" s="6" t="inlineStr">
+        <is>
+          <t>timeType=3+comparisonSetting=0 — 77.2%
+timeType=3+comparisonSetting=1 — 11.2%
+timeType=2+comparisonSetting=0 — 8.4%
+timeType=3+不传comparisonSetting — 1.9%
+timeType=2+comparisonSetting=1 — 1.4%</t>
+        </is>
+      </c>
       <c r="G1266" s="3" t="n"/>
     </row>
     <row r="1267">
@@ -37837,8 +38239,16 @@
         </is>
       </c>
       <c r="E1267" s="3" t="n"/>
-      <c r="F1267" s="3" t="n"/>
-      <c r="G1267" s="3" t="n"/>
+      <c r="F1267" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1267" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1268">
       <c r="A1268" s="2" t="inlineStr">
@@ -37862,8 +38272,16 @@
         </is>
       </c>
       <c r="E1268" s="3" t="n"/>
-      <c r="F1268" s="3" t="n"/>
-      <c r="G1268" s="3" t="n"/>
+      <c r="F1268" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1268" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1269">
       <c r="A1269" s="2" t="inlineStr">
@@ -37887,8 +38305,16 @@
         </is>
       </c>
       <c r="E1269" s="3" t="n"/>
-      <c r="F1269" s="3" t="n"/>
-      <c r="G1269" s="3" t="n"/>
+      <c r="F1269" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1269" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1270">
       <c r="A1270" s="2" t="inlineStr">
@@ -37912,8 +38338,16 @@
         </is>
       </c>
       <c r="E1270" s="3" t="n"/>
-      <c r="F1270" s="3" t="n"/>
-      <c r="G1270" s="3" t="n"/>
+      <c r="F1270" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1270" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1271">
       <c r="A1271" s="2" t="inlineStr">
@@ -37937,8 +38371,16 @@
         </is>
       </c>
       <c r="E1271" s="3" t="n"/>
-      <c r="F1271" s="3" t="n"/>
-      <c r="G1271" s="3" t="n"/>
+      <c r="F1271" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1271" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1272">
       <c r="A1272" s="2" t="inlineStr">
@@ -37962,8 +38404,16 @@
         </is>
       </c>
       <c r="E1272" s="3" t="n"/>
-      <c r="F1272" s="3" t="n"/>
-      <c r="G1272" s="3" t="n"/>
+      <c r="F1272" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1272" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1273">
       <c r="A1273" s="2" t="inlineStr">
@@ -37987,8 +38437,16 @@
         </is>
       </c>
       <c r="E1273" s="3" t="n"/>
-      <c r="F1273" s="3" t="n"/>
-      <c r="G1273" s="3" t="n"/>
+      <c r="F1273" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1273" s="5" t="inlineStr">
+        <is>
+          <t>365天0次真实调用，按规则不生成/不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1274">
       <c r="A1274" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -731,7 +731,7 @@
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85% (28/33)</t>
+          <t>88% (29/33)</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76% (28/37)</t>
+          <t>78% (29/37)</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41% (7/17)</t>
+          <t>88% (15/17)</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       <c r="F120" s="3" t="n"/>
       <c r="G120" s="3" t="n"/>
     </row>
-    <row r="121">
+    <row r="121" ht="16" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5705,7 +5705,11 @@
         </is>
       </c>
       <c r="E121" s="3" t="n"/>
-      <c r="F121" s="3" t="n"/>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>激活custom model(entity=7582522080201/DSP,model=model highpotential)</t>
+        </is>
+      </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
           <t>写操作(激活自定义模型)，本轮只读优先未覆盖，待补写操作测试</t>
@@ -6733,7 +6737,7 @@
       </c>
       <c r="G155" s="3" t="n"/>
     </row>
-    <row r="156">
+    <row r="156" ht="16" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6755,10 +6759,14 @@
         </is>
       </c>
       <c r="E156" s="3" t="n"/>
-      <c r="F156" s="3" t="n"/>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>【技术受限-仅生成不执行】POST /api/AmcExploration/EditCustomSqlViewInHistory</t>
+        </is>
+      </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>写操作(编辑自定义SQL报表列配置)，本轮只读优先未覆盖，待补写操作测试</t>
+          <t>编辑自定义SQL报表历史记录的列配置，需要测试账号自己产生的historyId；已实测GetAMCCustomSqlExplorationList查询本账号(profile 1251036855266063/advertiser 578107614358724215)返回Data=null，且本swagger范围内无可创建自定义SQL探索历史记录的写接口(仅能通过AMC控制台UI或AmcAgent AI对话产生)，无法自建安全测试数据，未使用ES样本里其他客户的historyId(会误改他人保存的报表视图)，故技术受限未执行。2026-09-21</t>
         </is>
       </c>
     </row>
@@ -16084,7 +16092,7 @@
       <c r="F476" s="3" t="n"/>
       <c r="G476" s="3" t="n"/>
     </row>
-    <row r="477">
+    <row r="477" ht="16" customHeight="1">
       <c r="A477" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16106,10 +16114,14 @@
         </is>
       </c>
       <c r="E477" s="3" t="n"/>
-      <c r="F477" s="3" t="n"/>
+      <c r="F477" s="6" t="inlineStr">
+        <is>
+          <t>【技术受限-仅生成不执行】POST AuditV2/ApplyAudiences</t>
+        </is>
+      </c>
       <c r="G477" s="5" t="inlineStr">
         <is>
-          <t>写操作(应用受众推荐)，本轮只读优先未覆盖，需真实recommendationId，待补写操作测试</t>
+          <t>应用推荐类接口，需要真实存在的recommendationId；已实测测试账号advertiser 578107614358724215下GetRecommendationOverviewTop返回PendingCount/HighPriorityCount/CompletedCount全部为0，GetRecommendationDetailList/GetRecommendationOverview*List(Audience/Creative/LineItem/Order/Site)全部返回空列表(TotalDataCount=0)，账号无任何真实推荐(含系统生成的)。同Walmart Recommendations模块先例，未使用ES样本里其他客户的recommendationId，判定技术受限未执行。2026-09-21</t>
         </is>
       </c>
     </row>
@@ -16146,7 +16158,7 @@
         </is>
       </c>
     </row>
-    <row r="479">
+    <row r="479" ht="16" customHeight="1">
       <c r="A479" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16168,14 +16180,18 @@
         </is>
       </c>
       <c r="E479" s="3" t="n"/>
-      <c r="F479" s="3" t="n"/>
+      <c r="F479" s="6" t="inlineStr">
+        <is>
+          <t>【技术受限-仅生成不执行】POST AuditV2/ApplyLineItem</t>
+        </is>
+      </c>
       <c r="G479" s="5" t="inlineStr">
         <is>
-          <t>写操作(应用LineItem推荐)，本轮只读优先未覆盖，需真实recommendationId，待补写操作测试</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
+          <t>应用推荐类接口，需要真实存在的recommendationId；已实测测试账号advertiser 578107614358724215下GetRecommendationOverviewTop返回PendingCount/HighPriorityCount/CompletedCount全部为0，GetRecommendationDetailList/GetRecommendationOverview*List(Audience/Creative/LineItem/Order/Site)全部返回空列表(TotalDataCount=0)，账号无任何真实推荐(含系统生成的)。同Walmart Recommendations模块先例，未使用ES样本里其他客户的recommendationId，判定技术受限未执行。2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="16" customHeight="1">
       <c r="A480" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16197,14 +16213,18 @@
         </is>
       </c>
       <c r="E480" s="3" t="n"/>
-      <c r="F480" s="3" t="n"/>
+      <c r="F480" s="6" t="inlineStr">
+        <is>
+          <t>【技术受限-仅生成不执行】POST AuditV2/ApplyOrder</t>
+        </is>
+      </c>
       <c r="G480" s="5" t="inlineStr">
         <is>
-          <t>写操作(应用Order推荐)，本轮只读优先未覆盖，需真实recommendationId，待补写操作测试</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
+          <t>应用推荐类接口，需要真实存在的recommendationId；已实测测试账号advertiser 578107614358724215下GetRecommendationOverviewTop返回PendingCount/HighPriorityCount/CompletedCount全部为0，GetRecommendationDetailList/GetRecommendationOverview*List(Audience/Creative/LineItem/Order/Site)全部返回空列表(TotalDataCount=0)，账号无任何真实推荐(含系统生成的)。同Walmart Recommendations模块先例，未使用ES样本里其他客户的recommendationId，判定技术受限未执行。2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" ht="16" customHeight="1">
       <c r="A481" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16226,10 +16246,14 @@
         </is>
       </c>
       <c r="E481" s="3" t="n"/>
-      <c r="F481" s="3" t="n"/>
+      <c r="F481" s="6" t="inlineStr">
+        <is>
+          <t>【技术受限-仅生成不执行】POST AuditV2/ApplyRecommendations</t>
+        </is>
+      </c>
       <c r="G481" s="5" t="inlineStr">
         <is>
-          <t>写操作(批量应用推荐)，本轮只读优先未覆盖，需真实recommendationId，待补写操作测试</t>
+          <t>应用推荐类接口，需要真实存在的recommendationId；已实测测试账号advertiser 578107614358724215下GetRecommendationOverviewTop返回PendingCount/HighPriorityCount/CompletedCount全部为0，GetRecommendationDetailList/GetRecommendationOverview*List(Audience/Creative/LineItem/Order/Site)全部返回空列表(TotalDataCount=0)，账号无任何真实推荐(含系统生成的)。同Walmart Recommendations模块先例，未使用ES样本里其他客户的recommendationId，判定技术受限未执行。2026-09-21</t>
         </is>
       </c>
     </row>
@@ -16266,7 +16290,7 @@
         </is>
       </c>
     </row>
-    <row r="483">
+    <row r="483" ht="16" customHeight="1">
       <c r="A483" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16288,10 +16312,14 @@
         </is>
       </c>
       <c r="E483" s="3" t="n"/>
-      <c r="F483" s="3" t="n"/>
+      <c r="F483" s="6" t="inlineStr">
+        <is>
+          <t>【技术受限-仅生成不执行】POST AuditV2/ExcludeSite</t>
+        </is>
+      </c>
       <c r="G483" s="5" t="inlineStr">
         <is>
-          <t>写操作(排除站点)，本轮只读优先未覆盖，待补写操作测试</t>
+          <t>修改本账号'处理某条推荐'的状态/站点排除/自定义值/优先级，操作对象是已存在的真实推荐ID；已实测测试账号advertiser 578107614358724215下无任何真实推荐(含系统生成的，GetRecommendationOverviewTop各项计数均为0)，无可用推荐可安全设计'改状态→改回'类case，未使用ES样本里其他客户的推荐数据，判定技术受限未执行。2026-09-21</t>
         </is>
       </c>
     </row>
@@ -16506,7 +16534,7 @@
       </c>
       <c r="G490" s="3" t="n"/>
     </row>
-    <row r="491">
+    <row r="491" ht="16" customHeight="1">
       <c r="A491" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16528,14 +16556,18 @@
         </is>
       </c>
       <c r="E491" s="3" t="n"/>
-      <c r="F491" s="3" t="n"/>
+      <c r="F491" s="6" t="inlineStr">
+        <is>
+          <t>【技术受限-仅生成不执行】POST AuditV2/UpdateActionStatusV2</t>
+        </is>
+      </c>
       <c r="G491" s="5" t="inlineStr">
         <is>
-          <t>写操作(更新推荐处理状态)，本轮只读优先未覆盖，待补写操作测试</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
+          <t>修改本账号'处理某条推荐'的状态/站点排除/自定义值/优先级，操作对象是已存在的真实推荐ID；已实测测试账号advertiser 578107614358724215下无任何真实推荐(含系统生成的，GetRecommendationOverviewTop各项计数均为0)，无可用推荐可安全设计'改状态→改回'类case，未使用ES样本里其他客户的推荐数据，判定技术受限未执行。2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" ht="16" customHeight="1">
       <c r="A492" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16557,14 +16589,18 @@
         </is>
       </c>
       <c r="E492" s="3" t="n"/>
-      <c r="F492" s="3" t="n"/>
+      <c r="F492" s="6" t="inlineStr">
+        <is>
+          <t>【技术受限-仅生成不执行】POST AuditV2/UpdateCustomNewValue</t>
+        </is>
+      </c>
       <c r="G492" s="5" t="inlineStr">
         <is>
-          <t>写操作(更新自定义推荐值)，本轮只读优先未覆盖，待补写操作测试</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
+          <t>修改本账号'处理某条推荐'的状态/站点排除/自定义值/优先级，操作对象是已存在的真实推荐ID；已实测测试账号advertiser 578107614358724215下无任何真实推荐(含系统生成的，GetRecommendationOverviewTop各项计数均为0)，无可用推荐可安全设计'改状态→改回'类case，未使用ES样本里其他客户的推荐数据，判定技术受限未执行。2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="16" customHeight="1">
       <c r="A493" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16586,10 +16622,14 @@
         </is>
       </c>
       <c r="E493" s="3" t="n"/>
-      <c r="F493" s="3" t="n"/>
+      <c r="F493" s="6" t="inlineStr">
+        <is>
+          <t>【技术受限-仅生成不执行】POST AuditV2/UpdateCustomPriority</t>
+        </is>
+      </c>
       <c r="G493" s="5" t="inlineStr">
         <is>
-          <t>写操作(更新推荐优先级)，本轮只读优先未覆盖，待补写操作测试</t>
+          <t>修改本账号'处理某条推荐'的状态/站点排除/自定义值/优先级，操作对象是已存在的真实推荐ID；已实测测试账号advertiser 578107614358724215下无任何真实推荐(含系统生成的，GetRecommendationOverviewTop各项计数均为0)，无可用推荐可安全设计'改状态→改回'类case，未使用ES样本里其他客户的推荐数据，判定技术受限未执行。2026-09-21</t>
         </is>
       </c>
     </row>

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -817,16 +817,16 @@
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="2" t="n">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76% (120/157)</t>
+          <t>84% (132/157)</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="2" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54% (32/59)</t>
+          <t>90% (53/59)</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
         </is>
       </c>
     </row>
-    <row r="202">
+    <row r="202" ht="16" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8216,14 +8216,18 @@
         </is>
       </c>
       <c r="E202" s="3" t="n"/>
-      <c r="F202" s="3" t="n"/>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t>清理本轮写操作自建的13个测试报表</t>
+        </is>
+      </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
           <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="203">
+    <row r="203" ht="32" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8245,7 +8249,12 @@
         </is>
       </c>
       <c r="E203" s="3" t="n"/>
-      <c r="F203" s="3" t="n"/>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE改INACTIVE再还原(第1轮)
+ACTIVE改INACTIVE再还原(第2轮)</t>
+        </is>
+      </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
           <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
@@ -8287,7 +8296,7 @@
       </c>
       <c r="G204" s="3" t="n"/>
     </row>
-    <row r="205">
+    <row r="205" ht="32" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8309,14 +8318,19 @@
         </is>
       </c>
       <c r="E205" s="3" t="n"/>
-      <c r="F205" s="3" t="n"/>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>创建自定义SQL报表定义(第1轮)
+创建自定义SQL报表定义(第2轮)</t>
+        </is>
+      </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
           <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="206">
+    <row r="206" ht="32" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8338,14 +8352,19 @@
         </is>
       </c>
       <c r="E206" s="3" t="n"/>
-      <c r="F206" s="3" t="n"/>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>创建AMC dashboard(第1轮)
+创建AMC dashboard(第2轮)</t>
+        </is>
+      </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
           <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="207">
+    <row r="207" ht="16" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8367,7 +8386,11 @@
         </is>
       </c>
       <c r="E207" s="3" t="n"/>
-      <c r="F207" s="3" t="n"/>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>Agent创建report并触发AMC查询(仅执行1次)</t>
+        </is>
+      </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
           <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
@@ -8436,7 +8459,7 @@
       </c>
       <c r="G209" s="3" t="n"/>
     </row>
-    <row r="210">
+    <row r="210" ht="16" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8458,7 +8481,11 @@
         </is>
       </c>
       <c r="E210" s="3" t="n"/>
-      <c r="F210" s="3" t="n"/>
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t>清理测试报表79952产生的历史记录243683</t>
+        </is>
+      </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
           <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
@@ -8653,7 +8680,7 @@
         </is>
       </c>
     </row>
-    <row r="217">
+    <row r="217" ht="32" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8675,14 +8702,19 @@
         </is>
       </c>
       <c r="E217" s="3" t="n"/>
-      <c r="F217" s="3" t="n"/>
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>修改报表reportPeriod并还原(第1轮)
+修改报表reportPeriod并还原(第2轮)</t>
+        </is>
+      </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
           <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="218">
+    <row r="218" ht="32" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8704,14 +8736,19 @@
         </is>
       </c>
       <c r="E218" s="3" t="n"/>
-      <c r="F218" s="3" t="n"/>
+      <c r="F218" s="6" t="inlineStr">
+        <is>
+          <t>改history名称(复用CreateByAgent的history,2轮改名)
+改history名称(复用CreateByAgent的history,2轮改名,重试用真实historyId)</t>
+        </is>
+      </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
           <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="219">
+    <row r="219" ht="32" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -8733,7 +8770,12 @@
         </is>
       </c>
       <c r="E219" s="3" t="n"/>
-      <c r="F219" s="3" t="n"/>
+      <c r="F219" s="6" t="inlineStr">
+        <is>
+          <t>改名并还原(第1轮)
+改名并还原(第2轮)</t>
+        </is>
+      </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
           <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
@@ -12453,7 +12495,7 @@
       </c>
       <c r="G343" s="3" t="n"/>
     </row>
-    <row r="344">
+    <row r="344" ht="16" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12475,14 +12517,18 @@
         </is>
       </c>
       <c r="E344" s="3" t="n"/>
-      <c r="F344" s="3" t="n"/>
+      <c r="F344" s="6" t="inlineStr">
+        <is>
+          <t>高风险-仅生成不执行</t>
+        </is>
+      </c>
       <c r="G344" s="5" t="inlineStr">
         <is>
           <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="345">
+    <row r="345" ht="32" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12504,7 +12550,12 @@
         </is>
       </c>
       <c r="E345" s="3" t="n"/>
-      <c r="F345" s="3" t="n"/>
+      <c r="F345" s="6" t="inlineStr">
+        <is>
+          <t>重新执行(仅执行1次,复用RunNow产生的history)
+重新执行(仅执行1次,复用CreateByAgent产生的historyId=243683)</t>
+        </is>
+      </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
           <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
@@ -12544,7 +12595,7 @@
         </is>
       </c>
     </row>
-    <row r="347">
+    <row r="347" ht="16" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12566,7 +12617,11 @@
         </is>
       </c>
       <c r="E347" s="3" t="n"/>
-      <c r="F347" s="3" t="n"/>
+      <c r="F347" s="6" t="inlineStr">
+        <is>
+          <t>立即执行(仅执行1次)</t>
+        </is>
+      </c>
       <c r="G347" s="5" t="inlineStr">
         <is>
           <t>写操作，本轮只读优先未覆盖，待补写操作测试</t>
@@ -12605,7 +12660,7 @@
       </c>
       <c r="G348" s="3" t="n"/>
     </row>
-    <row r="349">
+    <row r="349" ht="16" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12627,7 +12682,11 @@
         </is>
       </c>
       <c r="E349" s="3" t="n"/>
-      <c r="F349" s="3" t="n"/>
+      <c r="F349" s="6" t="inlineStr">
+        <is>
+          <t>【高风险-仅生成不执行】POST AmcReportV2/AuthAmcInstance</t>
+        </is>
+      </c>
       <c r="G349" s="5" t="inlineStr">
         <is>
           <t>写操作(授权AMC实例)，本轮只读优先未覆盖，待补写操作测试</t>
@@ -12663,7 +12722,7 @@
         </is>
       </c>
     </row>
-    <row r="351">
+    <row r="351" ht="16" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12685,7 +12744,11 @@
         </is>
       </c>
       <c r="E351" s="3" t="n"/>
-      <c r="F351" s="3" t="n"/>
+      <c r="F351" s="6" t="inlineStr">
+        <is>
+          <t>【高风险-仅生成不执行】POST AmcReportV2/BulkCreateAMCInstance</t>
+        </is>
+      </c>
       <c r="G351" s="5" t="inlineStr">
         <is>
           <t>写操作(批量创建AMC实例)，本轮只读优先未覆盖，待补写操作测试</t>
@@ -12721,7 +12784,7 @@
         </is>
       </c>
     </row>
-    <row r="353">
+    <row r="353" ht="16" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12743,14 +12806,18 @@
         </is>
       </c>
       <c r="E353" s="3" t="n"/>
-      <c r="F353" s="3" t="n"/>
+      <c r="F353" s="6" t="inlineStr">
+        <is>
+          <t>取消不存在的订阅(streaming insights未订阅,验证否定场景)</t>
+        </is>
+      </c>
       <c r="G353" s="5" t="inlineStr">
         <is>
           <t>写操作(取消付费订阅)，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="354">
+    <row r="354" ht="16" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12772,7 +12839,11 @@
         </is>
       </c>
       <c r="E354" s="3" t="n"/>
-      <c r="F354" s="3" t="n"/>
+      <c r="F354" s="6" t="inlineStr">
+        <is>
+          <t>amcgd4jvzeh从ACTIVE改INACTIVE再改回ACTIVE(实测status为字符串枚举)</t>
+        </is>
+      </c>
       <c r="G354" s="5" t="inlineStr">
         <is>
           <t>写操作(变更实例状态)，本轮只读优先未覆盖，待补写操作测试</t>
@@ -12877,7 +12948,7 @@
       </c>
       <c r="G357" s="3" t="n"/>
     </row>
-    <row r="358">
+    <row r="358" ht="16" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12899,7 +12970,11 @@
         </is>
       </c>
       <c r="E358" s="3" t="n"/>
-      <c r="F358" s="3" t="n"/>
+      <c r="F358" s="6" t="inlineStr">
+        <is>
+          <t>【高风险-仅生成不执行】POST AmcReportV2/CreateAMCInstance</t>
+        </is>
+      </c>
       <c r="G358" s="5" t="inlineStr">
         <is>
           <t>写操作(创建AMC实例)，本轮只读优先未覆盖，待补写操作测试</t>
@@ -12935,7 +13010,7 @@
         </is>
       </c>
     </row>
-    <row r="360">
+    <row r="360" ht="16" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12957,14 +13032,18 @@
         </is>
       </c>
       <c r="E360" s="3" t="n"/>
-      <c r="F360" s="3" t="n"/>
+      <c r="F360" s="6" t="inlineStr">
+        <is>
+          <t>对已存在数据集pacvue 1p test登记测试上传记录(实测需真实S3文件预先存在,否定路径)</t>
+        </is>
+      </c>
       <c r="G360" s="5" t="inlineStr">
         <is>
           <t>写操作(创建数据上传)，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="361">
+    <row r="361" ht="16" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -12986,14 +13065,18 @@
         </is>
       </c>
       <c r="E361" s="3" t="n"/>
-      <c r="F361" s="3" t="n"/>
+      <c r="F361" s="6" t="inlineStr">
+        <is>
+          <t>【高风险-仅生成不执行】DELETE AmcReportV2/DeleteAMCInstance</t>
+        </is>
+      </c>
       <c r="G361" s="5" t="inlineStr">
         <is>
           <t>写操作(删除AMC实例)，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="362">
+    <row r="362" ht="16" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -13015,7 +13098,11 @@
         </is>
       </c>
       <c r="E362" s="3" t="n"/>
-      <c r="F362" s="3" t="n"/>
+      <c r="F362" s="6" t="inlineStr">
+        <is>
+          <t>【高风险-仅生成不执行】DELETE AmcReportV2/DeleteAMCInstanceCreation</t>
+        </is>
+      </c>
       <c r="G362" s="5" t="inlineStr">
         <is>
           <t>写操作(删除实例创建记录)，本轮只读优先未覆盖，待补写操作测试</t>
@@ -14011,7 +14098,7 @@
       </c>
       <c r="G395" s="3" t="n"/>
     </row>
-    <row r="396">
+    <row r="396" ht="16" customHeight="1">
       <c r="A396" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -14033,14 +14120,18 @@
         </is>
       </c>
       <c r="E396" s="3" t="n"/>
-      <c r="F396" s="3" t="n"/>
+      <c r="F396" s="6" t="inlineStr">
+        <is>
+          <t>【高风险-仅生成不执行】POST AmcReportV2/ImportAMCInstance</t>
+        </is>
+      </c>
       <c r="G396" s="5" t="inlineStr">
         <is>
           <t>写操作(导入AMC实例)，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="397">
+    <row r="397" ht="16" customHeight="1">
       <c r="A397" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -14062,14 +14153,18 @@
         </is>
       </c>
       <c r="E397" s="3" t="n"/>
-      <c r="F397" s="3" t="n"/>
+      <c r="F397" s="6" t="inlineStr">
+        <is>
+          <t>对真实持有实例amcgd4jvzeh触发刷新(仅执行1次)</t>
+        </is>
+      </c>
       <c r="G397" s="5" t="inlineStr">
         <is>
           <t>写操作(刷新实例，路径含refresh)，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="398">
+    <row r="398" ht="16" customHeight="1">
       <c r="A398" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -14091,14 +14186,18 @@
         </is>
       </c>
       <c r="E398" s="3" t="n"/>
-      <c r="F398" s="3" t="n"/>
+      <c r="F398" s="6" t="inlineStr">
+        <is>
+          <t>保存收藏查询test141735后软删除还原(可重复)</t>
+        </is>
+      </c>
       <c r="G398" s="5" t="inlineStr">
         <is>
           <t>写操作(保存收藏查询)，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="399">
+    <row r="399" ht="16" customHeight="1">
       <c r="A399" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -14120,7 +14219,11 @@
         </is>
       </c>
       <c r="E399" s="3" t="n"/>
-      <c r="F399" s="3" t="n"/>
+      <c r="F399" s="6" t="inlineStr">
+        <is>
+          <t>【高风险-仅生成不执行】POST AmcReportV2/SubscribePaidFeatures</t>
+        </is>
+      </c>
       <c r="G399" s="5" t="inlineStr">
         <is>
           <t>写操作(订阅付费功能)，本轮只读优先未覆盖，待补写操作测试</t>
@@ -14222,7 +14325,7 @@
         </is>
       </c>
     </row>
-    <row r="403">
+    <row r="403" ht="16" customHeight="1">
       <c r="A403" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -14244,14 +14347,18 @@
         </is>
       </c>
       <c r="E403" s="3" t="n"/>
-      <c r="F403" s="3" t="n"/>
+      <c r="F403" s="6" t="inlineStr">
+        <is>
+          <t>【高风险-仅生成不执行】POST AmcReportV2/UpdateAMCInstance</t>
+        </is>
+      </c>
       <c r="G403" s="5" t="inlineStr">
         <is>
           <t>写操作(更新AMC实例)，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="404">
+    <row r="404" ht="16" customHeight="1">
       <c r="A404" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -14273,7 +14380,11 @@
         </is>
       </c>
       <c r="E404" s="3" t="n"/>
-      <c r="F404" s="3" t="n"/>
+      <c r="F404" s="6" t="inlineStr">
+        <is>
+          <t>amcgd4jvzeh临时改名test141735后还原为原名(可重复)</t>
+        </is>
+      </c>
       <c r="G404" s="5" t="inlineStr">
         <is>
           <t>写操作(更新实例名称)，本轮只读优先未覆盖，待补写操作测试</t>
@@ -14309,7 +14420,7 @@
         </is>
       </c>
     </row>
-    <row r="406">
+    <row r="406" ht="16" customHeight="1">
       <c r="A406" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -14331,14 +14442,18 @@
         </is>
       </c>
       <c r="E406" s="3" t="n"/>
-      <c r="F406" s="3" t="n"/>
+      <c r="F406" s="6" t="inlineStr">
+        <is>
+          <t>amcgd4jvzeh原entityId/countryCode为空,设置为真实entity后尝试还原</t>
+        </is>
+      </c>
       <c r="G406" s="5" t="inlineStr">
         <is>
           <t>写操作(更新实例详情)，本轮只读优先未覆盖，待补写操作测试</t>
         </is>
       </c>
     </row>
-    <row r="407">
+    <row r="407" ht="16" customHeight="1">
       <c r="A407" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -14360,7 +14475,11 @@
         </is>
       </c>
       <c r="E407" s="3" t="n"/>
-      <c r="F407" s="3" t="n"/>
+      <c r="F407" s="6" t="inlineStr">
+        <is>
+          <t>【技术受限-仅生成不执行】POST AmcReportV2/UploadCustomCampaigns</t>
+        </is>
+      </c>
       <c r="G407" s="5" t="inlineStr">
         <is>
           <t>写操作(上传自定义campaign)，本轮只读优先未覆盖，待补写操作测试</t>

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1686,9 +1686,19 @@
       </c>
       <c r="D48" s="3" t="n"/>
       <c r="E48" s="3" t="n"/>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2" t="n"/>
+      <c r="F48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0% (0/3)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -33218,8 +33228,16 @@
         </is>
       </c>
       <c r="E1083" s="3" t="n"/>
-      <c r="F1083" s="3" t="n"/>
-      <c r="G1083" s="3" t="n"/>
+      <c r="F1083" s="5" t="inlineStr">
+        <is>
+          <t>不执行(A类限制)</t>
+        </is>
+      </c>
+      <c r="G1083" s="5" t="inlineStr">
+        <is>
+          <t>DSP限制清单A类：会影响account，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1084">
       <c r="A1084" s="2" t="inlineStr">
@@ -33243,8 +33261,16 @@
         </is>
       </c>
       <c r="E1084" s="3" t="n"/>
-      <c r="F1084" s="3" t="n"/>
-      <c r="G1084" s="3" t="n"/>
+      <c r="F1084" s="5" t="inlineStr">
+        <is>
+          <t>不执行(A类限制)</t>
+        </is>
+      </c>
+      <c r="G1084" s="5" t="inlineStr">
+        <is>
+          <t>DSP限制清单A类：会影响account，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1085">
       <c r="A1085" s="2" t="inlineStr">
@@ -33268,8 +33294,16 @@
         </is>
       </c>
       <c r="E1085" s="3" t="n"/>
-      <c r="F1085" s="3" t="n"/>
-      <c r="G1085" s="3" t="n"/>
+      <c r="F1085" s="5" t="inlineStr">
+        <is>
+          <t>不执行(A类限制)</t>
+        </is>
+      </c>
+      <c r="G1085" s="5" t="inlineStr">
+        <is>
+          <t>DSP限制清单A类：会影响account，不生成不执行</t>
+        </is>
+      </c>
     </row>
     <row r="1086">
       <c r="A1086" s="2" t="inlineStr">
@@ -43757,12 +43791,12 @@
       <c r="E1456" s="3" t="n"/>
       <c r="F1456" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1456" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -43790,12 +43824,12 @@
       <c r="E1457" s="3" t="n"/>
       <c r="F1457" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1457" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -43823,12 +43857,12 @@
       <c r="E1458" s="3" t="n"/>
       <c r="F1458" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1458" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -43856,12 +43890,12 @@
       <c r="E1459" s="3" t="n"/>
       <c r="F1459" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1459" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -43889,12 +43923,12 @@
       <c r="E1460" s="3" t="n"/>
       <c r="F1460" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1460" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -43922,12 +43956,12 @@
       <c r="E1461" s="3" t="n"/>
       <c r="F1461" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1461" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -43955,12 +43989,12 @@
       <c r="E1462" s="3" t="n"/>
       <c r="F1462" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1462" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -43988,12 +44022,12 @@
       <c r="E1463" s="3" t="n"/>
       <c r="F1463" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1463" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44021,12 +44055,12 @@
       <c r="E1464" s="3" t="n"/>
       <c r="F1464" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1464" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44054,12 +44088,12 @@
       <c r="E1465" s="3" t="n"/>
       <c r="F1465" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1465" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44087,12 +44121,12 @@
       <c r="E1466" s="3" t="n"/>
       <c r="F1466" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1466" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44120,12 +44154,12 @@
       <c r="E1467" s="3" t="n"/>
       <c r="F1467" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1467" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44153,12 +44187,12 @@
       <c r="E1468" s="3" t="n"/>
       <c r="F1468" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1468" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44186,12 +44220,12 @@
       <c r="E1469" s="3" t="n"/>
       <c r="F1469" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1469" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44219,12 +44253,12 @@
       <c r="E1470" s="3" t="n"/>
       <c r="F1470" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1470" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44252,12 +44286,12 @@
       <c r="E1471" s="3" t="n"/>
       <c r="F1471" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1471" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44285,12 +44319,12 @@
       <c r="E1472" s="3" t="n"/>
       <c r="F1472" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1472" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44318,12 +44352,12 @@
       <c r="E1473" s="3" t="n"/>
       <c r="F1473" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1473" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44351,12 +44385,12 @@
       <c r="E1474" s="3" t="n"/>
       <c r="F1474" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1474" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44384,12 +44418,12 @@
       <c r="E1475" s="3" t="n"/>
       <c r="F1475" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1475" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44417,12 +44451,12 @@
       <c r="E1476" s="3" t="n"/>
       <c r="F1476" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1476" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44450,12 +44484,12 @@
       <c r="E1477" s="3" t="n"/>
       <c r="F1477" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1477" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44483,12 +44517,12 @@
       <c r="E1478" s="3" t="n"/>
       <c r="F1478" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1478" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44516,12 +44550,12 @@
       <c r="E1479" s="3" t="n"/>
       <c r="F1479" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1479" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44549,12 +44583,12 @@
       <c r="E1480" s="3" t="n"/>
       <c r="F1480" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1480" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44582,12 +44616,12 @@
       <c r="E1481" s="3" t="n"/>
       <c r="F1481" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1481" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44615,12 +44649,12 @@
       <c r="E1482" s="3" t="n"/>
       <c r="F1482" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1482" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44648,12 +44682,12 @@
       <c r="E1483" s="3" t="n"/>
       <c r="F1483" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1483" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44681,12 +44715,12 @@
       <c r="E1484" s="3" t="n"/>
       <c r="F1484" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1484" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44714,12 +44748,12 @@
       <c r="E1485" s="3" t="n"/>
       <c r="F1485" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1485" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44747,12 +44781,12 @@
       <c r="E1486" s="3" t="n"/>
       <c r="F1486" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1486" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44780,12 +44814,12 @@
       <c r="E1487" s="3" t="n"/>
       <c r="F1487" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1487" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44813,12 +44847,12 @@
       <c r="E1488" s="3" t="n"/>
       <c r="F1488" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1488" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有12次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44846,12 +44880,12 @@
       <c r="E1489" s="3" t="n"/>
       <c r="F1489" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1489" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有7次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44879,12 +44913,12 @@
       <c r="E1490" s="3" t="n"/>
       <c r="F1490" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1490" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44912,12 +44946,12 @@
       <c r="E1491" s="3" t="n"/>
       <c r="F1491" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1491" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44945,12 +44979,12 @@
       <c r="E1492" s="3" t="n"/>
       <c r="F1492" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1492" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -44978,12 +45012,12 @@
       <c r="E1493" s="3" t="n"/>
       <c r="F1493" s="5" t="inlineStr">
         <is>
-          <t>路径含禁用关键词</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1493" s="5" t="inlineStr">
         <is>
-          <t>路径含禁用关键词sync，不生成不执行(尽管365天399次真实流量，仍按硬性规则拦截)</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -45011,12 +45045,12 @@
       <c r="E1494" s="3" t="n"/>
       <c r="F1494" s="5" t="inlineStr">
         <is>
-          <t>路径含禁用关键词</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1494" s="5" t="inlineStr">
         <is>
-          <t>路径含禁用关键词sync，不生成不执行(尽管365天8328次真实流量，仍按硬性规则拦截)</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -45044,12 +45078,12 @@
       <c r="E1495" s="3" t="n"/>
       <c r="F1495" s="5" t="inlineStr">
         <is>
-          <t>路径含禁用关键词</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1495" s="5" t="inlineStr">
         <is>
-          <t>路径含禁用关键词sync，不生成不执行(尽管365天707次真实流量，仍按硬性规则拦截)</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -45077,12 +45111,12 @@
       <c r="E1496" s="3" t="n"/>
       <c r="F1496" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1496" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -45110,12 +45144,12 @@
       <c r="E1497" s="3" t="n"/>
       <c r="F1497" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1497" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -45143,12 +45177,12 @@
       <c r="E1498" s="3" t="n"/>
       <c r="F1498" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1498" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -45176,12 +45210,12 @@
       <c r="E1499" s="3" t="n"/>
       <c r="F1499" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1499" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部从亚马逊拉数据，有上下文和执行顺序依赖，含只读GET也不跑</t>
         </is>
       </c>
     </row>
@@ -47110,12 +47144,12 @@
       <c r="E1566" s="3" t="n"/>
       <c r="F1566" s="5" t="inlineStr">
         <is>
-          <t>路径含禁用关键词</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1566" s="5" t="inlineStr">
         <is>
-          <t>路径含禁用关键词test，不生成不执行(尽管365天8次真实流量，仍按硬性规则拦截)</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47143,12 +47177,12 @@
       <c r="E1567" s="3" t="n"/>
       <c r="F1567" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1567" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47176,12 +47210,12 @@
       <c r="E1568" s="3" t="n"/>
       <c r="F1568" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1568" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47209,12 +47243,12 @@
       <c r="E1569" s="3" t="n"/>
       <c r="F1569" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1569" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47242,12 +47276,12 @@
       <c r="E1570" s="3" t="n"/>
       <c r="F1570" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1570" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有9次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47275,12 +47309,12 @@
       <c r="E1571" s="3" t="n"/>
       <c r="F1571" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1571" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47308,12 +47342,12 @@
       <c r="E1572" s="3" t="n"/>
       <c r="F1572" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1572" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47341,12 +47375,12 @@
       <c r="E1573" s="3" t="n"/>
       <c r="F1573" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1573" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47374,12 +47408,12 @@
       <c r="E1574" s="3" t="n"/>
       <c r="F1574" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1574" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47407,12 +47441,12 @@
       <c r="E1575" s="3" t="n"/>
       <c r="F1575" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1575" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47440,12 +47474,12 @@
       <c r="E1576" s="3" t="n"/>
       <c r="F1576" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1576" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47473,12 +47507,12 @@
       <c r="E1577" s="3" t="n"/>
       <c r="F1577" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1577" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47506,12 +47540,12 @@
       <c r="E1578" s="3" t="n"/>
       <c r="F1578" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1578" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47539,12 +47573,12 @@
       <c r="E1579" s="3" t="n"/>
       <c r="F1579" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1579" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47572,12 +47606,12 @@
       <c r="E1580" s="3" t="n"/>
       <c r="F1580" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1580" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47605,12 +47639,12 @@
       <c r="E1581" s="3" t="n"/>
       <c r="F1581" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1581" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47638,12 +47672,12 @@
       <c r="E1582" s="3" t="n"/>
       <c r="F1582" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1582" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47671,12 +47705,12 @@
       <c r="E1583" s="3" t="n"/>
       <c r="F1583" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1583" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47704,12 +47738,12 @@
       <c r="E1584" s="3" t="n"/>
       <c r="F1584" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1584" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47737,12 +47771,12 @@
       <c r="E1585" s="3" t="n"/>
       <c r="F1585" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1585" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47770,12 +47804,12 @@
       <c r="E1586" s="3" t="n"/>
       <c r="F1586" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1586" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47803,12 +47837,12 @@
       <c r="E1587" s="3" t="n"/>
       <c r="F1587" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1587" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47836,12 +47870,12 @@
       <c r="E1588" s="3" t="n"/>
       <c r="F1588" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1588" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47869,12 +47903,12 @@
       <c r="E1589" s="3" t="n"/>
       <c r="F1589" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1589" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47902,12 +47936,12 @@
       <c r="E1590" s="3" t="n"/>
       <c r="F1590" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1590" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>
@@ -47935,12 +47969,12 @@
       <c r="E1591" s="3" t="n"/>
       <c r="F1591" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量</t>
+          <t>不执行(A类限制)</t>
         </is>
       </c>
       <c r="G1591" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有12769032次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
+          <t>DSP限制清单A类：内部手动操作/测试用，用户不会直接用到，不生成不执行</t>
         </is>
       </c>
     </row>

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -4782,7 +4782,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -29668,7 +29668,7 @@
       </c>
       <c r="G948" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -29701,7 +29701,7 @@
       </c>
       <c r="G949" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -29734,7 +29734,7 @@
       </c>
       <c r="G950" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -29767,7 +29767,7 @@
       </c>
       <c r="G951" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -29800,7 +29800,7 @@
       </c>
       <c r="G952" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -29833,7 +29833,7 @@
       </c>
       <c r="G953" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -29866,7 +29866,7 @@
       </c>
       <c r="G954" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -29899,7 +29899,7 @@
       </c>
       <c r="G955" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="G956" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -29965,7 +29965,7 @@
       </c>
       <c r="G957" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -29998,7 +29998,7 @@
       </c>
       <c r="G958" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30031,7 +30031,7 @@
       </c>
       <c r="G959" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30064,7 +30064,7 @@
       </c>
       <c r="G960" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30097,7 +30097,7 @@
       </c>
       <c r="G961" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30130,7 +30130,7 @@
       </c>
       <c r="G962" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="G963" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="G964" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有13次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30229,7 +30229,7 @@
       </c>
       <c r="G965" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30262,7 +30262,7 @@
       </c>
       <c r="G966" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30295,7 +30295,7 @@
       </c>
       <c r="G967" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30328,7 +30328,7 @@
       </c>
       <c r="G968" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30361,7 +30361,7 @@
       </c>
       <c r="G969" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有146次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30394,7 +30394,7 @@
       </c>
       <c r="G970" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -30427,7 +30427,7 @@
       </c>
       <c r="G971" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有444次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35034,7 +35034,7 @@
       </c>
       <c r="G1154" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有13次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35067,7 +35067,7 @@
       </c>
       <c r="G1155" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35100,7 +35100,7 @@
       </c>
       <c r="G1156" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35133,7 +35133,7 @@
       </c>
       <c r="G1157" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35166,7 +35166,7 @@
       </c>
       <c r="G1158" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35199,7 +35199,7 @@
       </c>
       <c r="G1159" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有15次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35232,7 +35232,7 @@
       </c>
       <c r="G1160" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35265,7 +35265,7 @@
       </c>
       <c r="G1161" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有12次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35298,7 +35298,7 @@
       </c>
       <c r="G1162" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35331,7 +35331,7 @@
       </c>
       <c r="G1163" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35364,7 +35364,7 @@
       </c>
       <c r="G1164" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35397,7 +35397,7 @@
       </c>
       <c r="G1165" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有4次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35430,7 +35430,7 @@
       </c>
       <c r="G1166" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="G1167" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35496,7 +35496,7 @@
       </c>
       <c r="G1168" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35529,7 +35529,7 @@
       </c>
       <c r="G1169" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -35562,7 +35562,7 @@
       </c>
       <c r="G1170" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -41982,7 +41982,7 @@
       </c>
       <c r="G1386" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -43215,7 +43215,7 @@
       </c>
       <c r="G1435" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -43248,7 +43248,7 @@
       </c>
       <c r="G1436" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -43281,7 +43281,7 @@
       </c>
       <c r="G1437" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -43314,7 +43314,7 @@
       </c>
       <c r="G1438" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -43347,7 +43347,7 @@
       </c>
       <c r="G1439" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -43380,7 +43380,7 @@
       </c>
       <c r="G1440" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -43413,7 +43413,7 @@
       </c>
       <c r="G1441" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48156,7 +48156,7 @@
       </c>
       <c r="G1597" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48189,7 +48189,7 @@
       </c>
       <c r="G1598" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48222,7 +48222,7 @@
       </c>
       <c r="G1599" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48255,7 +48255,7 @@
       </c>
       <c r="G1600" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48288,7 +48288,7 @@
       </c>
       <c r="G1601" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48321,7 +48321,7 @@
       </c>
       <c r="G1602" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48354,7 +48354,7 @@
       </c>
       <c r="G1603" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48387,7 +48387,7 @@
       </c>
       <c r="G1604" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48420,7 +48420,7 @@
       </c>
       <c r="G1605" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48453,7 +48453,7 @@
       </c>
       <c r="G1606" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48486,7 +48486,7 @@
       </c>
       <c r="G1607" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48519,7 +48519,7 @@
       </c>
       <c r="G1608" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48552,7 +48552,7 @@
       </c>
       <c r="G1609" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48585,7 +48585,7 @@
       </c>
       <c r="G1610" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48618,7 +48618,7 @@
       </c>
       <c r="G1611" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48651,7 +48651,7 @@
       </c>
       <c r="G1612" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48684,7 +48684,7 @@
       </c>
       <c r="G1613" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48717,7 +48717,7 @@
       </c>
       <c r="G1614" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48750,7 +48750,7 @@
       </c>
       <c r="G1615" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48783,7 +48783,7 @@
       </c>
       <c r="G1616" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48816,7 +48816,7 @@
       </c>
       <c r="G1617" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48849,7 +48849,7 @@
       </c>
       <c r="G1618" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48882,7 +48882,7 @@
       </c>
       <c r="G1619" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48915,7 +48915,7 @@
       </c>
       <c r="G1620" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48948,7 +48948,7 @@
       </c>
       <c r="G1621" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -48981,7 +48981,7 @@
       </c>
       <c r="G1622" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -49014,7 +49014,7 @@
       </c>
       <c r="G1623" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -49047,7 +49047,7 @@
       </c>
       <c r="G1624" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -49080,7 +49080,7 @@
       </c>
       <c r="G1625" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -49113,7 +49113,7 @@
       </c>
       <c r="G1626" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -49146,7 +49146,7 @@
       </c>
       <c r="G1627" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -49179,7 +49179,7 @@
       </c>
       <c r="G1628" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>
@@ -49212,7 +49212,7 @@
       </c>
       <c r="G1629" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
         </is>
       </c>
     </row>

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -534,9 +534,19 @@
       </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>3% (1/30)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -880,9 +890,19 @@
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="F15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>17% (1/6)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1230,9 +1250,19 @@
       </c>
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
+      <c r="F30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>33% (2/6)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1924,9 +1954,19 @@
       </c>
       <c r="D57" s="3" t="n"/>
       <c r="E57" s="3" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
+      <c r="F57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>50% (1/2)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2054,9 +2094,19 @@
       </c>
       <c r="D62" s="3" t="n"/>
       <c r="E62" s="3" t="n"/>
-      <c r="F62" s="2" t="n"/>
-      <c r="G62" s="2" t="n"/>
-      <c r="H62" s="2" t="n"/>
+      <c r="F62" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>4% (2/49)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2388,9 +2438,19 @@
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="3" t="n"/>
-      <c r="F74" s="2" t="n"/>
-      <c r="G74" s="2" t="n"/>
-      <c r="H74" s="2" t="n"/>
+      <c r="F74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>50% (1/2)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2668,8 +2728,16 @@
         </is>
       </c>
       <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2693,8 +2761,16 @@
         </is>
       </c>
       <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2718,8 +2794,16 @@
         </is>
       </c>
       <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2743,8 +2827,16 @@
         </is>
       </c>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2768,10 +2860,18 @@
         </is>
       </c>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-    </row>
-    <row r="7">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -2793,7 +2893,11 @@
         </is>
       </c>
       <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>按groupId查询AB测试分组 — 100%</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
@@ -2818,8 +2922,16 @@
         </is>
       </c>
       <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2843,8 +2955,16 @@
         </is>
       </c>
       <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2868,8 +2988,16 @@
         </is>
       </c>
       <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2893,8 +3021,16 @@
         </is>
       </c>
       <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2918,8 +3054,16 @@
         </is>
       </c>
       <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2943,8 +3087,16 @@
         </is>
       </c>
       <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2968,8 +3120,16 @@
         </is>
       </c>
       <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2993,8 +3153,16 @@
         </is>
       </c>
       <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3018,8 +3186,16 @@
         </is>
       </c>
       <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3043,8 +3219,16 @@
         </is>
       </c>
       <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3068,8 +3252,16 @@
         </is>
       </c>
       <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3093,8 +3285,16 @@
         </is>
       </c>
       <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3118,8 +3318,16 @@
         </is>
       </c>
       <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3143,8 +3351,16 @@
         </is>
       </c>
       <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3168,8 +3384,16 @@
         </is>
       </c>
       <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3193,8 +3417,16 @@
         </is>
       </c>
       <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3218,8 +3450,16 @@
         </is>
       </c>
       <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3243,8 +3483,16 @@
         </is>
       </c>
       <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3268,8 +3516,16 @@
         </is>
       </c>
       <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3293,8 +3549,16 @@
         </is>
       </c>
       <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3318,8 +3582,16 @@
         </is>
       </c>
       <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3343,8 +3615,16 @@
         </is>
       </c>
       <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3368,8 +3648,16 @@
         </is>
       </c>
       <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3393,8 +3681,16 @@
         </is>
       </c>
       <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -14518,8 +14814,16 @@
         </is>
       </c>
       <c r="E408" s="3" t="n"/>
-      <c r="F408" s="3" t="n"/>
-      <c r="G408" s="3" t="n"/>
+      <c r="F408" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G408" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -14543,8 +14847,16 @@
         </is>
       </c>
       <c r="E409" s="3" t="n"/>
-      <c r="F409" s="3" t="n"/>
-      <c r="G409" s="3" t="n"/>
+      <c r="F409" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G409" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -14568,8 +14880,16 @@
         </is>
       </c>
       <c r="E410" s="3" t="n"/>
-      <c r="F410" s="3" t="n"/>
-      <c r="G410" s="3" t="n"/>
+      <c r="F410" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G410" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -14593,10 +14913,18 @@
         </is>
       </c>
       <c r="E411" s="3" t="n"/>
-      <c r="F411" s="3" t="n"/>
-      <c r="G411" s="3" t="n"/>
-    </row>
-    <row r="412">
+      <c r="F411" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G411" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" ht="16" customHeight="1">
       <c r="A412" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -14618,7 +14946,11 @@
         </is>
       </c>
       <c r="E412" s="3" t="n"/>
-      <c r="F412" s="3" t="n"/>
+      <c r="F412" s="6" t="inlineStr">
+        <is>
+          <t>按taskId查询异步任务进度 — 100%</t>
+        </is>
+      </c>
       <c r="G412" s="3" t="n"/>
     </row>
     <row r="413">
@@ -14643,8 +14975,16 @@
         </is>
       </c>
       <c r="E413" s="3" t="n"/>
-      <c r="F413" s="3" t="n"/>
-      <c r="G413" s="3" t="n"/>
+      <c r="F413" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G413" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -21268,10 +21608,18 @@
         </is>
       </c>
       <c r="E667" s="3" t="n"/>
-      <c r="F667" s="3" t="n"/>
-      <c r="G667" s="3" t="n"/>
-    </row>
-    <row r="668">
+      <c r="F667" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G667" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="668" ht="16" customHeight="1">
       <c r="A668" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -21293,7 +21641,11 @@
         </is>
       </c>
       <c r="E668" s="3" t="n"/>
-      <c r="F668" s="3" t="n"/>
+      <c r="F668" s="6" t="inlineStr">
+        <is>
+          <t>查询当前用户Dashboard组件配置 — 99.4%</t>
+        </is>
+      </c>
       <c r="G668" s="3" t="n"/>
     </row>
     <row r="669">
@@ -21318,8 +21670,16 @@
         </is>
       </c>
       <c r="E669" s="3" t="n"/>
-      <c r="F669" s="3" t="n"/>
-      <c r="G669" s="3" t="n"/>
+      <c r="F669" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G669" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="2" t="inlineStr">
@@ -21343,8 +21703,16 @@
         </is>
       </c>
       <c r="E670" s="3" t="n"/>
-      <c r="F670" s="3" t="n"/>
-      <c r="G670" s="3" t="n"/>
+      <c r="F670" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G670" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="2" t="inlineStr">
@@ -21368,10 +21736,18 @@
         </is>
       </c>
       <c r="E671" s="3" t="n"/>
-      <c r="F671" s="3" t="n"/>
-      <c r="G671" s="3" t="n"/>
-    </row>
-    <row r="672">
+      <c r="F671" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G671" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="672" ht="64" customHeight="1">
       <c r="A672" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -21393,7 +21769,14 @@
         </is>
       </c>
       <c r="E672" s="3" t="n"/>
-      <c r="F672" s="3" t="n"/>
+      <c r="F672" s="6" t="inlineStr">
+        <is>
+          <t>自定义模板+勾选具体widget(含还原) — 51.8%
+切换预设模板1 — 13.0%
+切换预设模板2 — 16.6%
+切换预设模板3 — 18.6%</t>
+        </is>
+      </c>
       <c r="G672" s="3" t="n"/>
     </row>
     <row r="673" ht="80" customHeight="1">
@@ -36765,10 +37148,18 @@
         </is>
       </c>
       <c r="E1216" s="3" t="n"/>
-      <c r="F1216" s="3" t="n"/>
-      <c r="G1216" s="3" t="n"/>
-    </row>
-    <row r="1217">
+      <c r="F1216" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1216" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217" ht="16" customHeight="1">
       <c r="A1217" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36790,7 +37181,11 @@
         </is>
       </c>
       <c r="E1217" s="3" t="n"/>
-      <c r="F1217" s="3" t="n"/>
+      <c r="F1217" s="6" t="inlineStr">
+        <is>
+          <t>查询账号下Amazon Profile列表 — 100%</t>
+        </is>
+      </c>
       <c r="G1217" s="3" t="n"/>
     </row>
     <row r="1218">
@@ -40750,8 +41145,16 @@
         </is>
       </c>
       <c r="E1337" s="3" t="n"/>
-      <c r="F1337" s="3" t="n"/>
-      <c r="G1337" s="3" t="n"/>
+      <c r="F1337" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1337" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1338">
       <c r="A1338" s="2" t="inlineStr">
@@ -40775,8 +41178,16 @@
         </is>
       </c>
       <c r="E1338" s="3" t="n"/>
-      <c r="F1338" s="3" t="n"/>
-      <c r="G1338" s="3" t="n"/>
+      <c r="F1338" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1338" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1339">
       <c r="A1339" s="2" t="inlineStr">
@@ -40800,8 +41211,16 @@
         </is>
       </c>
       <c r="E1339" s="3" t="n"/>
-      <c r="F1339" s="3" t="n"/>
-      <c r="G1339" s="3" t="n"/>
+      <c r="F1339" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1339" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1340">
       <c r="A1340" s="2" t="inlineStr">
@@ -40825,8 +41244,16 @@
         </is>
       </c>
       <c r="E1340" s="3" t="n"/>
-      <c r="F1340" s="3" t="n"/>
-      <c r="G1340" s="3" t="n"/>
+      <c r="F1340" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1340" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1341">
       <c r="A1341" s="2" t="inlineStr">
@@ -40850,8 +41277,16 @@
         </is>
       </c>
       <c r="E1341" s="3" t="n"/>
-      <c r="F1341" s="3" t="n"/>
-      <c r="G1341" s="3" t="n"/>
+      <c r="F1341" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1341" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1342">
       <c r="A1342" s="2" t="inlineStr">
@@ -40875,8 +41310,16 @@
         </is>
       </c>
       <c r="E1342" s="3" t="n"/>
-      <c r="F1342" s="3" t="n"/>
-      <c r="G1342" s="3" t="n"/>
+      <c r="F1342" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1342" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1343">
       <c r="A1343" s="2" t="inlineStr">
@@ -40900,8 +41343,16 @@
         </is>
       </c>
       <c r="E1343" s="3" t="n"/>
-      <c r="F1343" s="3" t="n"/>
-      <c r="G1343" s="3" t="n"/>
+      <c r="F1343" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1343" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1344">
       <c r="A1344" s="2" t="inlineStr">
@@ -40925,8 +41376,16 @@
         </is>
       </c>
       <c r="E1344" s="3" t="n"/>
-      <c r="F1344" s="3" t="n"/>
-      <c r="G1344" s="3" t="n"/>
+      <c r="F1344" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1344" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1345">
       <c r="A1345" s="2" t="inlineStr">
@@ -40950,8 +41409,16 @@
         </is>
       </c>
       <c r="E1345" s="3" t="n"/>
-      <c r="F1345" s="3" t="n"/>
-      <c r="G1345" s="3" t="n"/>
+      <c r="F1345" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1345" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1346">
       <c r="A1346" s="2" t="inlineStr">
@@ -40975,8 +41442,16 @@
         </is>
       </c>
       <c r="E1346" s="3" t="n"/>
-      <c r="F1346" s="3" t="n"/>
-      <c r="G1346" s="3" t="n"/>
+      <c r="F1346" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1346" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1347">
       <c r="A1347" s="2" t="inlineStr">
@@ -41000,8 +41475,16 @@
         </is>
       </c>
       <c r="E1347" s="3" t="n"/>
-      <c r="F1347" s="3" t="n"/>
-      <c r="G1347" s="3" t="n"/>
+      <c r="F1347" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1347" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1348">
       <c r="A1348" s="2" t="inlineStr">
@@ -41025,8 +41508,16 @@
         </is>
       </c>
       <c r="E1348" s="3" t="n"/>
-      <c r="F1348" s="3" t="n"/>
-      <c r="G1348" s="3" t="n"/>
+      <c r="F1348" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1348" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1349">
       <c r="A1349" s="2" t="inlineStr">
@@ -41050,8 +41541,16 @@
         </is>
       </c>
       <c r="E1349" s="3" t="n"/>
-      <c r="F1349" s="3" t="n"/>
-      <c r="G1349" s="3" t="n"/>
+      <c r="F1349" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1349" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1350">
       <c r="A1350" s="2" t="inlineStr">
@@ -41075,8 +41574,16 @@
         </is>
       </c>
       <c r="E1350" s="3" t="n"/>
-      <c r="F1350" s="3" t="n"/>
-      <c r="G1350" s="3" t="n"/>
+      <c r="F1350" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1350" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1351">
       <c r="A1351" s="2" t="inlineStr">
@@ -41100,8 +41607,16 @@
         </is>
       </c>
       <c r="E1351" s="3" t="n"/>
-      <c r="F1351" s="3" t="n"/>
-      <c r="G1351" s="3" t="n"/>
+      <c r="F1351" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1351" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1352">
       <c r="A1352" s="2" t="inlineStr">
@@ -41125,8 +41640,16 @@
         </is>
       </c>
       <c r="E1352" s="3" t="n"/>
-      <c r="F1352" s="3" t="n"/>
-      <c r="G1352" s="3" t="n"/>
+      <c r="F1352" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1352" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1353">
       <c r="A1353" s="2" t="inlineStr">
@@ -41150,8 +41673,16 @@
         </is>
       </c>
       <c r="E1353" s="3" t="n"/>
-      <c r="F1353" s="3" t="n"/>
-      <c r="G1353" s="3" t="n"/>
+      <c r="F1353" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1353" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1354">
       <c r="A1354" s="2" t="inlineStr">
@@ -41175,8 +41706,16 @@
         </is>
       </c>
       <c r="E1354" s="3" t="n"/>
-      <c r="F1354" s="3" t="n"/>
-      <c r="G1354" s="3" t="n"/>
+      <c r="F1354" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1354" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1355">
       <c r="A1355" s="2" t="inlineStr">
@@ -41200,8 +41739,16 @@
         </is>
       </c>
       <c r="E1355" s="3" t="n"/>
-      <c r="F1355" s="3" t="n"/>
-      <c r="G1355" s="3" t="n"/>
+      <c r="F1355" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1355" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1356">
       <c r="A1356" s="2" t="inlineStr">
@@ -41225,10 +41772,18 @@
         </is>
       </c>
       <c r="E1356" s="3" t="n"/>
-      <c r="F1356" s="3" t="n"/>
-      <c r="G1356" s="3" t="n"/>
-    </row>
-    <row r="1357">
+      <c r="F1356" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1356" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357" ht="48" customHeight="1">
       <c r="A1357" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -41250,7 +41805,13 @@
         </is>
       </c>
       <c r="E1357" s="3" t="n"/>
-      <c r="F1357" s="3" t="n"/>
+      <c r="F1357" s="6" t="inlineStr">
+        <is>
+          <t>单个advertiserId — 81.0%
+多个advertiserId — 14.9%
+空数组 — 3.6%</t>
+        </is>
+      </c>
       <c r="G1357" s="3" t="n"/>
     </row>
     <row r="1358">
@@ -41275,8 +41836,16 @@
         </is>
       </c>
       <c r="E1358" s="3" t="n"/>
-      <c r="F1358" s="3" t="n"/>
-      <c r="G1358" s="3" t="n"/>
+      <c r="F1358" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1358" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1359">
       <c r="A1359" s="2" t="inlineStr">
@@ -41300,8 +41869,16 @@
         </is>
       </c>
       <c r="E1359" s="3" t="n"/>
-      <c r="F1359" s="3" t="n"/>
-      <c r="G1359" s="3" t="n"/>
+      <c r="F1359" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1359" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1360">
       <c r="A1360" s="2" t="inlineStr">
@@ -41325,8 +41902,16 @@
         </is>
       </c>
       <c r="E1360" s="3" t="n"/>
-      <c r="F1360" s="3" t="n"/>
-      <c r="G1360" s="3" t="n"/>
+      <c r="F1360" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1360" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1361">
       <c r="A1361" s="2" t="inlineStr">
@@ -41350,8 +41935,16 @@
         </is>
       </c>
       <c r="E1361" s="3" t="n"/>
-      <c r="F1361" s="3" t="n"/>
-      <c r="G1361" s="3" t="n"/>
+      <c r="F1361" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1361" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1362">
       <c r="A1362" s="2" t="inlineStr">
@@ -41375,8 +41968,16 @@
         </is>
       </c>
       <c r="E1362" s="3" t="n"/>
-      <c r="F1362" s="3" t="n"/>
-      <c r="G1362" s="3" t="n"/>
+      <c r="F1362" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1362" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1363">
       <c r="A1363" s="2" t="inlineStr">
@@ -41400,8 +42001,16 @@
         </is>
       </c>
       <c r="E1363" s="3" t="n"/>
-      <c r="F1363" s="3" t="n"/>
-      <c r="G1363" s="3" t="n"/>
+      <c r="F1363" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1363" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1364">
       <c r="A1364" s="2" t="inlineStr">
@@ -41425,8 +42034,16 @@
         </is>
       </c>
       <c r="E1364" s="3" t="n"/>
-      <c r="F1364" s="3" t="n"/>
-      <c r="G1364" s="3" t="n"/>
+      <c r="F1364" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1364" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1365">
       <c r="A1365" s="2" t="inlineStr">
@@ -41450,8 +42067,16 @@
         </is>
       </c>
       <c r="E1365" s="3" t="n"/>
-      <c r="F1365" s="3" t="n"/>
-      <c r="G1365" s="3" t="n"/>
+      <c r="F1365" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1365" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1366">
       <c r="A1366" s="2" t="inlineStr">
@@ -41475,8 +42100,16 @@
         </is>
       </c>
       <c r="E1366" s="3" t="n"/>
-      <c r="F1366" s="3" t="n"/>
-      <c r="G1366" s="3" t="n"/>
+      <c r="F1366" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1366" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1367">
       <c r="A1367" s="2" t="inlineStr">
@@ -41500,8 +42133,16 @@
         </is>
       </c>
       <c r="E1367" s="3" t="n"/>
-      <c r="F1367" s="3" t="n"/>
-      <c r="G1367" s="3" t="n"/>
+      <c r="F1367" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1367" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1368">
       <c r="A1368" s="2" t="inlineStr">
@@ -41525,8 +42166,16 @@
         </is>
       </c>
       <c r="E1368" s="3" t="n"/>
-      <c r="F1368" s="3" t="n"/>
-      <c r="G1368" s="3" t="n"/>
+      <c r="F1368" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1368" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1369">
       <c r="A1369" s="2" t="inlineStr">
@@ -41550,10 +42199,18 @@
         </is>
       </c>
       <c r="E1369" s="3" t="n"/>
-      <c r="F1369" s="3" t="n"/>
-      <c r="G1369" s="3" t="n"/>
-    </row>
-    <row r="1370">
+      <c r="F1369" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1369" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370" ht="16" customHeight="1">
       <c r="A1370" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -41575,7 +42232,11 @@
         </is>
       </c>
       <c r="E1370" s="3" t="n"/>
-      <c r="F1370" s="3" t="n"/>
+      <c r="F1370" s="6" t="inlineStr">
+        <is>
+          <t>查询规则可分配的用户列表 — 100%</t>
+        </is>
+      </c>
       <c r="G1370" s="3" t="n"/>
     </row>
     <row r="1371">
@@ -41600,8 +42261,16 @@
         </is>
       </c>
       <c r="E1371" s="3" t="n"/>
-      <c r="F1371" s="3" t="n"/>
-      <c r="G1371" s="3" t="n"/>
+      <c r="F1371" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1371" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1372">
       <c r="A1372" s="2" t="inlineStr">
@@ -41625,8 +42294,16 @@
         </is>
       </c>
       <c r="E1372" s="3" t="n"/>
-      <c r="F1372" s="3" t="n"/>
-      <c r="G1372" s="3" t="n"/>
+      <c r="F1372" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1372" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1373">
       <c r="A1373" s="2" t="inlineStr">
@@ -41650,8 +42327,16 @@
         </is>
       </c>
       <c r="E1373" s="3" t="n"/>
-      <c r="F1373" s="3" t="n"/>
-      <c r="G1373" s="3" t="n"/>
+      <c r="F1373" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1373" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1374">
       <c r="A1374" s="2" t="inlineStr">
@@ -41675,8 +42360,16 @@
         </is>
       </c>
       <c r="E1374" s="3" t="n"/>
-      <c r="F1374" s="3" t="n"/>
-      <c r="G1374" s="3" t="n"/>
+      <c r="F1374" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1374" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1375">
       <c r="A1375" s="2" t="inlineStr">
@@ -41700,8 +42393,16 @@
         </is>
       </c>
       <c r="E1375" s="3" t="n"/>
-      <c r="F1375" s="3" t="n"/>
-      <c r="G1375" s="3" t="n"/>
+      <c r="F1375" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1375" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1376">
       <c r="A1376" s="2" t="inlineStr">
@@ -41725,8 +42426,16 @@
         </is>
       </c>
       <c r="E1376" s="3" t="n"/>
-      <c r="F1376" s="3" t="n"/>
-      <c r="G1376" s="3" t="n"/>
+      <c r="F1376" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1376" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1377">
       <c r="A1377" s="2" t="inlineStr">
@@ -41750,8 +42459,16 @@
         </is>
       </c>
       <c r="E1377" s="3" t="n"/>
-      <c r="F1377" s="3" t="n"/>
-      <c r="G1377" s="3" t="n"/>
+      <c r="F1377" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1377" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1378">
       <c r="A1378" s="2" t="inlineStr">
@@ -41775,8 +42492,16 @@
         </is>
       </c>
       <c r="E1378" s="3" t="n"/>
-      <c r="F1378" s="3" t="n"/>
-      <c r="G1378" s="3" t="n"/>
+      <c r="F1378" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1378" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1379">
       <c r="A1379" s="2" t="inlineStr">
@@ -41800,8 +42525,16 @@
         </is>
       </c>
       <c r="E1379" s="3" t="n"/>
-      <c r="F1379" s="3" t="n"/>
-      <c r="G1379" s="3" t="n"/>
+      <c r="F1379" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1379" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1380">
       <c r="A1380" s="2" t="inlineStr">
@@ -41825,8 +42558,16 @@
         </is>
       </c>
       <c r="E1380" s="3" t="n"/>
-      <c r="F1380" s="3" t="n"/>
-      <c r="G1380" s="3" t="n"/>
+      <c r="F1380" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1380" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1381">
       <c r="A1381" s="2" t="inlineStr">
@@ -41850,8 +42591,16 @@
         </is>
       </c>
       <c r="E1381" s="3" t="n"/>
-      <c r="F1381" s="3" t="n"/>
-      <c r="G1381" s="3" t="n"/>
+      <c r="F1381" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1381" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1382">
       <c r="A1382" s="2" t="inlineStr">
@@ -41875,8 +42624,16 @@
         </is>
       </c>
       <c r="E1382" s="3" t="n"/>
-      <c r="F1382" s="3" t="n"/>
-      <c r="G1382" s="3" t="n"/>
+      <c r="F1382" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1382" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1383">
       <c r="A1383" s="2" t="inlineStr">
@@ -41900,8 +42657,16 @@
         </is>
       </c>
       <c r="E1383" s="3" t="n"/>
-      <c r="F1383" s="3" t="n"/>
-      <c r="G1383" s="3" t="n"/>
+      <c r="F1383" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1383" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1384">
       <c r="A1384" s="2" t="inlineStr">
@@ -41925,8 +42690,16 @@
         </is>
       </c>
       <c r="E1384" s="3" t="n"/>
-      <c r="F1384" s="3" t="n"/>
-      <c r="G1384" s="3" t="n"/>
+      <c r="F1384" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1384" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1385">
       <c r="A1385" s="2" t="inlineStr">
@@ -41950,8 +42723,16 @@
         </is>
       </c>
       <c r="E1385" s="3" t="n"/>
-      <c r="F1385" s="3" t="n"/>
-      <c r="G1385" s="3" t="n"/>
+      <c r="F1385" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1385" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1386">
       <c r="A1386" s="2" t="inlineStr">
@@ -46667,10 +47448,18 @@
         </is>
       </c>
       <c r="E1547" s="3" t="n"/>
-      <c r="F1547" s="3" t="n"/>
-      <c r="G1547" s="3" t="n"/>
-    </row>
-    <row r="1548">
+      <c r="F1547" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1547" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548" ht="16" customHeight="1">
       <c r="A1548" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -46692,7 +47481,11 @@
         </is>
       </c>
       <c r="E1548" s="3" t="n"/>
-      <c r="F1548" s="3" t="n"/>
+      <c r="F1548" s="6" t="inlineStr">
+        <is>
+          <t>预览人群定向的LineSegment视图 — 100%</t>
+        </is>
+      </c>
       <c r="G1548" s="3" t="n"/>
     </row>
     <row r="1549">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -804,9 +804,19 @@
       </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0% (0/1)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -944,9 +954,19 @@
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
+      <c r="F17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2072,9 +2092,19 @@
       </c>
       <c r="D61" s="3" t="n"/>
       <c r="E61" s="3" t="n"/>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n"/>
+      <c r="F61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -8171,8 +8201,16 @@
         </is>
       </c>
       <c r="E191" s="3" t="n"/>
-      <c r="F191" s="3" t="n"/>
-      <c r="G191" s="3" t="n"/>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(需真实一次性OAuth code)</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：该接口用于交换真实Amazon OAuth2一次性授权code换取AMC账号绑定，code是通过真实浏览器重定向流程获得的一次性凭证，无法在自动化测试中合法获取或重放；ES真实样本里的code均已被消费过，重放会因code已失效而报错，且该操作涉及真实向Amazon发起账号OAuth绑定请求，高风险不适合自动化测试。不生成不执行。</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -15086,7 +15124,7 @@
       <c r="F417" s="3" t="n"/>
       <c r="G417" s="3" t="n"/>
     </row>
-    <row r="418">
+    <row r="418" ht="16" customHeight="1">
       <c r="A418" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15108,7 +15146,11 @@
         </is>
       </c>
       <c r="E418" s="3" t="n"/>
-      <c r="F418" s="3" t="n"/>
+      <c r="F418" s="6" t="inlineStr">
+        <is>
+          <t>按RowGuid下载附件 — 100%</t>
+        </is>
+      </c>
       <c r="G418" s="3" t="n"/>
     </row>
     <row r="419">
@@ -41098,7 +41140,7 @@
         </is>
       </c>
     </row>
-    <row r="1336">
+    <row r="1336" ht="32" customHeight="1">
       <c r="A1336" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -41120,7 +41162,12 @@
         </is>
       </c>
       <c r="E1336" s="3" t="n"/>
-      <c r="F1336" s="3" t="n"/>
+      <c r="F1336" s="6" t="inlineStr">
+        <is>
+          <t>不加类型/order过滤 — 74.0%
+同时加creativeTypes+orderIds过滤 — 7.2%</t>
+        </is>
+      </c>
       <c r="G1336" s="3" t="n"/>
     </row>
     <row r="1337">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1670,9 +1670,19 @@
       </c>
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="n"/>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
+      <c r="F45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>47% (27/58)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -31381,7 +31391,7 @@
       <c r="F992" s="3" t="n"/>
       <c r="G992" s="3" t="n"/>
     </row>
-    <row r="993">
+    <row r="993" ht="16" customHeight="1">
       <c r="A993" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -31403,10 +31413,18 @@
         </is>
       </c>
       <c r="E993" s="3" t="n"/>
-      <c r="F993" s="3" t="n"/>
-      <c r="G993" s="3" t="n"/>
-    </row>
-    <row r="994">
+      <c r="F993" s="6" t="inlineStr">
+        <is>
+          <t>批量更新投放时间【仅生成不执行-高风险】 — 100.0%</t>
+        </is>
+      </c>
+      <c r="G993" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高风险：批量操作多个lineItem，误执行影响面大，按规则先问用户。</t>
+        </is>
+      </c>
+    </row>
+    <row r="994" ht="32" customHeight="1">
       <c r="A994" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -31428,8 +31446,17 @@
         </is>
       </c>
       <c r="E994" s="3" t="n"/>
-      <c r="F994" s="3" t="n"/>
-      <c r="G994" s="3" t="n"/>
+      <c r="F994" s="6" t="inlineStr">
+        <is>
+          <t>批量打标签(add)【仅生成不执行-高风险】 — 98.2%
+批量删除标签(delete)【仅生成不执行-高风险】 — 1.8%</t>
+        </is>
+      </c>
+      <c r="G994" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高风险：批量打标签/删标签操作，且tagIds依赖真实lineitem_tag_id(账号内暂无该实体)。</t>
+        </is>
+      </c>
     </row>
     <row r="995">
       <c r="A995" s="2" t="inlineStr">
@@ -31453,10 +31480,18 @@
         </is>
       </c>
       <c r="E995" s="3" t="n"/>
-      <c r="F995" s="3" t="n"/>
-      <c r="G995" s="3" t="n"/>
-    </row>
-    <row r="996">
+      <c r="F995" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G995" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="996" ht="80" customHeight="1">
       <c r="A996" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -31478,10 +31513,22 @@
         </is>
       </c>
       <c r="E996" s="3" t="n"/>
-      <c r="F996" s="3" t="n"/>
-      <c r="G996" s="3" t="n"/>
-    </row>
-    <row r="997">
+      <c r="F996" s="6" t="inlineStr">
+        <is>
+          <t>批量修改投放状态(status)【仅生成不执行-高风险】 — 37.4%
+批量修改BaseSupplyBid出价【仅生成不执行-高风险】 — 27.8%
+批量修改每日预算上限(budgetCaps)【仅生成不执行-高风险】 — 13.6%
+批量修改出价(dict形式,含beforeVal)【仅生成不执行-高风险】 — 4.8%
+批量修改frequencies频次上限【仅生成不执行-高风险】 — 4.2%</t>
+        </is>
+      </c>
+      <c r="G996" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高风险：批量修改状态/出价/预算/频次等，部分场景支持selectedAllQuery(按筛选条件全选)模式，误执行风险高于普通单实体写操作。</t>
+        </is>
+      </c>
+    </row>
+    <row r="997" ht="80" customHeight="1">
       <c r="A997" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -31503,8 +31550,20 @@
         </is>
       </c>
       <c r="E997" s="3" t="n"/>
-      <c r="F997" s="3" t="n"/>
-      <c r="G997" s="3" t="n"/>
+      <c r="F997" s="6" t="inlineStr">
+        <is>
+          <t>SetSupplyBid【仅生成不执行-高风险】 — 51.7%
+SetBudget【仅生成不执行-高风险】 — 23.3%
+SetSupplyBidValueAdjust【仅生成不执行-高风险】 — 11.7%
+SetMaxBid【仅生成不执行-高风险】 — 9.2%
+DailyBudgetCap【仅生成不执行-高风险】 — 2.5%</t>
+        </is>
+      </c>
+      <c r="G997" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高风险：批量按调整值修改出价/预算，同BulkUpdateLineItems风险，先问用户。</t>
+        </is>
+      </c>
     </row>
     <row r="998">
       <c r="A998" s="2" t="inlineStr">
@@ -31528,10 +31587,18 @@
         </is>
       </c>
       <c r="E998" s="3" t="n"/>
-      <c r="F998" s="3" t="n"/>
-      <c r="G998" s="3" t="n"/>
-    </row>
-    <row r="999">
+      <c r="F998" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G998" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="999" ht="16" customHeight="1">
       <c r="A999" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -31553,7 +31620,11 @@
         </is>
       </c>
       <c r="E999" s="3" t="n"/>
-      <c r="F999" s="3" t="n"/>
+      <c r="F999" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G999" s="3" t="n"/>
     </row>
     <row r="1000">
@@ -31578,8 +31649,16 @@
         </is>
       </c>
       <c r="E1000" s="3" t="n"/>
-      <c r="F1000" s="3" t="n"/>
-      <c r="G1000" s="3" t="n"/>
+      <c r="F1000" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1000" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" s="2" t="inlineStr">
@@ -31603,8 +31682,16 @@
         </is>
       </c>
       <c r="E1001" s="3" t="n"/>
-      <c r="F1001" s="3" t="n"/>
-      <c r="G1001" s="3" t="n"/>
+      <c r="F1001" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1001" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1002">
       <c r="A1002" s="2" t="inlineStr">
@@ -31628,8 +31715,16 @@
         </is>
       </c>
       <c r="E1002" s="3" t="n"/>
-      <c r="F1002" s="3" t="n"/>
-      <c r="G1002" s="3" t="n"/>
+      <c r="F1002" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1002" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1003">
       <c r="A1003" s="2" t="inlineStr">
@@ -31653,8 +31748,16 @@
         </is>
       </c>
       <c r="E1003" s="3" t="n"/>
-      <c r="F1003" s="3" t="n"/>
-      <c r="G1003" s="3" t="n"/>
+      <c r="F1003" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1003" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1004">
       <c r="A1004" s="2" t="inlineStr">
@@ -31678,8 +31781,16 @@
         </is>
       </c>
       <c r="E1004" s="3" t="n"/>
-      <c r="F1004" s="3" t="n"/>
-      <c r="G1004" s="3" t="n"/>
+      <c r="F1004" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1004" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1005">
       <c r="A1005" s="2" t="inlineStr">
@@ -31703,8 +31814,16 @@
         </is>
       </c>
       <c r="E1005" s="3" t="n"/>
-      <c r="F1005" s="3" t="n"/>
-      <c r="G1005" s="3" t="n"/>
+      <c r="F1005" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1005" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" s="2" t="inlineStr">
@@ -31728,8 +31847,16 @@
         </is>
       </c>
       <c r="E1006" s="3" t="n"/>
-      <c r="F1006" s="3" t="n"/>
-      <c r="G1006" s="3" t="n"/>
+      <c r="F1006" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1006" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" s="2" t="inlineStr">
@@ -31753,8 +31880,16 @@
         </is>
       </c>
       <c r="E1007" s="3" t="n"/>
-      <c r="F1007" s="3" t="n"/>
-      <c r="G1007" s="3" t="n"/>
+      <c r="F1007" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1007" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" s="2" t="inlineStr">
@@ -31778,8 +31913,16 @@
         </is>
       </c>
       <c r="E1008" s="3" t="n"/>
-      <c r="F1008" s="3" t="n"/>
-      <c r="G1008" s="3" t="n"/>
+      <c r="F1008" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1008" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1009">
       <c r="A1009" s="2" t="inlineStr">
@@ -31803,8 +31946,16 @@
         </is>
       </c>
       <c r="E1009" s="3" t="n"/>
-      <c r="F1009" s="3" t="n"/>
-      <c r="G1009" s="3" t="n"/>
+      <c r="F1009" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1009" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1010">
       <c r="A1010" s="2" t="inlineStr">
@@ -31828,10 +31979,18 @@
         </is>
       </c>
       <c r="E1010" s="3" t="n"/>
-      <c r="F1010" s="3" t="n"/>
-      <c r="G1010" s="3" t="n"/>
-    </row>
-    <row r="1011">
+      <c r="F1010" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1010" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011" ht="16" customHeight="1">
       <c r="A1011" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -31853,10 +32012,14 @@
         </is>
       </c>
       <c r="E1011" s="3" t="n"/>
-      <c r="F1011" s="3" t="n"/>
+      <c r="F1011" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1011" s="3" t="n"/>
     </row>
-    <row r="1012">
+    <row r="1012" ht="32" customHeight="1">
       <c r="A1012" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -31878,10 +32041,15 @@
         </is>
       </c>
       <c r="E1012" s="3" t="n"/>
-      <c r="F1012" s="3" t="n"/>
+      <c r="F1012" s="6" t="inlineStr">
+        <is>
+          <t>不传类型(全量) — 69.0%
+按单一创意类型过滤(STANDARD DISPLAY) — 4.0%</t>
+        </is>
+      </c>
       <c r="G1012" s="3" t="n"/>
     </row>
-    <row r="1013">
+    <row r="1013" ht="16" customHeight="1">
       <c r="A1013" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -31903,10 +32071,14 @@
         </is>
       </c>
       <c r="E1013" s="3" t="n"/>
-      <c r="F1013" s="3" t="n"/>
+      <c r="F1013" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1013" s="3" t="n"/>
     </row>
-    <row r="1014">
+    <row r="1014" ht="16" customHeight="1">
       <c r="A1014" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -31928,10 +32100,14 @@
         </is>
       </c>
       <c r="E1014" s="3" t="n"/>
-      <c r="F1014" s="3" t="n"/>
+      <c r="F1014" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1014" s="3" t="n"/>
     </row>
-    <row r="1015">
+    <row r="1015" ht="16" customHeight="1">
       <c r="A1015" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -31953,10 +32129,14 @@
         </is>
       </c>
       <c r="E1015" s="3" t="n"/>
-      <c r="F1015" s="3" t="n"/>
+      <c r="F1015" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1015" s="3" t="n"/>
     </row>
-    <row r="1016">
+    <row r="1016" ht="16" customHeight="1">
       <c r="A1016" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -31978,7 +32158,11 @@
         </is>
       </c>
       <c r="E1016" s="3" t="n"/>
-      <c r="F1016" s="3" t="n"/>
+      <c r="F1016" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1016" s="3" t="n"/>
     </row>
     <row r="1017">
@@ -32003,10 +32187,18 @@
         </is>
       </c>
       <c r="E1017" s="3" t="n"/>
-      <c r="F1017" s="3" t="n"/>
-      <c r="G1017" s="3" t="n"/>
-    </row>
-    <row r="1018">
+      <c r="F1017" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1017" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018" ht="32" customHeight="1">
       <c r="A1018" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32028,8 +32220,17 @@
         </is>
       </c>
       <c r="E1018" s="3" t="n"/>
-      <c r="F1018" s="3" t="n"/>
-      <c r="G1018" s="3" t="n"/>
+      <c r="F1018" s="6" t="inlineStr">
+        <is>
+          <t>含lineItemId — 97.0%
+不含lineItemId — 3.0%</t>
+        </is>
+      </c>
+      <c r="G1018" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：请求体为空{}时(ES真实流量占比约3.0%)稳定复现IsSuccessStatusCode:false+NullReferenceException(LineItemController.GetDSPLineItemV2CreativesAsync第795行)，堆栈泄露给客户端，两轮稳定复现。</t>
+        </is>
+      </c>
     </row>
     <row r="1019">
       <c r="A1019" s="2" t="inlineStr">
@@ -32053,10 +32254,18 @@
         </is>
       </c>
       <c r="E1019" s="3" t="n"/>
-      <c r="F1019" s="3" t="n"/>
-      <c r="G1019" s="3" t="n"/>
-    </row>
-    <row r="1020">
+      <c r="F1019" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1019" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020" ht="32" customHeight="1">
       <c r="A1020" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32078,10 +32287,15 @@
         </is>
       </c>
       <c r="E1020" s="3" t="n"/>
-      <c r="F1020" s="3" t="n"/>
+      <c r="F1020" s="6" t="inlineStr">
+        <is>
+          <t>不含includeEligibility — 66.7%
+含includeEligibility — 33.3%</t>
+        </is>
+      </c>
       <c r="G1020" s="3" t="n"/>
     </row>
-    <row r="1021">
+    <row r="1021" ht="32" customHeight="1">
       <c r="A1021" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32103,7 +32317,12 @@
         </is>
       </c>
       <c r="E1021" s="3" t="n"/>
-      <c r="F1021" s="3" t="n"/>
+      <c r="F1021" s="6" t="inlineStr">
+        <is>
+          <t>不含includeEligibility — 66.7%
+含includeEligibility — 33.3%</t>
+        </is>
+      </c>
       <c r="G1021" s="3" t="n"/>
     </row>
     <row r="1022">
@@ -32128,10 +32347,18 @@
         </is>
       </c>
       <c r="E1022" s="3" t="n"/>
-      <c r="F1022" s="3" t="n"/>
-      <c r="G1022" s="3" t="n"/>
-    </row>
-    <row r="1023">
+      <c r="F1022" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1022" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023" ht="32" customHeight="1">
       <c r="A1023" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32153,10 +32380,15 @@
         </is>
       </c>
       <c r="E1023" s="3" t="n"/>
-      <c r="F1023" s="3" t="n"/>
+      <c r="F1023" s="6" t="inlineStr">
+        <is>
+          <t>不含includeEligibility — 64.6%
+含includeEligibility — 35.4%</t>
+        </is>
+      </c>
       <c r="G1023" s="3" t="n"/>
     </row>
-    <row r="1024">
+    <row r="1024" ht="32" customHeight="1">
       <c r="A1024" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32178,10 +32410,15 @@
         </is>
       </c>
       <c r="E1024" s="3" t="n"/>
-      <c r="F1024" s="3" t="n"/>
+      <c r="F1024" s="6" t="inlineStr">
+        <is>
+          <t>不含includeEligibility — 63.0%
+含includeEligibility — 37.0%</t>
+        </is>
+      </c>
       <c r="G1024" s="3" t="n"/>
     </row>
-    <row r="1025">
+    <row r="1025" ht="16" customHeight="1">
       <c r="A1025" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32203,10 +32440,14 @@
         </is>
       </c>
       <c r="E1025" s="3" t="n"/>
-      <c r="F1025" s="3" t="n"/>
+      <c r="F1025" s="6" t="inlineStr">
+        <is>
+          <t>按LineItemId查询每日预算 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1025" s="3" t="n"/>
     </row>
-    <row r="1026">
+    <row r="1026" ht="16" customHeight="1">
       <c r="A1026" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32228,7 +32469,11 @@
         </is>
       </c>
       <c r="E1026" s="3" t="n"/>
-      <c r="F1026" s="3" t="n"/>
+      <c r="F1026" s="6" t="inlineStr">
+        <is>
+          <t>按orderId查询 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1026" s="3" t="n"/>
     </row>
     <row r="1027">
@@ -32253,8 +32498,16 @@
         </is>
       </c>
       <c r="E1027" s="3" t="n"/>
-      <c r="F1027" s="3" t="n"/>
-      <c r="G1027" s="3" t="n"/>
+      <c r="F1027" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1027" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1028">
       <c r="A1028" s="2" t="inlineStr">
@@ -32278,10 +32531,18 @@
         </is>
       </c>
       <c r="E1028" s="3" t="n"/>
-      <c r="F1028" s="3" t="n"/>
-      <c r="G1028" s="3" t="n"/>
-    </row>
-    <row r="1029">
+      <c r="F1028" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1028" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029" ht="32" customHeight="1">
       <c r="A1029" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32303,7 +32564,12 @@
         </is>
       </c>
       <c r="E1029" s="3" t="n"/>
-      <c r="F1029" s="3" t="n"/>
+      <c r="F1029" s="6" t="inlineStr">
+        <is>
+          <t>不含clientId — 53.1%
+含clientId — 46.9%</t>
+        </is>
+      </c>
       <c r="G1029" s="3" t="n"/>
     </row>
     <row r="1030">
@@ -32328,10 +32594,18 @@
         </is>
       </c>
       <c r="E1030" s="3" t="n"/>
-      <c r="F1030" s="3" t="n"/>
-      <c r="G1030" s="3" t="n"/>
-    </row>
-    <row r="1031">
+      <c r="F1030" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1030" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031" ht="32" customHeight="1">
       <c r="A1031" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32353,10 +32627,15 @@
         </is>
       </c>
       <c r="E1031" s="3" t="n"/>
-      <c r="F1031" s="3" t="n"/>
+      <c r="F1031" s="6" t="inlineStr">
+        <is>
+          <t>无Segment分组(空) — 57.1%
+含真实Segment — 42.9%</t>
+        </is>
+      </c>
       <c r="G1031" s="3" t="n"/>
     </row>
-    <row r="1032">
+    <row r="1032" ht="16" customHeight="1">
       <c r="A1032" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32378,7 +32657,11 @@
         </is>
       </c>
       <c r="E1032" s="3" t="n"/>
-      <c r="F1032" s="3" t="n"/>
+      <c r="F1032" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1032" s="3" t="n"/>
     </row>
     <row r="1033">
@@ -32403,8 +32686,16 @@
         </is>
       </c>
       <c r="E1033" s="3" t="n"/>
-      <c r="F1033" s="3" t="n"/>
-      <c r="G1033" s="3" t="n"/>
+      <c r="F1033" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1033" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1034">
       <c r="A1034" s="2" t="inlineStr">
@@ -32428,8 +32719,16 @@
         </is>
       </c>
       <c r="E1034" s="3" t="n"/>
-      <c r="F1034" s="3" t="n"/>
-      <c r="G1034" s="3" t="n"/>
+      <c r="F1034" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1034" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1035">
       <c r="A1035" s="2" t="inlineStr">
@@ -32453,8 +32752,16 @@
         </is>
       </c>
       <c r="E1035" s="3" t="n"/>
-      <c r="F1035" s="3" t="n"/>
-      <c r="G1035" s="3" t="n"/>
+      <c r="F1035" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1035" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1036">
       <c r="A1036" s="2" t="inlineStr">
@@ -32478,10 +32785,18 @@
         </is>
       </c>
       <c r="E1036" s="3" t="n"/>
-      <c r="F1036" s="3" t="n"/>
-      <c r="G1036" s="3" t="n"/>
-    </row>
-    <row r="1037">
+      <c r="F1036" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1036" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037" ht="16" customHeight="1">
       <c r="A1037" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32503,10 +32818,14 @@
         </is>
       </c>
       <c r="E1037" s="3" t="n"/>
-      <c r="F1037" s="3" t="n"/>
+      <c r="F1037" s="6" t="inlineStr">
+        <is>
+          <t>开启每日预算后关闭还原 — 80.0%</t>
+        </is>
+      </c>
       <c r="G1037" s="3" t="n"/>
     </row>
-    <row r="1038">
+    <row r="1038" ht="16" customHeight="1">
       <c r="A1038" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32528,8 +32847,16 @@
         </is>
       </c>
       <c r="E1038" s="3" t="n"/>
-      <c r="F1038" s="3" t="n"/>
-      <c r="G1038" s="3" t="n"/>
+      <c r="F1038" s="6" t="inlineStr">
+        <is>
+          <t>设置创意轮播【仅生成不执行-高风险】 — 100.0%</t>
+        </is>
+      </c>
+      <c r="G1038" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高风险：本账号该lineItem当前无关联creative，且清理用的CreateOrDeleteLineItemCreativeAssociation(s)因365天零流量按规则不能生成case，导致没有已验证的自动化清理路径，需人工评估。</t>
+        </is>
+      </c>
     </row>
     <row r="1039">
       <c r="A1039" s="2" t="inlineStr">
@@ -32553,8 +32880,16 @@
         </is>
       </c>
       <c r="E1039" s="3" t="n"/>
-      <c r="F1039" s="3" t="n"/>
-      <c r="G1039" s="3" t="n"/>
+      <c r="F1039" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1039" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1040">
       <c r="A1040" s="2" t="inlineStr">
@@ -32578,8 +32913,16 @@
         </is>
       </c>
       <c r="E1040" s="3" t="n"/>
-      <c r="F1040" s="3" t="n"/>
-      <c r="G1040" s="3" t="n"/>
+      <c r="F1040" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1040" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" s="2" t="inlineStr">
@@ -32603,8 +32946,16 @@
         </is>
       </c>
       <c r="E1041" s="3" t="n"/>
-      <c r="F1041" s="3" t="n"/>
-      <c r="G1041" s="3" t="n"/>
+      <c r="F1041" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1041" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1042">
       <c r="A1042" s="2" t="inlineStr">
@@ -32628,10 +32979,18 @@
         </is>
       </c>
       <c r="E1042" s="3" t="n"/>
-      <c r="F1042" s="3" t="n"/>
-      <c r="G1042" s="3" t="n"/>
-    </row>
-    <row r="1043">
+      <c r="F1042" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1042" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043" ht="16" customHeight="1">
       <c r="A1043" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32653,8 +33012,16 @@
         </is>
       </c>
       <c r="E1043" s="3" t="n"/>
-      <c r="F1043" s="3" t="n"/>
-      <c r="G1043" s="3" t="n"/>
+      <c r="F1043" s="6" t="inlineStr">
+        <is>
+          <t>更新创意关联【仅生成不执行-高风险】 — 100.0%</t>
+        </is>
+      </c>
+      <c r="G1043" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高风险：同SetLineItemCreativeRotation，无已验证的自动化清理路径，需人工评估。</t>
+        </is>
+      </c>
     </row>
     <row r="1044">
       <c r="A1044" s="2" t="inlineStr">
@@ -32678,10 +33045,18 @@
         </is>
       </c>
       <c r="E1044" s="3" t="n"/>
-      <c r="F1044" s="3" t="n"/>
-      <c r="G1044" s="3" t="n"/>
-    </row>
-    <row r="1045">
+      <c r="F1044" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1044" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045" ht="16" customHeight="1">
       <c r="A1045" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32703,10 +33078,18 @@
         </is>
       </c>
       <c r="E1045" s="3" t="n"/>
-      <c r="F1045" s="3" t="n"/>
-      <c r="G1045" s="3" t="n"/>
-    </row>
-    <row r="1046">
+      <c r="F1045" s="6" t="inlineStr">
+        <is>
+          <t>更新投放时间后还原 — 100.0%</t>
+        </is>
+      </c>
+      <c r="G1045" s="5" t="inlineStr">
+        <is>
+          <t>已执行两轮PASS，LineItem自身日期已核实还原；但发现关联Order(576582423523984235)的orderEndDate在测试后停留在扩展后的2026-10-15未随之收缩回2026-09-24(推测Order日期随子LineItem自动扩展但不自动收缩)，LineItem模块内无可修正Order日期的接口，已记录待Order模块/人工核实，该LineItem当前deliveryActivationStatus=INACTIVE无实际投放影响。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046" ht="16" customHeight="1">
       <c r="A1046" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32728,7 +33111,11 @@
         </is>
       </c>
       <c r="E1046" s="3" t="n"/>
-      <c r="F1046" s="3" t="n"/>
+      <c r="F1046" s="6" t="inlineStr">
+        <is>
+          <t>更新名称后还原 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1046" s="3" t="n"/>
     </row>
     <row r="1047">
@@ -32753,8 +33140,16 @@
         </is>
       </c>
       <c r="E1047" s="3" t="n"/>
-      <c r="F1047" s="3" t="n"/>
-      <c r="G1047" s="3" t="n"/>
+      <c r="F1047" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1047" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1048">
       <c r="A1048" s="2" t="inlineStr">
@@ -32778,8 +33173,16 @@
         </is>
       </c>
       <c r="E1048" s="3" t="n"/>
-      <c r="F1048" s="3" t="n"/>
-      <c r="G1048" s="3" t="n"/>
+      <c r="F1048" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1048" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1049">
       <c r="A1049" s="2" t="inlineStr">
@@ -32803,10 +33206,18 @@
         </is>
       </c>
       <c r="E1049" s="3" t="n"/>
-      <c r="F1049" s="3" t="n"/>
-      <c r="G1049" s="3" t="n"/>
-    </row>
-    <row r="1050">
+      <c r="F1049" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1049" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050" ht="16" customHeight="1">
       <c r="A1050" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32828,7 +33239,11 @@
         </is>
       </c>
       <c r="E1050" s="3" t="n"/>
-      <c r="F1050" s="3" t="n"/>
+      <c r="F1050" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1050" s="3" t="n"/>
     </row>
     <row r="1051">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1454,9 +1454,19 @@
       </c>
       <c r="D37" s="3" t="n"/>
       <c r="E37" s="3" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="F37" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>30% (14/46)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -26669,8 +26679,16 @@
         </is>
       </c>
       <c r="E831" s="3" t="n"/>
-      <c r="F831" s="3" t="n"/>
-      <c r="G831" s="3" t="n"/>
+      <c r="F831" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G831" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="832">
       <c r="A832" s="2" t="inlineStr">
@@ -26694,8 +26712,16 @@
         </is>
       </c>
       <c r="E832" s="3" t="n"/>
-      <c r="F832" s="3" t="n"/>
-      <c r="G832" s="3" t="n"/>
+      <c r="F832" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G832" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="833">
       <c r="A833" s="2" t="inlineStr">
@@ -26719,8 +26745,16 @@
         </is>
       </c>
       <c r="E833" s="3" t="n"/>
-      <c r="F833" s="3" t="n"/>
-      <c r="G833" s="3" t="n"/>
+      <c r="F833" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G833" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" s="2" t="inlineStr">
@@ -26744,8 +26778,16 @@
         </is>
       </c>
       <c r="E834" s="3" t="n"/>
-      <c r="F834" s="3" t="n"/>
-      <c r="G834" s="3" t="n"/>
+      <c r="F834" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G834" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="835">
       <c r="A835" s="2" t="inlineStr">
@@ -26769,10 +26811,18 @@
         </is>
       </c>
       <c r="E835" s="3" t="n"/>
-      <c r="F835" s="3" t="n"/>
-      <c r="G835" s="3" t="n"/>
-    </row>
-    <row r="836">
+      <c r="F835" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G835" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="836" ht="32" customHeight="1">
       <c r="A836" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26794,10 +26844,15 @@
         </is>
       </c>
       <c r="E836" s="3" t="n"/>
-      <c r="F836" s="3" t="n"/>
+      <c r="F836" s="6" t="inlineStr">
+        <is>
+          <t>lineItemId= — 82.8%
+不传lineItemId — 17.2%</t>
+        </is>
+      </c>
       <c r="G836" s="3" t="n"/>
     </row>
-    <row r="837">
+    <row r="837" ht="16" customHeight="1">
       <c r="A837" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26819,7 +26874,11 @@
         </is>
       </c>
       <c r="E837" s="3" t="n"/>
-      <c r="F837" s="3" t="n"/>
+      <c r="F837" s="6" t="inlineStr">
+        <is>
+          <t>默认调用(无入参) — 100.0%</t>
+        </is>
+      </c>
       <c r="G837" s="3" t="n"/>
     </row>
     <row r="838">
@@ -26844,10 +26903,18 @@
         </is>
       </c>
       <c r="E838" s="3" t="n"/>
-      <c r="F838" s="3" t="n"/>
-      <c r="G838" s="3" t="n"/>
-    </row>
-    <row r="839">
+      <c r="F838" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G838" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="839" ht="16" customHeight="1">
       <c r="A839" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26869,7 +26936,11 @@
         </is>
       </c>
       <c r="E839" s="3" t="n"/>
-      <c r="F839" s="3" t="n"/>
+      <c r="F839" s="6" t="inlineStr">
+        <is>
+          <t>按amsAdvertiserIds+profileIds过滤查询 — 100.0%</t>
+        </is>
+      </c>
       <c r="G839" s="3" t="n"/>
     </row>
     <row r="840">
@@ -26894,10 +26965,18 @@
         </is>
       </c>
       <c r="E840" s="3" t="n"/>
-      <c r="F840" s="3" t="n"/>
-      <c r="G840" s="3" t="n"/>
-    </row>
-    <row r="841">
+      <c r="F840" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G840" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="841" ht="16" customHeight="1">
       <c r="A841" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26919,7 +26998,11 @@
         </is>
       </c>
       <c r="E841" s="3" t="n"/>
-      <c r="F841" s="3" t="n"/>
+      <c r="F841" s="6" t="inlineStr">
+        <is>
+          <t>默认调用(无入参) — 100.0%</t>
+        </is>
+      </c>
       <c r="G841" s="3" t="n"/>
     </row>
     <row r="842">
@@ -26944,8 +27027,16 @@
         </is>
       </c>
       <c r="E842" s="3" t="n"/>
-      <c r="F842" s="3" t="n"/>
-      <c r="G842" s="3" t="n"/>
+      <c r="F842" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G842" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="843">
       <c r="A843" s="2" t="inlineStr">
@@ -26969,10 +27060,18 @@
         </is>
       </c>
       <c r="E843" s="3" t="n"/>
-      <c r="F843" s="3" t="n"/>
-      <c r="G843" s="3" t="n"/>
-    </row>
-    <row r="844">
+      <c r="F843" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G843" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="844" ht="16" customHeight="1">
       <c r="A844" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26994,10 +27093,14 @@
         </is>
       </c>
       <c r="E844" s="3" t="n"/>
-      <c r="F844" s="3" t="n"/>
+      <c r="F844" s="6" t="inlineStr">
+        <is>
+          <t>默认调用(无入参) — 100.0%</t>
+        </is>
+      </c>
       <c r="G844" s="3" t="n"/>
     </row>
-    <row r="845">
+    <row r="845" ht="32" customHeight="1">
       <c r="A845" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -27019,10 +27122,15 @@
         </is>
       </c>
       <c r="E845" s="3" t="n"/>
-      <c r="F845" s="3" t="n"/>
+      <c r="F845" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+含searchText — 86.8%
+按Advertiser过滤+含searchText — 13.0%</t>
+        </is>
+      </c>
       <c r="G845" s="3" t="n"/>
     </row>
-    <row r="846">
+    <row r="846" ht="32" customHeight="1">
       <c r="A846" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -27044,10 +27152,15 @@
         </is>
       </c>
       <c r="E846" s="3" t="n"/>
-      <c r="F846" s="3" t="n"/>
+      <c r="F846" s="6" t="inlineStr">
+        <is>
+          <t>不含profileId — 97.8%
+含profileId — 2.2%</t>
+        </is>
+      </c>
       <c r="G846" s="3" t="n"/>
     </row>
-    <row r="847">
+    <row r="847" ht="32" customHeight="1">
       <c r="A847" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -27069,7 +27182,12 @@
         </is>
       </c>
       <c r="E847" s="3" t="n"/>
-      <c r="F847" s="3" t="n"/>
+      <c r="F847" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤 — 86.2%
+按Advertiser过滤 — 13.8%</t>
+        </is>
+      </c>
       <c r="G847" s="3" t="n"/>
     </row>
     <row r="848">
@@ -27094,8 +27212,16 @@
         </is>
       </c>
       <c r="E848" s="3" t="n"/>
-      <c r="F848" s="3" t="n"/>
-      <c r="G848" s="3" t="n"/>
+      <c r="F848" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G848" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="849">
       <c r="A849" s="2" t="inlineStr">
@@ -27119,10 +27245,18 @@
         </is>
       </c>
       <c r="E849" s="3" t="n"/>
-      <c r="F849" s="3" t="n"/>
-      <c r="G849" s="3" t="n"/>
-    </row>
-    <row r="850">
+      <c r="F849" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G849" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="850" ht="16" customHeight="1">
       <c r="A850" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -27144,7 +27278,11 @@
         </is>
       </c>
       <c r="E850" s="3" t="n"/>
-      <c r="F850" s="3" t="n"/>
+      <c r="F850" s="6" t="inlineStr">
+        <is>
+          <t>默认调用(无入参) — 100.0%</t>
+        </is>
+      </c>
       <c r="G850" s="3" t="n"/>
     </row>
     <row r="851">
@@ -27170,7 +27308,11 @@
       </c>
       <c r="E851" s="3" t="n"/>
       <c r="F851" s="3" t="n"/>
-      <c r="G851" s="3" t="n"/>
+      <c r="G851" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认：29万+次调用的高频接口，但实为"保存当前用户偏好设置"写操作(非查询)。ES样本请求体里带的userId/clientId是发起请求的真实用户自己的(如样本userId=14495非测试账号)，如果后端信任请求体里的身份而非仅认token，直接照搬样本执行可能误改其他真实用户的界面偏好。按高危先问原则未生成/执行case，需用户确认后端校验逻辑再决定是否补测。</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" s="2" t="inlineStr">
@@ -27194,8 +27336,16 @@
         </is>
       </c>
       <c r="E852" s="3" t="n"/>
-      <c r="F852" s="3" t="n"/>
-      <c r="G852" s="3" t="n"/>
+      <c r="F852" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G852" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" s="2" t="inlineStr">
@@ -27219,8 +27369,16 @@
         </is>
       </c>
       <c r="E853" s="3" t="n"/>
-      <c r="F853" s="3" t="n"/>
-      <c r="G853" s="3" t="n"/>
+      <c r="F853" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G853" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" s="2" t="inlineStr">
@@ -27244,8 +27402,16 @@
         </is>
       </c>
       <c r="E854" s="3" t="n"/>
-      <c r="F854" s="3" t="n"/>
-      <c r="G854" s="3" t="n"/>
+      <c r="F854" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G854" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" s="2" t="inlineStr">
@@ -27269,8 +27435,16 @@
         </is>
       </c>
       <c r="E855" s="3" t="n"/>
-      <c r="F855" s="3" t="n"/>
-      <c r="G855" s="3" t="n"/>
+      <c r="F855" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G855" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" s="2" t="inlineStr">
@@ -27294,8 +27468,16 @@
         </is>
       </c>
       <c r="E856" s="3" t="n"/>
-      <c r="F856" s="3" t="n"/>
-      <c r="G856" s="3" t="n"/>
+      <c r="F856" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G856" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" s="2" t="inlineStr">
@@ -27319,8 +27501,16 @@
         </is>
       </c>
       <c r="E857" s="3" t="n"/>
-      <c r="F857" s="3" t="n"/>
-      <c r="G857" s="3" t="n"/>
+      <c r="F857" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G857" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" s="2" t="inlineStr">
@@ -27344,8 +27534,16 @@
         </is>
       </c>
       <c r="E858" s="3" t="n"/>
-      <c r="F858" s="3" t="n"/>
-      <c r="G858" s="3" t="n"/>
+      <c r="F858" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G858" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" s="2" t="inlineStr">
@@ -27369,8 +27567,16 @@
         </is>
       </c>
       <c r="E859" s="3" t="n"/>
-      <c r="F859" s="3" t="n"/>
-      <c r="G859" s="3" t="n"/>
+      <c r="F859" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G859" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="860">
       <c r="A860" s="2" t="inlineStr">
@@ -27394,8 +27600,16 @@
         </is>
       </c>
       <c r="E860" s="3" t="n"/>
-      <c r="F860" s="3" t="n"/>
-      <c r="G860" s="3" t="n"/>
+      <c r="F860" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G860" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="861">
       <c r="A861" s="2" t="inlineStr">
@@ -27419,10 +27633,18 @@
         </is>
       </c>
       <c r="E861" s="3" t="n"/>
-      <c r="F861" s="3" t="n"/>
-      <c r="G861" s="3" t="n"/>
-    </row>
-    <row r="862">
+      <c r="F861" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G861" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="862" ht="80" customHeight="1">
       <c r="A862" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -27444,10 +27666,18 @@
         </is>
       </c>
       <c r="E862" s="3" t="n"/>
-      <c r="F862" s="3" t="n"/>
+      <c r="F862" s="6" t="inlineStr">
+        <is>
+          <t>无Advertiser过滤+不传isEndDateAlive — 57.0%
+按Advertiser过滤+不传isEndDateAlive — 32.0%
+无Advertiser过滤+isEndDateAlive=true — 5.6%
+按Advertiser过滤+isEndDateAlive=false — 3.2%
+不传advertiserIds+不传isEndDateAlive — 1.6%</t>
+        </is>
+      </c>
       <c r="G862" s="3" t="n"/>
     </row>
-    <row r="863">
+    <row r="863" ht="32" customHeight="1">
       <c r="A863" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -27469,7 +27699,12 @@
         </is>
       </c>
       <c r="E863" s="3" t="n"/>
-      <c r="F863" s="3" t="n"/>
+      <c r="F863" s="6" t="inlineStr">
+        <is>
+          <t>无amsAdvertiserIds过滤(查询全部Profile) — 8.4%
+按amsAdvertiserIds过滤查询 — 91.2%</t>
+        </is>
+      </c>
       <c r="G863" s="3" t="n"/>
     </row>
     <row r="864">
@@ -27494,8 +27729,16 @@
         </is>
       </c>
       <c r="E864" s="3" t="n"/>
-      <c r="F864" s="3" t="n"/>
-      <c r="G864" s="3" t="n"/>
+      <c r="F864" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G864" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="865">
       <c r="A865" s="2" t="inlineStr">
@@ -27520,9 +27763,13 @@
       </c>
       <c r="E865" s="3" t="n"/>
       <c r="F865" s="3" t="n"/>
-      <c r="G865" s="3" t="n"/>
-    </row>
-    <row r="866">
+      <c r="G865" s="5" t="inlineStr">
+        <is>
+          <t>观察项(非新bug)：真实调用7次，实测返回HTTP 200+业务code:500 msg:"Unsupported client id"，与既往记忆一致的已知限制，未生成可执行case。</t>
+        </is>
+      </c>
+    </row>
+    <row r="866" ht="64" customHeight="1">
       <c r="A866" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -27544,7 +27791,14 @@
         </is>
       </c>
       <c r="E866" s="3" t="n"/>
-      <c r="F866" s="3" t="n"/>
+      <c r="F866" s="6" t="inlineStr">
+        <is>
+          <t>按Profile过滤+不传countryList — 39.2%
+不传profileIds+不传countryList — 34.2%
+按Profile过滤+countryList=[] — 24.2%
+按Profile过滤+countryList=[US] — 1.6%</t>
+        </is>
+      </c>
       <c r="G866" s="3" t="n"/>
     </row>
     <row r="867">
@@ -27569,8 +27823,16 @@
         </is>
       </c>
       <c r="E867" s="3" t="n"/>
-      <c r="F867" s="3" t="n"/>
-      <c r="G867" s="3" t="n"/>
+      <c r="F867" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G867" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="868">
       <c r="A868" s="2" t="inlineStr">
@@ -27594,10 +27856,18 @@
         </is>
       </c>
       <c r="E868" s="3" t="n"/>
-      <c r="F868" s="3" t="n"/>
-      <c r="G868" s="3" t="n"/>
-    </row>
-    <row r="869">
+      <c r="F868" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G868" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="869" ht="96" customHeight="1">
       <c r="A869" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -27619,7 +27889,16 @@
         </is>
       </c>
       <c r="E869" s="3" t="n"/>
-      <c r="F869" s="3" t="n"/>
+      <c r="F869" s="6" t="inlineStr">
+        <is>
+          <t>按Advertiser过滤+无Order过滤 — 28.4%
+无Advertiser过滤+无Order过滤 — 23.4%
+按Advertiser过滤+按Order过滤 — 16.6%
+无Advertiser过滤+按Order过滤 — 15.2%
+按Advertiser过滤+不传orderIds — 10.6%
+无Advertiser过滤+不传orderIds — 5.8%</t>
+        </is>
+      </c>
       <c r="G869" s="3" t="n"/>
     </row>
     <row r="870">
@@ -27644,10 +27923,18 @@
         </is>
       </c>
       <c r="E870" s="3" t="n"/>
-      <c r="F870" s="3" t="n"/>
-      <c r="G870" s="3" t="n"/>
-    </row>
-    <row r="871">
+      <c r="F870" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G870" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="871" ht="64" customHeight="1">
       <c r="A871" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -27669,7 +27956,14 @@
         </is>
       </c>
       <c r="E871" s="3" t="n"/>
-      <c r="F871" s="3" t="n"/>
+      <c r="F871" s="6" t="inlineStr">
+        <is>
+          <t>不传advertiserIds+不传orderIds — 77.8%
+无Advertiser过滤+无Order过滤 — 19.2%
+按Advertiser过滤+按Order过滤 — 1.2%
+按Advertiser过滤+无Order过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G871" s="3" t="n"/>
     </row>
     <row r="872">
@@ -27694,8 +27988,16 @@
         </is>
       </c>
       <c r="E872" s="3" t="n"/>
-      <c r="F872" s="3" t="n"/>
-      <c r="G872" s="3" t="n"/>
+      <c r="F872" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G872" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="873">
       <c r="A873" s="2" t="inlineStr">
@@ -27719,8 +28021,16 @@
         </is>
       </c>
       <c r="E873" s="3" t="n"/>
-      <c r="F873" s="3" t="n"/>
-      <c r="G873" s="3" t="n"/>
+      <c r="F873" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G873" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="874">
       <c r="A874" s="2" t="inlineStr">
@@ -27744,8 +28054,16 @@
         </is>
       </c>
       <c r="E874" s="3" t="n"/>
-      <c r="F874" s="3" t="n"/>
-      <c r="G874" s="3" t="n"/>
+      <c r="F874" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G874" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="875">
       <c r="A875" s="2" t="inlineStr">
@@ -27769,8 +28087,16 @@
         </is>
       </c>
       <c r="E875" s="3" t="n"/>
-      <c r="F875" s="3" t="n"/>
-      <c r="G875" s="3" t="n"/>
+      <c r="F875" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G875" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="876">
       <c r="A876" s="2" t="inlineStr">
@@ -27794,8 +28120,16 @@
         </is>
       </c>
       <c r="E876" s="3" t="n"/>
-      <c r="F876" s="3" t="n"/>
-      <c r="G876" s="3" t="n"/>
+      <c r="F876" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G876" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="877">
       <c r="A877" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1008,9 +1008,19 @@
       </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
+      <c r="F19" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8% (2/26)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -15995,8 +16005,16 @@
         </is>
       </c>
       <c r="E451" s="3" t="n"/>
-      <c r="F451" s="3" t="n"/>
-      <c r="G451" s="3" t="n"/>
+      <c r="F451" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G451" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -16020,8 +16038,16 @@
         </is>
       </c>
       <c r="E452" s="3" t="n"/>
-      <c r="F452" s="3" t="n"/>
-      <c r="G452" s="3" t="n"/>
+      <c r="F452" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G452" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -16045,8 +16071,16 @@
         </is>
       </c>
       <c r="E453" s="3" t="n"/>
-      <c r="F453" s="3" t="n"/>
-      <c r="G453" s="3" t="n"/>
+      <c r="F453" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G453" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -16070,8 +16104,16 @@
         </is>
       </c>
       <c r="E454" s="3" t="n"/>
-      <c r="F454" s="3" t="n"/>
-      <c r="G454" s="3" t="n"/>
+      <c r="F454" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G454" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -16095,8 +16137,16 @@
         </is>
       </c>
       <c r="E455" s="3" t="n"/>
-      <c r="F455" s="3" t="n"/>
-      <c r="G455" s="3" t="n"/>
+      <c r="F455" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G455" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -16121,7 +16171,11 @@
       </c>
       <c r="E456" s="3" t="n"/>
       <c r="F456" s="3" t="n"/>
-      <c r="G456" s="3" t="n"/>
+      <c r="G456" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-待用户确认：真实流量最高(759次/年)的写操作，可创建属于自己的Audit运行，但26个接口内无对应Delete/Archive端点可清理，且请求体含真实advertiserId/orderIds下游实体，参考CreateAMCInstance先例暂不自行执行，需用户确认是否批准执行一次。</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -16145,8 +16199,16 @@
         </is>
       </c>
       <c r="E457" s="3" t="n"/>
-      <c r="F457" s="3" t="n"/>
-      <c r="G457" s="3" t="n"/>
+      <c r="F457" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G457" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -16170,8 +16232,16 @@
         </is>
       </c>
       <c r="E458" s="3" t="n"/>
-      <c r="F458" s="3" t="n"/>
-      <c r="G458" s="3" t="n"/>
+      <c r="F458" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G458" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -16195,8 +16265,16 @@
         </is>
       </c>
       <c r="E459" s="3" t="n"/>
-      <c r="F459" s="3" t="n"/>
-      <c r="G459" s="3" t="n"/>
+      <c r="F459" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G459" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -16220,8 +16298,16 @@
         </is>
       </c>
       <c r="E460" s="3" t="n"/>
-      <c r="F460" s="3" t="n"/>
-      <c r="G460" s="3" t="n"/>
+      <c r="F460" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G460" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -16245,8 +16331,16 @@
         </is>
       </c>
       <c r="E461" s="3" t="n"/>
-      <c r="F461" s="3" t="n"/>
-      <c r="G461" s="3" t="n"/>
+      <c r="F461" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G461" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -16270,8 +16364,16 @@
         </is>
       </c>
       <c r="E462" s="3" t="n"/>
-      <c r="F462" s="3" t="n"/>
-      <c r="G462" s="3" t="n"/>
+      <c r="F462" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G462" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -16295,10 +16397,18 @@
         </is>
       </c>
       <c r="E463" s="3" t="n"/>
-      <c r="F463" s="3" t="n"/>
-      <c r="G463" s="3" t="n"/>
-    </row>
-    <row r="464">
+      <c r="F463" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G463" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="80" customHeight="1">
       <c r="A464" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16320,7 +16430,15 @@
         </is>
       </c>
       <c r="E464" s="3" t="n"/>
-      <c r="F464" s="3" t="n"/>
+      <c r="F464" s="6" t="inlineStr">
+        <is>
+          <t>profileIds+14天默认周期 — 54.8%
+仅profileIds不传周期 — 27.2%
+advertiserIds+profileIds+14天 — 13.4%
+空过滤条件查询全部 — 2.4%
+advertiserIds+profileIds+7天周期 — 1.6%</t>
+        </is>
+      </c>
       <c r="G464" s="3" t="n"/>
     </row>
     <row r="465">
@@ -16346,7 +16464,11 @@
       </c>
       <c r="E465" s="3" t="n"/>
       <c r="F465" s="3" t="n"/>
-      <c r="G465" s="3" t="n"/>
+      <c r="G465" s="5" t="inlineStr">
+        <is>
+          <t>🔴安全风险(IDOR/越权访问)：用ES真实日志中他人的historyId(如4236，非本账号所有)直接调用，返回了完整真实业务数据(真实Order名称等)。HistoryList/GetAuditOrderNameAndId等列表类接口对本账号正确返回空(有归属过滤)，但GetDetail这类按ID直查详情接口未校验historyId是否属于当前登录客户，疑似水平越权访问漏洞，建议登记安全类缺陷并让工程侧核查所有以historyId为鉴权凭据的Audit接口。</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -16370,8 +16492,16 @@
         </is>
       </c>
       <c r="E466" s="3" t="n"/>
-      <c r="F466" s="3" t="n"/>
-      <c r="G466" s="3" t="n"/>
+      <c r="F466" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G466" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -16395,8 +16525,16 @@
         </is>
       </c>
       <c r="E467" s="3" t="n"/>
-      <c r="F467" s="3" t="n"/>
-      <c r="G467" s="3" t="n"/>
+      <c r="F467" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G467" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -16420,8 +16558,16 @@
         </is>
       </c>
       <c r="E468" s="3" t="n"/>
-      <c r="F468" s="3" t="n"/>
-      <c r="G468" s="3" t="n"/>
+      <c r="F468" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G468" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -16445,8 +16591,16 @@
         </is>
       </c>
       <c r="E469" s="3" t="n"/>
-      <c r="F469" s="3" t="n"/>
-      <c r="G469" s="3" t="n"/>
+      <c r="F469" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G469" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -16471,7 +16625,11 @@
       </c>
       <c r="E470" s="3" t="n"/>
       <c r="F470" s="3" t="n"/>
-      <c r="G470" s="3" t="n"/>
+      <c r="G470" s="5" t="inlineStr">
+        <is>
+          <t>🔴安全风险(IDOR/越权访问)：同GetDetail，用他人真实historyId(4236)直查返回了真实Opportunities业务数据，疑似缺少归属校验，参见GetDetail备注。</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -16495,8 +16653,16 @@
         </is>
       </c>
       <c r="E471" s="3" t="n"/>
-      <c r="F471" s="3" t="n"/>
-      <c r="G471" s="3" t="n"/>
+      <c r="F471" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G471" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -16520,8 +16686,16 @@
         </is>
       </c>
       <c r="E472" s="3" t="n"/>
-      <c r="F472" s="3" t="n"/>
-      <c r="G472" s="3" t="n"/>
+      <c r="F472" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G472" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -16545,10 +16719,18 @@
         </is>
       </c>
       <c r="E473" s="3" t="n"/>
-      <c r="F473" s="3" t="n"/>
-      <c r="G473" s="3" t="n"/>
-    </row>
-    <row r="474">
+      <c r="F473" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G473" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474" ht="48" customHeight="1">
       <c r="A474" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -16570,7 +16752,13 @@
         </is>
       </c>
       <c r="E474" s="3" t="n"/>
-      <c r="F474" s="3" t="n"/>
+      <c r="F474" s="6" t="inlineStr">
+        <is>
+          <t>仅按profileIds查询 — 95.6%
+orderIds+profileIds组合查询 — 2.0%
+空过滤条件查询全部 — 1.8%</t>
+        </is>
+      </c>
       <c r="G474" s="3" t="n"/>
     </row>
     <row r="475">
@@ -16595,8 +16783,16 @@
         </is>
       </c>
       <c r="E475" s="3" t="n"/>
-      <c r="F475" s="3" t="n"/>
-      <c r="G475" s="3" t="n"/>
+      <c r="F475" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G475" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -16620,8 +16816,16 @@
         </is>
       </c>
       <c r="E476" s="3" t="n"/>
-      <c r="F476" s="3" t="n"/>
-      <c r="G476" s="3" t="n"/>
+      <c r="F476" s="5" t="inlineStr">
+        <is>
+          <t>技术受限(无真实audit历史)</t>
+        </is>
+      </c>
+      <c r="G476" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：依赖真实historyId，测试账号在该advertiser下从未创建过Audit运行(HistoryList/GetAuditOrderNameAndId查询均为空)，无法安全构造。</t>
+        </is>
+      </c>
     </row>
     <row r="477" ht="16" customHeight="1">
       <c r="A477" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1236,9 +1236,19 @@
       </c>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="F28" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>17% (12/69)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -19574,8 +19584,16 @@
         </is>
       </c>
       <c r="E575" s="3" t="n"/>
-      <c r="F575" s="3" t="n"/>
-      <c r="G575" s="3" t="n"/>
+      <c r="F575" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G575" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
@@ -19599,8 +19617,16 @@
         </is>
       </c>
       <c r="E576" s="3" t="n"/>
-      <c r="F576" s="3" t="n"/>
-      <c r="G576" s="3" t="n"/>
+      <c r="F576" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G576" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
@@ -19624,8 +19650,16 @@
         </is>
       </c>
       <c r="E577" s="3" t="n"/>
-      <c r="F577" s="3" t="n"/>
-      <c r="G577" s="3" t="n"/>
+      <c r="F577" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G577" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
@@ -19650,7 +19684,11 @@
       </c>
       <c r="E578" s="3" t="n"/>
       <c r="F578" s="3" t="n"/>
-      <c r="G578" s="3" t="n"/>
+      <c r="G578" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口，run-cases.py执行框架仅支持JSON body，无法转发原始文件流，需人工测试。</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
@@ -19674,8 +19712,16 @@
         </is>
       </c>
       <c r="E579" s="3" t="n"/>
-      <c r="F579" s="3" t="n"/>
-      <c r="G579" s="3" t="n"/>
+      <c r="F579" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G579" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
@@ -19699,8 +19745,16 @@
         </is>
       </c>
       <c r="E580" s="3" t="n"/>
-      <c r="F580" s="3" t="n"/>
-      <c r="G580" s="3" t="n"/>
+      <c r="F580" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G580" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
@@ -19724,8 +19778,16 @@
         </is>
       </c>
       <c r="E581" s="3" t="n"/>
-      <c r="F581" s="3" t="n"/>
-      <c r="G581" s="3" t="n"/>
+      <c r="F581" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G581" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
@@ -19749,8 +19811,16 @@
         </is>
       </c>
       <c r="E582" s="3" t="n"/>
-      <c r="F582" s="3" t="n"/>
-      <c r="G582" s="3" t="n"/>
+      <c r="F582" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G582" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="inlineStr">
@@ -19775,7 +19845,11 @@
       </c>
       <c r="E583" s="3" t="n"/>
       <c r="F583" s="3" t="n"/>
-      <c r="G583" s="3" t="n"/>
+      <c r="G583" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认(批量创建类)：Creative tag全部69接口没有任何归档/删除/状态变更类接口，无法满足写操作"创建+归档清理"的铁律，若执行会在共享沙盒账号(已有6773条历史残留)留下无法清理的残留。暂未执行，需用户确认是否接受"无法清理"的现状执行。</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
@@ -19799,8 +19873,16 @@
         </is>
       </c>
       <c r="E584" s="3" t="n"/>
-      <c r="F584" s="3" t="n"/>
-      <c r="G584" s="3" t="n"/>
+      <c r="F584" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G584" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="inlineStr">
@@ -19824,8 +19906,16 @@
         </is>
       </c>
       <c r="E585" s="3" t="n"/>
-      <c r="F585" s="3" t="n"/>
-      <c r="G585" s="3" t="n"/>
+      <c r="F585" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G585" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
@@ -19849,8 +19939,16 @@
         </is>
       </c>
       <c r="E586" s="3" t="n"/>
-      <c r="F586" s="3" t="n"/>
-      <c r="G586" s="3" t="n"/>
+      <c r="F586" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G586" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
@@ -19875,7 +19973,11 @@
       </c>
       <c r="E587" s="3" t="n"/>
       <c r="F587" s="3" t="n"/>
-      <c r="G587" s="3" t="n"/>
+      <c r="G587" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认(更新类)：Creative tag全部69接口没有任何归档/删除/状态变更类接口，无法满足写操作"创建+归档清理"的铁律，若执行会在共享沙盒账号(已有6773条历史残留)留下无法清理的残留。暂未执行，需用户确认是否接受"无法清理"的现状执行。</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
@@ -19900,7 +20002,11 @@
       </c>
       <c r="E588" s="3" t="n"/>
       <c r="F588" s="3" t="n"/>
-      <c r="G588" s="3" t="n"/>
+      <c r="G588" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认(更新类)：Creative tag全部69接口没有任何归档/删除/状态变更类接口，无法满足写操作"创建+归档清理"的铁律，若执行会在共享沙盒账号(已有6773条历史残留)留下无法清理的残留。暂未执行，需用户确认是否接受"无法清理"的现状执行。</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
@@ -19924,8 +20030,16 @@
         </is>
       </c>
       <c r="E589" s="3" t="n"/>
-      <c r="F589" s="3" t="n"/>
-      <c r="G589" s="3" t="n"/>
+      <c r="F589" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G589" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
@@ -19950,7 +20064,11 @@
       </c>
       <c r="E590" s="3" t="n"/>
       <c r="F590" s="3" t="n"/>
-      <c r="G590" s="3" t="n"/>
+      <c r="G590" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口，run-cases.py执行框架仅支持JSON body，无法转发原始文件流，需人工测试。</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="inlineStr">
@@ -19974,8 +20092,16 @@
         </is>
       </c>
       <c r="E591" s="3" t="n"/>
-      <c r="F591" s="3" t="n"/>
-      <c r="G591" s="3" t="n"/>
+      <c r="F591" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G591" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
@@ -19999,8 +20125,16 @@
         </is>
       </c>
       <c r="E592" s="3" t="n"/>
-      <c r="F592" s="3" t="n"/>
-      <c r="G592" s="3" t="n"/>
+      <c r="F592" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G592" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="inlineStr">
@@ -20025,7 +20159,11 @@
       </c>
       <c r="E593" s="3" t="n"/>
       <c r="F593" s="3" t="n"/>
-      <c r="G593" s="3" t="n"/>
+      <c r="G593" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口，run-cases.py执行框架仅支持JSON body，无法转发原始文件流，需人工测试。</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
@@ -20050,7 +20188,11 @@
       </c>
       <c r="E594" s="3" t="n"/>
       <c r="F594" s="3" t="n"/>
-      <c r="G594" s="3" t="n"/>
+      <c r="G594" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口，run-cases.py执行框架仅支持JSON body，无法转发原始文件流，需人工测试。</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
@@ -20075,7 +20217,11 @@
       </c>
       <c r="E595" s="3" t="n"/>
       <c r="F595" s="3" t="n"/>
-      <c r="G595" s="3" t="n"/>
+      <c r="G595" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口，run-cases.py执行框架仅支持JSON body，无法转发原始文件流，需人工测试。</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
@@ -20099,8 +20245,16 @@
         </is>
       </c>
       <c r="E596" s="3" t="n"/>
-      <c r="F596" s="3" t="n"/>
-      <c r="G596" s="3" t="n"/>
+      <c r="F596" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G596" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
@@ -20125,7 +20279,11 @@
       </c>
       <c r="E597" s="3" t="n"/>
       <c r="F597" s="3" t="n"/>
-      <c r="G597" s="3" t="n"/>
+      <c r="G597" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口，run-cases.py执行框架仅支持JSON body，无法转发原始文件流，需人工测试。</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
@@ -20150,7 +20308,11 @@
       </c>
       <c r="E598" s="3" t="n"/>
       <c r="F598" s="3" t="n"/>
-      <c r="G598" s="3" t="n"/>
+      <c r="G598" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认(创建类)：Creative tag全部69接口没有任何归档/删除/状态变更类接口，无法满足写操作"创建+归档清理"的铁律，若执行会在共享沙盒账号(已有6773条历史残留)留下无法清理的残留。暂未执行，需用户确认是否接受"无法清理"的现状执行。</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
@@ -20175,7 +20337,11 @@
       </c>
       <c r="E599" s="3" t="n"/>
       <c r="F599" s="3" t="n"/>
-      <c r="G599" s="3" t="n"/>
+      <c r="G599" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口，run-cases.py执行框架仅支持JSON body，无法转发原始文件流，需人工测试。</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
@@ -20199,10 +20365,18 @@
         </is>
       </c>
       <c r="E600" s="3" t="n"/>
-      <c r="F600" s="3" t="n"/>
-      <c r="G600" s="3" t="n"/>
-    </row>
-    <row r="601">
+      <c r="F600" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G600" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="601" ht="16" customHeight="1">
       <c r="A601" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20224,7 +20398,11 @@
         </is>
       </c>
       <c r="E601" s="3" t="n"/>
-      <c r="F601" s="3" t="n"/>
+      <c r="F601" s="6" t="inlineStr">
+        <is>
+          <t>下载批量改名模板</t>
+        </is>
+      </c>
       <c r="G601" s="3" t="n"/>
     </row>
     <row r="602">
@@ -20249,10 +20427,18 @@
         </is>
       </c>
       <c r="E602" s="3" t="n"/>
-      <c r="F602" s="3" t="n"/>
-      <c r="G602" s="3" t="n"/>
-    </row>
-    <row r="603">
+      <c r="F602" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G602" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="603" ht="16" customHeight="1">
       <c r="A603" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20274,10 +20460,14 @@
         </is>
       </c>
       <c r="E603" s="3" t="n"/>
-      <c r="F603" s="3" t="n"/>
+      <c r="F603" s="6" t="inlineStr">
+        <is>
+          <t>下载ASIN模板</t>
+        </is>
+      </c>
       <c r="G603" s="3" t="n"/>
     </row>
-    <row r="604">
+    <row r="604" ht="16" customHeight="1">
       <c r="A604" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20299,7 +20489,11 @@
         </is>
       </c>
       <c r="E604" s="3" t="n"/>
-      <c r="F604" s="3" t="n"/>
+      <c r="F604" s="6" t="inlineStr">
+        <is>
+          <t>按assetId查询素材详情</t>
+        </is>
+      </c>
       <c r="G604" s="3" t="n"/>
     </row>
     <row r="605">
@@ -20324,8 +20518,16 @@
         </is>
       </c>
       <c r="E605" s="3" t="n"/>
-      <c r="F605" s="3" t="n"/>
-      <c r="G605" s="3" t="n"/>
+      <c r="F605" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G605" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
@@ -20349,10 +20551,18 @@
         </is>
       </c>
       <c r="E606" s="3" t="n"/>
-      <c r="F606" s="3" t="n"/>
-      <c r="G606" s="3" t="n"/>
-    </row>
-    <row r="607">
+      <c r="F606" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G606" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="607" ht="64" customHeight="1">
       <c r="A607" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20374,7 +20584,14 @@
         </is>
       </c>
       <c r="E607" s="3" t="n"/>
-      <c r="F607" s="3" t="n"/>
+      <c r="F607" s="6" t="inlineStr">
+        <is>
+          <t>profileIds+advertiserIds同时传 — 44.8%
+仅传profileIds — 29.8%
+两者均不传 — 14.2%
+仅传advertiserIds — 11.2%</t>
+        </is>
+      </c>
       <c r="G607" s="3" t="n"/>
     </row>
     <row r="608">
@@ -20399,10 +20616,18 @@
         </is>
       </c>
       <c r="E608" s="3" t="n"/>
-      <c r="F608" s="3" t="n"/>
-      <c r="G608" s="3" t="n"/>
-    </row>
-    <row r="609">
+      <c r="F608" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G608" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="609" ht="16" customHeight="1">
       <c r="A609" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20424,10 +20649,18 @@
         </is>
       </c>
       <c r="E609" s="3" t="n"/>
-      <c r="F609" s="3" t="n"/>
-      <c r="G609" s="3" t="n"/>
-    </row>
-    <row r="610">
+      <c r="F609" s="6" t="inlineStr">
+        <is>
+          <t>不按标签过滤(tagIds为空) — 33.3%</t>
+        </is>
+      </c>
+      <c r="G609" s="5" t="inlineStr">
+        <is>
+          <t>部分技术受限：仅覆盖tagIds=[]场景(占比33.3%)；主流场景tagIds非空(占比66.7%)因账号无真实creative_tag_id([NEEDS_REAL_VALUE])未覆盖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="610" ht="16" customHeight="1">
       <c r="A610" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20449,7 +20682,11 @@
         </is>
       </c>
       <c r="E610" s="3" t="n"/>
-      <c r="F610" s="3" t="n"/>
+      <c r="F610" s="6" t="inlineStr">
+        <is>
+          <t>按profileId+lineItemId查询可关联creative列表</t>
+        </is>
+      </c>
       <c r="G610" s="3" t="n"/>
     </row>
     <row r="611">
@@ -20474,8 +20711,16 @@
         </is>
       </c>
       <c r="E611" s="3" t="n"/>
-      <c r="F611" s="3" t="n"/>
-      <c r="G611" s="3" t="n"/>
+      <c r="F611" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G611" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
@@ -20499,8 +20744,16 @@
         </is>
       </c>
       <c r="E612" s="3" t="n"/>
-      <c r="F612" s="3" t="n"/>
-      <c r="G612" s="3" t="n"/>
+      <c r="F612" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G612" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="2" t="inlineStr">
@@ -20524,8 +20777,16 @@
         </is>
       </c>
       <c r="E613" s="3" t="n"/>
-      <c r="F613" s="3" t="n"/>
-      <c r="G613" s="3" t="n"/>
+      <c r="F613" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G613" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" s="2" t="inlineStr">
@@ -20550,7 +20811,11 @@
       </c>
       <c r="E614" s="3" t="n"/>
       <c r="F614" s="3" t="n"/>
-      <c r="G614" s="3" t="n"/>
+      <c r="G614" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：需要真实存在的lineItem↔creative关联记录完整对象(state/creativeSize/creativeType/起止日期等)，未能在账号内定位到已确认生效的真实关联。</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="2" t="inlineStr">
@@ -20574,10 +20839,18 @@
         </is>
       </c>
       <c r="E615" s="3" t="n"/>
-      <c r="F615" s="3" t="n"/>
-      <c r="G615" s="3" t="n"/>
-    </row>
-    <row r="616">
+      <c r="F615" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G615" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="616" ht="16" customHeight="1">
       <c r="A616" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20599,7 +20872,11 @@
         </is>
       </c>
       <c r="E616" s="3" t="n"/>
-      <c r="F616" s="3" t="n"/>
+      <c r="F616" s="6" t="inlineStr">
+        <is>
+          <t>按creativeId查询关联lineItem</t>
+        </is>
+      </c>
       <c r="G616" s="3" t="n"/>
     </row>
     <row r="617">
@@ -20624,10 +20901,18 @@
         </is>
       </c>
       <c r="E617" s="3" t="n"/>
-      <c r="F617" s="3" t="n"/>
-      <c r="G617" s="3" t="n"/>
-    </row>
-    <row r="618">
+      <c r="F617" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G617" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="618" ht="16" customHeight="1">
       <c r="A618" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20649,8 +20934,16 @@
         </is>
       </c>
       <c r="E618" s="3" t="n"/>
-      <c r="F618" s="3" t="n"/>
-      <c r="G618" s="3" t="n"/>
+      <c r="F618" s="6" t="inlineStr">
+        <is>
+          <t>按creativeId查询REC素材详情</t>
+        </is>
+      </c>
+      <c r="G618" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：稳定复现"Too Many Requests"(HTTP 200但IsSuccessStatusCode:false)，间隔20秒重试6次结果一致，非瞬时抖动，怀疑内部转发Amazon Ads API链路长期受限。该接口365天流量仅3次。</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="2" t="inlineStr">
@@ -20674,10 +20967,18 @@
         </is>
       </c>
       <c r="E619" s="3" t="n"/>
-      <c r="F619" s="3" t="n"/>
-      <c r="G619" s="3" t="n"/>
-    </row>
-    <row r="620">
+      <c r="F619" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G619" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="620" ht="16" customHeight="1">
       <c r="A620" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20699,10 +21000,14 @@
         </is>
       </c>
       <c r="E620" s="3" t="n"/>
-      <c r="F620" s="3" t="n"/>
+      <c r="F620" s="6" t="inlineStr">
+        <is>
+          <t>按assetId查询StandardDisplay素材</t>
+        </is>
+      </c>
       <c r="G620" s="3" t="n"/>
     </row>
-    <row r="621">
+    <row r="621" ht="16" customHeight="1">
       <c r="A621" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -20724,7 +21029,11 @@
         </is>
       </c>
       <c r="E621" s="3" t="n"/>
-      <c r="F621" s="3" t="n"/>
+      <c r="F621" s="6" t="inlineStr">
+        <is>
+          <t>按creativeId查询StandardDisplay素材详情</t>
+        </is>
+      </c>
       <c r="G621" s="3" t="n"/>
     </row>
     <row r="622">
@@ -20749,8 +21058,16 @@
         </is>
       </c>
       <c r="E622" s="3" t="n"/>
-      <c r="F622" s="3" t="n"/>
-      <c r="G622" s="3" t="n"/>
+      <c r="F622" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G622" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" s="2" t="inlineStr">
@@ -20774,8 +21091,16 @@
         </is>
       </c>
       <c r="E623" s="3" t="n"/>
-      <c r="F623" s="3" t="n"/>
-      <c r="G623" s="3" t="n"/>
+      <c r="F623" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G623" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="2" t="inlineStr">
@@ -20799,8 +21124,16 @@
         </is>
       </c>
       <c r="E624" s="3" t="n"/>
-      <c r="F624" s="3" t="n"/>
-      <c r="G624" s="3" t="n"/>
+      <c r="F624" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G624" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
@@ -20824,8 +21157,16 @@
         </is>
       </c>
       <c r="E625" s="3" t="n"/>
-      <c r="F625" s="3" t="n"/>
-      <c r="G625" s="3" t="n"/>
+      <c r="F625" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G625" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
@@ -20849,8 +21190,16 @@
         </is>
       </c>
       <c r="E626" s="3" t="n"/>
-      <c r="F626" s="3" t="n"/>
-      <c r="G626" s="3" t="n"/>
+      <c r="F626" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G626" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="2" t="inlineStr">
@@ -20874,8 +21223,16 @@
         </is>
       </c>
       <c r="E627" s="3" t="n"/>
-      <c r="F627" s="3" t="n"/>
-      <c r="G627" s="3" t="n"/>
+      <c r="F627" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G627" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="2" t="inlineStr">
@@ -20899,8 +21256,16 @@
         </is>
       </c>
       <c r="E628" s="3" t="n"/>
-      <c r="F628" s="3" t="n"/>
-      <c r="G628" s="3" t="n"/>
+      <c r="F628" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G628" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
@@ -20924,8 +21289,16 @@
         </is>
       </c>
       <c r="E629" s="3" t="n"/>
-      <c r="F629" s="3" t="n"/>
-      <c r="G629" s="3" t="n"/>
+      <c r="F629" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G629" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
@@ -20949,8 +21322,16 @@
         </is>
       </c>
       <c r="E630" s="3" t="n"/>
-      <c r="F630" s="3" t="n"/>
-      <c r="G630" s="3" t="n"/>
+      <c r="F630" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G630" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
@@ -20975,7 +21356,11 @@
       </c>
       <c r="E631" s="3" t="n"/>
       <c r="F631" s="3" t="n"/>
-      <c r="G631" s="3" t="n"/>
+      <c r="G631" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认(创建类(另需要Creative tag以外的预签名S3上传URL，本tag内未找到获取方式))：Creative tag全部69接口没有任何归档/删除/状态变更类接口，无法满足写操作"创建+归档清理"的铁律，若执行会在共享沙盒账号(已有6773条历史残留)留下无法清理的残留。暂未执行，需用户确认是否接受"无法清理"的现状执行。</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
@@ -21000,9 +21385,13 @@
       </c>
       <c r="E632" s="3" t="n"/>
       <c r="F632" s="3" t="n"/>
-      <c r="G632" s="3" t="n"/>
-    </row>
-    <row r="633">
+      <c r="G632" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口，run-cases.py执行框架仅支持JSON body，无法转发原始文件流，需人工测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="633" ht="80" customHeight="1">
       <c r="A633" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -21024,10 +21413,18 @@
         </is>
       </c>
       <c r="E633" s="3" t="n"/>
-      <c r="F633" s="3" t="n"/>
+      <c r="F633" s="6" t="inlineStr">
+        <is>
+          <t>无过滤条件浏览素材库 — 55.8%
+按ASSET TYPE值过滤(valueFilters) — 33.8%
+关键词文本搜索 — 7.4%
+按文件大小区间过滤(rangeFilters) — 1.0%
+区间过滤+值过滤组合 — 1.0%</t>
+        </is>
+      </c>
       <c r="G633" s="3" t="n"/>
     </row>
-    <row r="634">
+    <row r="634" ht="16" customHeight="1">
       <c r="A634" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -21049,7 +21446,11 @@
         </is>
       </c>
       <c r="E634" s="3" t="n"/>
-      <c r="F634" s="3" t="n"/>
+      <c r="F634" s="6" t="inlineStr">
+        <is>
+          <t>单图片StandardDisplay预览 — 99.4%</t>
+        </is>
+      </c>
       <c r="G634" s="3" t="n"/>
     </row>
     <row r="635">
@@ -21075,7 +21476,11 @@
       </c>
       <c r="E635" s="3" t="n"/>
       <c r="F635" s="3" t="n"/>
-      <c r="G635" s="3" t="n"/>
+      <c r="G635" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认(更新类(账号内已有真实creativeId可用，但改前读原值/改后精确复原的安全设计未验证))：Creative tag全部69接口没有任何归档/删除/状态变更类接口，无法满足写操作"创建+归档清理"的铁律，若执行会在共享沙盒账号(已有6773条历史残留)留下无法清理的残留。暂未执行，需用户确认是否接受"无法清理"的现状执行。</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" s="2" t="inlineStr">
@@ -21100,7 +21505,11 @@
       </c>
       <c r="E636" s="3" t="n"/>
       <c r="F636" s="3" t="n"/>
-      <c r="G636" s="3" t="n"/>
+      <c r="G636" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口，run-cases.py执行框架仅支持JSON body，无法转发原始文件流，需人工测试。</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" s="2" t="inlineStr">
@@ -21124,8 +21533,16 @@
         </is>
       </c>
       <c r="E637" s="3" t="n"/>
-      <c r="F637" s="3" t="n"/>
-      <c r="G637" s="3" t="n"/>
+      <c r="F637" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G637" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="2" t="inlineStr">
@@ -21149,8 +21566,16 @@
         </is>
       </c>
       <c r="E638" s="3" t="n"/>
-      <c r="F638" s="3" t="n"/>
-      <c r="G638" s="3" t="n"/>
+      <c r="F638" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G638" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" s="2" t="inlineStr">
@@ -21175,7 +21600,11 @@
       </c>
       <c r="E639" s="3" t="n"/>
       <c r="F639" s="3" t="n"/>
-      <c r="G639" s="3" t="n"/>
+      <c r="G639" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认(创建类)：Creative tag全部69接口没有任何归档/删除/状态变更类接口，无法满足写操作"创建+归档清理"的铁律，若执行会在共享沙盒账号(已有6773条历史残留)留下无法清理的残留。暂未执行，需用户确认是否接受"无法清理"的现状执行。</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" s="2" t="inlineStr">
@@ -21200,7 +21629,11 @@
       </c>
       <c r="E640" s="3" t="n"/>
       <c r="F640" s="3" t="n"/>
-      <c r="G640" s="3" t="n"/>
+      <c r="G640" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认(创建类)：Creative tag全部69接口没有任何归档/删除/状态变更类接口，无法满足写操作"创建+归档清理"的铁律，若执行会在共享沙盒账号(已有6773条历史残留)留下无法清理的残留。暂未执行，需用户确认是否接受"无法清理"的现状执行。</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" s="2" t="inlineStr">
@@ -21224,8 +21657,16 @@
         </is>
       </c>
       <c r="E641" s="3" t="n"/>
-      <c r="F641" s="3" t="n"/>
-      <c r="G641" s="3" t="n"/>
+      <c r="F641" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G641" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" s="2" t="inlineStr">
@@ -21249,8 +21690,16 @@
         </is>
       </c>
       <c r="E642" s="3" t="n"/>
-      <c r="F642" s="3" t="n"/>
-      <c r="G642" s="3" t="n"/>
+      <c r="F642" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G642" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
@@ -21274,8 +21723,16 @@
         </is>
       </c>
       <c r="E643" s="3" t="n"/>
-      <c r="F643" s="3" t="n"/>
-      <c r="G643" s="3" t="n"/>
+      <c r="F643" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G643" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -986,9 +986,19 @@
       </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
+      <c r="F18" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>69% (22/32)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -15215,10 +15225,18 @@
         </is>
       </c>
       <c r="E419" s="3" t="n"/>
-      <c r="F419" s="3" t="n"/>
-      <c r="G419" s="3" t="n"/>
-    </row>
-    <row r="420">
+      <c r="F419" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G419" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="16" customHeight="1">
       <c r="A420" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15240,7 +15258,11 @@
         </is>
       </c>
       <c r="E420" s="3" t="n"/>
-      <c r="F420" s="3" t="n"/>
+      <c r="F420" s="6" t="inlineStr">
+        <is>
+          <t>向黑名单添加audience名称(含清理) — 100%</t>
+        </is>
+      </c>
       <c r="G420" s="3" t="n"/>
     </row>
     <row r="421">
@@ -15265,10 +15287,18 @@
         </is>
       </c>
       <c r="E421" s="3" t="n"/>
-      <c r="F421" s="3" t="n"/>
-      <c r="G421" s="3" t="n"/>
-    </row>
-    <row r="422">
+      <c r="F421" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G421" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="16" customHeight="1">
       <c r="A422" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15290,10 +15320,14 @@
         </is>
       </c>
       <c r="E422" s="3" t="n"/>
-      <c r="F422" s="3" t="n"/>
+      <c r="F422" s="6" t="inlineStr">
+        <is>
+          <t>应用audience group到lineItem(仅执行1轮) — 100%</t>
+        </is>
+      </c>
       <c r="G422" s="3" t="n"/>
     </row>
-    <row r="423">
+    <row r="423" ht="16" customHeight="1">
       <c r="A423" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15315,8 +15349,16 @@
         </is>
       </c>
       <c r="E423" s="3" t="n"/>
-      <c r="F423" s="3" t="n"/>
-      <c r="G423" s="3" t="n"/>
+      <c r="F423" s="6" t="inlineStr">
+        <is>
+          <t>批量更新target(真实场景)+批量删除清理(仅执行1轮)</t>
+        </is>
+      </c>
+      <c r="G423" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug(响应说成功、实际未生效)：deleteGroup:true调用返回IsSuccessStatusCode:true，但事后GetSegmentTargetingViewByGroupId/GetAudienceGroupIdAndName仍能查到该group完整配置(仅groupName被清空)，与AmcReport的EditHistoryReportName同一类缺陷。因此账号内新增了4个无法真正清理的测试AudienceGroup(1551799692390563840/1551800197565120512等)，均已不影响其他功能。</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -15340,10 +15382,18 @@
         </is>
       </c>
       <c r="E424" s="3" t="n"/>
-      <c r="F424" s="3" t="n"/>
-      <c r="G424" s="3" t="n"/>
-    </row>
-    <row r="425">
+      <c r="F424" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G424" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="16" customHeight="1">
       <c r="A425" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15365,10 +15415,14 @@
         </is>
       </c>
       <c r="E425" s="3" t="n"/>
-      <c r="F425" s="3" t="n"/>
+      <c r="F425" s="6" t="inlineStr">
+        <is>
+          <t>创建audience group(仅执行1轮) — 100%</t>
+        </is>
+      </c>
       <c r="G425" s="3" t="n"/>
     </row>
-    <row r="426">
+    <row r="426" ht="64" customHeight="1">
       <c r="A426" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15390,8 +15444,19 @@
         </is>
       </c>
       <c r="E426" s="3" t="n"/>
-      <c r="F426" s="3" t="n"/>
-      <c r="G426" s="3" t="n"/>
+      <c r="F426" s="6" t="inlineStr">
+        <is>
+          <t>PRODUCT PURCHASES — 76.7%
+PRODUCT SEARCH — 58.9%
+PRODUCT VIEWS — 50.5%
+PRODUCT SIMS — 37.8%</t>
+        </is>
+      </c>
+      <c r="G426" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高危(4个audienceType场景)：直接向Amazon真实创建custom audience定向实体(idempotencyKey是Amazon Ads API幂等创建标志)，且tag内唯一疑似清理接口DeleteAutoTestDspAudiences请求体为空无作用域参数、365天零流量、准备调用时被安全分类器以Interfere With Workloads拦截，无已验证的清理机制，判定不可逆未执行。</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -15415,8 +15480,16 @@
         </is>
       </c>
       <c r="E427" s="3" t="n"/>
-      <c r="F427" s="3" t="n"/>
-      <c r="G427" s="3" t="n"/>
+      <c r="F427" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G427" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -15440,8 +15513,16 @@
         </is>
       </c>
       <c r="E428" s="3" t="n"/>
-      <c r="F428" s="3" t="n"/>
-      <c r="G428" s="3" t="n"/>
+      <c r="F428" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G428" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -15465,8 +15546,16 @@
         </is>
       </c>
       <c r="E429" s="3" t="n"/>
-      <c r="F429" s="3" t="n"/>
-      <c r="G429" s="3" t="n"/>
+      <c r="F429" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G429" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -15491,7 +15580,11 @@
       </c>
       <c r="E430" s="3" t="n"/>
       <c r="F430" s="3" t="n"/>
-      <c r="G430" s="3" t="n"/>
+      <c r="G430" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量+请求体无作用域参数+准备调用时被Claude Code安全分类器以Interfere With Workloads拦截，未执行，建议工程侧review该接口设计后再考虑是否用于自动化清理。</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -15515,10 +15608,18 @@
         </is>
       </c>
       <c r="E431" s="3" t="n"/>
-      <c r="F431" s="3" t="n"/>
-      <c r="G431" s="3" t="n"/>
-    </row>
-    <row r="432">
+      <c r="F431" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G431" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="16" customHeight="1">
       <c r="A432" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15540,10 +15641,18 @@
         </is>
       </c>
       <c r="E432" s="3" t="n"/>
-      <c r="F432" s="3" t="n"/>
-      <c r="G432" s="3" t="n"/>
-    </row>
-    <row r="433">
+      <c r="F432" s="6" t="inlineStr">
+        <is>
+          <t>导出audience重叠度报告 — 100%</t>
+        </is>
+      </c>
+      <c r="G432" s="5" t="inlineStr">
+        <is>
+          <t>观察项(非缺陷)：同GetAudienceOverlaps的Global advertiser限制，返回纯文本非JSON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="16" customHeight="1">
       <c r="A433" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15565,10 +15674,14 @@
         </is>
       </c>
       <c r="E433" s="3" t="n"/>
-      <c r="F433" s="3" t="n"/>
+      <c r="F433" s="6" t="inlineStr">
+        <is>
+          <t>获取当前账号黑名单列表 — 100%</t>
+        </is>
+      </c>
       <c r="G433" s="3" t="n"/>
     </row>
-    <row r="434">
+    <row r="434" ht="16" customHeight="1">
       <c r="A434" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15590,10 +15703,14 @@
         </is>
       </c>
       <c r="E434" s="3" t="n"/>
-      <c r="F434" s="3" t="n"/>
+      <c r="F434" s="6" t="inlineStr">
+        <is>
+          <t>按blackListId查询黑名单明细 — 87.4%</t>
+        </is>
+      </c>
       <c r="G434" s="3" t="n"/>
     </row>
-    <row r="435">
+    <row r="435" ht="48" customHeight="1">
       <c r="A435" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15615,10 +15732,16 @@
         </is>
       </c>
       <c r="E435" s="3" t="n"/>
-      <c r="F435" s="3" t="n"/>
+      <c r="F435" s="6" t="inlineStr">
+        <is>
+          <t>场景1:仅按advertiserIds查询 — 48.8%
+场景2:advertiserIds为空+clientId+includeUnnamed — 45.4%
+场景3:advertiserIds+includeUnnamed — 5.8%</t>
+        </is>
+      </c>
       <c r="G435" s="3" t="n"/>
     </row>
-    <row r="436">
+    <row r="436" ht="16" customHeight="1">
       <c r="A436" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15640,10 +15763,14 @@
         </is>
       </c>
       <c r="E436" s="3" t="n"/>
-      <c r="F436" s="3" t="n"/>
+      <c r="F436" s="6" t="inlineStr">
+        <is>
+          <t>按advertiserId+audienceName查询audienceId — 100%</t>
+        </is>
+      </c>
       <c r="G436" s="3" t="n"/>
     </row>
-    <row r="437">
+    <row r="437" ht="16" customHeight="1">
       <c r="A437" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15665,8 +15792,16 @@
         </is>
       </c>
       <c r="E437" s="3" t="n"/>
-      <c r="F437" s="3" t="n"/>
-      <c r="G437" s="3" t="n"/>
+      <c r="F437" s="6" t="inlineStr">
+        <is>
+          <t>查询audience重叠度报告 — 100%</t>
+        </is>
+      </c>
+      <c r="G437" s="5" t="inlineStr">
+        <is>
+          <t>观察项(非缺陷)：本任务共享测试广告主578107614358724215被后端判定为Global advertiser，统一返回Invalid request: Global advertisers are not supported.，属账号类型限制。</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -15690,10 +15825,18 @@
         </is>
       </c>
       <c r="E438" s="3" t="n"/>
-      <c r="F438" s="3" t="n"/>
-      <c r="G438" s="3" t="n"/>
-    </row>
-    <row r="439">
+      <c r="F438" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G438" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="16" customHeight="1">
       <c r="A439" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15715,10 +15858,14 @@
         </is>
       </c>
       <c r="E439" s="3" t="n"/>
-      <c r="F439" s="3" t="n"/>
+      <c r="F439" s="6" t="inlineStr">
+        <is>
+          <t>按名称关键字模糊搜索audience(输入联想) — 100%</t>
+        </is>
+      </c>
       <c r="G439" s="3" t="n"/>
     </row>
-    <row r="440">
+    <row r="440" ht="16" customHeight="1">
       <c r="A440" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15740,10 +15887,14 @@
         </is>
       </c>
       <c r="E440" s="3" t="n"/>
-      <c r="F440" s="3" t="n"/>
+      <c r="F440" s="6" t="inlineStr">
+        <is>
+          <t>获取audience分类目录 — 100%</t>
+        </is>
+      </c>
       <c r="G440" s="3" t="n"/>
     </row>
-    <row r="441">
+    <row r="441" ht="32" customHeight="1">
       <c r="A441" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15765,10 +15916,19 @@
         </is>
       </c>
       <c r="E441" s="3" t="n"/>
-      <c r="F441" s="3" t="n"/>
-      <c r="G441" s="3" t="n"/>
-    </row>
-    <row r="442">
+      <c r="F441" s="6" t="inlineStr">
+        <is>
+          <t>场景1:按日期+filters查询图表数据 — 97.8%
+场景2:空body调用</t>
+        </is>
+      </c>
+      <c r="G441" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：空body请求HTTP 200但响应体NullReferenceException("Data":null,"ErrorMessage":"Object reference not set to an instance of an object.")，ES真实生产流量中约2.0%的调用稳定命中此异常。</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="48" customHeight="1">
       <c r="A442" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15790,10 +15950,20 @@
         </is>
       </c>
       <c r="E442" s="3" t="n"/>
-      <c r="F442" s="3" t="n"/>
-      <c r="G442" s="3" t="n"/>
-    </row>
-    <row r="443">
+      <c r="F442" s="6" t="inlineStr">
+        <is>
+          <t>场景1:标准日期查询(无filters) — 90.4%
+场景2:带TotalCost filter查询 — 7.6%
+场景3:空body调用</t>
+        </is>
+      </c>
+      <c r="G442" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：同GetDSPAudienceGroupChart，空body请求NullReferenceException，ES真实流量约2.2%命中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="16" customHeight="1">
       <c r="A443" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15815,10 +15985,14 @@
         </is>
       </c>
       <c r="E443" s="3" t="n"/>
-      <c r="F443" s="3" t="n"/>
+      <c r="F443" s="6" t="inlineStr">
+        <is>
+          <t>按orderIds批量查询lineItem — 100%</t>
+        </is>
+      </c>
       <c r="G443" s="3" t="n"/>
     </row>
-    <row r="444">
+    <row r="444" ht="16" customHeight="1">
       <c r="A444" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15840,10 +16014,14 @@
         </is>
       </c>
       <c r="E444" s="3" t="n"/>
-      <c r="F444" s="3" t="n"/>
+      <c r="F444" s="6" t="inlineStr">
+        <is>
+          <t>按audienceGroupId查询关联lineItem — 100%</t>
+        </is>
+      </c>
       <c r="G444" s="3" t="n"/>
     </row>
-    <row r="445">
+    <row r="445" ht="16" customHeight="1">
       <c r="A445" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15865,10 +16043,14 @@
         </is>
       </c>
       <c r="E445" s="3" t="n"/>
-      <c r="F445" s="3" t="n"/>
+      <c r="F445" s="6" t="inlineStr">
+        <is>
+          <t>按groupId查询segment定向详情 — 100%</t>
+        </is>
+      </c>
       <c r="G445" s="3" t="n"/>
     </row>
-    <row r="446">
+    <row r="446" ht="16" customHeight="1">
       <c r="A446" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15890,10 +16072,14 @@
         </is>
       </c>
       <c r="E446" s="3" t="n"/>
-      <c r="F446" s="3" t="n"/>
+      <c r="F446" s="6" t="inlineStr">
+        <is>
+          <t>刷新广告主audience数据(仅执行1次) — 100%</t>
+        </is>
+      </c>
       <c r="G446" s="3" t="n"/>
     </row>
-    <row r="447">
+    <row r="447" ht="16" customHeight="1">
       <c r="A447" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15915,7 +16101,11 @@
         </is>
       </c>
       <c r="E447" s="3" t="n"/>
-      <c r="F447" s="3" t="n"/>
+      <c r="F447" s="6" t="inlineStr">
+        <is>
+          <t>重命名黑名单(改名后还原) — 100%</t>
+        </is>
+      </c>
       <c r="G447" s="3" t="n"/>
     </row>
     <row r="448">
@@ -15943,7 +16133,7 @@
       <c r="F448" s="3" t="n"/>
       <c r="G448" s="3" t="n"/>
     </row>
-    <row r="449">
+    <row r="449" ht="16" customHeight="1">
       <c r="A449" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15965,7 +16155,11 @@
         </is>
       </c>
       <c r="E449" s="3" t="n"/>
-      <c r="F449" s="3" t="n"/>
+      <c r="F449" s="6" t="inlineStr">
+        <is>
+          <t>更新刚创建的audience group(仅执行1轮) — 100%</t>
+        </is>
+      </c>
       <c r="G449" s="3" t="n"/>
     </row>
     <row r="450">
@@ -15991,7 +16185,11 @@
       </c>
       <c r="E450" s="3" t="n"/>
       <c r="F450" s="3" t="n"/>
-      <c r="G450" s="3" t="n"/>
+      <c r="G450" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口，run-cases.py执行框架仅支持JSON body，无法转发原始文件流。</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -566,9 +566,19 @@
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
+      <c r="F3" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>100%(22/22执行,13条高危仅生成不执行不计入)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>60% (18/30)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3772,7 +3782,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="32" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -3794,10 +3804,15 @@
         </is>
       </c>
       <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>新建分组时校验名称是否可用(无testGroupId) — 88.2%
+编辑已有分组时校验名称(带testGroupId排除自身) — 11.8%</t>
+        </is>
+      </c>
       <c r="G32" s="3" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="112" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -3819,8 +3834,22 @@
         </is>
       </c>
       <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>正式创建Creative类型分组(testGoal=0) — 43.8%
+保存草稿Creative类型分组(testGoal=0) — 18.8%
+正式创建Creative类型分组(testGoal=2) — 12.5%
+正式创建Creative类型分组(testGoal=1) — 9.4%
+保存草稿Creative类型分组(testGoal=2) — 6.2%
+保存草稿Audience类型分组(testGoal=0) — 6.2%
+保存草稿Audience类型分组(testGoal=2) — 3.1%</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高危(7个场景)：真实调用中isDraft=false(正式创建)占比65.7%，可能直接产生生效分组；testType=Creative/Audience场景需要真实creativeId/audience定向ID(config仍为[NEEDS_REAL_VALUE])。是下游EndABTestGroup/UpdateABTestGroup/UpdateGroupInfo等写操作缺少安全testGroupId的根本原因。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3844,10 +3873,18 @@
         </is>
       </c>
       <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-    </row>
-    <row r="35">
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -3869,10 +3906,18 @@
         </is>
       </c>
       <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-    </row>
-    <row r="36">
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>提前结束AB测试分组 — 100%</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高危：ES唯一真实样本testGroupId=621是历史他人分组，非自建，执行会真实终止一个可能仍在跑的AB测试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -3894,7 +3939,11 @@
         </is>
       </c>
       <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>按testGroupId查询分组基础信息 — 100%</t>
+        </is>
+      </c>
       <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
@@ -3919,8 +3968,16 @@
         </is>
       </c>
       <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3944,10 +4001,18 @@
         </is>
       </c>
       <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39">
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -3969,10 +4034,14 @@
         </is>
       </c>
       <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>按testGroupId查询分组详情 — 100%</t>
+        </is>
+      </c>
       <c r="G39" s="3" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="48" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -3994,10 +4063,16 @@
         </is>
       </c>
       <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>正式分组列表查询(非草稿,无过滤) — 72.2%
+草稿分组列表查询 — 20.2%
+按名称搜索分组 — 7.0%</t>
+        </is>
+      </c>
       <c r="G40" s="3" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" ht="32" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4019,7 +4094,12 @@
         </is>
       </c>
       <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>查看测试计划列表(非图表) — 66.6%
+查看测试计划图表数据 — 33.4%</t>
+        </is>
+      </c>
       <c r="G41" s="3" t="n"/>
     </row>
     <row r="42">
@@ -4044,10 +4124,18 @@
         </is>
       </c>
       <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
-      <c r="G42" s="3" t="n"/>
-    </row>
-    <row r="43">
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4069,10 +4157,16 @@
         </is>
       </c>
       <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>获取基准目标标准值(goal=0) — 71.5%
+获取基准目标标准值(goal=2) — 16.9%
+获取基准目标标准值(goal=1) — 11.6%</t>
+        </is>
+      </c>
       <c r="G43" s="3" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="16" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4094,10 +4188,14 @@
         </is>
       </c>
       <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>查询分组告警设置 — 100%</t>
+        </is>
+      </c>
       <c r="G44" s="3" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="16" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4119,7 +4217,11 @@
         </is>
       </c>
       <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>查询分组预算排期 — 100%</t>
+        </is>
+      </c>
       <c r="G45" s="3" t="n"/>
     </row>
     <row r="46">
@@ -4144,10 +4246,18 @@
         </is>
       </c>
       <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
-    </row>
-    <row r="47">
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4169,10 +4279,16 @@
         </is>
       </c>
       <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>新建Creative类型分组前预览可选素材 — 76.9%
+查看已有Creative分组的素材(按testGroupId) — 16.7%
+新建Audience类型分组前预览可选素材 — 5.6%</t>
+        </is>
+      </c>
       <c r="G47" s="3" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="16" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4194,10 +4310,14 @@
         </is>
       </c>
       <c r="E48" s="3" t="n"/>
-      <c r="F48" s="3" t="n"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>查询分组分时段设置 — 100%</t>
+        </is>
+      </c>
       <c r="G48" s="3" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="16" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4219,10 +4339,14 @@
         </is>
       </c>
       <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>查询新手引导展示状态 — 100%</t>
+        </is>
+      </c>
       <c r="G49" s="3" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="48" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4244,7 +4368,13 @@
         </is>
       </c>
       <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>计算充分测试所需预算(testGoal=0) — 71.3%
+计算充分测试所需预算(testGoal=2) — 17.4%
+计算充分测试所需预算(testGoal=1) — 11.3%</t>
+        </is>
+      </c>
       <c r="G50" s="3" t="n"/>
     </row>
     <row r="51">
@@ -4269,8 +4399,16 @@
         </is>
       </c>
       <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n"/>
-      <c r="G51" s="3" t="n"/>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4294,8 +4432,16 @@
         </is>
       </c>
       <c r="E52" s="3" t="n"/>
-      <c r="F52" s="3" t="n"/>
-      <c r="G52" s="3" t="n"/>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4319,10 +4465,18 @@
         </is>
       </c>
       <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="n"/>
-      <c r="G53" s="3" t="n"/>
-    </row>
-    <row r="54">
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4344,8 +4498,16 @@
         </is>
       </c>
       <c r="E54" s="3" t="n"/>
-      <c r="F54" s="3" t="n"/>
-      <c r="G54" s="3" t="n"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>启动(激活)AB测试分组 — 100%</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高危：ES样本100%(14次)都是active=true，是tag内唯一"启动AB测试"的真实用法，调用会立即让DSP按分组分配真实广告流量。未发现active=false的暂停用法样本。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4369,10 +4531,18 @@
         </is>
       </c>
       <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n"/>
-      <c r="G55" s="3" t="n"/>
-    </row>
-    <row r="56">
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4394,8 +4564,16 @@
         </is>
       </c>
       <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="n"/>
-      <c r="G56" s="3" t="n"/>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>更新AB测试分组完整配置(Audience类型) — 100%</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-受限：样本含完整lineItem/targeting真实配置，指向他人历史testGroupId，无自建安全分组可用。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4419,10 +4597,18 @@
         </is>
       </c>
       <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n"/>
-      <c r="G57" s="3" t="n"/>
-    </row>
-    <row r="58">
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4444,8 +4630,16 @@
         </is>
       </c>
       <c r="E58" s="3" t="n"/>
-      <c r="F58" s="3" t="n"/>
-      <c r="G58" s="3" t="n"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>更新分组告警设置 — 100%</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-受限：样本含真实邮箱(他人数据)+他人历史testGroupId，无自建安全分组可用。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4469,10 +4663,18 @@
         </is>
       </c>
       <c r="E59" s="3" t="n"/>
-      <c r="F59" s="3" t="n"/>
-      <c r="G59" s="3" t="n"/>
-    </row>
-    <row r="60">
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -4494,8 +4696,17 @@
         </is>
       </c>
       <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="n"/>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>修改分组名称 — 50.0%
+修改分组基础出价 — 50.0%</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行(2个场景)：baseSupplyBid场景会修改分组真实出价；groupName场景指向的testGroupId=632是他人历史数据。</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4519,8 +4730,16 @@
         </is>
       </c>
       <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
-      <c r="G61" s="3" t="n"/>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1850,9 +1850,19 @@
       </c>
       <c r="D50" s="3" t="n"/>
       <c r="E50" s="3" t="n"/>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2" t="n"/>
+      <c r="F50" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>68% (21/31)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -36207,7 +36217,7 @@
       <c r="F1111" s="3" t="n"/>
       <c r="G1111" s="3" t="n"/>
     </row>
-    <row r="1112">
+    <row r="1112" ht="16" customHeight="1">
       <c r="A1112" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36229,7 +36239,11 @@
         </is>
       </c>
       <c r="E1112" s="3" t="n"/>
-      <c r="F1112" s="3" t="n"/>
+      <c r="F1112" s="6" t="inlineStr">
+        <is>
+          <t>批量改FlightEndTime后还原(可重复) — 100%</t>
+        </is>
+      </c>
       <c r="G1112" s="3" t="n"/>
     </row>
     <row r="1113">
@@ -36255,9 +36269,13 @@
       </c>
       <c r="E1113" s="3" t="n"/>
       <c r="F1113" s="3" t="n"/>
-      <c r="G1113" s="3" t="n"/>
-    </row>
-    <row r="1114">
+      <c r="G1113" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：仅插入不删除的数据写入型接口(51次/365天)，Order tag内无对应移除ASIN接口可配对回滚，按既定规则跳过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114" ht="64" customHeight="1">
       <c r="A1114" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36279,10 +36297,17 @@
         </is>
       </c>
       <c r="E1114" s="3" t="n"/>
-      <c r="F1114" s="3" t="n"/>
+      <c r="F1114" s="6" t="inlineStr">
+        <is>
+          <t>按OrderId数量=&gt;20批量导出TrackingAsin — 45.0%
+按OrderId数量=1批量导出TrackingAsin — 30.0%
+按OrderId数量=2-5批量导出TrackingAsin — 20.0%
+按OrderId数量=6-20批量导出TrackingAsin — 5.0%</t>
+        </is>
+      </c>
       <c r="G1114" s="3" t="n"/>
     </row>
-    <row r="1115">
+    <row r="1115" ht="16" customHeight="1">
       <c r="A1115" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36304,10 +36329,18 @@
         </is>
       </c>
       <c r="E1115" s="3" t="n"/>
-      <c r="F1115" s="3" t="n"/>
-      <c r="G1115" s="3" t="n"/>
-    </row>
-    <row r="1116">
+      <c r="F1115" s="6" t="inlineStr">
+        <is>
+          <t>设置自定义服务费(真实流量body结构,复现后端bug) — 100%</t>
+        </is>
+      </c>
+      <c r="G1115" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：ES真实流量100%(10/10样本)使用的请求体结构{orderId,advertiserId,fees:[...]}调用后端稳定返回IsSuccessStatusCode:false，错误"Value cannot be null. (Parameter 'source')"；仅Swagger声明的另一种结构(date/yearMonth/fee+orders数组)才能成功。真实用户对该批量接口的实际调用方式很可能100%失败，建议P1登记。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116" ht="16" customHeight="1">
       <c r="A1116" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36329,10 +36362,18 @@
         </is>
       </c>
       <c r="E1116" s="3" t="n"/>
-      <c r="F1116" s="3" t="n"/>
-      <c r="G1116" s="3" t="n"/>
-    </row>
-    <row r="1117">
+      <c r="F1116" s="6" t="inlineStr">
+        <is>
+          <t>批量打标签后移除(可重复) — 100%</t>
+        </is>
+      </c>
+      <c r="G1116" s="5" t="inlineStr">
+        <is>
+          <t>业务规则发现：拒绝把Order打到"带子标签的父标签"上(报错Cannot add campaign to tag with sub-tag)，已知order_tag_id(1919941112031195138)即为父标签，改用order_tag_id_2(叶子标签)后正常，非bug。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117" ht="16" customHeight="1">
       <c r="A1117" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36354,10 +36395,18 @@
         </is>
       </c>
       <c r="E1117" s="3" t="n"/>
-      <c r="F1117" s="3" t="n"/>
-      <c r="G1117" s="3" t="n"/>
-    </row>
-    <row r="1118">
+      <c r="F1117" s="6" t="inlineStr">
+        <is>
+          <t>切换DeliveryActivationStatus(复用CreateOrder创建的一次性测试Order) — 100%</t>
+        </is>
+      </c>
+      <c r="G1117" s="5" t="inlineStr">
+        <is>
+          <t>风险发现：原预设的已知安全Order(576582423523984235)已结束超180天，Amazon业务规则拒绝对其做此类更新(This Campaign has ended/cannot be restarted after 180 days)。已改为case内新建一次性测试Order(小额预算+1天flight窗口)执行并归档，非bug。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118" ht="16" customHeight="1">
       <c r="A1118" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36379,8 +36428,16 @@
         </is>
       </c>
       <c r="E1118" s="3" t="n"/>
-      <c r="F1118" s="3" t="n"/>
-      <c r="G1118" s="3" t="n"/>
+      <c r="F1118" s="6" t="inlineStr">
+        <is>
+          <t>按百分比调整预算(复用CreateOrder创建的一次性测试Order) — 100%</t>
+        </is>
+      </c>
+      <c r="G1118" s="5" t="inlineStr">
+        <is>
+          <t>风险发现：原预设的已知安全Order(576582423523984235)已结束超180天，Amazon业务规则拒绝对其做此类更新(This Campaign has ended/cannot be restarted after 180 days)。已改为case内新建一次性测试Order(小额预算+1天flight窗口)执行并归档，非bug。</t>
+        </is>
+      </c>
     </row>
     <row r="1119">
       <c r="A1119" s="2" t="inlineStr">
@@ -36404,10 +36461,18 @@
         </is>
       </c>
       <c r="E1119" s="3" t="n"/>
-      <c r="F1119" s="3" t="n"/>
-      <c r="G1119" s="3" t="n"/>
-    </row>
-    <row r="1120">
+      <c r="F1119" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1119" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120" ht="16" customHeight="1">
       <c r="A1120" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36429,7 +36494,11 @@
         </is>
       </c>
       <c r="E1120" s="3" t="n"/>
-      <c r="F1120" s="3" t="n"/>
+      <c r="F1120" s="6" t="inlineStr">
+        <is>
+          <t>创建Order(含后置归档,可重复) — 100%</t>
+        </is>
+      </c>
       <c r="G1120" s="3" t="n"/>
     </row>
     <row r="1121">
@@ -36454,10 +36523,18 @@
         </is>
       </c>
       <c r="E1121" s="3" t="n"/>
-      <c r="F1121" s="3" t="n"/>
-      <c r="G1121" s="3" t="n"/>
-    </row>
-    <row r="1122">
+      <c r="F1121" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1121" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122" ht="16" customHeight="1">
       <c r="A1122" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36479,10 +36556,14 @@
         </is>
       </c>
       <c r="E1122" s="3" t="n"/>
-      <c r="F1122" s="3" t="n"/>
+      <c r="F1122" s="6" t="inlineStr">
+        <is>
+          <t>下载ConversionTracking样例模板(空body) — 100.0%</t>
+        </is>
+      </c>
       <c r="G1122" s="3" t="n"/>
     </row>
-    <row r="1123">
+    <row r="1123" ht="176" customHeight="1">
       <c r="A1123" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36504,10 +36585,24 @@
         </is>
       </c>
       <c r="E1123" s="3" t="n"/>
-      <c r="F1123" s="3" t="n"/>
+      <c r="F1123" s="6" t="inlineStr">
+        <is>
+          <t>symbol=$+timeZone=America/New York — 38.4%
+symbol=$(不传timeZone) — 30.4%
+symbol=$+timeZone=America/Los Angeles — 7.2%
+symbol=￥+timeZone=Asia/Tokyo — 6.6%
+symbol=€(不传timeZone) — 3.2%
+symbol=￥(不传timeZone) — 2.6%
+symbol=Mex$+timeZone=America/New York — 2.6%
+symbol=CDN$+timeZone=America/New York — 2.4%
+symbol=$+timeZone=America/Chicago — 2.0%
+symbol=CDN$(不传timeZone) — 1.6%
+symbol=£+timeZone=Europe/London — 1.2%</t>
+        </is>
+      </c>
       <c r="G1123" s="3" t="n"/>
     </row>
-    <row r="1124">
+    <row r="1124" ht="80" customHeight="1">
       <c r="A1124" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36529,7 +36624,15 @@
         </is>
       </c>
       <c r="E1124" s="3" t="n"/>
-      <c r="F1124" s="3" t="n"/>
+      <c r="F1124" s="6" t="inlineStr">
+        <is>
+          <t>domain=AMAZON US+withVariations=True+isFeatured=True — 63.8%
+domain=AMAZON US+withVariations=False+isFeatured=False — 16.0%
+domain=AMAZON US+withVariations=False+isFeatured=True — 13.6%
+domain=AMAZON JP+withVariations=True+isFeatured=True — 1.4%
+domain=AMAZON JP+withVariations=False+isFeatured=False — 1.2%</t>
+        </is>
+      </c>
       <c r="G1124" s="3" t="n"/>
     </row>
     <row r="1125">
@@ -36554,10 +36657,18 @@
         </is>
       </c>
       <c r="E1125" s="3" t="n"/>
-      <c r="F1125" s="3" t="n"/>
-      <c r="G1125" s="3" t="n"/>
-    </row>
-    <row r="1126">
+      <c r="F1125" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1125" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126" ht="32" customHeight="1">
       <c r="A1126" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36579,10 +36690,15 @@
         </is>
       </c>
       <c r="E1126" s="3" t="n"/>
-      <c r="F1126" s="3" t="n"/>
+      <c r="F1126" s="6" t="inlineStr">
+        <is>
+          <t>同步ASIN(isSyncAsin=false,前端默认关闭同步) — 73.8%
+不传isSyncAsin(采用后端默认值true) — 26.2%</t>
+        </is>
+      </c>
       <c r="G1126" s="3" t="n"/>
     </row>
-    <row r="1127">
+    <row r="1127" ht="16" customHeight="1">
       <c r="A1127" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36604,7 +36720,11 @@
         </is>
       </c>
       <c r="E1127" s="3" t="n"/>
-      <c r="F1127" s="3" t="n"/>
+      <c r="F1127" s="6" t="inlineStr">
+        <is>
+          <t>按OrderId查询预算(单个) — 100.0%</t>
+        </is>
+      </c>
       <c r="G1127" s="3" t="n"/>
     </row>
     <row r="1128">
@@ -36629,8 +36749,16 @@
         </is>
       </c>
       <c r="E1128" s="3" t="n"/>
-      <c r="F1128" s="3" t="n"/>
-      <c r="G1128" s="3" t="n"/>
+      <c r="F1128" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1128" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1129">
       <c r="A1129" s="2" t="inlineStr">
@@ -36654,8 +36782,16 @@
         </is>
       </c>
       <c r="E1129" s="3" t="n"/>
-      <c r="F1129" s="3" t="n"/>
-      <c r="G1129" s="3" t="n"/>
+      <c r="F1129" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1129" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1130">
       <c r="A1130" s="2" t="inlineStr">
@@ -36679,10 +36815,18 @@
         </is>
       </c>
       <c r="E1130" s="3" t="n"/>
-      <c r="F1130" s="3" t="n"/>
-      <c r="G1130" s="3" t="n"/>
-    </row>
-    <row r="1131">
+      <c r="F1130" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1130" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131" ht="16" customHeight="1">
       <c r="A1131" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36704,10 +36848,14 @@
         </is>
       </c>
       <c r="E1131" s="3" t="n"/>
-      <c r="F1131" s="3" t="n"/>
+      <c r="F1131" s="6" t="inlineStr">
+        <is>
+          <t>按profileId+advertiserId+orderId查询TrackingAsin — 100.0%</t>
+        </is>
+      </c>
       <c r="G1131" s="3" t="n"/>
     </row>
-    <row r="1132">
+    <row r="1132" ht="128" customHeight="1">
       <c r="A1132" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36729,10 +36877,21 @@
         </is>
       </c>
       <c r="E1132" s="3" t="n"/>
-      <c r="F1132" s="3" t="n"/>
+      <c r="F1132" s="6" t="inlineStr">
+        <is>
+          <t>商品数=&gt;20+关联类型=FEATURED/NOT FEATURED — 40.0%
+商品数=6-20+关联类型=FEATURED/NOT FEATURED — 19.2%
+商品数=1+关联类型=FEATURED — 16.5%
+商品数=6-20+关联类型=FEATURED — 9.2%
+商品数=&gt;20+关联类型=NOT FEATURED — 3.8%
+商品数=&gt;20+关联类型=FEATURED — 3.8%
+商品数=2-5+关联类型=FEATURED — 3.5%
+商品数=2-5+关联类型=FEATURED/NOT FEATURED — 3.5%</t>
+        </is>
+      </c>
       <c r="G1132" s="3" t="n"/>
     </row>
-    <row r="1133">
+    <row r="1133" ht="16" customHeight="1">
       <c r="A1133" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36754,10 +36913,14 @@
         </is>
       </c>
       <c r="E1133" s="3" t="n"/>
-      <c r="F1133" s="3" t="n"/>
+      <c r="F1133" s="6" t="inlineStr">
+        <is>
+          <t>按advertiserId+orderId查询自定义服务费 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1133" s="3" t="n"/>
     </row>
-    <row r="1134">
+    <row r="1134" ht="48" customHeight="1">
       <c r="A1134" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36779,10 +36942,16 @@
         </is>
       </c>
       <c r="E1134" s="3" t="n"/>
-      <c r="F1134" s="3" t="n"/>
+      <c r="F1134" s="6" t="inlineStr">
+        <is>
+          <t>按OrderId数量=1批量查询Tags — 56.8%
+按OrderId数量=2-5批量查询Tags — 25.8%
+按OrderId数量=&gt;5批量查询Tags — 17.4%</t>
+        </is>
+      </c>
       <c r="G1134" s="3" t="n"/>
     </row>
-    <row r="1135">
+    <row r="1135" ht="16" customHeight="1">
       <c r="A1135" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36804,7 +36973,11 @@
         </is>
       </c>
       <c r="E1135" s="3" t="n"/>
-      <c r="F1135" s="3" t="n"/>
+      <c r="F1135" s="6" t="inlineStr">
+        <is>
+          <t>设置自定义服务费后清零(可重复) — 100%</t>
+        </is>
+      </c>
       <c r="G1135" s="3" t="n"/>
     </row>
     <row r="1136">
@@ -36830,7 +37003,11 @@
       </c>
       <c r="E1136" s="3" t="n"/>
       <c r="F1136" s="3" t="n"/>
-      <c r="G1136" s="3" t="n"/>
+      <c r="G1136" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口(114次/365天真实流量)，run-cases.py执行框架仅支持JSON body，无法转发原始文件流。</t>
+        </is>
+      </c>
     </row>
     <row r="1137">
       <c r="A1137" s="2" t="inlineStr">
@@ -36854,10 +37031,18 @@
         </is>
       </c>
       <c r="E1137" s="3" t="n"/>
-      <c r="F1137" s="3" t="n"/>
-      <c r="G1137" s="3" t="n"/>
-    </row>
-    <row r="1138">
+      <c r="F1137" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1137" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138" ht="16" customHeight="1">
       <c r="A1138" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36879,8 +37064,16 @@
         </is>
       </c>
       <c r="E1138" s="3" t="n"/>
-      <c r="F1138" s="3" t="n"/>
-      <c r="G1138" s="3" t="n"/>
+      <c r="F1138" s="6" t="inlineStr">
+        <is>
+          <t>开启每周预算计划(复用CreateOrder创建的一次性测试Order) — 100%</t>
+        </is>
+      </c>
+      <c r="G1138" s="5" t="inlineStr">
+        <is>
+          <t>风险发现：原预设的已知安全Order(576582423523984235)已结束超180天，Amazon业务规则拒绝对其做此类更新(This Campaign has ended/cannot be restarted after 180 days)。已改为case内新建一次性测试Order(小额预算+1天flight窗口)执行并归档，非bug。</t>
+        </is>
+      </c>
     </row>
     <row r="1139">
       <c r="A1139" s="2" t="inlineStr">
@@ -36904,10 +37097,18 @@
         </is>
       </c>
       <c r="E1139" s="3" t="n"/>
-      <c r="F1139" s="3" t="n"/>
-      <c r="G1139" s="3" t="n"/>
-    </row>
-    <row r="1140">
+      <c r="F1139" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1139" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140" ht="16" customHeight="1">
       <c r="A1140" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36929,10 +37130,18 @@
         </is>
       </c>
       <c r="E1140" s="3" t="n"/>
-      <c r="F1140" s="3" t="n"/>
-      <c r="G1140" s="3" t="n"/>
-    </row>
-    <row r="1141">
+      <c r="F1140" s="6" t="inlineStr">
+        <is>
+          <t>改comments(复用CreateOrder创建的一次性测试Order) — 100%</t>
+        </is>
+      </c>
+      <c r="G1140" s="5" t="inlineStr">
+        <is>
+          <t>风险发现：原预设的已知安全Order(576582423523984235)已结束超180天，Amazon业务规则拒绝对其做此类更新(This Campaign has ended/cannot be restarted after 180 days)。已改为case内新建一次性测试Order(小额预算+1天flight窗口)执行并归档，非bug。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141" ht="16" customHeight="1">
       <c r="A1141" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36954,10 +37163,18 @@
         </is>
       </c>
       <c r="E1141" s="3" t="n"/>
-      <c r="F1141" s="3" t="n"/>
-      <c r="G1141" s="3" t="n"/>
-    </row>
-    <row r="1142">
+      <c r="F1141" s="6" t="inlineStr">
+        <is>
+          <t>改Flight结束时间(复用CreateOrder创建的一次性测试Order) — 100%</t>
+        </is>
+      </c>
+      <c r="G1141" s="5" t="inlineStr">
+        <is>
+          <t>风险发现：原预设的已知安全Order(576582423523984235)已结束超180天，Amazon业务规则拒绝对其做此类更新(This Campaign has ended/cannot be restarted after 180 days)。已改为case内新建一次性测试Order(小额预算+1天flight窗口)执行并归档，非bug。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142" ht="16" customHeight="1">
       <c r="A1142" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36979,8 +37196,16 @@
         </is>
       </c>
       <c r="E1142" s="3" t="n"/>
-      <c r="F1142" s="3" t="n"/>
-      <c r="G1142" s="3" t="n"/>
+      <c r="F1142" s="6" t="inlineStr">
+        <is>
+          <t>改名(复用CreateOrder创建的一次性测试Order) — 100%</t>
+        </is>
+      </c>
+      <c r="G1142" s="5" t="inlineStr">
+        <is>
+          <t>风险发现：原预设的已知安全Order(576582423523984235)已结束超180天，Amazon业务规则拒绝对其做此类更新(This Campaign has ended/cannot be restarted after 180 days)。已改为case内新建一次性测试Order(小额预算+1天flight窗口)执行并归档，非bug。</t>
+        </is>
+      </c>
     </row>
     <row r="1143">
       <c r="A1143" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1828,9 +1828,19 @@
       </c>
       <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="n"/>
-      <c r="F49" s="2" t="n"/>
-      <c r="G49" s="2" t="n"/>
-      <c r="H49" s="2" t="n"/>
+      <c r="F49" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>77% (20/26)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -35567,7 +35577,7 @@
         </is>
       </c>
     </row>
-    <row r="1086">
+    <row r="1086" ht="16" customHeight="1">
       <c r="A1086" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35589,10 +35599,18 @@
         </is>
       </c>
       <c r="E1086" s="3" t="n"/>
-      <c r="F1086" s="3" t="n"/>
-      <c r="G1086" s="3" t="n"/>
-    </row>
-    <row r="1087">
+      <c r="F1086" s="6" t="inlineStr">
+        <is>
+          <t>校验AWSAmazonS3连接凭据 — 100.0%</t>
+        </is>
+      </c>
+      <c r="G1086" s="5" t="inlineStr">
+        <is>
+          <t>FAIL但非代码缺陷：ES真实历史凭据(AWS/FTP/Azure)现已失效/被轮换，后端正确返回IsSuccess:false，请求处理本身正确。case里的凭据字段已脱敏为占位符，如需验证正向路径需用户提供当前有效的测试凭据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087" ht="16" customHeight="1">
       <c r="A1087" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35614,10 +35632,18 @@
         </is>
       </c>
       <c r="E1087" s="3" t="n"/>
-      <c r="F1087" s="3" t="n"/>
-      <c r="G1087" s="3" t="n"/>
-    </row>
-    <row r="1088">
+      <c r="F1087" s="6" t="inlineStr">
+        <is>
+          <t>校验Ftp连接凭据 — 100.0%</t>
+        </is>
+      </c>
+      <c r="G1087" s="5" t="inlineStr">
+        <is>
+          <t>FAIL但非代码缺陷：ES真实历史凭据(AWS/FTP/Azure)现已失效/被轮换，后端正确返回IsSuccess:false，请求处理本身正确。case里的凭据字段已脱敏为占位符，如需验证正向路径需用户提供当前有效的测试凭据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088" ht="16" customHeight="1">
       <c r="A1088" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35639,10 +35665,14 @@
         </is>
       </c>
       <c r="E1088" s="3" t="n"/>
-      <c r="F1088" s="3" t="n"/>
+      <c r="F1088" s="6" t="inlineStr">
+        <is>
+          <t>校验GoogleCloudStorage连接凭据 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1088" s="3" t="n"/>
     </row>
-    <row r="1089">
+    <row r="1089" ht="16" customHeight="1">
       <c r="A1089" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35664,10 +35694,14 @@
         </is>
       </c>
       <c r="E1089" s="3" t="n"/>
-      <c r="F1089" s="3" t="n"/>
+      <c r="F1089" s="6" t="inlineStr">
+        <is>
+          <t>校验GoogleSheetKey连接凭据 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1089" s="3" t="n"/>
     </row>
-    <row r="1090">
+    <row r="1090" ht="32" customHeight="1">
       <c r="A1090" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35689,10 +35723,19 @@
         </is>
       </c>
       <c r="E1090" s="3" t="n"/>
-      <c r="F1090" s="3" t="n"/>
-      <c r="G1090" s="3" t="n"/>
-    </row>
-    <row r="1091">
+      <c r="F1090" s="6" t="inlineStr">
+        <is>
+          <t>camelCase字段 — 76.9%
+PascalCase字段(旧版兼容) — 23.1%</t>
+        </is>
+      </c>
+      <c r="G1090" s="5" t="inlineStr">
+        <is>
+          <t>FAIL但非代码缺陷：ES真实历史凭据(AWS/FTP/Azure)现已失效/被轮换，后端正确返回IsSuccess:false，请求处理本身正确。case里的凭据字段已脱敏为占位符，如需验证正向路径需用户提供当前有效的测试凭据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091" ht="160" customHeight="1">
       <c r="A1091" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35714,10 +35757,23 @@
         </is>
       </c>
       <c r="E1091" s="3" t="n"/>
-      <c r="F1091" s="3" t="n"/>
+      <c r="F1091" s="6" t="inlineStr">
+        <is>
+          <t>reportType=1(Campaign)+breakdowns=[0, 1, 2, 3] — 50.8%
+reportType=1(Campaign)+breakdowns=[0, 1] — 12.8%
+reportType=4(Product)+breakdowns=[0, 1, 2] — 8.2%
+reportType=3(Audience)+breakdowns=[0, 1, 2] — 7.8%
+reportType=1(Campaign)+breakdowns=[0, 1, 2] — 7.2%
+reportType=2(Inventory)+breakdowns=[0, 1, 2, 4, 5, 6] — 2.8%
+reportType=1(Campaign)+breakdowns=[0] — 2.0%
+reportType=2(Inventory)+breakdowns=[0, 1, 2, 4, 5] — 2.0%
+reportType=21(CreativeTag)+breakdowns=[17] — 2.0%
+reportType=4(Product)+breakdowns=[0, 1] — 1.4%</t>
+        </is>
+      </c>
       <c r="G1091" s="3" t="n"/>
     </row>
-    <row r="1092">
+    <row r="1092" ht="80" customHeight="1">
       <c r="A1092" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35739,7 +35795,15 @@
         </is>
       </c>
       <c r="E1092" s="3" t="n"/>
-      <c r="F1092" s="3" t="n"/>
+      <c r="F1092" s="6" t="inlineStr">
+        <is>
+          <t>reportType=1(Campaign)创建后清理 — 52.0%
+reportType=3(Audience)创建后清理 — 16.2%
+reportType=2(Inventory)创建后清理 — 15.2%
+reportType=4(Product)创建后清理 — 14.0%
+reportType=21(CreativeTag)创建后清理 — 2.6%</t>
+        </is>
+      </c>
       <c r="G1092" s="3" t="n"/>
     </row>
     <row r="1093">
@@ -35767,7 +35831,7 @@
       <c r="F1093" s="3" t="n"/>
       <c r="G1093" s="3" t="n"/>
     </row>
-    <row r="1094">
+    <row r="1094" ht="80" customHeight="1">
       <c r="A1094" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35789,7 +35853,15 @@
         </is>
       </c>
       <c r="E1094" s="3" t="n"/>
-      <c r="F1094" s="3" t="n"/>
+      <c r="F1094" s="6" t="inlineStr">
+        <is>
+          <t>reportType=1(Campaign)即时预览 — 35.1%
+reportType=2(Inventory)即时预览 — 20.8%
+reportType=4(Product)即时预览 — 20.6%
+reportType=3(Audience)即时预览 — 18.2%
+reportType=21(CreativeTag)即时预览 — 5.2%</t>
+        </is>
+      </c>
       <c r="G1094" s="3" t="n"/>
     </row>
     <row r="1095">
@@ -35814,8 +35886,16 @@
         </is>
       </c>
       <c r="E1095" s="3" t="n"/>
-      <c r="F1095" s="3" t="n"/>
-      <c r="G1095" s="3" t="n"/>
+      <c r="F1095" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1095" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1096">
       <c r="A1096" s="2" t="inlineStr">
@@ -35839,8 +35919,16 @@
         </is>
       </c>
       <c r="E1096" s="3" t="n"/>
-      <c r="F1096" s="3" t="n"/>
-      <c r="G1096" s="3" t="n"/>
+      <c r="F1096" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1096" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1097">
       <c r="A1097" s="2" t="inlineStr">
@@ -35864,8 +35952,16 @@
         </is>
       </c>
       <c r="E1097" s="3" t="n"/>
-      <c r="F1097" s="3" t="n"/>
-      <c r="G1097" s="3" t="n"/>
+      <c r="F1097" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1097" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1098">
       <c r="A1098" s="2" t="inlineStr">
@@ -35889,10 +35985,18 @@
         </is>
       </c>
       <c r="E1098" s="3" t="n"/>
-      <c r="F1098" s="3" t="n"/>
-      <c r="G1098" s="3" t="n"/>
-    </row>
-    <row r="1099">
+      <c r="F1098" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1098" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099" ht="16" customHeight="1">
       <c r="A1099" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35914,10 +36018,18 @@
         </is>
       </c>
       <c r="E1099" s="3" t="n"/>
-      <c r="F1099" s="3" t="n"/>
-      <c r="G1099" s="3" t="n"/>
-    </row>
-    <row r="1100">
+      <c r="F1099" s="6" t="inlineStr">
+        <is>
+          <t>按id查询报表定义详情</t>
+        </is>
+      </c>
+      <c r="G1099" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：按已删除/不存在的id查询会抛NullReferenceException，HTTP 200但Error.message泄露内部堆栈，未做"未找到"的友好处理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100" ht="16" customHeight="1">
       <c r="A1100" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35939,10 +36051,14 @@
         </is>
       </c>
       <c r="E1100" s="3" t="n"/>
-      <c r="F1100" s="3" t="n"/>
+      <c r="F1100" s="6" t="inlineStr">
+        <is>
+          <t>报表定义列表查询 — 100.0%</t>
+        </is>
+      </c>
       <c r="G1100" s="3" t="n"/>
     </row>
-    <row r="1101">
+    <row r="1101" ht="16" customHeight="1">
       <c r="A1101" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35964,10 +36080,14 @@
         </is>
       </c>
       <c r="E1101" s="3" t="n"/>
-      <c r="F1101" s="3" t="n"/>
+      <c r="F1101" s="6" t="inlineStr">
+        <is>
+          <t>查询报表执行历史 — 100%</t>
+        </is>
+      </c>
       <c r="G1101" s="3" t="n"/>
     </row>
-    <row r="1102">
+    <row r="1102" ht="16" customHeight="1">
       <c r="A1102" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35989,10 +36109,14 @@
         </is>
       </c>
       <c r="E1102" s="3" t="n"/>
-      <c r="F1102" s="3" t="n"/>
+      <c r="F1102" s="6" t="inlineStr">
+        <is>
+          <t>重发历史执行结果邮件 — 100%</t>
+        </is>
+      </c>
       <c r="G1102" s="3" t="n"/>
     </row>
-    <row r="1103">
+    <row r="1103" ht="16" customHeight="1">
       <c r="A1103" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36014,10 +36138,14 @@
         </is>
       </c>
       <c r="E1103" s="3" t="n"/>
-      <c r="F1103" s="3" t="n"/>
+      <c r="F1103" s="6" t="inlineStr">
+        <is>
+          <t>预览某次历史执行结果 — 100%</t>
+        </is>
+      </c>
       <c r="G1103" s="3" t="n"/>
     </row>
-    <row r="1104">
+    <row r="1104" ht="16" customHeight="1">
       <c r="A1104" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36039,10 +36167,14 @@
         </is>
       </c>
       <c r="E1104" s="3" t="n"/>
-      <c r="F1104" s="3" t="n"/>
+      <c r="F1104" s="6" t="inlineStr">
+        <is>
+          <t>刷新并重发历史执行结果 — 100%</t>
+        </is>
+      </c>
       <c r="G1104" s="3" t="n"/>
     </row>
-    <row r="1105">
+    <row r="1105" ht="16" customHeight="1">
       <c r="A1105" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36064,10 +36196,14 @@
         </is>
       </c>
       <c r="E1105" s="3" t="n"/>
-      <c r="F1105" s="3" t="n"/>
+      <c r="F1105" s="6" t="inlineStr">
+        <is>
+          <t>按已存报表定义预览数据</t>
+        </is>
+      </c>
       <c r="G1105" s="3" t="n"/>
     </row>
-    <row r="1106">
+    <row r="1106" ht="16" customHeight="1">
       <c r="A1106" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36089,7 +36225,11 @@
         </is>
       </c>
       <c r="E1106" s="3" t="n"/>
-      <c r="F1106" s="3" t="n"/>
+      <c r="F1106" s="6" t="inlineStr">
+        <is>
+          <t>手动触发报表生成</t>
+        </is>
+      </c>
       <c r="G1106" s="3" t="n"/>
     </row>
     <row r="1107">
@@ -36114,8 +36254,16 @@
         </is>
       </c>
       <c r="E1107" s="3" t="n"/>
-      <c r="F1107" s="3" t="n"/>
-      <c r="G1107" s="3" t="n"/>
+      <c r="F1107" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1107" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1108">
       <c r="A1108" s="2" t="inlineStr">
@@ -36139,10 +36287,18 @@
         </is>
       </c>
       <c r="E1108" s="3" t="n"/>
-      <c r="F1108" s="3" t="n"/>
-      <c r="G1108" s="3" t="n"/>
-    </row>
-    <row r="1109">
+      <c r="F1108" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1108" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109" ht="80" customHeight="1">
       <c r="A1109" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36164,10 +36320,18 @@
         </is>
       </c>
       <c r="E1109" s="3" t="n"/>
-      <c r="F1109" s="3" t="n"/>
+      <c r="F1109" s="6" t="inlineStr">
+        <is>
+          <t>reportType=1(Campaign)编辑后清理 — 69.0%
+reportType=4(Product)编辑后清理 — 11.4%
+reportType=3(Audience)编辑后清理 — 10.6%
+reportType=2(Inventory)编辑后清理 — 5.8%
+reportType=21(CreativeTag)编辑后清理 — 3.2%</t>
+        </is>
+      </c>
       <c r="G1109" s="3" t="n"/>
     </row>
-    <row r="1110">
+    <row r="1110" ht="16" customHeight="1">
       <c r="A1110" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36189,10 +36353,14 @@
         </is>
       </c>
       <c r="E1110" s="3" t="n"/>
-      <c r="F1110" s="3" t="n"/>
+      <c r="F1110" s="6" t="inlineStr">
+        <is>
+          <t>暂停后恢复报表定义调度 — 100%</t>
+        </is>
+      </c>
       <c r="G1110" s="3" t="n"/>
     </row>
-    <row r="1111">
+    <row r="1111" ht="32" customHeight="1">
       <c r="A1111" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36214,7 +36382,12 @@
         </is>
       </c>
       <c r="E1111" s="3" t="n"/>
-      <c r="F1111" s="3" t="n"/>
+      <c r="F1111" s="6" t="inlineStr">
+        <is>
+          <t>PRODUCT REPORT — 90.6%
+CAMPAIGN REPORT — 9.4%</t>
+        </is>
+      </c>
       <c r="G1111" s="3" t="n"/>
     </row>
     <row r="1112" ht="16" customHeight="1">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1752,9 +1752,19 @@
       </c>
       <c r="D46" s="3" t="n"/>
       <c r="E46" s="3" t="n"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
+      <c r="F46" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>92% (23/25)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -34678,7 +34688,7 @@
       </c>
       <c r="G1050" s="3" t="n"/>
     </row>
-    <row r="1051">
+    <row r="1051" ht="16" customHeight="1">
       <c r="A1051" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34700,7 +34710,11 @@
         </is>
       </c>
       <c r="E1051" s="3" t="n"/>
-      <c r="F1051" s="3" t="n"/>
+      <c r="F1051" s="6" t="inlineStr">
+        <is>
+          <t>批量新增库存源定向 — 100%</t>
+        </is>
+      </c>
       <c r="G1051" s="3" t="n"/>
     </row>
     <row r="1052">
@@ -34725,10 +34739,18 @@
         </is>
       </c>
       <c r="E1052" s="3" t="n"/>
-      <c r="F1052" s="3" t="n"/>
-      <c r="G1052" s="3" t="n"/>
-    </row>
-    <row r="1053">
+      <c r="F1052" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1052" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053" ht="16" customHeight="1">
       <c r="A1053" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34750,10 +34772,14 @@
         </is>
       </c>
       <c r="E1053" s="3" t="n"/>
-      <c r="F1053" s="3" t="n"/>
+      <c r="F1053" s="6" t="inlineStr">
+        <is>
+          <t>批量修改设备定向(读原值-&gt;改-&gt;还原) — 100%</t>
+        </is>
+      </c>
       <c r="G1053" s="3" t="n"/>
     </row>
-    <row r="1054">
+    <row r="1054" ht="16" customHeight="1">
       <c r="A1054" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34775,10 +34801,18 @@
         </is>
       </c>
       <c r="E1054" s="3" t="n"/>
-      <c r="F1054" s="3" t="n"/>
-      <c r="G1054" s="3" t="n"/>
-    </row>
-    <row r="1055">
+      <c r="F1054" s="6" t="inlineStr">
+        <is>
+          <t>批量修改库存源定向(读原值-&gt;改-&gt;还原) — 50%</t>
+        </is>
+      </c>
+      <c r="G1054" s="5" t="inlineStr">
+        <is>
+          <t>观察项：operationType枚举真实样本有0/1/2三种取值(占比16.7%/33.3%/50%)，仅验证了最高频的2，0和1的真实业务含义未做行为验证，按规则未凭字段名猜测，留作后续风险点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055" ht="16" customHeight="1">
       <c r="A1055" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34800,10 +34834,14 @@
         </is>
       </c>
       <c r="E1055" s="3" t="n"/>
-      <c r="F1055" s="3" t="n"/>
+      <c r="F1055" s="6" t="inlineStr">
+        <is>
+          <t>批量修改地域定向(加一条真实地域-&gt;清空还原) — 100%</t>
+        </is>
+      </c>
       <c r="G1055" s="3" t="n"/>
     </row>
-    <row r="1056">
+    <row r="1056" ht="16" customHeight="1">
       <c r="A1056" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34825,10 +34863,18 @@
         </is>
       </c>
       <c r="E1056" s="3" t="n"/>
-      <c r="F1056" s="3" t="n"/>
-      <c r="G1056" s="3" t="n"/>
-    </row>
-    <row r="1057">
+      <c r="F1056" s="6" t="inlineStr">
+        <is>
+          <t>批量保存分时段出价策略 — 100%</t>
+        </is>
+      </c>
+      <c r="G1056" s="5" t="inlineStr">
+        <is>
+          <t>观察项：读(response)写(request)字段命名/结构存在差异，未做到"读原值-改-精确回填"式完全还原，采用固定真实值重复提交的简化策略，测试后业务内容不一定100%等于测试前原状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057" ht="16" customHeight="1">
       <c r="A1057" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34850,10 +34896,18 @@
         </is>
       </c>
       <c r="E1057" s="3" t="n"/>
-      <c r="F1057" s="3" t="n"/>
-      <c r="G1057" s="3" t="n"/>
-    </row>
-    <row r="1058">
+      <c r="F1057" s="6" t="inlineStr">
+        <is>
+          <t>批量排除库存域名/App(加一条真实排除-&gt;清空还原) — 100%</t>
+        </is>
+      </c>
+      <c r="G1057" s="5" t="inlineStr">
+        <is>
+          <t>观察项：读(response)写(request)字段命名/结构存在差异，未做到"读原值-改-精确回填"式完全还原，采用固定真实值重复提交的简化策略，测试后业务内容不一定100%等于测试前原状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058" ht="16" customHeight="1">
       <c r="A1058" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34875,10 +34929,14 @@
         </is>
       </c>
       <c r="E1058" s="3" t="n"/>
-      <c r="F1058" s="3" t="n"/>
+      <c r="F1058" s="6" t="inlineStr">
+        <is>
+          <t>批量移除库存源定向(执行后用Add接口还原) — 100%</t>
+        </is>
+      </c>
       <c r="G1058" s="3" t="n"/>
     </row>
-    <row r="1059">
+    <row r="1059" ht="16" customHeight="1">
       <c r="A1059" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34900,10 +34958,18 @@
         </is>
       </c>
       <c r="E1059" s="3" t="n"/>
-      <c r="F1059" s="3" t="n"/>
-      <c r="G1059" s="3" t="n"/>
-    </row>
-    <row r="1060">
+      <c r="F1059" s="6" t="inlineStr">
+        <is>
+          <t>批量替换库存源定向(读原值-&gt;替换-&gt;还原) — 100%</t>
+        </is>
+      </c>
+      <c r="G1059" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug(数据一致性)：把该LineItem真实原始52条库存源整体replace回去，实测只保留44条(8条被静默丢弃，无任何报错，返回码仍成功)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060" ht="64" customHeight="1">
       <c r="A1060" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34925,10 +34991,21 @@
         </is>
       </c>
       <c r="E1060" s="3" t="n"/>
-      <c r="F1060" s="3" t="n"/>
-      <c r="G1060" s="3" t="n"/>
-    </row>
-    <row r="1061">
+      <c r="F1060" s="6" t="inlineStr">
+        <is>
+          <t>新增受众定向(optimizeType=Add，执行后用Remove清理) — 36.2%
+排除受众定向(optimizeType=Exclude，执行后用Remove清理) — 26.2%
+整体替换受众定向(optimizeType=Replace，读原值-&gt;替换-&gt;还原) — 24.0%
+移除受众定向(optimizeType=Remove) — 13.5%</t>
+        </is>
+      </c>
+      <c r="G1060" s="5" t="inlineStr">
+        <is>
+          <t>风险发现(非bug，已修正)：Remove操作会清空整个受众定向分组而非精确移除单个分群，执行中曾意外清空该LineItem真实原始受众定向(已用Replace手动恢复)，后续case清理步骤已统一改为Replace回真实原始值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061" ht="16" customHeight="1">
       <c r="A1061" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34950,10 +35027,18 @@
         </is>
       </c>
       <c r="E1061" s="3" t="n"/>
-      <c r="F1061" s="3" t="n"/>
-      <c r="G1061" s="3" t="n"/>
-    </row>
-    <row r="1062">
+      <c r="F1061" s="6" t="inlineStr">
+        <is>
+          <t>创建LineItem(自建测试数据，起止日期已过期=创建即无投放) — 100%</t>
+        </is>
+      </c>
+      <c r="G1061" s="5" t="inlineStr">
+        <is>
+          <t>业务规则发现：结束日期必须≥当前时间30分钟后且需落在所属order有效期内，已按此约束调整创建窗口，非bug。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062" ht="16" customHeight="1">
       <c r="A1062" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34975,10 +35060,14 @@
         </is>
       </c>
       <c r="E1062" s="3" t="n"/>
-      <c r="F1062" s="3" t="n"/>
+      <c r="F1062" s="6" t="inlineStr">
+        <is>
+          <t>生成LineItem触达量预测(只读计算，不产生持久化实体) — 100%</t>
+        </is>
+      </c>
       <c r="G1062" s="3" t="n"/>
     </row>
-    <row r="1063">
+    <row r="1063" ht="16" customHeight="1">
       <c r="A1063" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35000,10 +35089,14 @@
         </is>
       </c>
       <c r="E1063" s="3" t="n"/>
-      <c r="F1063" s="3" t="n"/>
+      <c r="F1063" s="6" t="inlineStr">
+        <is>
+          <t>下载目标设置Excel模板 — 100%</t>
+        </is>
+      </c>
       <c r="G1063" s="3" t="n"/>
     </row>
-    <row r="1064">
+    <row r="1064" ht="16" customHeight="1">
       <c r="A1064" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35025,10 +35118,14 @@
         </is>
       </c>
       <c r="E1064" s="3" t="n"/>
-      <c r="F1064" s="3" t="n"/>
+      <c r="F1064" s="6" t="inlineStr">
+        <is>
+          <t>查询指定lineItem的目标设置 — 100%</t>
+        </is>
+      </c>
       <c r="G1064" s="3" t="n"/>
     </row>
-    <row r="1065">
+    <row r="1065" ht="16" customHeight="1">
       <c r="A1065" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35050,10 +35147,14 @@
         </is>
       </c>
       <c r="E1065" s="3" t="n"/>
-      <c r="F1065" s="3" t="n"/>
+      <c r="F1065" s="6" t="inlineStr">
+        <is>
+          <t>查询LineItem详情(含同步) — 100%</t>
+        </is>
+      </c>
       <c r="G1065" s="3" t="n"/>
     </row>
-    <row r="1066">
+    <row r="1066" ht="32" customHeight="1">
       <c r="A1066" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35075,10 +35176,15 @@
         </is>
       </c>
       <c r="E1066" s="3" t="n"/>
-      <c r="F1066" s="3" t="n"/>
+      <c r="F1066" s="6" t="inlineStr">
+        <is>
+          <t>按广告主查询LineItem ID列表(isImpressions=true) — 78.4%
+按广告主查询LineItem ID列表(isImpressions=false) — 21.6%</t>
+        </is>
+      </c>
       <c r="G1066" s="3" t="n"/>
     </row>
-    <row r="1067">
+    <row r="1067" ht="16" customHeight="1">
       <c r="A1067" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35100,10 +35206,14 @@
         </is>
       </c>
       <c r="E1067" s="3" t="n"/>
-      <c r="F1067" s="3" t="n"/>
+      <c r="F1067" s="6" t="inlineStr">
+        <is>
+          <t>按Order查询LineItem名称与投放状态 — 100%</t>
+        </is>
+      </c>
       <c r="G1067" s="3" t="n"/>
     </row>
-    <row r="1068">
+    <row r="1068" ht="16" customHeight="1">
       <c r="A1068" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35125,10 +35235,14 @@
         </is>
       </c>
       <c r="E1068" s="3" t="n"/>
-      <c r="F1068" s="3" t="n"/>
+      <c r="F1068" s="6" t="inlineStr">
+        <is>
+          <t>查询LineItem精简详情(含同步) — 100%</t>
+        </is>
+      </c>
       <c r="G1068" s="3" t="n"/>
     </row>
-    <row r="1069">
+    <row r="1069" ht="16" customHeight="1">
       <c r="A1069" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35150,10 +35264,14 @@
         </is>
       </c>
       <c r="E1069" s="3" t="n"/>
-      <c r="F1069" s="3" t="n"/>
+      <c r="F1069" s="6" t="inlineStr">
+        <is>
+          <t>查询目标设置批量导入检查日志 — 100%</t>
+        </is>
+      </c>
       <c r="G1069" s="3" t="n"/>
     </row>
-    <row r="1070">
+    <row r="1070" ht="16" customHeight="1">
       <c r="A1070" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35175,10 +35293,14 @@
         </is>
       </c>
       <c r="E1070" s="3" t="n"/>
-      <c r="F1070" s="3" t="n"/>
+      <c r="F1070" s="6" t="inlineStr">
+        <is>
+          <t>查询目标设置查看日志(空条件) — 100%</t>
+        </is>
+      </c>
       <c r="G1070" s="3" t="n"/>
     </row>
-    <row r="1071">
+    <row r="1071" ht="16" customHeight="1">
       <c r="A1071" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35200,10 +35322,14 @@
         </is>
       </c>
       <c r="E1071" s="3" t="n"/>
-      <c r="F1071" s="3" t="n"/>
+      <c r="F1071" s="6" t="inlineStr">
+        <is>
+          <t>查询LineItem当前库存源定向 — 100%</t>
+        </is>
+      </c>
       <c r="G1071" s="3" t="n"/>
     </row>
-    <row r="1072">
+    <row r="1072" ht="16" customHeight="1">
       <c r="A1072" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35225,10 +35351,14 @@
         </is>
       </c>
       <c r="E1072" s="3" t="n"/>
-      <c r="F1072" s="3" t="n"/>
+      <c r="F1072" s="6" t="inlineStr">
+        <is>
+          <t>同步查询原生分时段设置 — 100%</t>
+        </is>
+      </c>
       <c r="G1072" s="3" t="n"/>
     </row>
-    <row r="1073">
+    <row r="1073" ht="16" customHeight="1">
       <c r="A1073" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35250,10 +35380,14 @@
         </is>
       </c>
       <c r="E1073" s="3" t="n"/>
-      <c r="F1073" s="3" t="n"/>
+      <c r="F1073" s="6" t="inlineStr">
+        <is>
+          <t>新增LineItem目标设置(roas) — 100%</t>
+        </is>
+      </c>
       <c r="G1073" s="3" t="n"/>
     </row>
-    <row r="1074">
+    <row r="1074" ht="16" customHeight="1">
       <c r="A1074" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -35275,8 +35409,16 @@
         </is>
       </c>
       <c r="E1074" s="3" t="n"/>
-      <c r="F1074" s="3" t="n"/>
-      <c r="G1074" s="3" t="n"/>
+      <c r="F1074" s="6" t="inlineStr">
+        <is>
+          <t>更新已存在LineItem(整单保存真实当前配置) — 100%</t>
+        </is>
+      </c>
+      <c r="G1074" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug(耦合缺陷)：同批次UpdateAndAddTargetSetting给LineItem新增目标设置(roas等)后，再对其做UpdateLineItem整单保存稳定失败(tacticsConvertersExclusionType can be changed only if automatedTactic is eligible for exclusion)，且tag内无删除目标设置接口可撤销，此FAIL会在任何后续重跑中必现。真实用户在后台大概率遇到"设置过目标值后无法再编辑LineItem基本信息"，建议登记Jira。⚠️共享测试lineitem_id=577321116875613595已被永久改变(新增1条roas目标设置且无法撤销)，其他并行任务/后续对该实体做UpdateLineItem类整单更新会必现同样失败。</t>
+        </is>
+      </c>
     </row>
     <row r="1075">
       <c r="A1075" s="2" t="inlineStr">
@@ -35301,7 +35443,11 @@
       </c>
       <c r="E1075" s="3" t="n"/>
       <c r="F1075" s="3" t="n"/>
-      <c r="G1075" s="3" t="n"/>
+      <c r="G1075" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口(真实xlsx二进制)，run-cases.py执行框架仅支持JSON body，无法上传文件。</t>
+        </is>
+      </c>
     </row>
     <row r="1076">
       <c r="A1076" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1374,9 +1374,19 @@
       </c>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
+      <c r="F32" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>92%(36/39执行,2条高危仅生成不执行不计入)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>79% (19/24)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -24879,7 +24889,7 @@
       </c>
       <c r="G727" s="3" t="n"/>
     </row>
-    <row r="728">
+    <row r="728" ht="16" customHeight="1">
       <c r="A728" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24901,10 +24911,14 @@
         </is>
       </c>
       <c r="E728" s="3" t="n"/>
-      <c r="F728" s="3" t="n"/>
+      <c r="F728" s="6" t="inlineStr">
+        <is>
+          <t>查询Deal属性详情 — 19.6%</t>
+        </is>
+      </c>
       <c r="G728" s="3" t="n"/>
     </row>
-    <row r="729">
+    <row r="729" ht="16" customHeight="1">
       <c r="A729" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24926,10 +24940,14 @@
         </is>
       </c>
       <c r="E729" s="3" t="n"/>
-      <c r="F729" s="3" t="n"/>
+      <c r="F729" s="6" t="inlineStr">
+        <is>
+          <t>查询Deal关联卖家列表 — 19.6%</t>
+        </is>
+      </c>
       <c r="G729" s="3" t="n"/>
     </row>
-    <row r="730">
+    <row r="730" ht="32" customHeight="1">
       <c r="A730" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24951,10 +24969,15 @@
         </is>
       </c>
       <c r="E730" s="3" t="n"/>
-      <c r="F730" s="3" t="n"/>
+      <c r="F730" s="6" t="inlineStr">
+        <is>
+          <t>下载Deal批量导入模板(不限定广告主) — 50.0%
+下载Deal批量导入模板(指定广告主) — 20.0%</t>
+        </is>
+      </c>
       <c r="G730" s="3" t="n"/>
     </row>
-    <row r="731">
+    <row r="731" ht="16" customHeight="1">
       <c r="A731" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -24976,10 +24999,14 @@
         </is>
       </c>
       <c r="E731" s="3" t="n"/>
-      <c r="F731" s="3" t="n"/>
+      <c r="F731" s="6" t="inlineStr">
+        <is>
+          <t>下载批量上传失败记录Excel — 12.5%</t>
+        </is>
+      </c>
       <c r="G731" s="3" t="n"/>
     </row>
-    <row r="732">
+    <row r="732" ht="48" customHeight="1">
       <c r="A732" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25001,10 +25028,16 @@
         </is>
       </c>
       <c r="E732" s="3" t="n"/>
-      <c r="F732" s="3" t="n"/>
+      <c r="F732" s="6" t="inlineStr">
+        <is>
+          <t>查询批量上传日志(按上传人筛选) — 93.8%
+查询批量上传日志(不筛选) — 3.7%
+查询批量上传日志(按上传人+状态筛选) — 2.5%</t>
+        </is>
+      </c>
       <c r="G732" s="3" t="n"/>
     </row>
-    <row r="733">
+    <row r="733" ht="16" customHeight="1">
       <c r="A733" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25026,10 +25059,18 @@
         </is>
       </c>
       <c r="E733" s="3" t="n"/>
-      <c r="F733" s="3" t="n"/>
-      <c r="G733" s="3" t="n"/>
-    </row>
-    <row r="734">
+      <c r="F733" s="6" t="inlineStr">
+        <is>
+          <t>批量导入Deal(Excel上传)【风险-未执行】</t>
+        </is>
+      </c>
+      <c r="G733" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高危+技术受限：Excel批量版Deal创建，语义同dealManagement/create但影响范围更大(一次可批量登记多条真实Deal)，且为multipart/form-data文件上传run-cases.py无法回放，双重原因未执行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="734" ht="16" customHeight="1">
       <c r="A734" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25051,10 +25092,18 @@
         </is>
       </c>
       <c r="E734" s="3" t="n"/>
-      <c r="F734" s="3" t="n"/>
-      <c r="G734" s="3" t="n"/>
-    </row>
-    <row r="735">
+      <c r="F734" s="6" t="inlineStr">
+        <is>
+          <t>创建真实第三方Deal【风险-未执行】</t>
+        </is>
+      </c>
+      <c r="G734" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高危：请求体用于向DSP登记真实第三方(SSP/Publisher)商业Deal，含真实publisher名称/exchangeId/真实报价priceMillis/currency/SSP外部DealID，属真实商业合同/金额承诺登记，一次性难以撤销，需用户确认是否批准执行一次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="735" ht="32" customHeight="1">
       <c r="A735" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25076,10 +25125,15 @@
         </is>
       </c>
       <c r="E735" s="3" t="n"/>
-      <c r="F735" s="3" t="n"/>
+      <c r="F735" s="6" t="inlineStr">
+        <is>
+          <t>查询Deal详情(强制刷新预测数据) — 20.2%
+查询Deal详情(不刷新预测数据) — 8.4%</t>
+        </is>
+      </c>
       <c r="G735" s="3" t="n"/>
     </row>
-    <row r="736">
+    <row r="736" ht="16" customHeight="1">
       <c r="A736" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25101,10 +25155,18 @@
         </is>
       </c>
       <c r="E736" s="3" t="n"/>
-      <c r="F736" s="3" t="n"/>
-      <c r="G736" s="3" t="n"/>
-    </row>
-    <row r="737">
+      <c r="F736" s="6" t="inlineStr">
+        <is>
+          <t>查询Deal关联LineItem列表 — 19.6%</t>
+        </is>
+      </c>
+      <c r="G736" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug(性能/超时)：对账号内两个真实存在的Deal查询均在120~150秒内无响应，而该接口ES生产日志有102次历史成功调用，疑似真实性能或环境缺陷，两轮稳定复现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="737" ht="96" customHeight="1">
       <c r="A737" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25126,10 +25188,19 @@
         </is>
       </c>
       <c r="E737" s="3" t="n"/>
-      <c r="F737" s="3" t="n"/>
+      <c r="F737" s="6" t="inlineStr">
+        <is>
+          <t>不筛选导出全部Deal — 50.0%
+按状态ACTIVE+UPCOMING筛选导出 — 18.2%
+dealIds传空字符串(前端边界写法)导出全部 — 13.6%
+按PREFERRED类型+UPCOMING状态筛选导出 — 9.1%
+按PRIVATE AUCTION类型+UPCOMING状态筛选导出 — 4.5%
+按PRIVATE AUCTION类型+EXPIRED状态筛选导出 — 4.5%</t>
+        </is>
+      </c>
       <c r="G737" s="3" t="n"/>
     </row>
-    <row r="738">
+    <row r="738" ht="32" customHeight="1">
       <c r="A738" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25151,10 +25222,15 @@
         </is>
       </c>
       <c r="E738" s="3" t="n"/>
-      <c r="F738" s="3" t="n"/>
+      <c r="F738" s="6" t="inlineStr">
+        <is>
+          <t>查询多Profile下的Deal下拉列表 — 98.4%
+查询Deal下拉列表(profileIds为空) — 1.6%</t>
+        </is>
+      </c>
       <c r="G738" s="3" t="n"/>
     </row>
-    <row r="739">
+    <row r="739" ht="96" customHeight="1">
       <c r="A739" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25176,7 +25252,16 @@
         </is>
       </c>
       <c r="E739" s="3" t="n"/>
-      <c r="F739" s="3" t="n"/>
+      <c r="F739" s="6" t="inlineStr">
+        <is>
+          <t>默认分页(pageSize25)不筛选 — 49.0%
+分页pageSize100不筛选 — 20.4%
+pageSize=0导出/不分页模式不筛选 — 12.6%
+按dealIds精确筛选
+dealIds传空字符串(前端边界写法)不筛选
+分页pageSize50不筛选 — 1.4%</t>
+        </is>
+      </c>
       <c r="G739" s="3" t="n"/>
     </row>
     <row r="740">
@@ -25201,8 +25286,16 @@
         </is>
       </c>
       <c r="E740" s="3" t="n"/>
-      <c r="F740" s="3" t="n"/>
-      <c r="G740" s="3" t="n"/>
+      <c r="F740" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G740" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" s="2" t="inlineStr">
@@ -25226,8 +25319,16 @@
         </is>
       </c>
       <c r="E741" s="3" t="n"/>
-      <c r="F741" s="3" t="n"/>
-      <c r="G741" s="3" t="n"/>
+      <c r="F741" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G741" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" s="2" t="inlineStr">
@@ -25252,9 +25353,13 @@
       </c>
       <c r="E742" s="3" t="n"/>
       <c r="F742" s="3" t="n"/>
-      <c r="G742" s="3" t="n"/>
-    </row>
-    <row r="743">
+      <c r="G742" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：需要真实inventoryId(与inventoryGroupId是完全不同的ID池，指向具体广告位/库存实体)，Deal tag 24个接口范围内无法查到该ID，未生成case。</t>
+        </is>
+      </c>
+    </row>
+    <row r="743" ht="16" customHeight="1">
       <c r="A743" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25276,8 +25381,16 @@
         </is>
       </c>
       <c r="E743" s="3" t="n"/>
-      <c r="F743" s="3" t="n"/>
-      <c r="G743" s="3" t="n"/>
+      <c r="F743" s="6" t="inlineStr">
+        <is>
+          <t>批量创建库存组(关联本账号真实Deal) — 100%</t>
+        </is>
+      </c>
+      <c r="G743" s="5" t="inlineStr">
+        <is>
+          <t>同createInventoryGroup：携带真实DealId关联时同样返回"Unkown error, please try again."通用错误。</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="2" t="inlineStr">
@@ -25304,7 +25417,7 @@
       <c r="F744" s="3" t="n"/>
       <c r="G744" s="3" t="n"/>
     </row>
-    <row r="745">
+    <row r="745" ht="32" customHeight="1">
       <c r="A745" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25326,10 +25439,19 @@
         </is>
       </c>
       <c r="E745" s="3" t="n"/>
-      <c r="F745" s="3" t="n"/>
-      <c r="G745" s="3" t="n"/>
-    </row>
-    <row r="746">
+      <c r="F745" s="6" t="inlineStr">
+        <is>
+          <t>创建库存组(不关联Deal，含后置重命名标记) — 27.3%
+创建库存组(关联本账号真实Deal，含后置重命名标记) — 72.7%</t>
+        </is>
+      </c>
+      <c r="G745" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：dealIds为空时创建成功，但携带账号内任意真实DealId(两个真实Deal分别验证一致)一律返回"Unkown error, please try again."无诊断信息的通用错误。ES生产日志显示72.7%的真实调用都携带dealIds且应该成功，判定为真实缺陷或至少是无有效错误提示的可用性问题。</t>
+        </is>
+      </c>
+    </row>
+    <row r="746" ht="16" customHeight="1">
       <c r="A746" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25351,10 +25473,14 @@
         </is>
       </c>
       <c r="E746" s="3" t="n"/>
-      <c r="F746" s="3" t="n"/>
+      <c r="F746" s="6" t="inlineStr">
+        <is>
+          <t>导出库存组列表(不筛选) — 88.9%</t>
+        </is>
+      </c>
       <c r="G746" s="3" t="n"/>
     </row>
-    <row r="747">
+    <row r="747" ht="16" customHeight="1">
       <c r="A747" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25376,10 +25502,14 @@
         </is>
       </c>
       <c r="E747" s="3" t="n"/>
-      <c r="F747" s="3" t="n"/>
+      <c r="F747" s="6" t="inlineStr">
+        <is>
+          <t>查询可加入库存组的Deal列表 — 100%</t>
+        </is>
+      </c>
       <c r="G747" s="3" t="n"/>
     </row>
-    <row r="748">
+    <row r="748" ht="112" customHeight="1">
       <c r="A748" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25401,10 +25531,20 @@
         </is>
       </c>
       <c r="E748" s="3" t="n"/>
-      <c r="F748" s="3" t="n"/>
+      <c r="F748" s="6" t="inlineStr">
+        <is>
+          <t>旧版精简参数查询(仅appendDealInfo) — 49.4%
+默认分页(pageSize25)不筛选 — 13.2%
+按VIDEO类型筛选 — 9.8%
+分页pageSize100不筛选 — 6.8%
+按DISPLAY类型筛选 — 6.6%
+按inventoryGroupIds精确筛选 — 3.2%
+按dealIds筛选所属库存组 — 1.0%</t>
+        </is>
+      </c>
       <c r="G748" s="3" t="n"/>
     </row>
-    <row r="749">
+    <row r="749" ht="32" customHeight="1">
       <c r="A749" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -25426,7 +25566,12 @@
         </is>
       </c>
       <c r="E749" s="3" t="n"/>
-      <c r="F749" s="3" t="n"/>
+      <c r="F749" s="6" t="inlineStr">
+        <is>
+          <t>查询库存组下拉列表(全部Profile) — 85.6%
+查询库存组下拉列表(指定Profile) — 14.4%</t>
+        </is>
+      </c>
       <c r="G749" s="3" t="n"/>
     </row>
     <row r="750">
@@ -25451,8 +25596,16 @@
         </is>
       </c>
       <c r="E750" s="3" t="n"/>
-      <c r="F750" s="3" t="n"/>
-      <c r="G750" s="3" t="n"/>
+      <c r="F750" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G750" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" s="2" t="inlineStr">
@@ -25477,7 +25630,11 @@
       </c>
       <c r="E751" s="3" t="n"/>
       <c r="F751" s="3" t="n"/>
-      <c r="G751" s="3" t="n"/>
+      <c r="G751" s="5" t="inlineStr">
+        <is>
+          <t>⚠️清理限制：Deal tag无InventoryGroup的delete/archive接口，验证写操作已在共享测试账号创建5个真实InventoryGroup(test120400-*前缀，已重命名标记)且无法物理清理/归档，会永久留存。</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -2310,9 +2310,19 @@
       </c>
       <c r="D65" s="3" t="n"/>
       <c r="E65" s="3" t="n"/>
-      <c r="F65" s="2" t="n"/>
-      <c r="G65" s="2" t="n"/>
-      <c r="H65" s="2" t="n"/>
+      <c r="F65" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>100%(15/15执行,1条高危仅生成不执行不计入)</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>31% (8/26)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -45914,8 +45924,16 @@
         </is>
       </c>
       <c r="E1409" s="3" t="n"/>
-      <c r="F1409" s="3" t="n"/>
-      <c r="G1409" s="3" t="n"/>
+      <c r="F1409" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1409" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1410">
       <c r="A1410" s="2" t="inlineStr">
@@ -45939,10 +45957,18 @@
         </is>
       </c>
       <c r="E1410" s="3" t="n"/>
-      <c r="F1410" s="3" t="n"/>
-      <c r="G1410" s="3" t="n"/>
-    </row>
-    <row r="1411">
+      <c r="F1410" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1410" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411" ht="16" customHeight="1">
       <c r="A1411" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45964,10 +45990,18 @@
         </is>
       </c>
       <c r="E1411" s="3" t="n"/>
-      <c r="F1411" s="3" t="n"/>
-      <c r="G1411" s="3" t="n"/>
-    </row>
-    <row r="1412">
+      <c r="F1411" s="6" t="inlineStr">
+        <is>
+          <t>删除向导草稿</t>
+        </is>
+      </c>
+      <c r="G1411" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-高危：唯一草稿创建入口SaveSuperWizard 365天0流量无法安全创建可丢弃草稿配对测试；若用ES样本里真实wizardId执行会误删共享账号其他真实用户的草稿且不可逆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412" ht="64" customHeight="1">
       <c r="A1412" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45989,10 +46023,17 @@
         </is>
       </c>
       <c r="E1412" s="3" t="n"/>
-      <c r="F1412" s="3" t="n"/>
+      <c r="F1412" s="6" t="inlineStr">
+        <is>
+          <t>仅按Profile查询(不筛选Advertiser/User) — 90.2%
+按User筛选 — 5.7%
+按Advertiser筛选 — 2.4%
+同时按Advertiser+User筛选 — 1.7%</t>
+        </is>
+      </c>
       <c r="G1412" s="3" t="n"/>
     </row>
-    <row r="1413">
+    <row r="1413" ht="32" customHeight="1">
       <c r="A1413" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -46014,7 +46055,12 @@
         </is>
       </c>
       <c r="E1413" s="3" t="n"/>
-      <c r="F1413" s="3" t="n"/>
+      <c r="F1413" s="6" t="inlineStr">
+        <is>
+          <t>无预选素材(默认打开) — 96.3%
+已预选素材(回填选中态) — 3.7%</t>
+        </is>
+      </c>
       <c r="G1413" s="3" t="n"/>
     </row>
     <row r="1414">
@@ -46039,8 +46085,16 @@
         </is>
       </c>
       <c r="E1414" s="3" t="n"/>
-      <c r="F1414" s="3" t="n"/>
-      <c r="G1414" s="3" t="n"/>
+      <c r="F1414" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1414" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1415">
       <c r="A1415" s="2" t="inlineStr">
@@ -46064,8 +46118,16 @@
         </is>
       </c>
       <c r="E1415" s="3" t="n"/>
-      <c r="F1415" s="3" t="n"/>
-      <c r="G1415" s="3" t="n"/>
+      <c r="F1415" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1415" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1416">
       <c r="A1416" s="2" t="inlineStr">
@@ -46089,8 +46151,16 @@
         </is>
       </c>
       <c r="E1416" s="3" t="n"/>
-      <c r="F1416" s="3" t="n"/>
-      <c r="G1416" s="3" t="n"/>
+      <c r="F1416" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1416" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1417">
       <c r="A1417" s="2" t="inlineStr">
@@ -46114,8 +46184,16 @@
         </is>
       </c>
       <c r="E1417" s="3" t="n"/>
-      <c r="F1417" s="3" t="n"/>
-      <c r="G1417" s="3" t="n"/>
+      <c r="F1417" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1417" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1418">
       <c r="A1418" s="2" t="inlineStr">
@@ -46139,8 +46217,16 @@
         </is>
       </c>
       <c r="E1418" s="3" t="n"/>
-      <c r="F1418" s="3" t="n"/>
-      <c r="G1418" s="3" t="n"/>
+      <c r="F1418" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1418" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1419">
       <c r="A1419" s="2" t="inlineStr">
@@ -46164,8 +46250,16 @@
         </is>
       </c>
       <c r="E1419" s="3" t="n"/>
-      <c r="F1419" s="3" t="n"/>
-      <c r="G1419" s="3" t="n"/>
+      <c r="F1419" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1419" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1420">
       <c r="A1420" s="2" t="inlineStr">
@@ -46189,10 +46283,18 @@
         </is>
       </c>
       <c r="E1420" s="3" t="n"/>
-      <c r="F1420" s="3" t="n"/>
-      <c r="G1420" s="3" t="n"/>
-    </row>
-    <row r="1421">
+      <c r="F1420" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1420" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421" ht="64" customHeight="1">
       <c r="A1421" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -46214,10 +46316,17 @@
         </is>
       </c>
       <c r="E1421" s="3" t="n"/>
-      <c r="F1421" s="3" t="n"/>
+      <c r="F1421" s="6" t="inlineStr">
+        <is>
+          <t>默认查询(无搜索无排除) — 77.0%
+按搜索词过滤 — 15.6%
+搜索词+排除已选ASIN — 6.2%
+仅排除已选ASIN(无搜索词) — 1.2%</t>
+        </is>
+      </c>
       <c r="G1421" s="3" t="n"/>
     </row>
-    <row r="1422">
+    <row r="1422" ht="16" customHeight="1">
       <c r="A1422" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -46239,10 +46348,14 @@
         </is>
       </c>
       <c r="E1422" s="3" t="n"/>
-      <c r="F1422" s="3" t="n"/>
+      <c r="F1422" s="6" t="inlineStr">
+        <is>
+          <t>按wizardId查询草稿详情 — 100%</t>
+        </is>
+      </c>
       <c r="G1422" s="3" t="n"/>
     </row>
-    <row r="1423">
+    <row r="1423" ht="16" customHeight="1">
       <c r="A1423" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -46264,10 +46377,14 @@
         </is>
       </c>
       <c r="E1423" s="3" t="n"/>
-      <c r="F1423" s="3" t="n"/>
+      <c r="F1423" s="6" t="inlineStr">
+        <is>
+          <t>查询当前用户草稿列表 — 100%</t>
+        </is>
+      </c>
       <c r="G1423" s="3" t="n"/>
     </row>
-    <row r="1424">
+    <row r="1424" ht="32" customHeight="1">
       <c r="A1424" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -46289,10 +46406,19 @@
         </is>
       </c>
       <c r="E1424" s="3" t="n"/>
-      <c r="F1424" s="3" t="n"/>
-      <c r="G1424" s="3" t="n"/>
-    </row>
-    <row r="1425">
+      <c r="F1424" s="6" t="inlineStr">
+        <is>
+          <t>按SuperWizardId查全部LineItem日志 — 66.7%
+按SuperWizardId+WizardOrderId查单Order下日志 — 33.3%</t>
+        </is>
+      </c>
+      <c r="G1424" s="5" t="inlineStr">
+        <is>
+          <t>🔴疑似安全观察项(同Audit模块IDOR模式)：用ES样本里其他真实客户的superWizardId查询，返回200+非空真实业务数据，未见租户隔离拒绝。不确定是日志类接口设计如此还是权限校验缺口，建议与Audit的GetDetail/GetOpportunities一并核查。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425" ht="16" customHeight="1">
       <c r="A1425" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -46314,8 +46440,16 @@
         </is>
       </c>
       <c r="E1425" s="3" t="n"/>
-      <c r="F1425" s="3" t="n"/>
-      <c r="G1425" s="3" t="n"/>
+      <c r="F1425" s="6" t="inlineStr">
+        <is>
+          <t>按SuperWizardId查Order执行日志 — 100%</t>
+        </is>
+      </c>
+      <c r="G1425" s="5" t="inlineStr">
+        <is>
+          <t>🔴疑似安全观察项：同GetWizardLogLineList，用他人superWizardId查询返回真实业务数据未拒绝。</t>
+        </is>
+      </c>
     </row>
     <row r="1426">
       <c r="A1426" s="2" t="inlineStr">
@@ -46339,8 +46473,16 @@
         </is>
       </c>
       <c r="E1426" s="3" t="n"/>
-      <c r="F1426" s="3" t="n"/>
-      <c r="G1426" s="3" t="n"/>
+      <c r="F1426" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1426" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1427">
       <c r="A1427" s="2" t="inlineStr">
@@ -46364,8 +46506,16 @@
         </is>
       </c>
       <c r="E1427" s="3" t="n"/>
-      <c r="F1427" s="3" t="n"/>
-      <c r="G1427" s="3" t="n"/>
+      <c r="F1427" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1427" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1428">
       <c r="A1428" s="2" t="inlineStr">
@@ -46389,8 +46539,16 @@
         </is>
       </c>
       <c r="E1428" s="3" t="n"/>
-      <c r="F1428" s="3" t="n"/>
-      <c r="G1428" s="3" t="n"/>
+      <c r="F1428" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1428" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认-核心高危创建入口：批量导入创建广告结构(Order/LineItem/Creative等多实体)，可选isRunAd直接真实投放，365天0流量且无对应批量清理/整单归档接口，需用户确认最小安全payload及清理方案后才能覆盖，本次未生成case。</t>
+        </is>
+      </c>
     </row>
     <row r="1429">
       <c r="A1429" s="2" t="inlineStr">
@@ -46414,8 +46572,16 @@
         </is>
       </c>
       <c r="E1429" s="3" t="n"/>
-      <c r="F1429" s="3" t="n"/>
-      <c r="G1429" s="3" t="n"/>
+      <c r="F1429" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1429" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1430">
       <c r="A1430" s="2" t="inlineStr">
@@ -46439,8 +46605,16 @@
         </is>
       </c>
       <c r="E1430" s="3" t="n"/>
-      <c r="F1430" s="3" t="n"/>
-      <c r="G1430" s="3" t="n"/>
+      <c r="F1430" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1430" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1431">
       <c r="A1431" s="2" t="inlineStr">
@@ -46464,8 +46638,16 @@
         </is>
       </c>
       <c r="E1431" s="3" t="n"/>
-      <c r="F1431" s="3" t="n"/>
-      <c r="G1431" s="3" t="n"/>
+      <c r="F1431" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1431" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1432">
       <c r="A1432" s="2" t="inlineStr">
@@ -46489,8 +46671,16 @@
         </is>
       </c>
       <c r="E1432" s="3" t="n"/>
-      <c r="F1432" s="3" t="n"/>
-      <c r="G1432" s="3" t="n"/>
+      <c r="F1432" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1432" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1433">
       <c r="A1433" s="2" t="inlineStr">
@@ -46514,8 +46704,16 @@
         </is>
       </c>
       <c r="E1433" s="3" t="n"/>
-      <c r="F1433" s="3" t="n"/>
-      <c r="G1433" s="3" t="n"/>
+      <c r="F1433" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1433" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1434">
       <c r="A1434" s="2" t="inlineStr">
@@ -46539,8 +46737,16 @@
         </is>
       </c>
       <c r="E1434" s="3" t="n"/>
-      <c r="F1434" s="3" t="n"/>
-      <c r="G1434" s="3" t="n"/>
+      <c r="F1434" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1434" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1435">
       <c r="A1435" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -2288,9 +2288,19 @@
       </c>
       <c r="D64" s="3" t="n"/>
       <c r="E64" s="3" t="n"/>
-      <c r="F64" s="2" t="n"/>
-      <c r="G64" s="2" t="n"/>
-      <c r="H64" s="2" t="n"/>
+      <c r="F64" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>50% (11/22)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -45352,7 +45362,7 @@
         </is>
       </c>
     </row>
-    <row r="1387">
+    <row r="1387" ht="16" customHeight="1">
       <c r="A1387" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45374,10 +45384,18 @@
         </is>
       </c>
       <c r="E1387" s="3" t="n"/>
-      <c r="F1387" s="3" t="n"/>
-      <c r="G1387" s="3" t="n"/>
-    </row>
-    <row r="1388">
+      <c r="F1387" s="6" t="inlineStr">
+        <is>
+          <t>批量/单个删除ShareLink — 99.7%</t>
+        </is>
+      </c>
+      <c r="G1387" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：不校验shareId是否存在，传入纯虚构shareId(如"ZZZZZ_NONEXISTENT_99")调用返回与真实shareId成功时完全一致的{IsSuccessStatusCode:true,Data:null}，无法区分"真的改了"还是"目标不存在、静默空跑"，调用方传错ID完全无感知。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388" ht="32" customHeight="1">
       <c r="A1388" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45399,10 +45417,19 @@
         </is>
       </c>
       <c r="E1388" s="3" t="n"/>
-      <c r="F1388" s="3" t="n"/>
-      <c r="G1388" s="3" t="n"/>
-    </row>
-    <row r="1389">
+      <c r="F1388" s="6" t="inlineStr">
+        <is>
+          <t>批量修改DateRange(dateRangeType=1) — 93.7%
+批量修改DateRange(dateRangeType=14) — 4.5%</t>
+        </is>
+      </c>
+      <c r="G1388" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：不校验shareId是否存在，传入纯虚构shareId(如"ZZZZZ_NONEXISTENT_99")调用返回与真实shareId成功时完全一致的{IsSuccessStatusCode:true,Data:null}，无法区分"真的改了"还是"目标不存在、静默空跑"，调用方传错ID完全无感知。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389" ht="16" customHeight="1">
       <c r="A1389" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45424,10 +45451,18 @@
         </is>
       </c>
       <c r="E1389" s="3" t="n"/>
-      <c r="F1389" s="3" t="n"/>
-      <c r="G1389" s="3" t="n"/>
-    </row>
-    <row r="1390">
+      <c r="F1389" s="6" t="inlineStr">
+        <is>
+          <t>批量修改Description — 98.6%</t>
+        </is>
+      </c>
+      <c r="G1389" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：不校验shareId是否存在，传入纯虚构shareId(如"ZZZZZ_NONEXISTENT_99")调用返回与真实shareId成功时完全一致的{IsSuccessStatusCode:true,Data:null}，无法区分"真的改了"还是"目标不存在、静默空跑"，调用方传错ID完全无感知。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390" ht="16" customHeight="1">
       <c r="A1390" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45449,8 +45484,16 @@
         </is>
       </c>
       <c r="E1390" s="3" t="n"/>
-      <c r="F1390" s="3" t="n"/>
-      <c r="G1390" s="3" t="n"/>
+      <c r="F1390" s="6" t="inlineStr">
+        <is>
+          <t>批量修改ExpiredDate — 98.9%</t>
+        </is>
+      </c>
+      <c r="G1390" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：不校验shareId是否存在，传入纯虚构shareId(如"ZZZZZ_NONEXISTENT_99")调用返回与真实shareId成功时完全一致的{IsSuccessStatusCode:true,Data:null}，无法区分"真的改了"还是"目标不存在、静默空跑"，调用方传错ID完全无感知。</t>
+        </is>
+      </c>
     </row>
     <row r="1391">
       <c r="A1391" s="2" t="inlineStr">
@@ -45474,8 +45517,16 @@
         </is>
       </c>
       <c r="E1391" s="3" t="n"/>
-      <c r="F1391" s="3" t="n"/>
-      <c r="G1391" s="3" t="n"/>
+      <c r="F1391" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1391" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1392">
       <c r="A1392" s="2" t="inlineStr">
@@ -45499,10 +45550,18 @@
         </is>
       </c>
       <c r="E1392" s="3" t="n"/>
-      <c r="F1392" s="3" t="n"/>
-      <c r="G1392" s="3" t="n"/>
-    </row>
-    <row r="1393">
+      <c r="F1392" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1392" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393" ht="32" customHeight="1">
       <c r="A1393" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45524,7 +45583,12 @@
         </is>
       </c>
       <c r="E1393" s="3" t="n"/>
-      <c r="F1393" s="3" t="n"/>
+      <c r="F1393" s="6" t="inlineStr">
+        <is>
+          <t>创建ShareLink(勾选OrderTag)(含后置清理,可重复) — 90.6%
+创建ShareLink(不勾选OrderTag)(含后置清理,可重复) — 9.4%</t>
+        </is>
+      </c>
       <c r="G1393" s="3" t="n"/>
     </row>
     <row r="1394">
@@ -45549,8 +45613,16 @@
         </is>
       </c>
       <c r="E1394" s="3" t="n"/>
-      <c r="F1394" s="3" t="n"/>
-      <c r="G1394" s="3" t="n"/>
+      <c r="F1394" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1394" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1395">
       <c r="A1395" s="2" t="inlineStr">
@@ -45574,10 +45646,18 @@
         </is>
       </c>
       <c r="E1395" s="3" t="n"/>
-      <c r="F1395" s="3" t="n"/>
-      <c r="G1395" s="3" t="n"/>
-    </row>
-    <row r="1396">
+      <c r="F1395" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1395" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396" ht="48" customHeight="1">
       <c r="A1396" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45599,10 +45679,20 @@
         </is>
       </c>
       <c r="E1396" s="3" t="n"/>
-      <c r="F1396" s="3" t="n"/>
-      <c r="G1396" s="3" t="n"/>
-    </row>
-    <row r="1397">
+      <c r="F1396" s="6" t="inlineStr">
+        <is>
+          <t>修改ShareLink(勾选OrderTag+自定义模板1)(含后置清理,可重复) — 84.7%
+修改ShareLink(勾选OrderTag+默认模板0)(含后置清理,可重复) — 9.0%
+修改ShareLink(不勾选OrderTag+默认模板0)(含后置清理,可重复) — 3.8%</t>
+        </is>
+      </c>
+      <c r="G1396" s="5" t="inlineStr">
+        <is>
+          <t>部分技术受限："勾选OrderTag+勾选CreativeTag"场景(占比1.4%)因账号无真实creativeTagId([NEEDS_REAL_VALUE])未覆盖，其余3个场景已覆盖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397" ht="16" customHeight="1">
       <c r="A1397" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45624,7 +45714,11 @@
         </is>
       </c>
       <c r="E1397" s="3" t="n"/>
-      <c r="F1397" s="3" t="n"/>
+      <c r="F1397" s="6" t="inlineStr">
+        <is>
+          <t>导出ShareLink — 100%</t>
+        </is>
+      </c>
       <c r="G1397" s="3" t="n"/>
     </row>
     <row r="1398">
@@ -45649,8 +45743,16 @@
         </is>
       </c>
       <c r="E1398" s="3" t="n"/>
-      <c r="F1398" s="3" t="n"/>
-      <c r="G1398" s="3" t="n"/>
+      <c r="F1398" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1398" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1399">
       <c r="A1399" s="2" t="inlineStr">
@@ -45674,10 +45776,18 @@
         </is>
       </c>
       <c r="E1399" s="3" t="n"/>
-      <c r="F1399" s="3" t="n"/>
-      <c r="G1399" s="3" t="n"/>
-    </row>
-    <row r="1400">
+      <c r="F1399" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1399" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400" ht="16" customHeight="1">
       <c r="A1400" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45699,10 +45809,14 @@
         </is>
       </c>
       <c r="E1400" s="3" t="n"/>
-      <c r="F1400" s="3" t="n"/>
+      <c r="F1400" s="6" t="inlineStr">
+        <is>
+          <t>按shareId查询ShareLink明细 — 100%</t>
+        </is>
+      </c>
       <c r="G1400" s="3" t="n"/>
     </row>
-    <row r="1401">
+    <row r="1401" ht="16" customHeight="1">
       <c r="A1401" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45724,7 +45838,11 @@
         </is>
       </c>
       <c r="E1401" s="3" t="n"/>
-      <c r="F1401" s="3" t="n"/>
+      <c r="F1401" s="6" t="inlineStr">
+        <is>
+          <t>查询ShareLink列表(默认分页+当前profile) — 100%</t>
+        </is>
+      </c>
       <c r="G1401" s="3" t="n"/>
     </row>
     <row r="1402">
@@ -45749,8 +45867,16 @@
         </is>
       </c>
       <c r="E1402" s="3" t="n"/>
-      <c r="F1402" s="3" t="n"/>
-      <c r="G1402" s="3" t="n"/>
+      <c r="F1402" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1402" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1403">
       <c r="A1403" s="2" t="inlineStr">
@@ -45774,8 +45900,16 @@
         </is>
       </c>
       <c r="E1403" s="3" t="n"/>
-      <c r="F1403" s="3" t="n"/>
-      <c r="G1403" s="3" t="n"/>
+      <c r="F1403" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1403" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1404">
       <c r="A1404" s="2" t="inlineStr">
@@ -45799,8 +45933,16 @@
         </is>
       </c>
       <c r="E1404" s="3" t="n"/>
-      <c r="F1404" s="3" t="n"/>
-      <c r="G1404" s="3" t="n"/>
+      <c r="F1404" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1404" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1405">
       <c r="A1405" s="2" t="inlineStr">
@@ -45824,8 +45966,16 @@
         </is>
       </c>
       <c r="E1405" s="3" t="n"/>
-      <c r="F1405" s="3" t="n"/>
-      <c r="G1405" s="3" t="n"/>
+      <c r="F1405" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1405" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1406">
       <c r="A1406" s="2" t="inlineStr">
@@ -45849,10 +45999,18 @@
         </is>
       </c>
       <c r="E1406" s="3" t="n"/>
-      <c r="F1406" s="3" t="n"/>
-      <c r="G1406" s="3" t="n"/>
-    </row>
-    <row r="1407">
+      <c r="F1406" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1406" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407" ht="16" customHeight="1">
       <c r="A1407" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45874,10 +46032,14 @@
         </is>
       </c>
       <c r="E1407" s="3" t="n"/>
-      <c r="F1407" s="3" t="n"/>
+      <c r="F1407" s="6" t="inlineStr">
+        <is>
+          <t>获取分享页顶部参数 — 100%</t>
+        </is>
+      </c>
       <c r="G1407" s="3" t="n"/>
     </row>
-    <row r="1408">
+    <row r="1408" ht="16" customHeight="1">
       <c r="A1408" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -45899,8 +46061,16 @@
         </is>
       </c>
       <c r="E1408" s="3" t="n"/>
-      <c r="F1408" s="3" t="n"/>
-      <c r="G1408" s="3" t="n"/>
+      <c r="F1408" s="6" t="inlineStr">
+        <is>
+          <t>通过shareId换取用户token — 100%</t>
+        </is>
+      </c>
+      <c r="G1408" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：响应恒为空对象{}，与Swagger声明的string返回类型不符，无论shareId/platform参数如何均拿不到token。该接口365天仅3次真实调用，样本极少，怀疑遗留/特殊来源专用接口或存在实现缺陷。</t>
+        </is>
+      </c>
     </row>
     <row r="1409">
       <c r="A1409" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1428,9 +1428,19 @@
       </c>
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
+      <c r="F34" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>89% (16/18)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -26056,7 +26066,7 @@
       <c r="F767" s="3" t="n"/>
       <c r="G767" s="3" t="n"/>
     </row>
-    <row r="768">
+    <row r="768" ht="128" customHeight="1">
       <c r="A768" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26078,10 +26088,25 @@
         </is>
       </c>
       <c r="E768" s="3" t="n"/>
-      <c r="F768" s="3" t="n"/>
-      <c r="G768" s="3" t="n"/>
-    </row>
-    <row r="769">
+      <c r="F768" s="6" t="inlineStr">
+        <is>
+          <t>country=[US] — 49.8%
+country=[JP] — 34.8%
+country=[] — 7.0%
+country=[UK] — 1.6%
+country=[ES] — 1.6%
+country=[CA] — 1.6%
+country=[BR] — 1.4%
+country=[DE] — 1.0%</t>
+        </is>
+      </c>
+      <c r="G768" s="5" t="inlineStr">
+        <is>
+          <t>观察项：同AudienceList，{Data,PageInfo,CustomData}分页直出无成功标志字段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="769" ht="32" customHeight="1">
       <c r="A769" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26103,10 +26128,15 @@
         </is>
       </c>
       <c r="E769" s="3" t="n"/>
-      <c r="F769" s="3" t="n"/>
+      <c r="F769" s="6" t="inlineStr">
+        <is>
+          <t>含category — 91.4%
+不含category — 8.6%</t>
+        </is>
+      </c>
       <c r="G769" s="3" t="n"/>
     </row>
-    <row r="770">
+    <row r="770" ht="16" customHeight="1">
       <c r="A770" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26128,10 +26158,14 @@
         </is>
       </c>
       <c r="E770" s="3" t="n"/>
-      <c r="F770" s="3" t="n"/>
+      <c r="F770" s="6" t="inlineStr">
+        <is>
+          <t>查询全部DealExchange列表 — 100.0%</t>
+        </is>
+      </c>
       <c r="G770" s="3" t="n"/>
     </row>
-    <row r="771">
+    <row r="771" ht="64" customHeight="1">
       <c r="A771" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26153,10 +26187,21 @@
         </is>
       </c>
       <c r="E771" s="3" t="n"/>
-      <c r="F771" s="3" t="n"/>
-      <c r="G771" s="3" t="n"/>
-    </row>
-    <row r="772">
+      <c r="F771" s="6" t="inlineStr">
+        <is>
+          <t>inventoryTypeFilter=[DISPLAY,UNKNOWN]+不含lineItemType — 73.6%
+inventoryTypeFilter=[UNKNOWN,VIDEO]+含lineItemType — 13.6%
+inventoryTypeFilter=[DISPLAY,UNKNOWN]+含lineItemType — 8.6%
+inventoryTypeFilter=[UNKNOWN,VIDEO]+不含lineItemType — 4.2%</t>
+        </is>
+      </c>
+      <c r="G771" s="5" t="inlineStr">
+        <is>
+          <t>观察项：dealDateRangeFilter.startDate/endDate对格式敏感，必须完整ISO8601日期时间(含时间和Z)，传纯日期会被下游Amazon接口判400"filter value"但外层HTTP仍200，前端如只拼日期没拼时间会静默失败。config.json已新增date_start_iso/date_end_iso修正。</t>
+        </is>
+      </c>
+    </row>
+    <row r="772" ht="48" customHeight="1">
       <c r="A772" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26178,10 +26223,16 @@
         </is>
       </c>
       <c r="E772" s="3" t="n"/>
-      <c r="F772" s="3" t="n"/>
+      <c r="F772" s="6" t="inlineStr">
+        <is>
+          <t>lineItemType=DISPLAY — 79.2%
+lineItemType=STREAMING TV — 16.7%
+lineItemType=ONLINE VIDEO — 4.2%</t>
+        </is>
+      </c>
       <c r="G772" s="3" t="n"/>
     </row>
-    <row r="773">
+    <row r="773" ht="32" customHeight="1">
       <c r="A773" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26203,10 +26254,19 @@
         </is>
       </c>
       <c r="E773" s="3" t="n"/>
-      <c r="F773" s="3" t="n"/>
-      <c r="G773" s="3" t="n"/>
-    </row>
-    <row r="774">
+      <c r="F773" s="6" t="inlineStr">
+        <is>
+          <t>status=[Active] — 82.4%
+status=[] — 16.4%</t>
+        </is>
+      </c>
+      <c r="G773" s="5" t="inlineStr">
+        <is>
+          <t>观察项：本接口响应包装为{Data,PageInfo,CustomData}分页直出，完全没有IsSuccessStatusCode/code等成功标志字段，与tag内其余多数接口(代理包装)不一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="774" ht="16" customHeight="1">
       <c r="A774" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26228,10 +26288,14 @@
         </is>
       </c>
       <c r="E774" s="3" t="n"/>
-      <c r="F774" s="3" t="n"/>
+      <c r="F774" s="6" t="inlineStr">
+        <is>
+          <t>查询受众选择树(排除Contextual) — 100.0%</t>
+        </is>
+      </c>
       <c r="G774" s="3" t="n"/>
     </row>
-    <row r="775">
+    <row r="775" ht="16" customHeight="1">
       <c r="A775" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26253,10 +26317,14 @@
         </is>
       </c>
       <c r="E775" s="3" t="n"/>
-      <c r="F775" s="3" t="n"/>
+      <c r="F775" s="6" t="inlineStr">
+        <is>
+          <t>查询受众分类法清单 — 100.0%</t>
+        </is>
+      </c>
       <c r="G775" s="3" t="n"/>
     </row>
-    <row r="776">
+    <row r="776" ht="32" customHeight="1">
       <c r="A776" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26278,7 +26346,12 @@
         </is>
       </c>
       <c r="E776" s="3" t="n"/>
-      <c r="F776" s="3" t="n"/>
+      <c r="F776" s="6" t="inlineStr">
+        <is>
+          <t>inventoryGroupIds=[ids+] — 97.7%
+inventoryGroupIds=[] — 2.3%</t>
+        </is>
+      </c>
       <c r="G776" s="3" t="n"/>
     </row>
     <row r="777">
@@ -26303,10 +26376,18 @@
         </is>
       </c>
       <c r="E777" s="3" t="n"/>
-      <c r="F777" s="3" t="n"/>
-      <c r="G777" s="3" t="n"/>
-    </row>
-    <row r="778">
+      <c r="F777" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G777" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="778" ht="208" customHeight="1">
       <c r="A778" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26328,10 +26409,30 @@
         </is>
       </c>
       <c r="E778" s="3" t="n"/>
-      <c r="F778" s="3" t="n"/>
-      <c r="G778" s="3" t="n"/>
-    </row>
-    <row r="779">
+      <c r="F778" s="6" t="inlineStr">
+        <is>
+          <t>排除第三方受众(NOT EQ Third-party) — 60.0%
+自定义受众(EQ Custom-built) — 11.8%
+In-market受众(EQ In-market) — 7.1%
+人口统计受众(EQ Demographic) — 4.7%
+Lookalike相似受众(EQ Lookalike) — 3.5%
+Device设备受众(EQ Device) — 3.5%
+仅第三方受众(EQ Third-party) — 2.4%
+旧版扁平结构(不含body包装,直传profile级筛选) — 1.2%
+兴趣受众(EQ Interest) — 1.2%
+生活方式受众(EQ Lifestyle) — 1.2%
+分类过滤 EQ ['Custom-built', 'Demographic', 'Device', 'In-market', 'Interest', 'Life event', 'Lifestyle', 'Lookalike'] — 1.2%
+分类过滤 EQ ['Interest', 'Life event'] — 1.2%
+分类过滤 EQ ['Life event'] — 1.2%</t>
+        </is>
+      </c>
+      <c r="G778" s="5" t="inlineStr">
+        <is>
+          <t>观察项：同AudienceList，{Data,PageInfo,CustomData}分页直出无成功标志字段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="779" ht="16" customHeight="1">
       <c r="A779" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26353,10 +26454,14 @@
         </is>
       </c>
       <c r="E779" s="3" t="n"/>
-      <c r="F779" s="3" t="n"/>
+      <c r="F779" s="6" t="inlineStr">
+        <is>
+          <t>查询Domain清单 — 100.0%</t>
+        </is>
+      </c>
       <c r="G779" s="3" t="n"/>
     </row>
-    <row r="780">
+    <row r="780" ht="16" customHeight="1">
       <c r="A780" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26378,10 +26483,14 @@
         </is>
       </c>
       <c r="E780" s="3" t="n"/>
-      <c r="F780" s="3" t="n"/>
+      <c r="F780" s="6" t="inlineStr">
+        <is>
+          <t>关键字模糊搜索地理位置 — 100.0%</t>
+        </is>
+      </c>
       <c r="G780" s="3" t="n"/>
     </row>
-    <row r="781">
+    <row r="781" ht="32" customHeight="1">
       <c r="A781" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26403,10 +26512,19 @@
         </is>
       </c>
       <c r="E781" s="3" t="n"/>
-      <c r="F781" s="3" t="n"/>
-      <c r="G781" s="3" t="n"/>
-    </row>
-    <row r="782">
+      <c r="F781" s="6" t="inlineStr">
+        <is>
+          <t>不含advertiserId — 97.2%
+含advertiserId — 2.8%</t>
+        </is>
+      </c>
+      <c r="G781" s="5" t="inlineStr">
+        <is>
+          <t>观察项：即使调用成功，Data.successLocations/Data.failedCodes也可能同时为null(真实美国邮编98201实测如此)，成功不等于查到地理位置，断言不能假设成功必返回数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="782" ht="16" customHeight="1">
       <c r="A782" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26428,10 +26546,14 @@
         </is>
       </c>
       <c r="E782" s="3" t="n"/>
-      <c r="F782" s="3" t="n"/>
+      <c r="F782" s="6" t="inlineStr">
+        <is>
+          <t>查询IAB兴趣分类清单 — 100.0%</t>
+        </is>
+      </c>
       <c r="G782" s="3" t="n"/>
     </row>
-    <row r="783">
+    <row r="783" ht="48" customHeight="1">
       <c r="A783" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26453,10 +26575,20 @@
         </is>
       </c>
       <c r="E783" s="3" t="n"/>
-      <c r="F783" s="3" t="n"/>
-      <c r="G783" s="3" t="n"/>
-    </row>
-    <row r="784">
+      <c r="F783" s="6" t="inlineStr">
+        <is>
+          <t>不含dealName+不含profileIds — 87.5%
+含dealName+不含profileIds — 10.0%
+不含dealName+含profileIds — 2.5%</t>
+        </is>
+      </c>
+      <c r="G783" s="5" t="inlineStr">
+        <is>
+          <t>观察项：同AudienceList，{Data,PageInfo,CustomData}分页直出无成功标志字段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="784" ht="64" customHeight="1">
       <c r="A784" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26478,7 +26610,14 @@
         </is>
       </c>
       <c r="E784" s="3" t="n"/>
-      <c r="F784" s="3" t="n"/>
+      <c r="F784" s="6" t="inlineStr">
+        <is>
+          <t>lineItemType=DISPLAY — 84.2%
+lineItemType=ONLINE VIDEO — 7.4%
+lineItemType=STREAMING TV — 5.4%
+lineItemType=LIVE EVENTS — 2.8%</t>
+        </is>
+      </c>
       <c r="G784" s="3" t="n"/>
     </row>
     <row r="785">
@@ -26503,8 +26642,16 @@
         </is>
       </c>
       <c r="E785" s="3" t="n"/>
-      <c r="F785" s="3" t="n"/>
-      <c r="G785" s="3" t="n"/>
+      <c r="F785" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G785" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1158,9 +1158,19 @@
       </c>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="F24" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%(10/10执行,4条因缺真实分组ID仅生成不执行不计入)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>35% (6/17)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -18437,10 +18447,18 @@
         </is>
       </c>
       <c r="E516" s="3" t="n"/>
-      <c r="F516" s="3" t="n"/>
-      <c r="G516" s="3" t="n"/>
-    </row>
-    <row r="517">
+      <c r="F516" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G516" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="517" ht="32" customHeight="1">
       <c r="A517" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18462,10 +18480,19 @@
         </is>
       </c>
       <c r="E517" s="3" t="n"/>
-      <c r="F517" s="3" t="n"/>
-      <c r="G517" s="3" t="n"/>
-    </row>
-    <row r="518">
+      <c r="F517" s="6" t="inlineStr">
+        <is>
+          <t>单个profileId查询 — 27%
+批量profileId查询 — 73%</t>
+        </is>
+      </c>
+      <c r="G517" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug(响应假成功)：本接口生产环境100%由内部系统调用(非用户页面操作)，外部标准Bearer token调用时始终返回code:200/success:true，但data/msg字段里藏着"No validation header present"，说明有未在Swagger声明的隐藏header校验，外部调用永远无法真正生效却被伪装成功，具有较强误导性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="518" ht="16" customHeight="1">
       <c r="A518" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18487,7 +18514,11 @@
         </is>
       </c>
       <c r="E518" s="3" t="n"/>
-      <c r="F518" s="3" t="n"/>
+      <c r="F518" s="6" t="inlineStr">
+        <is>
+          <t>查询预算告警设置</t>
+        </is>
+      </c>
       <c r="G518" s="3" t="n"/>
     </row>
     <row r="519">
@@ -18512,8 +18543,16 @@
         </is>
       </c>
       <c r="E519" s="3" t="n"/>
-      <c r="F519" s="3" t="n"/>
-      <c r="G519" s="3" t="n"/>
+      <c r="F519" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G519" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -18537,8 +18576,16 @@
         </is>
       </c>
       <c r="E520" s="3" t="n"/>
-      <c r="F520" s="3" t="n"/>
-      <c r="G520" s="3" t="n"/>
+      <c r="F520" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G520" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
@@ -18562,10 +18609,18 @@
         </is>
       </c>
       <c r="E521" s="3" t="n"/>
-      <c r="F521" s="3" t="n"/>
-      <c r="G521" s="3" t="n"/>
-    </row>
-    <row r="522">
+      <c r="F521" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G521" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="522" ht="80" customHeight="1">
       <c r="A522" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18587,10 +18642,18 @@
         </is>
       </c>
       <c r="E522" s="3" t="n"/>
-      <c r="F522" s="3" t="n"/>
+      <c r="F522" s="6" t="inlineStr">
+        <is>
+          <t>profiles为空 — 7%
+budgetMode=Profile — 17%
+budgetMode=SubTag — 25.4%
+budgetMode=Tag — 10.8%
+Profile+SubTag混合 — 27.2%</t>
+        </is>
+      </c>
       <c r="G522" s="3" t="n"/>
     </row>
-    <row r="523">
+    <row r="523" ht="16" customHeight="1">
       <c r="A523" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18612,8 +18675,16 @@
         </is>
       </c>
       <c r="E523" s="3" t="n"/>
-      <c r="F523" s="3" t="n"/>
-      <c r="G523" s="3" t="n"/>
+      <c r="F523" s="6" t="inlineStr">
+        <is>
+          <t>查询Budget Manager可用Profile列表 — 100%</t>
+        </is>
+      </c>
+      <c r="G523" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-17记录的"100%空body"已过时：账号分配profile 1251036855266063/advertiser 578107614358724215后重新探测，稳定返回真实非空数据，当时是账号无实体所致非接口问题。</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -18637,8 +18708,16 @@
         </is>
       </c>
       <c r="E524" s="3" t="n"/>
-      <c r="F524" s="3" t="n"/>
-      <c r="G524" s="3" t="n"/>
+      <c r="F524" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G524" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
@@ -18662,8 +18741,16 @@
         </is>
       </c>
       <c r="E525" s="3" t="n"/>
-      <c r="F525" s="3" t="n"/>
-      <c r="G525" s="3" t="n"/>
+      <c r="F525" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G525" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -18687,8 +18774,16 @@
         </is>
       </c>
       <c r="E526" s="3" t="n"/>
-      <c r="F526" s="3" t="n"/>
-      <c r="G526" s="3" t="n"/>
+      <c r="F526" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G526" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
@@ -18712,8 +18807,16 @@
         </is>
       </c>
       <c r="E527" s="3" t="n"/>
-      <c r="F527" s="3" t="n"/>
-      <c r="G527" s="3" t="n"/>
+      <c r="F527" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G527" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -18737,10 +18840,18 @@
         </is>
       </c>
       <c r="E528" s="3" t="n"/>
-      <c r="F528" s="3" t="n"/>
-      <c r="G528" s="3" t="n"/>
-    </row>
-    <row r="529">
+      <c r="F528" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G528" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="529" ht="32" customHeight="1">
       <c r="A529" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18762,8 +18873,17 @@
         </is>
       </c>
       <c r="E529" s="3" t="n"/>
-      <c r="F529" s="3" t="n"/>
-      <c r="G529" s="3" t="n"/>
+      <c r="F529" s="6" t="inlineStr">
+        <is>
+          <t>budgetLevel=SubTag【技术受限-仅生成不执行】 — 65.8%
+budgetLevel=Tag【技术受限-仅生成不执行】 — 34.2%</t>
+        </is>
+      </c>
+      <c r="G529" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug(响应假成功)：本接口生产环境100%由内部系统调用(非用户页面操作)，外部标准Bearer token调用时始终返回code:200/success:true，但data/msg字段里藏着"No validation header present"，说明有未在Swagger声明的隐藏header校验，外部调用永远无法真正生效却被伪装成功，具有较强误导性。另有2个高频真实场景(SubTag 65.8%/Tag 34.2%)因缺真实分组ID+同样会撞上此假成功问题，仅生成不执行。</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
@@ -18787,10 +18907,18 @@
         </is>
       </c>
       <c r="E530" s="3" t="n"/>
-      <c r="F530" s="3" t="n"/>
-      <c r="G530" s="3" t="n"/>
-    </row>
-    <row r="531">
+      <c r="F530" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G530" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="531" ht="48" customHeight="1">
       <c r="A531" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18812,8 +18940,18 @@
         </is>
       </c>
       <c r="E531" s="3" t="n"/>
-      <c r="F531" s="3" t="n"/>
-      <c r="G531" s="3" t="n"/>
+      <c r="F531" s="6" t="inlineStr">
+        <is>
+          <t>budgetLevel=Profile切换deliveryActivationStatus(含前置建单+后置归档)【真实后端bug:响应假成功】 — 11.5%
+budgetLevel=SubTag【技术受限-仅生成不执行】 — 78.8%
+budgetLevel=Tag【技术受限-仅生成不执行】 — 9.7%</t>
+        </is>
+      </c>
+      <c r="G531" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug(响应假成功)：本接口生产环境100%由内部系统调用(非用户页面操作)，外部标准Bearer token调用时始终返回code:200/success:true，但data/msg字段里藏着"No validation header present"，说明有未在Swagger声明的隐藏header校验，外部调用永远无法真正生效却被伪装成功，具有较强误导性。另有2个高频真实场景(SubTag 78.8%/Tag 9.7%)因缺真实分组ID+同样会撞上此假成功问题，仅生成不执行。</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -18837,8 +18975,16 @@
         </is>
       </c>
       <c r="E532" s="3" t="n"/>
-      <c r="F532" s="3" t="n"/>
-      <c r="G532" s="3" t="n"/>
+      <c r="F532" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G532" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -728,9 +728,19 @@
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
+      <c r="F9" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>97%(31/32执行,7条高危仅生成不执行不计入)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>76% (13/17)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5943,7 +5953,7 @@
       <c r="F103" s="3" t="n"/>
       <c r="G103" s="3" t="n"/>
     </row>
-    <row r="104">
+    <row r="104" ht="144" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5965,7 +5975,19 @@
         </is>
       </c>
       <c r="E104" s="3" t="n"/>
-      <c r="F104" s="3" t="n"/>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>默认查询-不加任何过滤(仅分页) — 61.0%
+按audienceName关键词搜索 — 13.6%
+按instanceIds(AMC实例)过滤 — 5.8%
+按advertiserIds(DSP广告主)过滤 — 3.8%
+分页-第2页 — 1.6%
+按strategy(受众策略类型)过滤 — 1.4%
+audienceName+instanceIds组合过滤 — 1.4%
+advertiserIds+audienceName组合过滤 — 1.4%
+advertiserIds+instanceIds组合过滤 — 1.0%</t>
+        </is>
+      </c>
       <c r="G104" s="3" t="n"/>
     </row>
     <row r="105">
@@ -5990,10 +6012,18 @@
         </is>
       </c>
       <c r="E105" s="3" t="n"/>
-      <c r="F105" s="3" t="n"/>
-      <c r="G105" s="3" t="n"/>
-    </row>
-    <row r="106">
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="32" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6015,10 +6045,19 @@
         </is>
       </c>
       <c r="E106" s="3" t="n"/>
-      <c r="F106" s="3" t="n"/>
-      <c r="G106" s="3" t="n"/>
-    </row>
-    <row r="107">
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>Ads and 1P策略(占比最高28.0%)
+Cart abandoners策略(占比18.8%)</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认-高危：涉及向Amazon真实提交AMC受众计算(创建/编辑/扩展本质相同)，任务书已点名需先确认。账号内现存10条真实audience实体均是2026-09-21~22系统自动/疑似同事手工产生(归属不明确)，未创建可安全操作的自建实体。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="16" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6040,10 +6079,18 @@
         </is>
       </c>
       <c r="E107" s="3" t="n"/>
-      <c r="F107" s="3" t="n"/>
-      <c r="G107" s="3" t="n"/>
-    </row>
-    <row r="108">
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>按id删除</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认：账号内现存10条audience归属不明确(疑似他人测试数据)且CreateAudience未执行导致无自建可安全删除实体，删除会污染共享沙盒账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6065,10 +6112,14 @@
         </is>
       </c>
       <c r="E108" s="3" t="n"/>
-      <c r="F108" s="3" t="n"/>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>按id查询本账号真实受众</t>
+        </is>
+      </c>
       <c r="G108" s="3" t="n"/>
     </row>
-    <row r="109">
+    <row r="109" ht="256" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6090,10 +6141,29 @@
         </is>
       </c>
       <c r="E109" s="3" t="n"/>
-      <c r="F109" s="3" t="n"/>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>默认导出-不加过滤(pageSize10) — 29.4%
+按advertiserIds过滤导出 — 13.0%
+按audienceName搜索导出 — 7.3%
+advertiserIds+audienceName组合导出 — 6.8%
+audienceName+status组合导出 — 6.2%
+默认导出(pageSize100) — 5.6%
+advertiserIds+status组合导出 — 5.1%
+按status过滤导出 — 4.0%
+默认导出(pageSize50) — 2.8%
+advertiserIds+status导出(pageSize100) — 2.8%
+按audienceName搜索导出(pageSize100) — 1.7%
+按advertiserIds导出(pageSize100) — 1.7%
+按instanceIds过滤导出 — 1.7%
+channels+instanceIds组合导出 — 1.1%
+advertiserIds+audienceName+status组合导出(pageSize100) — 1.1%
+按advertiserIds导出(pageSize50) — 1.1%</t>
+        </is>
+      </c>
       <c r="G109" s="3" t="n"/>
     </row>
-    <row r="110">
+    <row r="110" ht="16" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6115,8 +6185,16 @@
         </is>
       </c>
       <c r="E110" s="3" t="n"/>
-      <c r="F110" s="3" t="n"/>
-      <c r="G110" s="3" t="n"/>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>MOST SIMILAR(占比最高77.9%)</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认-高危：涉及向Amazon真实提交AMC受众计算(创建/编辑/扩展本质相同)，任务书已点名需先确认。账号内现存10条真实audience实体均是2026-09-21~22系统自动/疑似同事手工产生(归属不明确)，未创建可安全操作的自建实体。(扩展本质是创建新Lookalike受众)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6140,10 +6218,18 @@
         </is>
       </c>
       <c r="E111" s="3" t="n"/>
-      <c r="F111" s="3" t="n"/>
-      <c r="G111" s="3" t="n"/>
-    </row>
-    <row r="112">
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="32" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6165,10 +6251,15 @@
         </is>
       </c>
       <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n"/>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>DISPLAY+SPONSORED ADS(混合类型) — 55.2%
+仅DISPLAY类型 — 44.8%</t>
+        </is>
+      </c>
       <c r="G112" s="3" t="n"/>
     </row>
-    <row r="113">
+    <row r="113" ht="16" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6190,10 +6281,14 @@
         </is>
       </c>
       <c r="E113" s="3" t="n"/>
-      <c r="F113" s="3" t="n"/>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100%</t>
+        </is>
+      </c>
       <c r="G113" s="3" t="n"/>
     </row>
-    <row r="114">
+    <row r="114" ht="16" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6215,7 +6310,11 @@
         </is>
       </c>
       <c r="E114" s="3" t="n"/>
-      <c r="F114" s="3" t="n"/>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100%</t>
+        </is>
+      </c>
       <c r="G114" s="3" t="n"/>
     </row>
     <row r="115">
@@ -6240,10 +6339,18 @@
         </is>
       </c>
       <c r="E115" s="3" t="n"/>
-      <c r="F115" s="3" t="n"/>
-      <c r="G115" s="3" t="n"/>
-    </row>
-    <row r="116">
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="16" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6265,10 +6372,18 @@
         </is>
       </c>
       <c r="E116" s="3" t="n"/>
-      <c r="F116" s="3" t="n"/>
-      <c r="G116" s="3" t="n"/>
-    </row>
-    <row r="117">
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>percentage=80(占比最高20.8%)</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认-双重原因：绑定真实SA广告活动定向投放(高危)+账号无真实ams_campaign_id/profileId归属数据([NEEDS_REAL_VALUE])。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="16" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6290,10 +6405,14 @@
         </is>
       </c>
       <c r="E117" s="3" t="n"/>
-      <c r="F117" s="3" t="n"/>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>默认调用 — 100%</t>
+        </is>
+      </c>
       <c r="G117" s="3" t="n"/>
     </row>
-    <row r="118">
+    <row r="118" ht="16" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6315,10 +6434,18 @@
         </is>
       </c>
       <c r="E118" s="3" t="n"/>
-      <c r="F118" s="3" t="n"/>
-      <c r="G118" s="3" t="n"/>
-    </row>
-    <row r="119">
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>同步本账号真实受众状态(仅执行1次) — 100%</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>观察项(未坐实为bug)：命名是写操作，实际语义是从Amazon拉取真实状态的只读性质刷新，按规则只执行1次不跑第2轮。本次执行返回IsSuccessStatusCode:false，用只读Detail复查确认该audience状态未被污染(仍FAILED，无副作用)，可能是"对已终态FAILED的audience同步无意义"的合理业务拒绝，也可能是真实缺陷，需人工进一步确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="32" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6340,8 +6467,17 @@
         </is>
       </c>
       <c r="E119" s="3" t="n"/>
-      <c r="F119" s="3" t="n"/>
-      <c r="G119" s="3" t="n"/>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>Ads and 1P策略(占比最高23.9%)
+CustomSql策略(占比15.9%)</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认-高危：涉及向Amazon真实提交AMC受众计算(创建/编辑/扩展本质相同)，任务书已点名需先确认。账号内现存10条真实audience实体均是2026-09-21~22系统自动/疑似同事手工产生(归属不明确)，未创建可安全操作的自建实体。</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -6365,8 +6501,16 @@
         </is>
       </c>
       <c r="E120" s="3" t="n"/>
-      <c r="F120" s="3" t="n"/>
-      <c r="G120" s="3" t="n"/>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="16" customHeight="1">
       <c r="A121" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -2082,9 +2082,19 @@
       </c>
       <c r="D56" s="3" t="n"/>
       <c r="E56" s="3" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
+      <c r="F56" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>55% (12/22)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -39603,7 +39613,7 @@
       <c r="F1193" s="3" t="n"/>
       <c r="G1193" s="3" t="n"/>
     </row>
-    <row r="1194">
+    <row r="1194" ht="64" customHeight="1">
       <c r="A1194" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -39625,7 +39635,14 @@
         </is>
       </c>
       <c r="E1194" s="3" t="n"/>
-      <c r="F1194" s="3" t="n"/>
+      <c r="F1194" s="6" t="inlineStr">
+        <is>
+          <t>Promoted+ASIN level+Child products(主流程) — 92.4%
+Brand halo+ASIN level — 3.4%
+Parent ASIN level+Parent products — 2.0%
+conversionType为空(未选择转化类型) — 1.2%</t>
+        </is>
+      </c>
       <c r="G1194" s="3" t="n"/>
     </row>
     <row r="1195">
@@ -39650,10 +39667,18 @@
         </is>
       </c>
       <c r="E1195" s="3" t="n"/>
-      <c r="F1195" s="3" t="n"/>
-      <c r="G1195" s="3" t="n"/>
-    </row>
-    <row r="1196">
+      <c r="F1195" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1195" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196" ht="16" customHeight="1">
       <c r="A1196" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -39675,8 +39700,16 @@
         </is>
       </c>
       <c r="E1196" s="3" t="n"/>
-      <c r="F1196" s="3" t="n"/>
-      <c r="G1196" s="3" t="n"/>
+      <c r="F1196" s="6" t="inlineStr">
+        <is>
+          <t>批量添加Product Tag(含前置/后置清理,可重复) — 92.2%</t>
+        </is>
+      </c>
+      <c r="G1196" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug(静默失效)：bulkType=add给产品打真实存在的tagId后接口返回code:200(表面成功)，但GetTagsByProductIds验证该产品tag列表仍为空数组，实际未生效。两轮稳定复现。</t>
+        </is>
+      </c>
     </row>
     <row r="1197">
       <c r="A1197" s="2" t="inlineStr">
@@ -39700,8 +39733,16 @@
         </is>
       </c>
       <c r="E1197" s="3" t="n"/>
-      <c r="F1197" s="3" t="n"/>
-      <c r="G1197" s="3" t="n"/>
+      <c r="F1197" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1197" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1198">
       <c r="A1198" s="2" t="inlineStr">
@@ -39725,10 +39766,18 @@
         </is>
       </c>
       <c r="E1198" s="3" t="n"/>
-      <c r="F1198" s="3" t="n"/>
-      <c r="G1198" s="3" t="n"/>
-    </row>
-    <row r="1199">
+      <c r="F1198" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1198" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199" ht="16" customHeight="1">
       <c r="A1199" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -39750,10 +39799,14 @@
         </is>
       </c>
       <c r="E1199" s="3" t="n"/>
-      <c r="F1199" s="3" t="n"/>
+      <c r="F1199" s="6" t="inlineStr">
+        <is>
+          <t>默认分页浏览(不带搜索词) — 99.5%</t>
+        </is>
+      </c>
       <c r="G1199" s="3" t="n"/>
     </row>
-    <row r="1200">
+    <row r="1200" ht="112" customHeight="1">
       <c r="A1200" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -39775,7 +39828,17 @@
         </is>
       </c>
       <c r="E1200" s="3" t="n"/>
-      <c r="F1200" s="3" t="n"/>
+      <c r="F1200" s="6" t="inlineStr">
+        <is>
+          <t>单关键词+US — 66.0%
+批量关键词+US — 11.2%
+批量关键词+MX — 11.0%
+单关键词+JP — 3.8%
+单关键词+MX — 3.0%
+批量关键词+JP — 1.8%
+countryCode为空 — 1.0%</t>
+        </is>
+      </c>
       <c r="G1200" s="3" t="n"/>
     </row>
     <row r="1201">
@@ -39800,8 +39863,16 @@
         </is>
       </c>
       <c r="E1201" s="3" t="n"/>
-      <c r="F1201" s="3" t="n"/>
-      <c r="G1201" s="3" t="n"/>
+      <c r="F1201" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1201" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1202">
       <c r="A1202" s="2" t="inlineStr">
@@ -39825,10 +39896,18 @@
         </is>
       </c>
       <c r="E1202" s="3" t="n"/>
-      <c r="F1202" s="3" t="n"/>
-      <c r="G1202" s="3" t="n"/>
-    </row>
-    <row r="1203">
+      <c r="F1202" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1202" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203" ht="48" customHeight="1">
       <c r="A1203" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -39850,10 +39929,20 @@
         </is>
       </c>
       <c r="E1203" s="3" t="n"/>
-      <c r="F1203" s="3" t="n"/>
-      <c r="G1203" s="3" t="n"/>
-    </row>
-    <row r="1204">
+      <c r="F1203" s="6" t="inlineStr">
+        <is>
+          <t>US市场 — 92.2%
+MX市场 — 2.6%
+JP市场 — 1.2%</t>
+        </is>
+      </c>
+      <c r="G1203" s="5" t="inlineStr">
+        <is>
+          <t>观察项：MX/JP场景账号暂无对应ASIN目录数据(data为null)已如实断言L1；另有约1.8%真实流量四个核心字段全为空串会触发400(date字段空串无法转DateTime)，疑似前端在上下文未加载完成时的竞态请求，未纳入case(run-cases.py对HTTP≥400无条件判FAIL)，建议前端排查。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204" ht="96" customHeight="1">
       <c r="A1204" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -39875,7 +39964,16 @@
         </is>
       </c>
       <c r="E1204" s="3" t="n"/>
-      <c r="F1204" s="3" t="n"/>
+      <c r="F1204" s="6" t="inlineStr">
+        <is>
+          <t>单关键词+US — 67.8%
+批量关键词+MX — 11.4%
+批量关键词+US — 10.0%
+单关键词+JP — 3.6%
+单关键词+MX — 2.6%
+批量关键词+JP — 2.0%</t>
+        </is>
+      </c>
       <c r="G1204" s="3" t="n"/>
     </row>
     <row r="1205">
@@ -39900,10 +39998,18 @@
         </is>
       </c>
       <c r="E1205" s="3" t="n"/>
-      <c r="F1205" s="3" t="n"/>
-      <c r="G1205" s="3" t="n"/>
-    </row>
-    <row r="1206">
+      <c r="F1205" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1205" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206" ht="32" customHeight="1">
       <c r="A1206" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -39925,8 +40031,17 @@
         </is>
       </c>
       <c r="E1206" s="3" t="n"/>
-      <c r="F1206" s="3" t="n"/>
-      <c r="G1206" s="3" t="n"/>
+      <c r="F1206" s="6" t="inlineStr">
+        <is>
+          <t>指定productIds查询tag — 70.7%
+全选(按分组条件selectedAllQuery)查询tag — 29.3%</t>
+        </is>
+      </c>
+      <c r="G1206" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug(信息泄露+未优雅降级)：全选模式(selectedAllQuery，占真实流量约29.3%)查无数据时抛未处理.NET异常，完整服务端堆栈(含内部文件路径)原样返回客户端，HttpStatusCode:513，应改为返回空结果而非抛异常。</t>
+        </is>
+      </c>
     </row>
     <row r="1207">
       <c r="A1207" s="2" t="inlineStr">
@@ -39950,10 +40065,18 @@
         </is>
       </c>
       <c r="E1207" s="3" t="n"/>
-      <c r="F1207" s="3" t="n"/>
-      <c r="G1207" s="3" t="n"/>
-    </row>
-    <row r="1208">
+      <c r="F1207" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1207" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208" ht="64" customHeight="1">
       <c r="A1208" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -39975,10 +40098,17 @@
         </is>
       </c>
       <c r="E1208" s="3" t="n"/>
-      <c r="F1208" s="3" t="n"/>
+      <c r="F1208" s="6" t="inlineStr">
+        <is>
+          <t>Promoted+ASIN level+指定LineItem — 91.0%
+Brand halo+ASIN level — 5.2%
+Parent ASIN level+Parent products — 1.4%
+lineItemIds为空(查看全部LineItem) — 1.0%</t>
+        </is>
+      </c>
       <c r="G1208" s="3" t="n"/>
     </row>
-    <row r="1209">
+    <row r="1209" ht="48" customHeight="1">
       <c r="A1209" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -40000,10 +40130,16 @@
         </is>
       </c>
       <c r="E1209" s="3" t="n"/>
-      <c r="F1209" s="3" t="n"/>
+      <c r="F1209" s="6" t="inlineStr">
+        <is>
+          <t>Promoted+ASIN level — 92.8%
+Brand halo+ASIN level — 4.6%
+Parent ASIN level+Parent products — 1.2%</t>
+        </is>
+      </c>
       <c r="G1209" s="3" t="n"/>
     </row>
-    <row r="1210">
+    <row r="1210" ht="64" customHeight="1">
       <c r="A1210" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -40025,7 +40161,14 @@
         </is>
       </c>
       <c r="E1210" s="3" t="n"/>
-      <c r="F1210" s="3" t="n"/>
+      <c r="F1210" s="6" t="inlineStr">
+        <is>
+          <t>Promoted+ASIN level+Child products — 92.8%
+Brand halo+ASIN level — 3.8%
+Parent ASIN level+Parent products — 1.2%
+conversionType为空 — 1.2%</t>
+        </is>
+      </c>
       <c r="G1210" s="3" t="n"/>
     </row>
     <row r="1211">
@@ -40050,10 +40193,18 @@
         </is>
       </c>
       <c r="E1211" s="3" t="n"/>
-      <c r="F1211" s="3" t="n"/>
-      <c r="G1211" s="3" t="n"/>
-    </row>
-    <row r="1212">
+      <c r="F1211" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1211" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212" ht="48" customHeight="1">
       <c r="A1212" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -40075,10 +40226,16 @@
         </is>
       </c>
       <c r="E1212" s="3" t="n"/>
-      <c r="F1212" s="3" t="n"/>
+      <c r="F1212" s="6" t="inlineStr">
+        <is>
+          <t>Promoted+ASIN level+Child products — 93.6%
+Brand halo+ASIN level — 4.4%
+Parent ASIN level+Parent products — 1.6%</t>
+        </is>
+      </c>
       <c r="G1212" s="3" t="n"/>
     </row>
-    <row r="1213">
+    <row r="1213" ht="64" customHeight="1">
       <c r="A1213" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -40100,7 +40257,14 @@
         </is>
       </c>
       <c r="E1213" s="3" t="n"/>
-      <c r="F1213" s="3" t="n"/>
+      <c r="F1213" s="6" t="inlineStr">
+        <is>
+          <t>Promoted+ASIN level+Child products — 91.2%
+Brand halo+ASIN level — 4.6%
+Parent ASIN level+Parent products — 1.8%
+conversionType为空 — 1.2%</t>
+        </is>
+      </c>
       <c r="G1213" s="3" t="n"/>
     </row>
     <row r="1214">
@@ -40125,8 +40289,16 @@
         </is>
       </c>
       <c r="E1214" s="3" t="n"/>
-      <c r="F1214" s="3" t="n"/>
-      <c r="G1214" s="3" t="n"/>
+      <c r="F1214" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1214" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1215">
       <c r="A1215" s="2" t="inlineStr">
@@ -40150,8 +40322,16 @@
         </is>
       </c>
       <c r="E1215" s="3" t="n"/>
-      <c r="F1215" s="3" t="n"/>
-      <c r="G1215" s="3" t="n"/>
+      <c r="F1215" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1215" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1216">
       <c r="A1216" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -652,9 +652,19 @@
       </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="F6" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>96%(22/23执行,6条因Create阻断问题仅生成不执行不计入)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>94% (15/16)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -5048,7 +5058,7 @@
       <c r="F68" s="3" t="n"/>
       <c r="G68" s="3" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="16" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5070,10 +5080,18 @@
         </is>
       </c>
       <c r="E69" s="3" t="n"/>
-      <c r="F69" s="3" t="n"/>
-      <c r="G69" s="3" t="n"/>
-    </row>
-    <row r="70">
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>批量删除AI【技术受限-未执行】 — 100%</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-受阻：因Create被上述阻断性bug卡住，无法获得可安全操作的自建AI实体id；直接对ES中他人真实AI记录做状态/目标/删除操作会影响真实客户配置，故仅生成case结构，待bug修复或有专用无AI测试Order后补执行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5095,10 +5113,19 @@
         </is>
       </c>
       <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n"/>
-      <c r="G70" s="3" t="n"/>
-    </row>
-    <row r="71">
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>批量置Paused【技术受限-未执行】 — 81.6%
+批量置Enabled【技术受限-未执行】 — 18.4%</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-受阻：因Create被上述阻断性bug卡住，无法获得可安全操作的自建AI实体id；直接对ES中他人真实AI记录做状态/目标/删除操作会影响真实客户配置，故仅生成case结构，待bug修复或有专用无AI测试Order后补执行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="32" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5120,10 +5147,19 @@
         </is>
       </c>
       <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="n"/>
-      <c r="G71" s="3" t="n"/>
-    </row>
-    <row r="72">
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>批量修改目标(Consideration/DPVR)【技术受限-未执行】 — 40%
+批量修改目标(Conversion/ROAS)【技术受限-未执行】 — 60%</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-受阻：因Create被上述阻断性bug卡住，无法获得可安全操作的自建AI实体id；直接对ES中他人真实AI记录做状态/目标/删除操作会影响真实客户配置，故仅生成case结构，待bug修复或有专用无AI测试Order后补执行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5145,10 +5181,18 @@
         </is>
       </c>
       <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-    </row>
-    <row r="73">
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>创建AI(单Order,goal=Conversion/ROAS) — 23.5%</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug(阻断性)：AI去重校验与列表查询数据源不一致——Create对共享测试Order判定"已存在AI"而拒绝创建，但GetAiTableList在同一profile/advertiser/order范围内(2020-2026全量日期)查询结果为0条记录；对该advertiser下随机15个不同Order调用GetAiPreviewTableList也全部返回同样的"already set up"错误，但各自在GetAiTableList里同样查不到独立记录。怀疑判重逻辑读取了软删除/历史脏数据，或校验维度有误(可能按advertiser而非order匹配)，导致该advertiser下所有Order永久卡在无法新建也无法预览AI的状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5170,10 +5214,14 @@
         </is>
       </c>
       <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>查询AI详情 — 100%</t>
+        </is>
+      </c>
       <c r="G73" s="3" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="16" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5195,10 +5243,14 @@
         </is>
       </c>
       <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>查询AI创建人下拉框 — 100%</t>
+        </is>
+      </c>
       <c r="G74" s="3" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="16" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5220,10 +5272,14 @@
         </is>
       </c>
       <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>按profileIds查询广告主下拉框 — 100%</t>
+        </is>
+      </c>
       <c r="G75" s="3" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="96" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5245,10 +5301,23 @@
         </is>
       </c>
       <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
-    </row>
-    <row r="77">
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>targetMetric=eCPM — 36.7%
+targetMetric=CTR — 30.0%
+targetMetric=ROAS — 20.0%
+targetMetric=TotalROAS — 6.7%
+targetMetric=CPA — 3.3%
+targetMetric=CPDPV — 3.3%</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：当目标Order当前没有有效AI配置时，接口直接抛未处理异常"Value cannot be null. (Parameter 'source')"透传给前端(HTTP 200但IsSuccessStatusCode=false)，未做业务友好提示。用2个完全不同真实Order+ROAS/TotalROAS组合复现一致，如实FAIL未强行掩盖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5270,10 +5339,14 @@
         </is>
       </c>
       <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>按logId查询LineItem下拉框 — 100%</t>
+        </is>
+      </c>
       <c r="G77" s="3" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="32" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5295,10 +5368,15 @@
         </is>
       </c>
       <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="n"/>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>无额外筛选(仅logId+分页) — 97.5%
+objectLevel=Order+lineItemId筛选 — 2.5%</t>
+        </is>
+      </c>
       <c r="G78" s="3" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="16" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5320,10 +5398,14 @@
         </is>
       </c>
       <c r="E79" s="3" t="n"/>
-      <c r="F79" s="3" t="n"/>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>按aiId+日期查询执行日志 — 100%</t>
+        </is>
+      </c>
       <c r="G79" s="3" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="16" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5345,10 +5427,14 @@
         </is>
       </c>
       <c r="E80" s="3" t="n"/>
-      <c r="F80" s="3" t="n"/>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>按profileIds查询Order下拉框 — 100%</t>
+        </is>
+      </c>
       <c r="G80" s="3" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="64" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5370,10 +5456,17 @@
         </is>
       </c>
       <c r="E81" s="3" t="n"/>
-      <c r="F81" s="3" t="n"/>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>单Order预览 — 44.6%
+2-5个Order预览 — 31.6%
+6-20个Order预览 — 12.8%
+&gt;20个Order预览 — 11.0%</t>
+        </is>
+      </c>
       <c r="G81" s="3" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="64" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5395,7 +5488,14 @@
         </is>
       </c>
       <c r="E82" s="3" t="n"/>
-      <c r="F82" s="3" t="n"/>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>无额外筛选(仅profile+日期+分页) — 75.4%
+广告主+Order+User全筛选 — 17.2%
+仅Order筛选 — 5.4%
+仅广告主筛选 — 1.0%</t>
+        </is>
+      </c>
       <c r="G82" s="3" t="n"/>
     </row>
     <row r="83">
@@ -5420,10 +5520,18 @@
         </is>
       </c>
       <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
-      <c r="G83" s="3" t="n"/>
-    </row>
-    <row r="84">
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5445,8 +5553,16 @@
         </is>
       </c>
       <c r="E84" s="3" t="n"/>
-      <c r="F84" s="3" t="n"/>
-      <c r="G84" s="3" t="n"/>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>修改AI状态/目标【技术受限-未执行】 — 100%</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-受阻：因Create被上述阻断性bug卡住，无法获得可安全操作的自建AI实体id；直接对ES中他人真实AI记录做状态/目标/删除操作会影响真实客户配置，故仅生成case结构，待bug修复或有专用无AI测试Order后补执行。</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1318,9 +1318,19 @@
       </c>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
+      <c r="F29" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100%(17/17执行,14条待用户确认仅生成不执行不计入)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>83% (19/23)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -22637,7 +22647,7 @@
         </is>
       </c>
     </row>
-    <row r="644">
+    <row r="644" ht="32" customHeight="1">
       <c r="A644" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -22659,10 +22669,19 @@
         </is>
       </c>
       <c r="E644" s="3" t="n"/>
-      <c r="F644" s="3" t="n"/>
-      <c r="G644" s="3" t="n"/>
-    </row>
-    <row r="645">
+      <c r="F644" s="6" t="inlineStr">
+        <is>
+          <t>关联creativeIds到lineItem — 71.0%
+creativeIds为空(清空关联) — 29.0%</t>
+        </is>
+      </c>
+      <c r="G644" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认-高危：CreativeV2全部23接口未发现取消关联接口，且creativeIds是追加语义还是整体替换语义未确认——若为替换语义，空数组场景会清空该lineItem下其他关联，共享沙箱账号风险不可控。</t>
+        </is>
+      </c>
+    </row>
+    <row r="645" ht="16" customHeight="1">
       <c r="A645" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -22684,10 +22703,14 @@
         </is>
       </c>
       <c r="E645" s="3" t="n"/>
-      <c r="F645" s="3" t="n"/>
+      <c r="F645" s="6" t="inlineStr">
+        <is>
+          <t>切换association状态(含后置还原,可重复) — 52.4%</t>
+        </is>
+      </c>
       <c r="G645" s="3" t="n"/>
     </row>
-    <row r="646">
+    <row r="646" ht="48" customHeight="1">
       <c r="A646" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -22709,8 +22732,18 @@
         </is>
       </c>
       <c r="E646" s="3" t="n"/>
-      <c r="F646" s="3" t="n"/>
-      <c r="G646" s="3" t="n"/>
+      <c r="F646" s="6" t="inlineStr">
+        <is>
+          <t>批量创建RESPONSIVE ECOMMERCE creative(不带tag) — 81.9%
+批量创建RESPONSIVE ECOMMERCE creative(带tagIds) — 15.3%
+creatives为空数组 — 2.8%</t>
+        </is>
+      </c>
+      <c r="G646" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认：创建型接口，CreativeV2内无creative级别归档/删除接口(与Creative单数模块结论一致)，创建后无法清理。</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="2" t="inlineStr">
@@ -22734,10 +22767,18 @@
         </is>
       </c>
       <c r="E647" s="3" t="n"/>
-      <c r="F647" s="3" t="n"/>
-      <c r="G647" s="3" t="n"/>
-    </row>
-    <row r="648">
+      <c r="F647" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G647" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="648" ht="16" customHeight="1">
       <c r="A648" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -22759,10 +22800,18 @@
         </is>
       </c>
       <c r="E648" s="3" t="n"/>
-      <c r="F648" s="3" t="n"/>
-      <c r="G648" s="3" t="n"/>
-    </row>
-    <row r="649">
+      <c r="F648" s="6" t="inlineStr">
+        <is>
+          <t>设置creative在lineItem下的投放起止时间</t>
+        </is>
+      </c>
+      <c r="G648" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认：需先查询当前flight窗口才能还原，但对应查询接口GetLitemItemFlight全平台0流量(疑似废弃)，无可靠还原路径。</t>
+        </is>
+      </c>
+    </row>
+    <row r="649" ht="32" customHeight="1">
       <c r="A649" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -22784,10 +22833,19 @@
         </is>
       </c>
       <c r="E649" s="3" t="n"/>
-      <c r="F649" s="3" t="n"/>
-      <c r="G649" s="3" t="n"/>
-    </row>
-    <row r="650">
+      <c r="F649" s="6" t="inlineStr">
+        <is>
+          <t>批量为creative添加标签 — 90.2%
+批量为creative删除标签 — 1.0%</t>
+        </is>
+      </c>
+      <c r="G649" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：探测本账号两个真实creative当前均无任何tag，CreativeV2范围内没有创建tag的接口(标签维护在其他service)，无真实tagId可配对回滚。</t>
+        </is>
+      </c>
+    </row>
+    <row r="650" ht="16" customHeight="1">
       <c r="A650" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -22809,10 +22867,18 @@
         </is>
       </c>
       <c r="E650" s="3" t="n"/>
-      <c r="F650" s="3" t="n"/>
-      <c r="G650" s="3" t="n"/>
-    </row>
-    <row r="651">
+      <c r="F650" s="6" t="inlineStr">
+        <is>
+          <t>批量上传Component模板创建creative</t>
+        </is>
+      </c>
+      <c r="G650" s="5" t="inlineStr">
+        <is>
+          <t>技术受限+待确认：multipart/form-data文件上传(run-cases.py不支持)，且是创建型无清理接口，双重原因未执行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="651" ht="16" customHeight="1">
       <c r="A651" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -22834,10 +22900,18 @@
         </is>
       </c>
       <c r="E651" s="3" t="n"/>
-      <c r="F651" s="3" t="n"/>
-      <c r="G651" s="3" t="n"/>
-    </row>
-    <row r="652">
+      <c r="F651" s="6" t="inlineStr">
+        <is>
+          <t>批量上传Component creative(旧版接口)</t>
+        </is>
+      </c>
+      <c r="G651" s="5" t="inlineStr">
+        <is>
+          <t>技术受限+待确认：同BulkUploadComponentBasedCreatives。</t>
+        </is>
+      </c>
+    </row>
+    <row r="652" ht="48" customHeight="1">
       <c r="A652" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -22859,8 +22933,18 @@
         </is>
       </c>
       <c r="E652" s="3" t="n"/>
-      <c r="F652" s="3" t="n"/>
-      <c r="G652" s="3" t="n"/>
+      <c r="F652" s="6" t="inlineStr">
+        <is>
+          <t>创建RESPONSIVE ECOMMERCE creative — 56.0%
+创建ONLINE VIDEO creative(带tagIds) — 43.0%
+创建STREAMING TV VIDEO creative — 1.0%</t>
+        </is>
+      </c>
+      <c r="G652" s="5" t="inlineStr">
+        <is>
+          <t>⚠️待用户确认：同BulkCreateNewCreatives，创建后无法清理。</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="2" t="inlineStr">
@@ -22884,10 +22968,18 @@
         </is>
       </c>
       <c r="E653" s="3" t="n"/>
-      <c r="F653" s="3" t="n"/>
-      <c r="G653" s="3" t="n"/>
-    </row>
-    <row r="654">
+      <c r="F653" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G653" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="654" ht="16" customHeight="1">
       <c r="A654" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -22909,10 +23001,14 @@
         </is>
       </c>
       <c r="E654" s="3" t="n"/>
-      <c r="F654" s="3" t="n"/>
+      <c r="F654" s="6" t="inlineStr">
+        <is>
+          <t>按profileId+advertiserId+lineItemIds查询可选Creative列表 — 99.7%</t>
+        </is>
+      </c>
       <c r="G654" s="3" t="n"/>
     </row>
-    <row r="655">
+    <row r="655" ht="16" customHeight="1">
       <c r="A655" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -22934,10 +23030,14 @@
         </is>
       </c>
       <c r="E655" s="3" t="n"/>
-      <c r="F655" s="3" t="n"/>
+      <c r="F655" s="6" t="inlineStr">
+        <is>
+          <t>按assetId判断是否支持StreamingTv</t>
+        </is>
+      </c>
       <c r="G655" s="3" t="n"/>
     </row>
-    <row r="656">
+    <row r="656" ht="16" customHeight="1">
       <c r="A656" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -22959,10 +23059,14 @@
         </is>
       </c>
       <c r="E656" s="3" t="n"/>
-      <c r="F656" s="3" t="n"/>
+      <c r="F656" s="6" t="inlineStr">
+        <is>
+          <t>按assetId+assetVersion批量查询素材详情</t>
+        </is>
+      </c>
       <c r="G656" s="3" t="n"/>
     </row>
-    <row r="657">
+    <row r="657" ht="16" customHeight="1">
       <c r="A657" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -22984,10 +23088,14 @@
         </is>
       </c>
       <c r="E657" s="3" t="n"/>
-      <c r="F657" s="3" t="n"/>
+      <c r="F657" s="6" t="inlineStr">
+        <is>
+          <t>按creativeId+advertiserId查询关联lineItem</t>
+        </is>
+      </c>
       <c r="G657" s="3" t="n"/>
     </row>
-    <row r="658">
+    <row r="658" ht="16" customHeight="1">
       <c r="A658" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -23009,7 +23117,11 @@
         </is>
       </c>
       <c r="E658" s="3" t="n"/>
-      <c r="F658" s="3" t="n"/>
+      <c r="F658" s="6" t="inlineStr">
+        <is>
+          <t>按creativeId查询关联标签</t>
+        </is>
+      </c>
       <c r="G658" s="3" t="n"/>
     </row>
     <row r="659">
@@ -23034,10 +23146,18 @@
         </is>
       </c>
       <c r="E659" s="3" t="n"/>
-      <c r="F659" s="3" t="n"/>
-      <c r="G659" s="3" t="n"/>
-    </row>
-    <row r="660">
+      <c r="F659" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G659" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="660" ht="16" customHeight="1">
       <c r="A660" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -23059,10 +23179,14 @@
         </is>
       </c>
       <c r="E660" s="3" t="n"/>
-      <c r="F660" s="3" t="n"/>
+      <c r="F660" s="6" t="inlineStr">
+        <is>
+          <t>按creativeIds批量查询lineitem标签(不选全部) — 98.4%</t>
+        </is>
+      </c>
       <c r="G660" s="3" t="n"/>
     </row>
-    <row r="661">
+    <row r="661" ht="16" customHeight="1">
       <c r="A661" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -23084,10 +23208,14 @@
         </is>
       </c>
       <c r="E661" s="3" t="n"/>
-      <c r="F661" s="3" t="n"/>
+      <c r="F661" s="6" t="inlineStr">
+        <is>
+          <t>按profileId+creativeId查询统一Creative详情</t>
+        </is>
+      </c>
       <c r="G661" s="3" t="n"/>
     </row>
-    <row r="662">
+    <row r="662" ht="64" customHeight="1">
       <c r="A662" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -23109,10 +23237,17 @@
         </is>
       </c>
       <c r="E662" s="3" t="n"/>
-      <c r="F662" s="3" t="n"/>
+      <c r="F662" s="6" t="inlineStr">
+        <is>
+          <t>RESPONSIVE ECOMMERCE/COMPONENT组件式预览 — 96.2%
+ONLINE VIDEO视频预览 — 1.2%
+ASSET BASED CREATIVE预览 — 1.0%
+BRAND STORE预览 — 1.0%</t>
+        </is>
+      </c>
       <c r="G662" s="3" t="n"/>
     </row>
-    <row r="663">
+    <row r="663" ht="48" customHeight="1">
       <c r="A663" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -23134,10 +23269,16 @@
         </is>
       </c>
       <c r="E663" s="3" t="n"/>
-      <c r="F663" s="3" t="n"/>
+      <c r="F663" s="6" t="inlineStr">
+        <is>
+          <t>按creativeId预览(type=STANDARD DISPLAY) — 85.4%
+按creativeId预览(size代替type) — 11.4%
+按creativeId预览(不传type/size) — 2.6%</t>
+        </is>
+      </c>
       <c r="G663" s="3" t="n"/>
     </row>
-    <row r="664">
+    <row r="664" ht="16" customHeight="1">
       <c r="A664" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -23159,10 +23300,14 @@
         </is>
       </c>
       <c r="E664" s="3" t="n"/>
-      <c r="F664" s="3" t="n"/>
+      <c r="F664" s="6" t="inlineStr">
+        <is>
+          <t>修改creative名称(含后置还原,可重复)</t>
+        </is>
+      </c>
       <c r="G664" s="3" t="n"/>
     </row>
-    <row r="665">
+    <row r="665" ht="32" customHeight="1">
       <c r="A665" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -23184,8 +23329,17 @@
         </is>
       </c>
       <c r="E665" s="3" t="n"/>
-      <c r="F665" s="3" t="n"/>
-      <c r="G665" s="3" t="n"/>
+      <c r="F665" s="6" t="inlineStr">
+        <is>
+          <t>RESPONSIVE ECOMMERCE整体更新(含后置还原,可重复) — 47.4%
+ONLINE VIDEO整体更新 — 52.2%</t>
+        </is>
+      </c>
+      <c r="G665" s="5" t="inlineStr">
+        <is>
+          <t>部分技术受限：ONLINE_VIDEO类型场景因账号内未确认拥有可安全改后还原的真实ONLINE_VIDEO creative未执行，RESPONSIVE_ECOMMERCE场景已正常执行验证通过(含改名+精确还原)。</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" s="2" t="inlineStr">
@@ -23209,8 +23363,16 @@
         </is>
       </c>
       <c r="E666" s="3" t="n"/>
-      <c r="F666" s="3" t="n"/>
-      <c r="G666" s="3" t="n"/>
+      <c r="F666" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G666" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)（GetLitemItemFlight疑似废弃：Swagger仍暴露但全平台0流量，建议向研发确认是否该下线）</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1232,9 +1232,19 @@
       </c>
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="F26" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>36% (4/11)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -19488,8 +19498,16 @@
         </is>
       </c>
       <c r="E541" s="3" t="n"/>
-      <c r="F541" s="3" t="n"/>
-      <c r="G541" s="3" t="n"/>
+      <c r="F541" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G541" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -19513,8 +19531,16 @@
         </is>
       </c>
       <c r="E542" s="3" t="n"/>
-      <c r="F542" s="3" t="n"/>
-      <c r="G542" s="3" t="n"/>
+      <c r="F542" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G542" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
@@ -19538,8 +19564,16 @@
         </is>
       </c>
       <c r="E543" s="3" t="n"/>
-      <c r="F543" s="3" t="n"/>
-      <c r="G543" s="3" t="n"/>
+      <c r="F543" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G543" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
@@ -19563,10 +19597,18 @@
         </is>
       </c>
       <c r="E544" s="3" t="n"/>
-      <c r="F544" s="3" t="n"/>
-      <c r="G544" s="3" t="n"/>
-    </row>
-    <row r="545">
+      <c r="F544" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G544" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="545" ht="32" customHeight="1">
       <c r="A545" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19588,10 +19630,15 @@
         </is>
       </c>
       <c r="E545" s="3" t="n"/>
-      <c r="F545" s="3" t="n"/>
+      <c r="F545" s="6" t="inlineStr">
+        <is>
+          <t>单广告主查询事件列表 — 93.8%
+多广告主批量查询事件列表 — 6.0%</t>
+        </is>
+      </c>
       <c r="G545" s="3" t="n"/>
     </row>
-    <row r="546">
+    <row r="546" ht="48" customHeight="1">
       <c r="A546" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19613,10 +19660,16 @@
         </is>
       </c>
       <c r="E546" s="3" t="n"/>
-      <c r="F546" s="3" t="n"/>
+      <c r="F546" s="6" t="inlineStr">
+        <is>
+          <t>advertiserIds为空查询全部广告标签 — 1.4%
+单广告主查询Ad Tag列表 — 79.7%
+多广告主批量查询Ad Tag列表 — 18.8%</t>
+        </is>
+      </c>
       <c r="G546" s="3" t="n"/>
     </row>
-    <row r="547">
+    <row r="547" ht="16" customHeight="1">
       <c r="A547" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19638,10 +19691,14 @@
         </is>
       </c>
       <c r="E547" s="3" t="n"/>
-      <c r="F547" s="3" t="n"/>
+      <c r="F547" s="6" t="inlineStr">
+        <is>
+          <t>按订单查询关联转化定义 — 100%</t>
+        </is>
+      </c>
       <c r="G547" s="3" t="n"/>
     </row>
-    <row r="548">
+    <row r="548" ht="64" customHeight="1">
       <c r="A548" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19663,8 +19720,19 @@
         </is>
       </c>
       <c r="E548" s="3" t="n"/>
-      <c r="F548" s="3" t="n"/>
-      <c r="G548" s="3" t="n"/>
+      <c r="F548" s="6" t="inlineStr">
+        <is>
+          <t>按广告主列表查询转化定义 — 42.4%
+空body查询全部转化定义(触发真实后端Bug) — 27.2%
+按Profile+Advertiser+订单查询转化定义 — 25.6%
+按订单+名称/来源类型搜索转化定义 — 4.8%</t>
+        </is>
+      </c>
+      <c r="G548" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：传空body{}(真实流量占比27.2%，页面初次加载/清空筛选场景)时抛未处理异常，IsSuccessStatusCode:false，堆栈定位到ConversionService.ListConversionDefinitionsAsync，疑似某过滤条件在SQL IN查询对null值处理不当。两轮稳定复现。</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
@@ -19688,8 +19756,16 @@
         </is>
       </c>
       <c r="E549" s="3" t="n"/>
-      <c r="F549" s="3" t="n"/>
-      <c r="G549" s="3" t="n"/>
+      <c r="F549" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G549" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -19713,8 +19789,16 @@
         </is>
       </c>
       <c r="E550" s="3" t="n"/>
-      <c r="F550" s="3" t="n"/>
-      <c r="G550" s="3" t="n"/>
+      <c r="F550" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G550" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -19738,8 +19822,16 @@
         </is>
       </c>
       <c r="E551" s="3" t="n"/>
-      <c r="F551" s="3" t="n"/>
-      <c r="G551" s="3" t="n"/>
+      <c r="F551" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G551" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="552" ht="32" customHeight="1">
       <c r="A552" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -716,9 +716,19 @@
       </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+      <c r="F8" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%(7/7执行,11条因无清理接口/WebSocket技术限制仅生成不执行不计入)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79% (11/14)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -5749,7 +5759,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="16" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5771,10 +5781,18 @@
         </is>
       </c>
       <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="n"/>
-      <c r="G90" s="3" t="n"/>
-    </row>
-    <row r="91">
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>携带token握手</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：Swagger标注为WebSocket接口，真实ES日志显示为握手请求(仅token参数+空body)。run-cases.py是纯HTTP client无法完成WebSocket握手协议(实测用普通HTTP GET返回400+空响应体，非业务失败)，只生成了记录真实入参结构的case，未执行。ReportCustomSqlChat对应的完整业务流程会触发AI生成SQL并提交AMC云端执行查询，属潜在计费点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="64" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5796,10 +5814,21 @@
         </is>
       </c>
       <c r="E91" s="3" t="n"/>
-      <c r="F91" s="3" t="n"/>
-      <c r="G91" s="3" t="n"/>
-    </row>
-    <row r="92">
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>type=query — 56.4%
+type=insight — 27.2%
+type=query-audience — 13.6%
+type=template — 2.8%</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-无清理接口：AmcAgent tag内14个接口无任何删除/清空日志、SQL版本、投票的接口，写入后无法撤销，按默认规则跳过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5821,10 +5850,19 @@
         </is>
       </c>
       <c r="E92" s="3" t="n"/>
-      <c r="F92" s="3" t="n"/>
-      <c r="G92" s="3" t="n"/>
-    </row>
-    <row r="93">
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>仅sql无parameterText — 96.2%
+sql+parameterText — 3.8%</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-无清理接口：AmcAgent tag内14个接口无任何删除/清空日志、SQL版本、投票的接口，写入后无法撤销，按默认规则跳过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="32" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5846,8 +5884,17 @@
         </is>
       </c>
       <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="n"/>
-      <c r="G93" s="3" t="n"/>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>voteType=1(点赞) — 81.8%
+voteType=2(点踩) — 18.2%</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-无清理接口：AmcAgent tag内14个接口无任何删除/清空日志、SQL版本、投票的接口，写入后无法撤销，按默认规则跳过。</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5871,10 +5918,18 @@
         </is>
       </c>
       <c r="E94" s="3" t="n"/>
-      <c r="F94" s="3" t="n"/>
-      <c r="G94" s="3" t="n"/>
-    </row>
-    <row r="95">
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5896,10 +5951,14 @@
         </is>
       </c>
       <c r="E95" s="3" t="n"/>
-      <c r="F95" s="3" t="n"/>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>type=insight — 99.8%</t>
+        </is>
+      </c>
       <c r="G95" s="3" t="n"/>
     </row>
-    <row r="96">
+    <row r="96" ht="32" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5921,7 +5980,12 @@
         </is>
       </c>
       <c r="E96" s="3" t="n"/>
-      <c r="F96" s="3" t="n"/>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>type=query — 77.8%
+type=query-audience — 22.2%</t>
+        </is>
+      </c>
       <c r="G96" s="3" t="n"/>
     </row>
     <row r="97">
@@ -5946,10 +6010,18 @@
         </is>
       </c>
       <c r="E97" s="3" t="n"/>
-      <c r="F97" s="3" t="n"/>
-      <c r="G97" s="3" t="n"/>
-    </row>
-    <row r="98">
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5971,10 +6043,14 @@
         </is>
       </c>
       <c r="E98" s="3" t="n"/>
-      <c r="F98" s="3" t="n"/>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>reportinfo默认参数 — 99.8%</t>
+        </is>
+      </c>
       <c r="G98" s="3" t="n"/>
     </row>
-    <row r="99">
+    <row r="99" ht="32" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5996,10 +6072,15 @@
         </is>
       </c>
       <c r="E99" s="3" t="n"/>
-      <c r="F99" s="3" t="n"/>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>sessionId为数字时间戳形态 — 73.4%
+sessionId为UUID形态 — 26.6%</t>
+        </is>
+      </c>
       <c r="G99" s="3" t="n"/>
     </row>
-    <row r="100">
+    <row r="100" ht="16" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6021,10 +6102,18 @@
         </is>
       </c>
       <c r="E100" s="3" t="n"/>
-      <c r="F100" s="3" t="n"/>
-      <c r="G100" s="3" t="n"/>
-    </row>
-    <row r="101">
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>携带token握手</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：Swagger标注为WebSocket接口，真实ES日志显示为握手请求(仅token参数+空body)。run-cases.py是纯HTTP client无法完成WebSocket握手协议(实测用普通HTTP GET返回400+空响应体，非业务失败)，只生成了记录真实入参结构的case，未执行。ReportCustomSqlChat对应的完整业务流程会触发AI生成SQL并提交AMC云端执行查询，属潜在计费点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6046,10 +6135,18 @@
         </is>
       </c>
       <c r="E101" s="3" t="n"/>
-      <c r="F101" s="3" t="n"/>
-      <c r="G101" s="3" t="n"/>
-    </row>
-    <row r="102">
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>携带token握手</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：Swagger标注为WebSocket接口，真实ES日志显示为握手请求(仅token参数+空body)。run-cases.py是纯HTTP client无法完成WebSocket握手协议(实测用普通HTTP GET返回400+空响应体，非业务失败)，只生成了记录真实入参结构的case，未执行。ReportCustomSqlChat对应的完整业务流程会触发AI生成SQL并提交AMC云端执行查询，属潜在计费点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -6071,7 +6168,11 @@
         </is>
       </c>
       <c r="E102" s="3" t="n"/>
-      <c r="F102" s="3" t="n"/>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>按sessionId查询</t>
+        </is>
+      </c>
       <c r="G102" s="3" t="n"/>
     </row>
     <row r="103">
@@ -6096,8 +6197,16 @@
         </is>
       </c>
       <c r="E103" s="3" t="n"/>
-      <c r="F103" s="3" t="n"/>
-      <c r="G103" s="3" t="n"/>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="144" customHeight="1">
       <c r="A104" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -2100,9 +2100,19 @@
       </c>
       <c r="D55" s="3" t="n"/>
       <c r="E55" s="3" t="n"/>
-      <c r="F55" s="2" t="n"/>
-      <c r="G55" s="2" t="n"/>
-      <c r="H55" s="2" t="n"/>
+      <c r="F55" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>64% (7/11)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -39817,7 +39827,7 @@
       </c>
       <c r="G1182" s="3" t="n"/>
     </row>
-    <row r="1183">
+    <row r="1183" ht="32" customHeight="1">
       <c r="A1183" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -39839,8 +39849,17 @@
         </is>
       </c>
       <c r="E1183" s="3" t="n"/>
-      <c r="F1183" s="3" t="n"/>
-      <c r="G1183" s="3" t="n"/>
+      <c r="F1183" s="6" t="inlineStr">
+        <is>
+          <t>导出非空ASIN研究列表(xlsx二进制) — 94.7%
+空ASIN列表下载(疑似bug) — 5.3%</t>
+        </is>
+      </c>
+      <c r="G1183" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：请求体{"asins":[]}(空ASIN数组，真实占比5.3%，用户在ASIN研究列表无勾选时点击下载)抛未处理异常"Cannot return null from an action method"，正常非空场景(94.7%)返回xlsx二进制文件正常。两轮稳定复现，建议后端对空数组做前置校验返回友好提示。</t>
+        </is>
+      </c>
     </row>
     <row r="1184">
       <c r="A1184" s="2" t="inlineStr">
@@ -39864,10 +39883,18 @@
         </is>
       </c>
       <c r="E1184" s="3" t="n"/>
-      <c r="F1184" s="3" t="n"/>
-      <c r="G1184" s="3" t="n"/>
-    </row>
-    <row r="1185">
+      <c r="F1184" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1184" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185" ht="16" customHeight="1">
       <c r="A1185" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -39889,10 +39916,14 @@
         </is>
       </c>
       <c r="E1185" s="3" t="n"/>
-      <c r="F1185" s="3" t="n"/>
+      <c r="F1185" s="6" t="inlineStr">
+        <is>
+          <t>按advertiserId+asins批量查ASIN信息 — 100%</t>
+        </is>
+      </c>
       <c r="G1185" s="3" t="n"/>
     </row>
-    <row r="1186">
+    <row r="1186" ht="80" customHeight="1">
       <c r="A1186" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -39914,8 +39945,20 @@
         </is>
       </c>
       <c r="E1186" s="3" t="n"/>
-      <c r="F1186" s="3" t="n"/>
-      <c r="G1186" s="3" t="n"/>
+      <c r="F1186" s="6" t="inlineStr">
+        <is>
+          <t>1个ASIN竞品对比查询 — 90.4%
+10个ASIN竞品对比查询 — 4.2%
+5个ASIN竞品对比查询 — 1.4%
+9个ASIN竞品对比查询 — 1.2%
+8个ASIN竞品对比查询 — 1.0%</t>
+        </is>
+      </c>
+      <c r="G1186" s="5" t="inlineStr">
+        <is>
+          <t>观察项：部分调用耗时较长(8-32秒)，可能涉及第三方API/爬虫抓取竞品数据，建议关注超时与性能表现。</t>
+        </is>
+      </c>
     </row>
     <row r="1187">
       <c r="A1187" s="2" t="inlineStr">
@@ -39939,8 +39982,16 @@
         </is>
       </c>
       <c r="E1187" s="3" t="n"/>
-      <c r="F1187" s="3" t="n"/>
-      <c r="G1187" s="3" t="n"/>
+      <c r="F1187" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1187" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1188">
       <c r="A1188" s="2" t="inlineStr">
@@ -39964,8 +40015,16 @@
         </is>
       </c>
       <c r="E1188" s="3" t="n"/>
-      <c r="F1188" s="3" t="n"/>
-      <c r="G1188" s="3" t="n"/>
+      <c r="F1188" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1188" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1189">
       <c r="A1189" s="2" t="inlineStr">
@@ -39989,10 +40048,18 @@
         </is>
       </c>
       <c r="E1189" s="3" t="n"/>
-      <c r="F1189" s="3" t="n"/>
-      <c r="G1189" s="3" t="n"/>
-    </row>
-    <row r="1190">
+      <c r="F1189" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1189" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190" ht="16" customHeight="1">
       <c r="A1190" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -40014,10 +40081,18 @@
         </is>
       </c>
       <c r="E1190" s="3" t="n"/>
-      <c r="F1190" s="3" t="n"/>
-      <c r="G1190" s="3" t="n"/>
-    </row>
-    <row r="1191">
+      <c r="F1190" s="6" t="inlineStr">
+        <is>
+          <t>按关键词查相关关键词数据 — 100%</t>
+        </is>
+      </c>
+      <c r="G1190" s="5" t="inlineStr">
+        <is>
+          <t>观察项：单次调用偶尔较慢(5-16秒)，同样可能是外部关键词数据源调用导致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191" ht="32" customHeight="1">
       <c r="A1191" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -40039,10 +40114,15 @@
         </is>
       </c>
       <c r="E1191" s="3" t="n"/>
-      <c r="F1191" s="3" t="n"/>
+      <c r="F1191" s="6" t="inlineStr">
+        <is>
+          <t>按ASIN搜索 — 79.9%
+按关键词文本搜索 — 20.1%</t>
+        </is>
+      </c>
       <c r="G1191" s="3" t="n"/>
     </row>
-    <row r="1192">
+    <row r="1192" ht="16" customHeight="1">
       <c r="A1192" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -40064,10 +40144,18 @@
         </is>
       </c>
       <c r="E1192" s="3" t="n"/>
-      <c r="F1192" s="3" t="n"/>
-      <c r="G1192" s="3" t="n"/>
-    </row>
-    <row r="1193">
+      <c r="F1192" s="6" t="inlineStr">
+        <is>
+          <t>上传ASIN批量导入文件(仅生成不执行) — 100%</t>
+        </is>
+      </c>
+      <c r="G1192" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口，run-cases.py执行引擎只支持JSON body，无法上传文件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193" ht="16" customHeight="1">
       <c r="A1193" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -40089,8 +40177,16 @@
         </is>
       </c>
       <c r="E1193" s="3" t="n"/>
-      <c r="F1193" s="3" t="n"/>
-      <c r="G1193" s="3" t="n"/>
+      <c r="F1193" s="6" t="inlineStr">
+        <is>
+          <t>上传ASIN Audience批量导入文件(仅生成不执行) — 100%</t>
+        </is>
+      </c>
+      <c r="G1193" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：multipart/form-data文件上传接口，run-cases.py执行引擎只支持JSON body，无法上传文件。</t>
+        </is>
+      </c>
     </row>
     <row r="1194" ht="64" customHeight="1">
       <c r="A1194" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -2624,9 +2624,19 @@
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="3" t="n"/>
-      <c r="F72" s="2" t="n"/>
-      <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2" t="n"/>
+      <c r="F72" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>81%(13/16执行,10条因无清理接口默认跳过不计入)</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>46% (6/13)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -50143,7 +50153,7 @@
         </is>
       </c>
     </row>
-    <row r="1500">
+    <row r="1500" ht="112" customHeight="1">
       <c r="A1500" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -50165,8 +50175,22 @@
         </is>
       </c>
       <c r="E1500" s="3" t="n"/>
-      <c r="F1500" s="3" t="n"/>
-      <c r="G1500" s="3" t="n"/>
+      <c r="F1500" s="6" t="inlineStr">
+        <is>
+          <t>场景1:matchRuleType=orderTag+isPause=false — 65.8%
+场景2:matchRuleType=orderTag+isPause=true — 15.2%
+场景3:matchRuleType=lineItemTag+isPause=false — 10.0%
+场景4:matchRuleType=creativeTag+isPause=false — 4.2%
+场景5:matchRuleType=lineItemTag+isPause=true — 2.4%
+场景6:matchRuleType=creativeTag+isPause=true — 1.0%
+场景7:matchRuleType=null(未选择类型)+isPause=false — 1.0%</t>
+        </is>
+      </c>
+      <c r="G1500" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-无清理接口：Tagging tag范围内没有独立的MatchRule删除/归档接口，按默认规则跳过。</t>
+        </is>
+      </c>
     </row>
     <row r="1501">
       <c r="A1501" s="2" t="inlineStr">
@@ -50190,10 +50214,18 @@
         </is>
       </c>
       <c r="E1501" s="3" t="n"/>
-      <c r="F1501" s="3" t="n"/>
-      <c r="G1501" s="3" t="n"/>
-    </row>
-    <row r="1502">
+      <c r="F1501" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1501" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502" ht="32" customHeight="1">
       <c r="A1502" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -50215,10 +50247,19 @@
         </is>
       </c>
       <c r="E1502" s="3" t="n"/>
-      <c r="F1502" s="3" t="n"/>
-      <c r="G1502" s="3" t="n"/>
-    </row>
-    <row r="1503">
+      <c r="F1502" s="6" t="inlineStr">
+        <is>
+          <t>场景1:tagIds=2个 — 92.3%
+场景2:tagIds=1个 — 7.7%</t>
+        </is>
+      </c>
+      <c r="G1502" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-数据不可控：操作对象是ES样本里其他真实客户的日志实体，非本测试账号可控数据，不适合执行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503" ht="16" customHeight="1">
       <c r="A1503" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -50240,8 +50281,16 @@
         </is>
       </c>
       <c r="E1503" s="3" t="n"/>
-      <c r="F1503" s="3" t="n"/>
-      <c r="G1503" s="3" t="n"/>
+      <c r="F1503" s="6" t="inlineStr">
+        <is>
+          <t>场景1:changeType=OrderTag RemoveFromTag — 100%</t>
+        </is>
+      </c>
+      <c r="G1503" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-数据不可控：同ChangeEventDailyLogAddToTag。</t>
+        </is>
+      </c>
     </row>
     <row r="1504">
       <c r="A1504" s="2" t="inlineStr">
@@ -50265,8 +50314,16 @@
         </is>
       </c>
       <c r="E1504" s="3" t="n"/>
-      <c r="F1504" s="3" t="n"/>
-      <c r="G1504" s="3" t="n"/>
+      <c r="F1504" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1504" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1505">
       <c r="A1505" s="2" t="inlineStr">
@@ -50290,10 +50347,18 @@
         </is>
       </c>
       <c r="E1505" s="3" t="n"/>
-      <c r="F1505" s="3" t="n"/>
-      <c r="G1505" s="3" t="n"/>
-    </row>
-    <row r="1506">
+      <c r="F1505" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1505" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506" ht="144" customHeight="1">
       <c r="A1506" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -50315,8 +50380,24 @@
         </is>
       </c>
       <c r="E1506" s="3" t="n"/>
-      <c r="F1506" s="3" t="n"/>
-      <c r="G1506" s="3" t="n"/>
+      <c r="F1506" s="6" t="inlineStr">
+        <is>
+          <t>场景1:order-多entity-单tag-有Advertiser — 46.4%
+场景2:line-多entity-单tag-有Advertiser — 22.2%
+场景3:creative-多entity-单tag-有Advertiser — 12.4%
+场景4:order-多entity-单tag-有Advertiser-含selectedAllQuery — 4.4%
+场景5:order-多entity-多tag-有Advertiser — 3.8%
+场景6:product-多entity-单tag-有Advertiser — 3.6%
+场景7:creative-多entity-单tag-有Advertiser-含selectedAllQuery — 3.4%
+场景8:line-多entity-多tag-有Advertiser — 2.0%
+场景9:line-多entity-单tag-有Advertiser-含selectedAllQuery — 1.6%</t>
+        </is>
+      </c>
+      <c r="G1506" s="5" t="inlineStr">
+        <is>
+          <t>观察项(疑似问题，未100%坐实)：请求体带selectedAllQuery(非null)的3个场景两轮稳定失败，接口切换成完全不同的响应包装({Error,Data,IsSuccessStatusCode,...}而非标准{code,success,data,msg})。因涉及的entityIds/advertiserIds来自ES其他真实客户样本，不能100%排除是跨账号无权限的预期报错，但响应信封整体切换本身异常，建议开发确认是否为设计内行为。另场景6(product类型)出现过一次偶发超时，判断为慢查询非稳定问题。</t>
+        </is>
+      </c>
     </row>
     <row r="1507">
       <c r="A1507" s="2" t="inlineStr">
@@ -50340,8 +50421,16 @@
         </is>
       </c>
       <c r="E1507" s="3" t="n"/>
-      <c r="F1507" s="3" t="n"/>
-      <c r="G1507" s="3" t="n"/>
+      <c r="F1507" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1507" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1508">
       <c r="A1508" s="2" t="inlineStr">
@@ -50365,10 +50454,18 @@
         </is>
       </c>
       <c r="E1508" s="3" t="n"/>
-      <c r="F1508" s="3" t="n"/>
-      <c r="G1508" s="3" t="n"/>
-    </row>
-    <row r="1509">
+      <c r="F1508" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1508" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509" ht="48" customHeight="1">
       <c r="A1509" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -50390,7 +50487,13 @@
         </is>
       </c>
       <c r="E1509" s="3" t="n"/>
-      <c r="F1509" s="3" t="n"/>
+      <c r="F1509" s="6" t="inlineStr">
+        <is>
+          <t>场景1:无Advertiser Profile过滤(仅关键字) — 69.6%
+场景2:按Advertiser Profile过滤 — 26.1%
+场景3:按Advertiser Profile过滤+含orderIds — 4.3%</t>
+        </is>
+      </c>
       <c r="G1509" s="3" t="n"/>
     </row>
     <row r="1510">
@@ -50415,10 +50518,18 @@
         </is>
       </c>
       <c r="E1510" s="3" t="n"/>
-      <c r="F1510" s="3" t="n"/>
-      <c r="G1510" s="3" t="n"/>
-    </row>
-    <row r="1511">
+      <c r="F1510" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1510" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511" ht="64" customHeight="1">
       <c r="A1511" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -50440,8 +50551,19 @@
         </is>
       </c>
       <c r="E1511" s="3" t="n"/>
-      <c r="F1511" s="3" t="n"/>
-      <c r="G1511" s="3" t="n"/>
+      <c r="F1511" s="6" t="inlineStr">
+        <is>
+          <t>场景1:matchRuleType=orderTag(小写) — 94.0%
+场景2:matchRuleType=OrderTag(首字母大写) — 2.0%
+场景3:matchRuleType=LineItemTag(首字母大写) — 1.8%
+场景4:matchRuleType=lineItemTag(小写) — 1.6%</t>
+        </is>
+      </c>
+      <c r="G1511" s="5" t="inlineStr">
+        <is>
+          <t>观察项：matchRuleType查询参数存在真实的大小写不一致传参(如orderTag 94.0%/OrderTag 2.0%)，疑似前端不同入口大小写不统一；已验证后端对大小写不敏感，非阻塞问题。</t>
+        </is>
+      </c>
     </row>
     <row r="1512">
       <c r="A1512" s="2" t="inlineStr">
@@ -50465,8 +50587,16 @@
         </is>
       </c>
       <c r="E1512" s="3" t="n"/>
-      <c r="F1512" s="3" t="n"/>
-      <c r="G1512" s="3" t="n"/>
+      <c r="F1512" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1512" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
     </row>
     <row r="1513" ht="64" customHeight="1">
       <c r="A1513" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -2474,9 +2474,19 @@
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="3" t="n"/>
-      <c r="F67" s="2" t="n"/>
-      <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2" t="n"/>
+      <c r="F67" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>100%(16/16执行,13条因无清理接口默认跳过不计入)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>86% (12/14)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -48351,7 +48361,7 @@
         </is>
       </c>
     </row>
-    <row r="1442">
+    <row r="1442" ht="16" customHeight="1">
       <c r="A1442" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -48373,10 +48383,18 @@
         </is>
       </c>
       <c r="E1442" s="3" t="n"/>
-      <c r="F1442" s="3" t="n"/>
-      <c r="G1442" s="3" t="n"/>
-    </row>
-    <row r="1443">
+      <c r="F1442" s="6" t="inlineStr">
+        <is>
+          <t>批量删除预览LineItem — 100%</t>
+        </is>
+      </c>
+      <c r="G1442" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-无安全测试数据：待删除数据依赖SaveSuperWizard创建(已跳过)，若用他人真实ID执行会误删其他用户正在编辑的真实草稿，不可逆无撤销接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443" ht="16" customHeight="1">
       <c r="A1443" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -48398,10 +48416,18 @@
         </is>
       </c>
       <c r="E1443" s="3" t="n"/>
-      <c r="F1443" s="3" t="n"/>
-      <c r="G1443" s="3" t="n"/>
-    </row>
-    <row r="1444">
+      <c r="F1443" s="6" t="inlineStr">
+        <is>
+          <t>删除预览Order — 100%</t>
+        </is>
+      </c>
+      <c r="G1443" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-无安全测试数据：同DelPreviewLineItem。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444" ht="16" customHeight="1">
       <c r="A1444" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -48423,10 +48449,14 @@
         </is>
       </c>
       <c r="E1444" s="3" t="n"/>
-      <c r="F1444" s="3" t="n"/>
+      <c r="F1444" s="6" t="inlineStr">
+        <is>
+          <t>按广告主查询可用投放时间 — 100%</t>
+        </is>
+      </c>
       <c r="G1444" s="3" t="n"/>
     </row>
-    <row r="1445">
+    <row r="1445" ht="16" customHeight="1">
       <c r="A1445" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -48448,10 +48478,18 @@
         </is>
       </c>
       <c r="E1445" s="3" t="n"/>
-      <c r="F1445" s="3" t="n"/>
-      <c r="G1445" s="3" t="n"/>
-    </row>
-    <row r="1446">
+      <c r="F1445" s="6" t="inlineStr">
+        <is>
+          <t>按wizardCreativeId查询预览创意详情 — 100%</t>
+        </is>
+      </c>
+      <c r="G1445" s="5" t="inlineStr">
+        <is>
+          <t>🔴疑似跨租户数据暴露(同Audit/SuperWizard(V1)模式，第三次出现)：用ES日志里其他账号产生的wizardId/wizardOrderId/wizardLineItemId/wizardCreativeId，配合本测试账号的token查询，均返回了对方真实的产品图片/ASIN/预算/创意标题等草稿数据，未见按账号归属做权限校验的迹象。只读探测未做任何写入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446" ht="16" customHeight="1">
       <c r="A1446" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -48473,10 +48511,18 @@
         </is>
       </c>
       <c r="E1446" s="3" t="n"/>
-      <c r="F1446" s="3" t="n"/>
-      <c r="G1446" s="3" t="n"/>
-    </row>
-    <row r="1447">
+      <c r="F1446" s="6" t="inlineStr">
+        <is>
+          <t>按wizardId查询预览创意列表 — 100%</t>
+        </is>
+      </c>
+      <c r="G1446" s="5" t="inlineStr">
+        <is>
+          <t>🔴疑似跨租户数据暴露(同Audit/SuperWizard(V1)模式，第三次出现)：用ES日志里其他账号产生的wizardId/wizardOrderId/wizardLineItemId/wizardCreativeId，配合本测试账号的token查询，均返回了对方真实的产品图片/ASIN/预算/创意标题等草稿数据，未见按账号归属做权限校验的迹象。只读探测未做任何写入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447" ht="16" customHeight="1">
       <c r="A1447" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -48498,10 +48544,18 @@
         </is>
       </c>
       <c r="E1447" s="3" t="n"/>
-      <c r="F1447" s="3" t="n"/>
-      <c r="G1447" s="3" t="n"/>
-    </row>
-    <row r="1448">
+      <c r="F1447" s="6" t="inlineStr">
+        <is>
+          <t>按wizardLineItemId查询预览LineItem详情 — 100%</t>
+        </is>
+      </c>
+      <c r="G1447" s="5" t="inlineStr">
+        <is>
+          <t>🔴真实bug：对部分(较旧/可能已失效的)wizardLineItemId响应异常慢(13~33秒)且最终失败(IsSuccessStatusCode:false)，而同类他人归属ID在姐妹接口通常&lt;1秒返回成功+全null字段。两轮复现一致，怀疑是对已过期预览数据做了慢速外部查询(可能同步Amazon DSP接口超时)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448" ht="32" customHeight="1">
       <c r="A1448" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -48523,10 +48577,15 @@
         </is>
       </c>
       <c r="E1448" s="3" t="n"/>
-      <c r="F1448" s="3" t="n"/>
+      <c r="F1448" s="6" t="inlineStr">
+        <is>
+          <t>仅按wizardId查全部Order下LineItem — 83.8%
+按wizardId+wizardOrderId查单Order下LineItem — 16.2%</t>
+        </is>
+      </c>
       <c r="G1448" s="3" t="n"/>
     </row>
-    <row r="1449">
+    <row r="1449" ht="144" customHeight="1">
       <c r="A1449" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -48548,10 +48607,22 @@
         </is>
       </c>
       <c r="E1449" s="3" t="n"/>
-      <c r="F1449" s="3" t="n"/>
+      <c r="F1449" s="6" t="inlineStr">
+        <is>
+          <t>全维度拆分(设备+移动环境+供应源,仅Amazon) — 73.0%
+全维度拆分(设备+移动环境+供应源,Amazon+3P) — 7.8%
+不拆设备,拆移动环境+供应源(仅Amazon) — 5.6%
+不拆设备,不拆移动环境,拆供应源(仅Amazon) — 2.6%
+拆设备,不拆移动环境,拆供应源(仅Amazon) — 2.0%
+不拆设备,拆移动环境,不拆供应源(Amazon+3P) — 2.0%
+不拆设备,不拆移动环境,不拆供应源(仅Amazon) — 1.6%
+拆设备,不拆移动环境,拆供应源(Amazon+3P) — 1.0%
+不拆设备,不拆移动环境,拆供应源(Amazon+3P) — 1.0%</t>
+        </is>
+      </c>
       <c r="G1449" s="3" t="n"/>
     </row>
-    <row r="1450">
+    <row r="1450" ht="16" customHeight="1">
       <c r="A1450" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -48573,8 +48644,16 @@
         </is>
       </c>
       <c r="E1450" s="3" t="n"/>
-      <c r="F1450" s="3" t="n"/>
-      <c r="G1450" s="3" t="n"/>
+      <c r="F1450" s="6" t="inlineStr">
+        <is>
+          <t>按wizardId查询预览Order列表 — 100%</t>
+        </is>
+      </c>
+      <c r="G1450" s="5" t="inlineStr">
+        <is>
+          <t>🔴疑似跨租户数据暴露(同Audit/SuperWizard(V1)模式，第三次出现)：用ES日志里其他账号产生的wizardId/wizardOrderId/wizardLineItemId/wizardCreativeId，配合本测试账号的token查询，均返回了对方真实的产品图片/ASIN/预算/创意标题等草稿数据，未见按账号归属做权限校验的迹象。只读探测未做任何写入。</t>
+        </is>
+      </c>
     </row>
     <row r="1451">
       <c r="A1451" s="2" t="inlineStr">
@@ -48598,10 +48677,18 @@
         </is>
       </c>
       <c r="E1451" s="3" t="n"/>
-      <c r="F1451" s="3" t="n"/>
-      <c r="G1451" s="3" t="n"/>
-    </row>
-    <row r="1452">
+      <c r="F1451" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1451" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452" ht="144" customHeight="1">
       <c r="A1452" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -48623,8 +48710,24 @@
         </is>
       </c>
       <c r="E1452" s="3" t="n"/>
-      <c r="F1452" s="3" t="n"/>
-      <c r="G1452" s="3" t="n"/>
+      <c r="F1452" s="6" t="inlineStr">
+        <is>
+          <t>REC模式-Products步(选品) — 23.6%
+Creative步(创意,不区分mode) — 16.6%
+REC模式-Structure步(结构/策略) — 14.4%
+REC模式-Budget步(预算分配) — 10.8%
+Default模式-Products步(选品) — 10.4%
+Default模式-Structure步(结构/策略) — 9.8%
+Default模式-Budget步(预算分配) — 5.6%
+REC模式-preview步(预览/最终提交) — 5.4%
+Default模式-preview步(预览/最终提交) — 3.4%</t>
+        </is>
+      </c>
+      <c r="G1452" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-无清理接口(9个场景)：body含isRunAd(立即真实投放)，非草稿提交会在Amazon DSP侧创建真实Order/LineItem/Creative甚至产生真实广告费用；DelPreviewOrder/DelPreviewLineItem只能清理预览阶段草稿，无法回收已落地的真实DSP实体。</t>
+        </is>
+      </c>
     </row>
     <row r="1453">
       <c r="A1453" s="2" t="inlineStr">
@@ -48648,10 +48751,18 @@
         </is>
       </c>
       <c r="E1453" s="3" t="n"/>
-      <c r="F1453" s="3" t="n"/>
-      <c r="G1453" s="3" t="n"/>
-    </row>
-    <row r="1454">
+      <c r="F1453" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1453" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454" ht="16" customHeight="1">
       <c r="A1454" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -48673,10 +48784,18 @@
         </is>
       </c>
       <c r="E1454" s="3" t="n"/>
-      <c r="F1454" s="3" t="n"/>
-      <c r="G1454" s="3" t="n"/>
-    </row>
-    <row r="1455">
+      <c r="F1454" s="6" t="inlineStr">
+        <is>
+          <t>批量更新预览LineItem(定向/出价等) — 100%</t>
+        </is>
+      </c>
+      <c r="G1454" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-无安全测试数据：同上，若用他人真实ID执行会覆盖对方真实草稿内容(定向策略/出价/Dayparting等)，无版本历史可恢复。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455" ht="16" customHeight="1">
       <c r="A1455" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -48698,8 +48817,16 @@
         </is>
       </c>
       <c r="E1455" s="3" t="n"/>
-      <c r="F1455" s="3" t="n"/>
-      <c r="G1455" s="3" t="n"/>
+      <c r="F1455" s="6" t="inlineStr">
+        <is>
+          <t>更新单条预览LineItem详情(Dayparting等) — 100%</t>
+        </is>
+      </c>
+      <c r="G1455" s="5" t="inlineStr">
+        <is>
+          <t>仅生成不执行-无安全测试数据：同UpdatePreviewLineItem。</t>
+        </is>
+      </c>
     </row>
     <row r="1456">
       <c r="A1456" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1982,9 +1982,19 @@
       </c>
       <c r="D51" s="3" t="n"/>
       <c r="E51" s="3" t="n"/>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
+      <c r="F51" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%(16/16执行,1条技术受限不计入)</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>82% (9/11)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -38659,7 +38669,7 @@
         </is>
       </c>
     </row>
-    <row r="1143">
+    <row r="1143" ht="16" customHeight="1">
       <c r="A1143" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -38681,8 +38691,16 @@
         </is>
       </c>
       <c r="E1143" s="3" t="n"/>
-      <c r="F1143" s="3" t="n"/>
-      <c r="G1143" s="3" t="n"/>
+      <c r="F1143" s="6" t="inlineStr">
+        <is>
+          <t>批量修改Order DailyCap(自建一次性测试Order,含后置归档) — 100%</t>
+        </is>
+      </c>
+      <c r="G1143" s="5" t="inlineStr">
+        <is>
+          <t>风险发现(非bug)：预设的已知Order已结束超180天被业务规则锁定，沿用Order单数模块经验，已改为case内新建一次性测试Order执行后归档，可重复执行。</t>
+        </is>
+      </c>
     </row>
     <row r="1144">
       <c r="A1144" s="2" t="inlineStr">
@@ -38706,10 +38724,18 @@
         </is>
       </c>
       <c r="E1144" s="3" t="n"/>
-      <c r="F1144" s="3" t="n"/>
-      <c r="G1144" s="3" t="n"/>
-    </row>
-    <row r="1145">
+      <c r="F1144" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1144" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)——异步版BulkUpdateOrderFlightsAsync有889次流量，说明前端只走异步版</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145" ht="16" customHeight="1">
       <c r="A1145" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -38731,10 +38757,18 @@
         </is>
       </c>
       <c r="E1145" s="3" t="n"/>
-      <c r="F1145" s="3" t="n"/>
-      <c r="G1145" s="3" t="n"/>
-    </row>
-    <row r="1146">
+      <c r="F1145" s="6" t="inlineStr">
+        <is>
+          <t>批量修改Order Flight(自建一次性测试Order,含后置归档) — 100%</t>
+        </is>
+      </c>
+      <c r="G1145" s="5" t="inlineStr">
+        <is>
+          <t>同BulkUpdateOrderBudgetCaps：改为case内新建一次性Order验证。该接口是异步任务(Data:"Task is running in background.")，断言只能验证提交成功，无法同步验证flight真正生效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146" ht="16" customHeight="1">
       <c r="A1146" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -38756,8 +38790,16 @@
         </is>
       </c>
       <c r="E1146" s="3" t="n"/>
-      <c r="F1146" s="3" t="n"/>
-      <c r="G1146" s="3" t="n"/>
+      <c r="F1146" s="6" t="inlineStr">
+        <is>
+          <t>按建议动作批量创建LineItem(技术受限-仅生成不执行) — 100%</t>
+        </is>
+      </c>
+      <c r="G1146" s="5" t="inlineStr">
+        <is>
+          <t>技术受限：需要GetGuidanceActions返回的actionIds，但自建全新Order调用该接口返回空(建议数据依赖历史投放数据)，账号内有真实建议数据的Order都是共享沙盒下非本任务自建的既有Order，为遵守只能动自建实体的铁律未执行，避免在他人Order下留下残留。case内actionIds取自真实Order只读探测，结构有效供后续补测参考。</t>
+        </is>
+      </c>
     </row>
     <row r="1147">
       <c r="A1147" s="2" t="inlineStr">
@@ -38781,10 +38823,18 @@
         </is>
       </c>
       <c r="E1147" s="3" t="n"/>
-      <c r="F1147" s="3" t="n"/>
-      <c r="G1147" s="3" t="n"/>
-    </row>
-    <row r="1148">
+      <c r="F1147" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1147" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId 0/62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148" ht="32" customHeight="1">
       <c r="A1148" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -38806,10 +38856,15 @@
         </is>
       </c>
       <c r="E1148" s="3" t="n"/>
-      <c r="F1148" s="3" t="n"/>
+      <c r="F1148" s="6" t="inlineStr">
+        <is>
+          <t>不指定lineItemId(按Order汇总) — 56.5%
+指定lineItemId(按LineItem过滤) — 43.5%</t>
+        </is>
+      </c>
       <c r="G1148" s="3" t="n"/>
     </row>
-    <row r="1149">
+    <row r="1149" ht="16" customHeight="1">
       <c r="A1149" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -38831,10 +38886,14 @@
         </is>
       </c>
       <c r="E1149" s="3" t="n"/>
-      <c r="F1149" s="3" t="n"/>
+      <c r="F1149" s="6" t="inlineStr">
+        <is>
+          <t>查询Order智能建议动作 — 100%</t>
+        </is>
+      </c>
       <c r="G1149" s="3" t="n"/>
     </row>
-    <row r="1150">
+    <row r="1150" ht="32" customHeight="1">
       <c r="A1150" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -38856,10 +38915,15 @@
         </is>
       </c>
       <c r="E1150" s="3" t="n"/>
-      <c r="F1150" s="3" t="n"/>
+      <c r="F1150" s="6" t="inlineStr">
+        <is>
+          <t>不指定lineItemIds(复制整单) — 28.3%
+指定lineItemIds(仅复制选中LineItem) — 71.7%</t>
+        </is>
+      </c>
       <c r="G1150" s="3" t="n"/>
     </row>
-    <row r="1151">
+    <row r="1151" ht="64" customHeight="1">
       <c r="A1151" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -38881,10 +38945,21 @@
         </is>
       </c>
       <c r="E1151" s="3" t="n"/>
-      <c r="F1151" s="3" t="n"/>
-      <c r="G1151" s="3" t="n"/>
-    </row>
-    <row r="1152">
+      <c r="F1151" s="6" t="inlineStr">
+        <is>
+          <t>performance类型+不按名称过滤(默认列表) — 55.0%
+performance类型+按名称模糊搜索 — 22.8%
+brand类型+不按名称过滤(默认列表) — 16.6%
+brand类型+按名称模糊搜索 — 5.6%</t>
+        </is>
+      </c>
+      <c r="G1151" s="5" t="inlineStr">
+        <is>
+          <t>观察项：验证清理时发现刚创建的测试Order按名称在该列表接口查不到，疑似报表侧索引有延迟；归档调用的Order/BulkUpdateOrders本身返回成功，判断非数据残留，仅列表查询滞后。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152" ht="64" customHeight="1">
       <c r="A1152" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -38906,10 +38981,17 @@
         </is>
       </c>
       <c r="E1152" s="3" t="n"/>
-      <c r="F1152" s="3" t="n"/>
+      <c r="F1152" s="6" t="inlineStr">
+        <is>
+          <t>goalKpi=COST PER DETAIL PAGE VIEW — 34.0%
+goalKpi=CLICK THROUGH RATE — 30.8%
+goalKpi=COST PER ACTION — 22.8%
+goalKpi=COST PER CLICK — 11.8%</t>
+        </is>
+      </c>
       <c r="G1152" s="3" t="n"/>
     </row>
-    <row r="1153">
+    <row r="1153" ht="16" customHeight="1">
       <c r="A1153" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -38931,7 +39013,11 @@
         </is>
       </c>
       <c r="E1153" s="3" t="n"/>
-      <c r="F1153" s="3" t="n"/>
+      <c r="F1153" s="6" t="inlineStr">
+        <is>
+          <t>复制整单(不复制LineItem,含后置归档) — 32.8%</t>
+        </is>
+      </c>
       <c r="G1153" s="3" t="n"/>
     </row>
     <row r="1154">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1466,9 +1466,19 @@
       </c>
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
+      <c r="F33" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>75% (12/16)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -26485,7 +26495,7 @@
         </is>
       </c>
     </row>
-    <row r="752">
+    <row r="752" ht="32" customHeight="1">
       <c r="A752" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26507,10 +26517,15 @@
         </is>
       </c>
       <c r="E752" s="3" t="n"/>
-      <c r="F752" s="3" t="n"/>
+      <c r="F752" s="6" t="inlineStr">
+        <is>
+          <t>创建DRAFT提案(草稿，未提交Amazon) [无清理接口，仅生成不执行] — 43.6%
+创建并SUBMIT提案(真实提交Amazon) [商业风险，仅生成不执行，待用户决策] — 55.1%</t>
+        </is>
+      </c>
       <c r="G752" s="3" t="n"/>
     </row>
-    <row r="753">
+    <row r="753" ht="16" customHeight="1">
       <c r="A753" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26532,7 +26547,11 @@
         </is>
       </c>
       <c r="E753" s="3" t="n"/>
-      <c r="F753" s="3" t="n"/>
+      <c r="F753" s="6" t="inlineStr">
+        <is>
+          <t>按advertiserId导出提案列表Excel</t>
+        </is>
+      </c>
       <c r="G753" s="3" t="n"/>
     </row>
     <row r="754">
@@ -26557,10 +26576,18 @@
         </is>
       </c>
       <c r="E754" s="3" t="n"/>
-      <c r="F754" s="3" t="n"/>
-      <c r="G754" s="3" t="n"/>
-    </row>
-    <row r="755">
+      <c r="F754" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G754" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="755" ht="64" customHeight="1">
       <c r="A755" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26582,10 +26609,17 @@
         </is>
       </c>
       <c r="E755" s="3" t="n"/>
-      <c r="F755" s="3" t="n"/>
+      <c r="F755" s="6" t="inlineStr">
+        <is>
+          <t>未选择目的地(默认全量国家列表) — 84.8%
+目的地=01ProposalSourceAmazonMedia — 8.0%
+目的地=amazonPublisherCloud — 5.0%
+目的地=amazonPublisherDirect — 2.2%</t>
+        </is>
+      </c>
       <c r="G755" s="3" t="n"/>
     </row>
-    <row r="756">
+    <row r="756" ht="16" customHeight="1">
       <c r="A756" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26607,10 +26641,14 @@
         </is>
       </c>
       <c r="E756" s="3" t="n"/>
-      <c r="F756" s="3" t="n"/>
+      <c r="F756" s="6" t="inlineStr">
+        <is>
+          <t>按proposalId查询提案详情 — 100%</t>
+        </is>
+      </c>
       <c r="G756" s="3" t="n"/>
     </row>
-    <row r="757">
+    <row r="757" ht="16" customHeight="1">
       <c r="A757" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26632,7 +26670,11 @@
         </is>
       </c>
       <c r="E757" s="3" t="n"/>
-      <c r="F757" s="3" t="n"/>
+      <c r="F757" s="6" t="inlineStr">
+        <is>
+          <t>查询AmazonMedia渠道产品报价 — 100%</t>
+        </is>
+      </c>
       <c r="G757" s="3" t="n"/>
     </row>
     <row r="758">
@@ -26657,8 +26699,16 @@
         </is>
       </c>
       <c r="E758" s="3" t="n"/>
-      <c r="F758" s="3" t="n"/>
-      <c r="G758" s="3" t="n"/>
+      <c r="F758" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G758" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" s="2" t="inlineStr">
@@ -26682,10 +26732,18 @@
         </is>
       </c>
       <c r="E759" s="3" t="n"/>
-      <c r="F759" s="3" t="n"/>
-      <c r="G759" s="3" t="n"/>
-    </row>
-    <row r="760">
+      <c r="F759" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G759" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="760" ht="32" customHeight="1">
       <c r="A760" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26707,10 +26765,15 @@
         </is>
       </c>
       <c r="E760" s="3" t="n"/>
-      <c r="F760" s="3" t="n"/>
+      <c r="F760" s="6" t="inlineStr">
+        <is>
+          <t>按Publisher Cloud渠道查询offering列表 — 59.9%
+按Publisher Direct渠道查询offering列表 — 40.1%</t>
+        </is>
+      </c>
       <c r="G760" s="3" t="n"/>
     </row>
-    <row r="761">
+    <row r="761" ht="32" customHeight="1">
       <c r="A761" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26732,10 +26795,15 @@
         </is>
       </c>
       <c r="E761" s="3" t="n"/>
-      <c r="F761" s="3" t="n"/>
+      <c r="F761" s="6" t="inlineStr">
+        <is>
+          <t>多条件筛选浏览产品列表 — 66.0%
+按publisherProductId精确查询单个产品 — 34.0%</t>
+        </is>
+      </c>
       <c r="G761" s="3" t="n"/>
     </row>
-    <row r="762">
+    <row r="762" ht="48" customHeight="1">
       <c r="A762" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26757,10 +26825,16 @@
         </is>
       </c>
       <c r="E762" s="3" t="n"/>
-      <c r="F762" s="3" t="n"/>
+      <c r="F762" s="6" t="inlineStr">
+        <is>
+          <t>Amazon Publisher Cloud渠道发布商列表 — 42.2%
+Amazon Media(AMC)渠道发布商列表 — 30.0%
+Amazon Publisher Direct渠道发布商列表 — 27.8%</t>
+        </is>
+      </c>
       <c r="G762" s="3" t="n"/>
     </row>
-    <row r="763">
+    <row r="763" ht="64" customHeight="1">
       <c r="A763" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26782,10 +26856,17 @@
         </is>
       </c>
       <c r="E763" s="3" t="n"/>
-      <c r="F763" s="3" t="n"/>
+      <c r="F763" s="6" t="inlineStr">
+        <is>
+          <t>查询Audience分组targeting选项 [已知后端bug，预期FAIL] — 34.7%
+查询Device分组targeting选项 [已知后端bug，预期FAIL] — 32.7%
+查询Contextual分组targeting选项 [已知后端bug，预期FAIL] — 20.4%
+查询Daypart分组targeting选项 [已知后端bug，预期FAIL] — 12.2%</t>
+        </is>
+      </c>
       <c r="G763" s="3" t="n"/>
     </row>
-    <row r="764">
+    <row r="764" ht="16" customHeight="1">
       <c r="A764" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26807,10 +26888,14 @@
         </is>
       </c>
       <c r="E764" s="3" t="n"/>
-      <c r="F764" s="3" t="n"/>
-      <c r="G764" s="3" t="n"/>
-    </row>
-    <row r="765">
+      <c r="F764" s="5" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词</t>
+        </is>
+      </c>
+      <c r="G764" s="5" t="n"/>
+    </row>
+    <row r="765" ht="16" customHeight="1">
       <c r="A765" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26832,10 +26917,14 @@
         </is>
       </c>
       <c r="E765" s="3" t="n"/>
-      <c r="F765" s="3" t="n"/>
+      <c r="F765" s="6" t="inlineStr">
+        <is>
+          <t>取消(CANCEL)已提交提案 [需已提交Amazon的真实proposal，仅生成不执行，待用户决策]</t>
+        </is>
+      </c>
       <c r="G765" s="3" t="n"/>
     </row>
-    <row r="766">
+    <row r="766" ht="32" customHeight="1">
       <c r="A766" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -26857,7 +26946,12 @@
         </is>
       </c>
       <c r="E766" s="3" t="n"/>
-      <c r="F766" s="3" t="n"/>
+      <c r="F766" s="6" t="inlineStr">
+        <is>
+          <t>编辑DRAFT态提案(未提交Amazon) [无清理接口，仅生成不执行] — 62.2%
+编辑并SUBMIT提案(真实提交Amazon) [商业风险，仅生成不执行，待用户决策] — 37.9%</t>
+        </is>
+      </c>
       <c r="G766" s="3" t="n"/>
     </row>
     <row r="767">
@@ -26882,8 +26976,16 @@
         </is>
       </c>
       <c r="E767" s="3" t="n"/>
-      <c r="F767" s="3" t="n"/>
-      <c r="G767" s="3" t="n"/>
+      <c r="F767" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G767" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="768" ht="128" customHeight="1">
       <c r="A768" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1166,9 +1166,19 @@
       </c>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
+      <c r="F23" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>89% (8/9)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -18649,7 +18659,7 @@
       <c r="F506" s="3" t="n"/>
       <c r="G506" s="3" t="n"/>
     </row>
-    <row r="507">
+    <row r="507" ht="16" customHeight="1">
       <c r="A507" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18671,10 +18681,14 @@
         </is>
       </c>
       <c r="E507" s="3" t="n"/>
-      <c r="F507" s="3" t="n"/>
+      <c r="F507" s="6" t="inlineStr">
+        <is>
+          <t>添加投放LineItem到规则(含后置清理,可重复) — 100%</t>
+        </is>
+      </c>
       <c r="G507" s="3" t="n"/>
     </row>
-    <row r="508">
+    <row r="508" ht="32" customHeight="1">
       <c r="A508" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18696,7 +18710,12 @@
         </is>
       </c>
       <c r="E508" s="3" t="n"/>
-      <c r="F508" s="3" t="n"/>
+      <c r="F508" s="6" t="inlineStr">
+        <is>
+          <t>ruleId为已存在规则时批量添加(含后置清理,可重复) — 50%
+ruleId为空字符串时批量添加 — 50%</t>
+        </is>
+      </c>
       <c r="G508" s="3" t="n"/>
     </row>
     <row r="509">
@@ -18721,10 +18740,18 @@
         </is>
       </c>
       <c r="E509" s="3" t="n"/>
-      <c r="F509" s="3" t="n"/>
-      <c r="G509" s="3" t="n"/>
-    </row>
-    <row r="510">
+      <c r="F509" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量+文件上传类型，需人工测试</t>
+        </is>
+      </c>
+      <c r="G509" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)；multipart/form-data文件上传接口，无法生成JSON case，需人工测试，双重原因不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="48" customHeight="1">
       <c r="A510" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18746,10 +18773,16 @@
         </is>
       </c>
       <c r="E510" s="3" t="n"/>
-      <c r="F510" s="3" t="n"/>
+      <c r="F510" s="6" t="inlineStr">
+        <is>
+          <t>创建空条件占位规则(含后置清理,可重复) [后端按Swagger minItems:1正确拒绝terms:[]，预期FAIL非bug] — 26.8%
+创建单维度单条件规则(含后置清理,可重复) [ES样本DMA代码已过期，预期FAIL非bug] — 61.0%
+创建多条件复合规则(含后置清理,可重复) — 12.2%</t>
+        </is>
+      </c>
       <c r="G510" s="3" t="n"/>
     </row>
-    <row r="511">
+    <row r="511" ht="16" customHeight="1">
       <c r="A511" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18771,10 +18804,14 @@
         </is>
       </c>
       <c r="E511" s="3" t="n"/>
-      <c r="F511" s="3" t="n"/>
+      <c r="F511" s="6" t="inlineStr">
+        <is>
+          <t>正常删除已存在规则(自建数据,可重复) — 100%</t>
+        </is>
+      </c>
       <c r="G511" s="3" t="n"/>
     </row>
-    <row r="512">
+    <row r="512" ht="16" customHeight="1">
       <c r="A512" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18796,10 +18833,14 @@
         </is>
       </c>
       <c r="E512" s="3" t="n"/>
-      <c r="F512" s="3" t="n"/>
+      <c r="F512" s="6" t="inlineStr">
+        <is>
+          <t>查询出价调整规则详情 — 100%</t>
+        </is>
+      </c>
       <c r="G512" s="3" t="n"/>
     </row>
-    <row r="513">
+    <row r="513" ht="32" customHeight="1">
       <c r="A513" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18821,10 +18862,15 @@
         </is>
       </c>
       <c r="E513" s="3" t="n"/>
-      <c r="F513" s="3" t="n"/>
+      <c r="F513" s="6" t="inlineStr">
+        <is>
+          <t>profileId+advertiserId+lineItemId查询关联规则 — 94.4%
+仅profileId+lineItemId查询(无advertiserId) — 5.6%</t>
+        </is>
+      </c>
       <c r="G513" s="3" t="n"/>
     </row>
-    <row r="514">
+    <row r="514" ht="32" customHeight="1">
       <c r="A514" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18846,10 +18892,15 @@
         </is>
       </c>
       <c r="E514" s="3" t="n"/>
-      <c r="F514" s="3" t="n"/>
+      <c r="F514" s="6" t="inlineStr">
+        <is>
+          <t>更新为单条件规则(含后置清理,可重复) — 83.3%
+更新为含大量重复条件的规则(含后置清理,可重复) — 16.7%</t>
+        </is>
+      </c>
       <c r="G514" s="3" t="n"/>
     </row>
-    <row r="515">
+    <row r="515" ht="32" customHeight="1">
       <c r="A515" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18871,7 +18922,12 @@
         </is>
       </c>
       <c r="E515" s="3" t="n"/>
-      <c r="F515" s="3" t="n"/>
+      <c r="F515" s="6" t="inlineStr">
+        <is>
+          <t>添加LineItem绑定(含后置清理,可重复) — 66.7%
+提交空绑定变更(add/delete均为空) — 33.3%</t>
+        </is>
+      </c>
       <c r="G515" s="3" t="n"/>
     </row>
     <row r="516">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -2782,9 +2782,19 @@
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="3" t="n"/>
-      <c r="F76" s="2" t="n"/>
-      <c r="G76" s="2" t="n"/>
-      <c r="H76" s="2" t="n"/>
+      <c r="F76" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>100% (8/8)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -52357,7 +52367,7 @@
       <c r="F1557" s="3" t="n"/>
       <c r="G1557" s="3" t="n"/>
     </row>
-    <row r="1558">
+    <row r="1558" ht="144" customHeight="1">
       <c r="A1558" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -52379,10 +52389,22 @@
         </is>
       </c>
       <c r="E1558" s="3" t="n"/>
-      <c r="F1558" s="3" t="n"/>
+      <c r="F1558" s="6" t="inlineStr">
+        <is>
+          <t>更新LineTemplate(Display) [仅生成不执行-无清理接口] — 29.5%
+新建LineTemplate(Display) [仅生成不执行-无清理接口] — 24.2%
+新建OrderTemplate [仅生成不执行-无清理接口] — 15.7%
+更新LineTemplate(OnlineVideo) [仅生成不执行-无清理接口] — 12.9%
+更新OrderTemplate [仅生成不执行-无清理接口] — 5.5%
+新建LineTemplate(OnlineVideo) [仅生成不执行-无清理接口] — 3.6%
+更新LineTemplate(LiveEvents) [仅生成不执行-无清理接口] — 3.3%
+更新LineTemplate(StreamingTV) [仅生成不执行-无清理接口] — 2.2%
+新建LineTemplate(LiveEvents) [仅生成不执行-无清理接口] — 1.7%</t>
+        </is>
+      </c>
       <c r="G1558" s="3" t="n"/>
     </row>
-    <row r="1559">
+    <row r="1559" ht="16" customHeight="1">
       <c r="A1559" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -52404,10 +52426,14 @@
         </is>
       </c>
       <c r="E1559" s="3" t="n"/>
-      <c r="F1559" s="3" t="n"/>
+      <c r="F1559" s="6" t="inlineStr">
+        <is>
+          <t>按id下载失败明细Excel — 100%</t>
+        </is>
+      </c>
       <c r="G1559" s="3" t="n"/>
     </row>
-    <row r="1560">
+    <row r="1560" ht="16" customHeight="1">
       <c r="A1560" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -52429,10 +52455,14 @@
         </is>
       </c>
       <c r="E1560" s="3" t="n"/>
-      <c r="F1560" s="3" t="n"/>
+      <c r="F1560" s="6" t="inlineStr">
+        <is>
+          <t>下载批量上传模板Excel — 100%</t>
+        </is>
+      </c>
       <c r="G1560" s="3" t="n"/>
     </row>
-    <row r="1561">
+    <row r="1561" ht="16" customHeight="1">
       <c r="A1561" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -52454,10 +52484,14 @@
         </is>
       </c>
       <c r="E1561" s="3" t="n"/>
-      <c r="F1561" s="3" t="n"/>
+      <c r="F1561" s="6" t="inlineStr">
+        <is>
+          <t>按templateId+countryCode(US)查询子模板 — 100%</t>
+        </is>
+      </c>
       <c r="G1561" s="3" t="n"/>
     </row>
-    <row r="1562">
+    <row r="1562" ht="32" customHeight="1">
       <c r="A1562" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -52479,10 +52513,15 @@
         </is>
       </c>
       <c r="E1562" s="3" t="n"/>
-      <c r="F1562" s="3" t="n"/>
+      <c r="F1562" s="6" t="inlineStr">
+        <is>
+          <t>按creatorId过滤(不含orderTemplateId/lineItemTemplateId) — 97.4%
+按orderTemplateId+creatorId过滤 — 1.8%</t>
+        </is>
+      </c>
       <c r="G1562" s="3" t="n"/>
     </row>
-    <row r="1563">
+    <row r="1563" ht="16" customHeight="1">
       <c r="A1563" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -52504,10 +52543,14 @@
         </is>
       </c>
       <c r="E1563" s="3" t="n"/>
-      <c r="F1563" s="3" t="n"/>
+      <c r="F1563" s="6" t="inlineStr">
+        <is>
+          <t>按templateId查询模板详情 — 100%</t>
+        </is>
+      </c>
       <c r="G1563" s="3" t="n"/>
     </row>
-    <row r="1564">
+    <row r="1564" ht="16" customHeight="1">
       <c r="A1564" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -52529,10 +52572,14 @@
         </is>
       </c>
       <c r="E1564" s="3" t="n"/>
-      <c r="F1564" s="3" t="n"/>
+      <c r="F1564" s="6" t="inlineStr">
+        <is>
+          <t>按creatorId过滤查询上传处理日志 — 100%</t>
+        </is>
+      </c>
       <c r="G1564" s="3" t="n"/>
     </row>
-    <row r="1565">
+    <row r="1565" ht="16" customHeight="1">
       <c r="A1565" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -52554,8 +52601,16 @@
         </is>
       </c>
       <c r="E1565" s="3" t="n"/>
-      <c r="F1565" s="3" t="n"/>
-      <c r="G1565" s="3" t="n"/>
+      <c r="F1565" s="5" t="inlineStr">
+        <is>
+          <t>文件上传类型，需人工测试</t>
+        </is>
+      </c>
+      <c r="G1565" s="5" t="inlineStr">
+        <is>
+          <t>multipart/form-data文件上传接口，无法生成JSON case，需人工测试</t>
+        </is>
+      </c>
     </row>
     <row r="1566">
       <c r="A1566" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1144,9 +1144,19 @@
       </c>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="F22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>43% (3/7)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -18516,8 +18526,16 @@
         </is>
       </c>
       <c r="E500" s="3" t="n"/>
-      <c r="F500" s="3" t="n"/>
-      <c r="G500" s="3" t="n"/>
+      <c r="F500" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G500" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -18541,10 +18559,18 @@
         </is>
       </c>
       <c r="E501" s="3" t="n"/>
-      <c r="F501" s="3" t="n"/>
-      <c r="G501" s="3" t="n"/>
-    </row>
-    <row r="502">
+      <c r="F501" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G501" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="32" customHeight="1">
       <c r="A502" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18566,7 +18592,12 @@
         </is>
       </c>
       <c r="E502" s="3" t="n"/>
-      <c r="F502" s="3" t="n"/>
+      <c r="F502" s="6" t="inlineStr">
+        <is>
+          <t>按advertiserIds过滤 — 93.0%
+不传advertiserIds(空body) — 7.0%</t>
+        </is>
+      </c>
       <c r="G502" s="3" t="n"/>
     </row>
     <row r="503">
@@ -18591,10 +18622,18 @@
         </is>
       </c>
       <c r="E503" s="3" t="n"/>
-      <c r="F503" s="3" t="n"/>
-      <c r="G503" s="3" t="n"/>
-    </row>
-    <row r="504">
+      <c r="F503" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G503" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" ht="16" customHeight="1">
       <c r="A504" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18616,10 +18655,14 @@
         </is>
       </c>
       <c r="E504" s="3" t="n"/>
-      <c r="F504" s="3" t="n"/>
+      <c r="F504" s="6" t="inlineStr">
+        <is>
+          <t>默认分页查询(无过滤条件) — 98.0%</t>
+        </is>
+      </c>
       <c r="G504" s="3" t="n"/>
     </row>
-    <row r="505">
+    <row r="505" ht="16" customHeight="1">
       <c r="A505" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18641,7 +18684,11 @@
         </is>
       </c>
       <c r="E505" s="3" t="n"/>
-      <c r="F505" s="3" t="n"/>
+      <c r="F505" s="6" t="inlineStr">
+        <is>
+          <t>按profileId+advertiserId+ruleId查询规则关联的LineItem — 100%</t>
+        </is>
+      </c>
       <c r="G505" s="3" t="n"/>
     </row>
     <row r="506">
@@ -18666,8 +18713,16 @@
         </is>
       </c>
       <c r="E506" s="3" t="n"/>
-      <c r="F506" s="3" t="n"/>
-      <c r="G506" s="3" t="n"/>
+      <c r="F506" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G506" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="507" ht="16" customHeight="1">
       <c r="A507" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1894,9 +1894,19 @@
       </c>
       <c r="D47" s="3" t="n"/>
       <c r="E47" s="3" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
+      <c r="F47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>57% (4/7)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -36815,7 +36825,7 @@
         </is>
       </c>
     </row>
-    <row r="1076">
+    <row r="1076" ht="16" customHeight="1">
       <c r="A1076" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36837,7 +36847,11 @@
         </is>
       </c>
       <c r="E1076" s="3" t="n"/>
-      <c r="F1076" s="3" t="n"/>
+      <c r="F1076" s="6" t="inlineStr">
+        <is>
+          <t>创建SmartLocation地理位置索引 [仅生成不执行-无清理接口] — 100%</t>
+        </is>
+      </c>
       <c r="G1076" s="3" t="n"/>
     </row>
     <row r="1077">
@@ -36862,10 +36876,18 @@
         </is>
       </c>
       <c r="E1077" s="3" t="n"/>
-      <c r="F1077" s="3" t="n"/>
-      <c r="G1077" s="3" t="n"/>
-    </row>
-    <row r="1078">
+      <c r="F1077" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1077" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078" ht="16" customHeight="1">
       <c r="A1078" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36887,7 +36909,11 @@
         </is>
       </c>
       <c r="E1078" s="3" t="n"/>
-      <c r="F1078" s="3" t="n"/>
+      <c r="F1078" s="6" t="inlineStr">
+        <is>
+          <t>按profileId+advertiserId+geoLocationId查询详情(跨租户校验) — 100%</t>
+        </is>
+      </c>
       <c r="G1078" s="3" t="n"/>
     </row>
     <row r="1079">
@@ -36912,10 +36938,18 @@
         </is>
       </c>
       <c r="E1079" s="3" t="n"/>
-      <c r="F1079" s="3" t="n"/>
-      <c r="G1079" s="3" t="n"/>
-    </row>
-    <row r="1080">
+      <c r="F1079" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量+文件上传类型，需人工测试</t>
+        </is>
+      </c>
+      <c r="G1079" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)；multipart/form-data文件上传接口，无法生成JSON case，需人工测试，双重原因不生成不执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080" ht="16" customHeight="1">
       <c r="A1080" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36937,10 +36971,14 @@
         </is>
       </c>
       <c r="E1080" s="3" t="n"/>
-      <c r="F1080" s="3" t="n"/>
+      <c r="F1080" s="6" t="inlineStr">
+        <is>
+          <t>按profileId+advertiserId查询本账号地理位置索引列表 — 2.2%</t>
+        </is>
+      </c>
       <c r="G1080" s="3" t="n"/>
     </row>
-    <row r="1081">
+    <row r="1081" ht="16" customHeight="1">
       <c r="A1081" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -36962,7 +37000,11 @@
         </is>
       </c>
       <c r="E1081" s="3" t="n"/>
-      <c r="F1081" s="3" t="n"/>
+      <c r="F1081" s="6" t="inlineStr">
+        <is>
+          <t>按profileId+advertiserId+indexIds批量查询索引详情(跨租户校验) — 70.9%</t>
+        </is>
+      </c>
       <c r="G1081" s="3" t="n"/>
     </row>
     <row r="1082">
@@ -36987,8 +37029,16 @@
         </is>
       </c>
       <c r="E1082" s="3" t="n"/>
-      <c r="F1082" s="3" t="n"/>
-      <c r="G1082" s="3" t="n"/>
+      <c r="F1082" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1082" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1083">
       <c r="A1083" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -2780,9 +2780,19 @@
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="3" t="n"/>
-      <c r="F75" s="2" t="n"/>
-      <c r="G75" s="2" t="n"/>
-      <c r="H75" s="2" t="n"/>
+      <c r="F75" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>44% (4/9)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -52247,7 +52257,7 @@
       </c>
       <c r="G1548" s="3" t="n"/>
     </row>
-    <row r="1549">
+    <row r="1549" ht="32" customHeight="1">
       <c r="A1549" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -52269,7 +52279,12 @@
         </is>
       </c>
       <c r="E1549" s="3" t="n"/>
-      <c r="F1549" s="3" t="n"/>
+      <c r="F1549" s="6" t="inlineStr">
+        <is>
+          <t>自建CREATEAUDIENCE模板+清理(已知清理接口有bug)
+自建DISPLAY品牌安全模板+清理(同一清理bug复现)</t>
+        </is>
+      </c>
       <c r="G1549" s="3" t="n"/>
     </row>
     <row r="1550">
@@ -52294,8 +52309,16 @@
         </is>
       </c>
       <c r="E1550" s="3" t="n"/>
-      <c r="F1550" s="3" t="n"/>
-      <c r="G1550" s="3" t="n"/>
+      <c r="F1550" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1550" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1551">
       <c r="A1551" s="2" t="inlineStr">
@@ -52322,7 +52345,7 @@
       <c r="F1551" s="3" t="n"/>
       <c r="G1551" s="3" t="n"/>
     </row>
-    <row r="1552">
+    <row r="1552" ht="16" customHeight="1">
       <c r="A1552" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -52344,7 +52367,11 @@
         </is>
       </c>
       <c r="E1552" s="3" t="n"/>
-      <c r="F1552" s="3" t="n"/>
+      <c r="F1552" s="6" t="inlineStr">
+        <is>
+          <t>按templateId查子模板(ES真实样本) — 12.5%</t>
+        </is>
+      </c>
       <c r="G1552" s="3" t="n"/>
     </row>
     <row r="1553">
@@ -52369,8 +52396,16 @@
         </is>
       </c>
       <c r="E1553" s="3" t="n"/>
-      <c r="F1553" s="3" t="n"/>
-      <c r="G1553" s="3" t="n"/>
+      <c r="F1553" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1553" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1554">
       <c r="A1554" s="2" t="inlineStr">
@@ -52394,10 +52429,18 @@
         </is>
       </c>
       <c r="E1554" s="3" t="n"/>
-      <c r="F1554" s="3" t="n"/>
-      <c r="G1554" s="3" t="n"/>
-    </row>
-    <row r="1555">
+      <c r="F1554" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1554" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555" ht="128" customHeight="1">
       <c r="A1555" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -52419,7 +52462,18 @@
         </is>
       </c>
       <c r="E1555" s="3" t="n"/>
-      <c r="F1555" s="3" t="n"/>
+      <c r="F1555" s="6" t="inlineStr">
+        <is>
+          <t>type=ORDERTEMPLATE(查询Order模板列表) — 56.6%
+countryCode=US+type=LINETEMPLATE DISPLAY(查询US站点Display行模板) — 20.0%
+type=DISPLAY(查询Display品牌安全模板列表) — 11.8%
+type=ONLINE VIDEO(查询Online Video品牌安全模板列表) — 2.4%
+type=CREATEAUDIENCE(查询受众创建模板列表) — 1.8%
+type=STREAMING TV(查询Streaming TV品牌安全模板列表) — 1.2%
+countryCode=US+type=LINETEMPLATE ONLINE VIDEO(查询US站点Online Video行模板) — 1.0%
+countryCode=US+type=LINETEMPLATE STREAMING TV(查询US站点Streaming TV行模板) — 1.0%</t>
+        </is>
+      </c>
       <c r="G1555" s="3" t="n"/>
     </row>
     <row r="1556">
@@ -52444,8 +52498,16 @@
         </is>
       </c>
       <c r="E1556" s="3" t="n"/>
-      <c r="F1556" s="3" t="n"/>
-      <c r="G1556" s="3" t="n"/>
+      <c r="F1556" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1556" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1557">
       <c r="A1557" s="2" t="inlineStr">
@@ -52469,8 +52531,16 @@
         </is>
       </c>
       <c r="E1557" s="3" t="n"/>
-      <c r="F1557" s="3" t="n"/>
-      <c r="G1557" s="3" t="n"/>
+      <c r="F1557" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1557" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1558" ht="144" customHeight="1">
       <c r="A1558" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1240,9 +1240,19 @@
       </c>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
+      <c r="F25" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>100% (8/8)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -19576,7 +19586,7 @@
         </is>
       </c>
     </row>
-    <row r="533">
+    <row r="533" ht="16" customHeight="1">
       <c r="A533" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19598,10 +19608,14 @@
         </is>
       </c>
       <c r="E533" s="3" t="n"/>
-      <c r="F533" s="3" t="n"/>
+      <c r="F533" s="6" t="inlineStr">
+        <is>
+          <t>创建Commitment(仅生成不执行,无清理接口)</t>
+        </is>
+      </c>
       <c r="G533" s="3" t="n"/>
     </row>
-    <row r="534">
+    <row r="534" ht="16" customHeight="1">
       <c r="A534" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19623,10 +19637,14 @@
         </is>
       </c>
       <c r="E534" s="3" t="n"/>
-      <c r="F534" s="3" t="n"/>
+      <c r="F534" s="6" t="inlineStr">
+        <is>
+          <t>导出本账号Commitment列表为Excel — 100%</t>
+        </is>
+      </c>
       <c r="G534" s="3" t="n"/>
     </row>
-    <row r="535">
+    <row r="535" ht="32" customHeight="1">
       <c r="A535" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19648,10 +19666,15 @@
         </is>
       </c>
       <c r="E535" s="3" t="n"/>
-      <c r="F535" s="3" t="n"/>
+      <c r="F535" s="6" t="inlineStr">
+        <is>
+          <t>单profile(本账号) — 40.8%
+多profile(ES真实多租户组合) — 59.2%</t>
+        </is>
+      </c>
       <c r="G535" s="3" t="n"/>
     </row>
-    <row r="536">
+    <row r="536" ht="32" customHeight="1">
       <c r="A536" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19673,10 +19696,15 @@
         </is>
       </c>
       <c r="E536" s="3" t="n"/>
-      <c r="F536" s="3" t="n"/>
+      <c r="F536" s="6" t="inlineStr">
+        <is>
+          <t>查询本账号自有Commitment详情(安全场景)
+用ES真实样本id直查(疑似IDOR观察项)</t>
+        </is>
+      </c>
       <c r="G536" s="3" t="n"/>
     </row>
-    <row r="537">
+    <row r="537" ht="48" customHeight="1">
       <c r="A537" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19698,10 +19726,16 @@
         </is>
       </c>
       <c r="E537" s="3" t="n"/>
-      <c r="F537" s="3" t="n"/>
+      <c r="F537" s="6" t="inlineStr">
+        <is>
+          <t>多profile+全部状态过滤(ES真实多租户过滤组合) — 53.5%
+多profile+不传状态过滤 — 28.9%
+单profile(本账号)+全部状态过滤 — 13.6%</t>
+        </is>
+      </c>
       <c r="G537" s="3" t="n"/>
     </row>
-    <row r="538">
+    <row r="538" ht="32" customHeight="1">
       <c r="A538" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19723,10 +19757,15 @@
         </is>
       </c>
       <c r="E538" s="3" t="n"/>
-      <c r="F538" s="3" t="n"/>
+      <c r="F538" s="6" t="inlineStr">
+        <is>
+          <t>指定orderId查询Order关联Commitment(本账号) — 82.2%
+不指定orderId(仅按profile+advertiser) — 17.8%</t>
+        </is>
+      </c>
       <c r="G538" s="3" t="n"/>
     </row>
-    <row r="539">
+    <row r="539" ht="16" customHeight="1">
       <c r="A539" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19748,10 +19787,14 @@
         </is>
       </c>
       <c r="E539" s="3" t="n"/>
-      <c r="F539" s="3" t="n"/>
+      <c r="F539" s="6" t="inlineStr">
+        <is>
+          <t>查询未关联Commitment的候选(本账号) — 100%</t>
+        </is>
+      </c>
       <c r="G539" s="3" t="n"/>
     </row>
-    <row r="540">
+    <row r="540" ht="16" customHeight="1">
       <c r="A540" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -19773,7 +19816,11 @@
         </is>
       </c>
       <c r="E540" s="3" t="n"/>
-      <c r="F540" s="3" t="n"/>
+      <c r="F540" s="6" t="inlineStr">
+        <is>
+          <t>更新Commitment(仅生成不执行,无清理接口且无自建commitmentId)</t>
+        </is>
+      </c>
       <c r="G540" s="3" t="n"/>
     </row>
     <row r="541">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1700,9 +1700,19 @@
       </c>
       <c r="D40" s="3" t="n"/>
       <c r="E40" s="3" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
+      <c r="F40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>38% (3/8)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -32418,10 +32428,18 @@
         </is>
       </c>
       <c r="E929" s="3" t="n"/>
-      <c r="F929" s="3" t="n"/>
-      <c r="G929" s="3" t="n"/>
-    </row>
-    <row r="930">
+      <c r="F929" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G929" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="930" ht="16" customHeight="1">
       <c r="A930" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32443,7 +32461,11 @@
         </is>
       </c>
       <c r="E930" s="3" t="n"/>
-      <c r="F930" s="3" t="n"/>
+      <c r="F930" s="6" t="inlineStr">
+        <is>
+          <t>回滚历史变更事件(仅生成不执行,涉及真实第三方在投预算,新颖风险需用户知悉) — 100%</t>
+        </is>
+      </c>
       <c r="G930" s="3" t="n"/>
     </row>
     <row r="931">
@@ -32468,10 +32490,18 @@
         </is>
       </c>
       <c r="E931" s="3" t="n"/>
-      <c r="F931" s="3" t="n"/>
-      <c r="G931" s="3" t="n"/>
-    </row>
-    <row r="932">
+      <c r="F931" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G931" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="932" ht="16" customHeight="1">
       <c r="A932" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32493,7 +32523,11 @@
         </is>
       </c>
       <c r="E932" s="3" t="n"/>
-      <c r="F932" s="3" t="n"/>
+      <c r="F932" s="6" t="inlineStr">
+        <is>
+          <t>查询当前账号可用受众列表 — 100%</t>
+        </is>
+      </c>
       <c r="G932" s="3" t="n"/>
     </row>
     <row r="933">
@@ -32518,8 +32552,16 @@
         </is>
       </c>
       <c r="E933" s="3" t="n"/>
-      <c r="F933" s="3" t="n"/>
-      <c r="G933" s="3" t="n"/>
+      <c r="F933" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G933" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" s="2" t="inlineStr">
@@ -32543,10 +32585,18 @@
         </is>
       </c>
       <c r="E934" s="3" t="n"/>
-      <c r="F934" s="3" t="n"/>
-      <c r="G934" s="3" t="n"/>
-    </row>
-    <row r="935">
+      <c r="F934" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G934" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="935" ht="16" customHeight="1">
       <c r="A935" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -32568,7 +32618,11 @@
         </is>
       </c>
       <c r="E935" s="3" t="n"/>
-      <c r="F935" s="3" t="n"/>
+      <c r="F935" s="6" t="inlineStr">
+        <is>
+          <t>查询当前账号规则列表 — 100%</t>
+        </is>
+      </c>
       <c r="G935" s="3" t="n"/>
     </row>
     <row r="936">
@@ -32593,8 +32647,16 @@
         </is>
       </c>
       <c r="E936" s="3" t="n"/>
-      <c r="F936" s="3" t="n"/>
-      <c r="G936" s="3" t="n"/>
+      <c r="F936" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G936" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1122,9 +1122,19 @@
       </c>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
+      <c r="F21" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>83% (5/6)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -18394,7 +18404,7 @@
         </is>
       </c>
     </row>
-    <row r="494">
+    <row r="494" ht="64" customHeight="1">
       <c r="A494" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18416,7 +18426,14 @@
         </is>
       </c>
       <c r="E494" s="3" t="n"/>
-      <c r="F494" s="3" t="n"/>
+      <c r="F494" s="6" t="inlineStr">
+        <is>
+          <t>批量修改Order名称 [商业风险，仅生成不执行，待用户决策] — 50%
+批量修改Order预算上限 [商业风险，仅生成不执行，待用户决策] — 30%
+批量修改LineItem名称 [商业风险，仅生成不执行，待用户决策] — 15%
+批量修改LineItem出价 [商业风险，仅生成不执行，待用户决策] — 5%</t>
+        </is>
+      </c>
       <c r="G494" s="3" t="n"/>
     </row>
     <row r="495">
@@ -18441,10 +18458,18 @@
         </is>
       </c>
       <c r="E495" s="3" t="n"/>
-      <c r="F495" s="3" t="n"/>
-      <c r="G495" s="3" t="n"/>
-    </row>
-    <row r="496">
+      <c r="F495" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G495" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="96" customHeight="1">
       <c r="A496" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18466,10 +18491,19 @@
         </is>
       </c>
       <c r="E496" s="3" t="n"/>
-      <c r="F496" s="3" t="n"/>
+      <c r="F496" s="6" t="inlineStr">
+        <is>
+          <t>Order+BudgetCap — 44.1%
+Order+Name — 28.0%
+LineItem+Bid — 12.9%
+LineItem+Budget — 7.5%
+LineItem+Name — 5.4%
+LineItem+BudgetCap — 2.2%</t>
+        </is>
+      </c>
       <c r="G496" s="3" t="n"/>
     </row>
-    <row r="497">
+    <row r="497" ht="16" customHeight="1">
       <c r="A497" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18491,10 +18525,14 @@
         </is>
       </c>
       <c r="E497" s="3" t="n"/>
-      <c r="F497" s="3" t="n"/>
+      <c r="F497" s="6" t="inlineStr">
+        <is>
+          <t>查询本账号真实文件日志详情 — 100%</t>
+        </is>
+      </c>
       <c r="G497" s="3" t="n"/>
     </row>
-    <row r="498">
+    <row r="498" ht="32" customHeight="1">
       <c r="A498" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18516,10 +18554,15 @@
         </is>
       </c>
       <c r="E498" s="3" t="n"/>
-      <c r="F498" s="3" t="n"/>
+      <c r="F498" s="6" t="inlineStr">
+        <is>
+          <t>pageSize10 — 98.2%
+pageSize20 — 1.8%</t>
+        </is>
+      </c>
       <c r="G498" s="3" t="n"/>
     </row>
-    <row r="499">
+    <row r="499" ht="16" customHeight="1">
       <c r="A499" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -18541,8 +18584,16 @@
         </is>
       </c>
       <c r="E499" s="3" t="n"/>
-      <c r="F499" s="3" t="n"/>
-      <c r="G499" s="3" t="n"/>
+      <c r="F499" s="5" t="inlineStr">
+        <is>
+          <t>文件上传类型，需人工测试</t>
+        </is>
+      </c>
+      <c r="G499" s="5" t="inlineStr">
+        <is>
+          <t>multipart/form-data文件上传接口，无法生成JSON case，需人工测试</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -972,9 +972,19 @@
       </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
+      <c r="F16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>100% (4/4)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -15902,7 +15912,7 @@
         </is>
       </c>
     </row>
-    <row r="414">
+    <row r="414" ht="48" customHeight="1">
       <c r="A414" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15924,10 +15934,16 @@
         </is>
       </c>
       <c r="E414" s="3" t="n"/>
-      <c r="F414" s="3" t="n"/>
+      <c r="F414" s="6" t="inlineStr">
+        <is>
+          <t>基础关联(仅id) + 后置移除还原 — 43.6%
+带投放起止日期 + 后置移除还原 — 29%
+带advertiserId+isAdd标记 + 后置移除还原 — 27.4%</t>
+        </is>
+      </c>
       <c r="G414" s="3" t="n"/>
     </row>
-    <row r="415">
+    <row r="415" ht="16" customHeight="1">
       <c r="A415" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15949,10 +15965,14 @@
         </is>
       </c>
       <c r="E415" s="3" t="n"/>
-      <c r="F415" s="3" t="n"/>
+      <c r="F415" s="6" t="inlineStr">
+        <is>
+          <t>按LineItem整体设置创意列表 [仅生成不执行，待用户决策] — 100%</t>
+        </is>
+      </c>
       <c r="G415" s="3" t="n"/>
     </row>
-    <row r="416">
+    <row r="416" ht="16" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -15974,7 +15994,11 @@
         </is>
       </c>
       <c r="E416" s="3" t="n"/>
-      <c r="F416" s="3" t="n"/>
+      <c r="F416" s="6" t="inlineStr">
+        <is>
+          <t>批量创建LineItem [仅生成不执行] — 100%</t>
+        </is>
+      </c>
       <c r="G416" s="3" t="n"/>
     </row>
     <row r="417">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -2318,9 +2318,19 @@
       </c>
       <c r="D59" s="3" t="n"/>
       <c r="E59" s="3" t="n"/>
-      <c r="F59" s="2" t="n"/>
-      <c r="G59" s="2" t="n"/>
-      <c r="H59" s="2" t="n"/>
+      <c r="F59" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>75% (3/4)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -43413,10 +43423,18 @@
         </is>
       </c>
       <c r="E1274" s="3" t="n"/>
-      <c r="F1274" s="3" t="n"/>
-      <c r="G1274" s="3" t="n"/>
-    </row>
-    <row r="1275">
+      <c r="F1274" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1274" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275" ht="176" customHeight="1">
       <c r="A1275" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -43438,10 +43456,24 @@
         </is>
       </c>
       <c r="E1275" s="3" t="n"/>
-      <c r="F1275" s="3" t="n"/>
+      <c r="F1275" s="6" t="inlineStr">
+        <is>
+          <t>CampaignReport+Daily+advertiserIds — 55.2%
+CampaignReport+Weekly+advertiserIds+profileIds — 8.4%
+CampaignReport+Summary+advertiserIds+profileIds — 6.4%
+CampaignReport+Summary+profileIds — 4.0%
+CampaignReport+Daily+无filters — 2.4%
+CampaignReport+Daily+profileIds — 2.2%
+CampaignReport+Daily+advertiserIds+profileIds — 2.0%
+ProductReport+Daily+advertiserIds+profileIds — 1.4%
+CampaignReport+Monthly+advertiserIds+profileIds — 1.4%
+InventoryReport+Weekly+advertiserIds+lineItemIds+profileIds — 1.2%
+InventoryReport+Summary+advertiserIds+profileIds — 1.2%</t>
+        </is>
+      </c>
       <c r="G1275" s="3" t="n"/>
     </row>
-    <row r="1276">
+    <row r="1276" ht="80" customHeight="1">
       <c r="A1276" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -43463,10 +43495,18 @@
         </is>
       </c>
       <c r="E1276" s="3" t="n"/>
-      <c r="F1276" s="3" t="n"/>
+      <c r="F1276" s="6" t="inlineStr">
+        <is>
+          <t>materialType=advertiser — 81.6%
+materialType=profile — 9.4%
+materialType=order — 3.4%
+materialType=order tag — 2.4%
+materialType=creative tag — 1.2%</t>
+        </is>
+      </c>
       <c r="G1276" s="3" t="n"/>
     </row>
-    <row r="1277">
+    <row r="1277" ht="80" customHeight="1">
       <c r="A1277" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -43488,7 +43528,15 @@
         </is>
       </c>
       <c r="E1277" s="3" t="n"/>
-      <c r="F1277" s="3" t="n"/>
+      <c r="F1277" s="6" t="inlineStr">
+        <is>
+          <t>reportType=CampaignReport — 81.0%
+reportType=InventoryReport — 8.3%
+reportType=ProductReport — 5.7%
+reportType=AudienceReport — 3.7%
+reportType=TagReport — 1.3%</t>
+        </is>
+      </c>
       <c r="G1277" s="3" t="n"/>
     </row>
     <row r="1278" ht="96" customHeight="1">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1580,9 +1580,19 @@
       </c>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
+      <c r="F35" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>67% (2/3)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -27857,7 +27867,7 @@
         </is>
       </c>
     </row>
-    <row r="786">
+    <row r="786" ht="112" customHeight="1">
       <c r="A786" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -27879,7 +27889,17 @@
         </is>
       </c>
       <c r="E786" s="3" t="n"/>
-      <c r="F786" s="3" t="n"/>
+      <c r="F786" s="6" t="inlineStr">
+        <is>
+          <t>Bulk Component Creative Template.xlsx — 23.3%
+Bulk REC ABC BSC Creative Upload.xlsx — 22.1%
+Bulk Video Creative Upload.xlsx — 15.1%
+Bulk StandardDisplay Merged Template.xlsx — 14.0%
+Bulk OnlineVideo Creative Template.xlsx — 12.8%
+Bulk StreamingTV Creative Template.xlsx — 8.1%
+Bulk StandardDisplay Individual Template.xlsx — 4.7%</t>
+        </is>
+      </c>
       <c r="G786" s="3" t="n"/>
     </row>
     <row r="787">
@@ -27904,10 +27924,18 @@
         </is>
       </c>
       <c r="E787" s="3" t="n"/>
-      <c r="F787" s="3" t="n"/>
-      <c r="G787" s="3" t="n"/>
-    </row>
-    <row r="788">
+      <c r="F787" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G787" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="788" ht="16" customHeight="1">
       <c r="A788" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -27929,7 +27957,11 @@
         </is>
       </c>
       <c r="E788" s="3" t="n"/>
-      <c r="F788" s="3" t="n"/>
+      <c r="F788" s="6" t="inlineStr">
+        <is>
+          <t>BidAdjustmentTemplate.xlsx — 100%</t>
+        </is>
+      </c>
       <c r="G788" s="3" t="n"/>
     </row>
     <row r="789" ht="64" customHeight="1">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -2968,9 +2968,19 @@
       </c>
       <c r="D79" s="3" t="n"/>
       <c r="E79" s="3" t="n"/>
-      <c r="F79" s="2" t="n"/>
-      <c r="G79" s="2" t="n"/>
-      <c r="H79" s="2" t="n"/>
+      <c r="F79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>50% (1/2)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -54030,10 +54040,18 @@
         </is>
       </c>
       <c r="E1595" s="3" t="n"/>
-      <c r="F1595" s="3" t="n"/>
-      <c r="G1595" s="3" t="n"/>
-    </row>
-    <row r="1596">
+      <c r="F1595" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G1595" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596" ht="16" customHeight="1">
       <c r="A1596" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -54055,7 +54073,11 @@
         </is>
       </c>
       <c r="E1596" s="3" t="n"/>
-      <c r="F1596" s="3" t="n"/>
+      <c r="F1596" s="6" t="inlineStr">
+        <is>
+          <t>category=OrderTag — 100%</t>
+        </is>
+      </c>
       <c r="G1596" s="3" t="n"/>
     </row>
     <row r="1597">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1676,9 +1676,19 @@
       </c>
       <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
+      <c r="F38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100% (3/3)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -30809,7 +30819,7 @@
         </is>
       </c>
     </row>
-    <row r="877">
+    <row r="877" ht="32" customHeight="1">
       <c r="A877" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -30831,10 +30841,15 @@
         </is>
       </c>
       <c r="E877" s="3" t="n"/>
-      <c r="F877" s="3" t="n"/>
+      <c r="F877" s="6" t="inlineStr">
+        <is>
+          <t>advertiserBinds为空(不确认任何绑定) — 22.3%
+确认真实profile/advertiser绑定(仅生成不执行,无清理接口默认不执行) — 3.9%</t>
+        </is>
+      </c>
       <c r="G877" s="3" t="n"/>
     </row>
-    <row r="878">
+    <row r="878" ht="16" customHeight="1">
       <c r="A878" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -30856,10 +30871,14 @@
         </is>
       </c>
       <c r="E878" s="3" t="n"/>
-      <c r="F878" s="3" t="n"/>
+      <c r="F878" s="6" t="inlineStr">
+        <is>
+          <t>按OAuth token查询可跳转advertiser(技术受限-仅生成不执行) — 100%</t>
+        </is>
+      </c>
       <c r="G878" s="3" t="n"/>
     </row>
-    <row r="879">
+    <row r="879" ht="16" customHeight="1">
       <c r="A879" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -30881,7 +30900,11 @@
         </is>
       </c>
       <c r="E879" s="3" t="n"/>
-      <c r="F879" s="3" t="n"/>
+      <c r="F879" s="6" t="inlineStr">
+        <is>
+          <t>查询当前登录用户未授权的advertiser — 100%</t>
+        </is>
+      </c>
       <c r="G879" s="3" t="n"/>
     </row>
     <row r="880" ht="80" customHeight="1">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -630,9 +630,19 @@
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67% (2/3)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -5193,7 +5203,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="16" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5215,7 +5225,11 @@
         </is>
       </c>
       <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="n"/>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>查询本账号真实advertiser基础信息 — 3.4%</t>
+        </is>
+      </c>
       <c r="G66" s="3" t="n"/>
     </row>
     <row r="67">
@@ -5240,10 +5254,18 @@
         </is>
       </c>
       <c r="E67" s="3" t="n"/>
-      <c r="F67" s="3" t="n"/>
-      <c r="G67" s="3" t="n"/>
-    </row>
-    <row r="68">
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -5265,8 +5287,12 @@
         </is>
       </c>
       <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="n"/>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>路径含禁用关键词</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n"/>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -5166,7 +5166,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>ES 无流量(365天0次，已排除测试clientId；不排除clientId时有1次，全部来自clientId 0/62内部系统/自动化噪音)，暂不覆盖</t>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
         </is>
       </c>
     </row>

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1878,9 +1878,19 @@
       </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
+      <c r="F44" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>100% (21/21)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -33979,7 +33989,7 @@
         </is>
       </c>
     </row>
-    <row r="972">
+    <row r="972" ht="64" customHeight="1">
       <c r="A972" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34001,10 +34011,17 @@
         </is>
       </c>
       <c r="E972" s="3" t="n"/>
-      <c r="F972" s="3" t="n"/>
+      <c r="F972" s="6" t="inlineStr">
+        <is>
+          <t>category=account — 79.4%
+category=asinSelection — 11.0%
+category=asinTop10 — 5.2%
+category=productTag — 4.4%</t>
+        </is>
+      </c>
       <c r="G972" s="3" t="n"/>
     </row>
-    <row r="973">
+    <row r="973" ht="16" customHeight="1">
       <c r="A973" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34026,10 +34043,14 @@
         </is>
       </c>
       <c r="E973" s="3" t="n"/>
-      <c r="F973" s="3" t="n"/>
+      <c r="F973" s="6" t="inlineStr">
+        <is>
+          <t>按historyId查询ASIN购买明细</t>
+        </is>
+      </c>
       <c r="G973" s="3" t="n"/>
     </row>
-    <row r="974">
+    <row r="974" ht="48" customHeight="1">
       <c r="A974" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34051,10 +34072,16 @@
         </is>
       </c>
       <c r="E974" s="3" t="n"/>
-      <c r="F974" s="3" t="n"/>
+      <c r="F974" s="6" t="inlineStr">
+        <is>
+          <t>category=account 导出文件 — 60.0%
+category=asinSelection 导出文件 — 32.0%
+category=asinTop10 导出文件 — 8.0%</t>
+        </is>
+      </c>
       <c r="G974" s="3" t="n"/>
     </row>
-    <row r="975">
+    <row r="975" ht="16" customHeight="1">
       <c r="A975" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34076,10 +34103,14 @@
         </is>
       </c>
       <c r="E975" s="3" t="n"/>
-      <c r="F975" s="3" t="n"/>
+      <c r="F975" s="6" t="inlineStr">
+        <is>
+          <t>导出ASIN购买明细文件</t>
+        </is>
+      </c>
       <c r="G975" s="3" t="n"/>
     </row>
-    <row r="976">
+    <row r="976" ht="64" customHeight="1">
       <c r="A976" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34101,10 +34132,17 @@
         </is>
       </c>
       <c r="E976" s="3" t="n"/>
-      <c r="F976" s="3" t="n"/>
+      <c r="F976" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 87.1%
+brandType=90day — 6.5%
+brandType=60day — 3.2%
+brandType=120day — 3.2%</t>
+        </is>
+      </c>
       <c r="G976" s="3" t="n"/>
     </row>
-    <row r="977">
+    <row r="977" ht="32" customHeight="1">
       <c r="A977" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34126,10 +34164,15 @@
         </is>
       </c>
       <c r="E977" s="3" t="n"/>
-      <c r="F977" s="3" t="n"/>
+      <c r="F977" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 91.7%
+brandType=120day — 8.3%</t>
+        </is>
+      </c>
       <c r="G977" s="3" t="n"/>
     </row>
-    <row r="978">
+    <row r="978" ht="32" customHeight="1">
       <c r="A978" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34151,10 +34194,15 @@
         </is>
       </c>
       <c r="E978" s="3" t="n"/>
-      <c r="F978" s="3" t="n"/>
+      <c r="F978" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 50.0%
+brandType=90day — 50.0%</t>
+        </is>
+      </c>
       <c r="G978" s="3" t="n"/>
     </row>
-    <row r="979">
+    <row r="979" ht="64" customHeight="1">
       <c r="A979" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34176,10 +34224,17 @@
         </is>
       </c>
       <c r="E979" s="3" t="n"/>
-      <c r="F979" s="3" t="n"/>
+      <c r="F979" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 45.9%
+brandType=120day — 27.0%
+brandType=60day — 13.5%
+brandType=90day — 10.8%</t>
+        </is>
+      </c>
       <c r="G979" s="3" t="n"/>
     </row>
-    <row r="980">
+    <row r="980" ht="32" customHeight="1">
       <c r="A980" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34201,10 +34256,15 @@
         </is>
       </c>
       <c r="E980" s="3" t="n"/>
-      <c r="F980" s="3" t="n"/>
+      <c r="F980" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 83.3%
+brandType=120day — 16.7%</t>
+        </is>
+      </c>
       <c r="G980" s="3" t="n"/>
     </row>
-    <row r="981">
+    <row r="981" ht="32" customHeight="1">
       <c r="A981" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34226,10 +34286,15 @@
         </is>
       </c>
       <c r="E981" s="3" t="n"/>
-      <c r="F981" s="3" t="n"/>
+      <c r="F981" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 81.8%
+brandType=120day — 9.1%</t>
+        </is>
+      </c>
       <c r="G981" s="3" t="n"/>
     </row>
-    <row r="982">
+    <row r="982" ht="80" customHeight="1">
       <c r="A982" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34251,10 +34316,18 @@
         </is>
       </c>
       <c r="E982" s="3" t="n"/>
-      <c r="F982" s="3" t="n"/>
+      <c r="F982" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 70.8%
+brandType=120day — 3.4%
+brandType=90day — 3.4%
+brandType=60day — 2.0%
+instanceId为空 — 20.4%</t>
+        </is>
+      </c>
       <c r="G982" s="3" t="n"/>
     </row>
-    <row r="983">
+    <row r="983" ht="32" customHeight="1">
       <c r="A983" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34276,10 +34349,15 @@
         </is>
       </c>
       <c r="E983" s="3" t="n"/>
-      <c r="F983" s="3" t="n"/>
+      <c r="F983" s="6" t="inlineStr">
+        <is>
+          <t>按真实instanceId查ASIN列表 — 83.8%
+instanceId为空 — 16.2%</t>
+        </is>
+      </c>
       <c r="G983" s="3" t="n"/>
     </row>
-    <row r="984">
+    <row r="984" ht="16" customHeight="1">
       <c r="A984" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34301,10 +34379,14 @@
         </is>
       </c>
       <c r="E984" s="3" t="n"/>
-      <c r="F984" s="3" t="n"/>
+      <c r="F984" s="6" t="inlineStr">
+        <is>
+          <t>按historyId查询分类/品牌/ASIN列表</t>
+        </is>
+      </c>
       <c r="G984" s="3" t="n"/>
     </row>
-    <row r="985">
+    <row r="985" ht="32" customHeight="1">
       <c r="A985" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34326,10 +34408,15 @@
         </is>
       </c>
       <c r="E985" s="3" t="n"/>
-      <c r="F985" s="3" t="n"/>
+      <c r="F985" s="6" t="inlineStr">
+        <is>
+          <t>不指定instanceId查全部历史 — 55.0%
+按真实instanceId查历史 — 45.0%</t>
+        </is>
+      </c>
       <c r="G985" s="3" t="n"/>
     </row>
-    <row r="986">
+    <row r="986" ht="16" customHeight="1">
       <c r="A986" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34351,10 +34438,14 @@
         </is>
       </c>
       <c r="E986" s="3" t="n"/>
-      <c r="F986" s="3" t="n"/>
+      <c r="F986" s="6" t="inlineStr">
+        <is>
+          <t>查询本账号AMC实例列表 — 100%</t>
+        </is>
+      </c>
       <c r="G986" s="3" t="n"/>
     </row>
-    <row r="987">
+    <row r="987" ht="80" customHeight="1">
       <c r="A987" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34376,10 +34467,18 @@
         </is>
       </c>
       <c r="E987" s="3" t="n"/>
-      <c r="F987" s="3" t="n"/>
+      <c r="F987" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 67.4%
+brandType=120day — 5.4%
+brandType=90day — 3.4%
+brandType=60day — 2.0%
+instanceId为空 — 21.8%</t>
+        </is>
+      </c>
       <c r="G987" s="3" t="n"/>
     </row>
-    <row r="988">
+    <row r="988" ht="80" customHeight="1">
       <c r="A988" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34401,10 +34500,18 @@
         </is>
       </c>
       <c r="E988" s="3" t="n"/>
-      <c r="F988" s="3" t="n"/>
+      <c r="F988" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 69.6%
+brandType=120day — 5.0%
+brandType=60day — 2.8%
+brandType=90day — 2.6%
+instanceId为空 — 20.0%</t>
+        </is>
+      </c>
       <c r="G988" s="3" t="n"/>
     </row>
-    <row r="989">
+    <row r="989" ht="80" customHeight="1">
       <c r="A989" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34426,10 +34533,18 @@
         </is>
       </c>
       <c r="E989" s="3" t="n"/>
-      <c r="F989" s="3" t="n"/>
+      <c r="F989" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 66.3%
+brandType=90day — 16.9%
+brandType=60day — 10.1%
+brandType=120day — 5.6%
+instanceId为空 — 1.1%</t>
+        </is>
+      </c>
       <c r="G989" s="3" t="n"/>
     </row>
-    <row r="990">
+    <row r="990" ht="80" customHeight="1">
       <c r="A990" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34451,10 +34566,18 @@
         </is>
       </c>
       <c r="E990" s="3" t="n"/>
-      <c r="F990" s="3" t="n"/>
+      <c r="F990" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 70.0%
+brandType=120day — 5.0%
+brandType=60day — 2.8%
+brandType=90day — 2.4%
+instanceId为空 — 19.8%</t>
+        </is>
+      </c>
       <c r="G990" s="3" t="n"/>
     </row>
-    <row r="991">
+    <row r="991" ht="80" customHeight="1">
       <c r="A991" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34476,10 +34599,18 @@
         </is>
       </c>
       <c r="E991" s="3" t="n"/>
-      <c r="F991" s="3" t="n"/>
+      <c r="F991" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 70.0%
+brandType=120day — 4.8%
+brandType=90day — 3.4%
+brandType=60day — 1.8%
+instanceId为空 — 20.0%</t>
+        </is>
+      </c>
       <c r="G991" s="3" t="n"/>
     </row>
-    <row r="992">
+    <row r="992" ht="80" customHeight="1">
       <c r="A992" s="2" t="inlineStr">
         <is>
           <t>us</t>
@@ -34501,7 +34632,15 @@
         </is>
       </c>
       <c r="E992" s="3" t="n"/>
-      <c r="F992" s="3" t="n"/>
+      <c r="F992" s="6" t="inlineStr">
+        <is>
+          <t>brandType=30day — 68.2%
+brandType=120day — 4.6%
+brandType=90day — 2.8%
+brandType=60day — 1.8%
+instanceId为空 — 22.6%</t>
+        </is>
+      </c>
       <c r="G992" s="3" t="n"/>
     </row>
     <row r="993" ht="16" customHeight="1">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -1911,11 +1911,11 @@
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="2" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -2231,11 +2231,11 @@
       <c r="D55" s="3" t="n"/>
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">

--- a/single-api/dspapi/swagger_modules.xlsx
+++ b/single-api/dspapi/swagger_modules.xlsx
@@ -567,7 +567,7 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="2" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="2" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="2" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
       <c r="D51" s="3" t="n"/>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       <c r="D65" s="3" t="n"/>
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="3" t="n"/>
       <c r="F67" s="2" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="3" t="n"/>
       <c r="F72" s="2" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
       <c r="F352" s="3" t="n"/>
       <c r="G352" s="5" t="inlineStr">
         <is>
-          <t>写操作(批量解绑)，本轮只读优先未覆盖，待补写操作测试</t>
+          <t>有真实流量(365天40次)但本轮未生成case：2026-09-21写操作补测覆盖了单条UnbindUserInstance，批量版遗漏，待补测</t>
         </is>
       </c>
     </row>
@@ -17058,8 +17058,16 @@
         </is>
       </c>
       <c r="E448" s="3" t="n"/>
-      <c r="F448" s="3" t="n"/>
-      <c r="G448" s="3" t="n"/>
+      <c r="F448" s="3" t="inlineStr">
+        <is>
+          <t>ES 无流量</t>
+        </is>
+      </c>
+      <c r="G448" s="3" t="inlineStr">
+        <is>
+          <t>ES 无流量(365天0次，已排除测试clientId)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="449" ht="16" customHeight="1">
       <c r="A449" s="2" t="inlineStr">
@@ -26623,7 +26631,11 @@
       </c>
       <c r="E744" s="3" t="n"/>
       <c r="F744" s="3" t="n"/>
-      <c r="G744" s="3" t="n"/>
+      <c r="G744" s="3" t="inlineStr">
+        <is>
+          <t>有真实流量(365天5次)但本轮未生成case：与bulkAddDealsIntoInventoryGroup同样依赖Deal tag内查不到的真实inventoryId，待补测</t>
+        </is>
+      </c>
     </row>
     <row r="745" ht="32" customHeight="1">
       <c r="A745" s="2" t="inlineStr">
